--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kellydowd/claude_code/travel_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5062D1-EAC0-B143-A06D-1CA18462E271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399F3103-C5AB-0A4F-BF44-ABCA65041185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10721" uniqueCount="3212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10725" uniqueCount="3216">
   <si>
     <t>country</t>
   </si>
@@ -9660,6 +9660,18 @@
   </si>
   <si>
     <t>Missed it when the train was going over it :(</t>
+  </si>
+  <si>
+    <t>https://hotelsapp.onelink.me/fSyN/fvdfrctq</t>
+  </si>
+  <si>
+    <t>So fun - lots of loch ness monster lore on certain banks. Highly recommend biking there!</t>
+  </si>
+  <si>
+    <t>So cool to see the Highland Games in person</t>
+  </si>
+  <si>
+    <t>Right on the river, beautiful restaurant with lots of natural lighting. Amazing 2 or 3 course meals reasonably priced. GF marked on menu.</t>
   </si>
 </sst>
 </file>
@@ -45678,6 +45690,9 @@
       <c r="F742">
         <v>1</v>
       </c>
+      <c r="G742" s="2" t="s">
+        <v>3213</v>
+      </c>
       <c r="H742" s="2" t="s">
         <v>78</v>
       </c>
@@ -45722,6 +45737,9 @@
       <c r="E743" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="F743">
+        <v>0</v>
+      </c>
       <c r="H743" s="4" t="s">
         <v>78</v>
       </c>
@@ -45766,6 +45784,12 @@
       <c r="E744" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="F744">
+        <v>1</v>
+      </c>
+      <c r="G744" s="2" t="s">
+        <v>3214</v>
+      </c>
       <c r="H744" s="2" t="s">
         <v>78</v>
       </c>
@@ -46212,7 +46236,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="753" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A753" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46265,7 +46289,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="754" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A754" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46283,6 +46307,9 @@
       </c>
       <c r="F754">
         <v>1</v>
+      </c>
+      <c r="G754" s="2" t="s">
+        <v>3215</v>
       </c>
       <c r="H754" s="2" t="s">
         <v>45</v>
@@ -46321,7 +46348,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="755" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A755" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46374,7 +46401,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="756" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A756" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46427,7 +46454,7 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="757" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A757" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46480,7 +46507,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="758" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:23" ht="42" x14ac:dyDescent="0.2">
       <c r="A758" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46533,7 +46560,7 @@
         <v>2965</v>
       </c>
     </row>
-    <row r="759" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A759" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46586,7 +46613,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="760" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A760" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46630,7 +46657,7 @@
       </c>
       <c r="T760" s="2"/>
     </row>
-    <row r="761" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A761" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46674,7 +46701,7 @@
       </c>
       <c r="T761" s="4"/>
     </row>
-    <row r="762" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:23" ht="28" x14ac:dyDescent="0.2">
       <c r="A762" s="6" t="s">
         <v>2620</v>
       </c>
@@ -46733,8 +46760,11 @@
       <c r="V762" s="18" t="s">
         <v>3207</v>
       </c>
-    </row>
-    <row r="763" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W762" s="18" t="s">
+        <v>3212</v>
+      </c>
+    </row>
+    <row r="763" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A763" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46781,7 +46811,7 @@
       </c>
       <c r="T763" s="4"/>
     </row>
-    <row r="764" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A764" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46828,7 +46858,7 @@
       </c>
       <c r="T764" s="2"/>
     </row>
-    <row r="765" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A765" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46875,7 +46905,7 @@
       </c>
       <c r="T765" s="4"/>
     </row>
-    <row r="766" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A766" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46922,7 +46952,7 @@
       </c>
       <c r="T766" s="2"/>
     </row>
-    <row r="767" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A767" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46969,7 +46999,7 @@
       </c>
       <c r="T767" s="4"/>
     </row>
-    <row r="768" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A768" s="2" t="s">
         <v>2620</v>
       </c>
@@ -49315,6 +49345,7 @@
     <hyperlink ref="V717" r:id="rId276" xr:uid="{B981AA88-8A82-6B4E-B174-F1F5E3B7E754}"/>
     <hyperlink ref="V731" r:id="rId277" xr:uid="{E808DE25-914D-EA4E-B5CC-BE291FE44770}"/>
     <hyperlink ref="V762" r:id="rId278" xr:uid="{D3454BDC-84B2-844C-9387-D417DBAD80A4}"/>
+    <hyperlink ref="W762" r:id="rId279" xr:uid="{F6EE375E-2462-5947-969F-92314437D305}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kellydowd/claude_code/travel_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{399F3103-C5AB-0A4F-BF44-ABCA65041185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9E0C88-A941-174F-8303-32DCFE9D89CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="quick notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">places!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">places!$A$1:$T$811</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10725" uniqueCount="3216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10747" uniqueCount="3225">
   <si>
     <t>country</t>
   </si>
@@ -9672,6 +9672,33 @@
   </si>
   <si>
     <t>Right on the river, beautiful restaurant with lots of natural lighting. Amazing 2 or 3 course meals reasonably priced. GF marked on menu.</t>
+  </si>
+  <si>
+    <t>Browns</t>
+  </si>
+  <si>
+    <t>GF menu and asks if you're ceoliac. Was nice to get a traditional scottish breakfast that was gluten free and safe to eat!</t>
+  </si>
+  <si>
+    <t>Great location near George Square &amp; Queen Street Station</t>
+  </si>
+  <si>
+    <t>Blue Lagoon Fish &amp; Chips</t>
+  </si>
+  <si>
+    <t>GF fish &amp; chips!</t>
+  </si>
+  <si>
+    <t>add to map</t>
+  </si>
+  <si>
+    <t>https://www.findmeglutenfree.com/biz/browns/6593971262980096</t>
+  </si>
+  <si>
+    <t>https://www.findmeglutenfree.com/biz/blue-lagoon-fish-and-chips/5092287450841088</t>
+  </si>
+  <si>
+    <t>Great options for GF Italian food</t>
   </si>
 </sst>
 </file>
@@ -10136,7 +10163,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W809"/>
+  <dimension ref="A1:W811"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -42211,454 +42238,474 @@
       <c r="T670" s="2"/>
     </row>
     <row r="671" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A671" s="6" t="s">
+      <c r="A671" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="B671" s="6" t="s">
+      <c r="B671" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="C671" s="6" t="s">
+      <c r="C671" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="D671" s="6" t="s">
-        <v>2623</v>
-      </c>
-      <c r="E671" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F671">
+      <c r="D671" s="2" t="s">
+        <v>2635</v>
+      </c>
+      <c r="E671" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H671" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I671" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J671" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K671" s="3"/>
+      <c r="L671" s="2"/>
+      <c r="M671" s="2"/>
+      <c r="N671" s="2" t="s">
+        <v>2636</v>
+      </c>
+      <c r="O671" s="2" t="s">
+        <v>2637</v>
+      </c>
+      <c r="P671" s="2"/>
+      <c r="Q671" s="2"/>
+      <c r="R671" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="S671" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="T671" s="2"/>
+      <c r="U671" s="7"/>
+    </row>
+    <row r="672" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A672" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B672" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C672" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D672" s="4" t="s">
+        <v>2703</v>
+      </c>
+      <c r="E672" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F672">
         <v>1</v>
       </c>
-      <c r="H671" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I671" s="6" t="s">
+      <c r="G672" s="4" t="s">
+        <v>3224</v>
+      </c>
+      <c r="H672" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I672" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="J671" s="6" t="s">
+      <c r="J672" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K671" s="7"/>
-      <c r="L671" s="6" t="s">
+      <c r="K672" s="5" t="s">
+        <v>2704</v>
+      </c>
+      <c r="L672" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M672" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="N672" s="4" t="s">
+        <v>2705</v>
+      </c>
+      <c r="O672" s="4" t="s">
+        <v>2706</v>
+      </c>
+      <c r="P672" s="4"/>
+      <c r="Q672" s="4"/>
+      <c r="R672" s="4" t="s">
+        <v>2628</v>
+      </c>
+      <c r="S672" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="T672" s="4"/>
+    </row>
+    <row r="673" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A673" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D673" s="2" t="s">
+        <v>2660</v>
+      </c>
+      <c r="E673" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F673">
+        <v>1</v>
+      </c>
+      <c r="H673" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I673" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J673" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K673" s="3"/>
+      <c r="L673" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M671" s="6"/>
-      <c r="N671" s="6" t="s">
-        <v>2626</v>
-      </c>
-      <c r="O671" s="6" t="s">
-        <v>2627</v>
-      </c>
-      <c r="P671" s="6"/>
-      <c r="Q671" s="6"/>
-      <c r="R671" s="6" t="s">
+      <c r="M673" s="2"/>
+      <c r="N673" s="2" t="s">
+        <v>2661</v>
+      </c>
+      <c r="O673" s="2" t="s">
+        <v>2662</v>
+      </c>
+      <c r="P673" s="2"/>
+      <c r="Q673" s="2"/>
+      <c r="R673" s="2" t="s">
         <v>2628</v>
       </c>
-      <c r="S671" s="6" t="s">
+      <c r="S673" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="T671" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="U671" s="7"/>
-    </row>
-    <row r="672" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A672" s="2" t="s">
+      <c r="T673" s="2"/>
+    </row>
+    <row r="674" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A674" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="B672" s="2" t="s">
+      <c r="B674" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="C672" s="2" t="s">
+      <c r="C674" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="D672" s="2" t="s">
+      <c r="D674" s="4" t="s">
+        <v>2713</v>
+      </c>
+      <c r="E674" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H674" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I674" s="4" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J674" s="4" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K674" s="5" t="s">
+        <v>2714</v>
+      </c>
+      <c r="L674" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M674" s="4"/>
+      <c r="N674" s="4" t="s">
+        <v>2715</v>
+      </c>
+      <c r="O674" s="4" t="s">
+        <v>2716</v>
+      </c>
+      <c r="P674" s="4"/>
+      <c r="Q674" s="4"/>
+      <c r="R674" s="4" t="s">
+        <v>2628</v>
+      </c>
+      <c r="S674" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="T674" s="4"/>
+    </row>
+    <row r="675" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A675" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C675" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D675" s="2" t="s">
+        <v>2666</v>
+      </c>
+      <c r="E675" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F675">
+        <v>1</v>
+      </c>
+      <c r="H675" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I675" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J675" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K675" s="3"/>
+      <c r="L675" s="2"/>
+      <c r="M675" s="2"/>
+      <c r="N675" s="2" t="s">
+        <v>2667</v>
+      </c>
+      <c r="O675" s="2" t="s">
+        <v>2668</v>
+      </c>
+      <c r="P675" s="2"/>
+      <c r="Q675" s="2"/>
+      <c r="R675" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="S675" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="T675" s="2"/>
+    </row>
+    <row r="676" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A676" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B676" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C676" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D676" s="4" t="s">
+        <v>2663</v>
+      </c>
+      <c r="E676" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H676" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I676" s="4" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J676" s="4" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K676" s="5"/>
+      <c r="L676" s="4"/>
+      <c r="M676" s="4"/>
+      <c r="N676" s="4" t="s">
+        <v>2664</v>
+      </c>
+      <c r="O676" s="4" t="s">
+        <v>2665</v>
+      </c>
+      <c r="P676" s="4"/>
+      <c r="Q676" s="4"/>
+      <c r="R676" s="4" t="s">
+        <v>2628</v>
+      </c>
+      <c r="S676" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="T676" s="4"/>
+    </row>
+    <row r="677" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A677" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C677" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D677" s="2" t="s">
         <v>2629</v>
       </c>
-      <c r="E672" s="2" t="s">
+      <c r="E677" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H672" s="2" t="s">
+      <c r="F677">
+        <v>1</v>
+      </c>
+      <c r="H677" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I672" s="2" t="s">
+      <c r="I677" s="2" t="s">
         <v>2624</v>
       </c>
-      <c r="J672" s="2" t="s">
+      <c r="J677" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="K672" s="3"/>
-      <c r="L672" s="2"/>
-      <c r="M672" s="2"/>
-      <c r="N672" s="2" t="s">
+      <c r="K677" s="3"/>
+      <c r="L677" s="2"/>
+      <c r="M677" s="2"/>
+      <c r="N677" s="2" t="s">
         <v>2630</v>
       </c>
-      <c r="O672" s="2" t="s">
+      <c r="O677" s="2" t="s">
         <v>2631</v>
       </c>
-      <c r="P672" s="2"/>
-      <c r="Q672" s="2"/>
-      <c r="R672" s="2" t="s">
+      <c r="P677" s="2"/>
+      <c r="Q677" s="2"/>
+      <c r="R677" s="2" t="s">
         <v>2628</v>
       </c>
-      <c r="S672" s="2" t="s">
+      <c r="S677" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="T672" s="2"/>
-    </row>
-    <row r="673" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A673" s="4" t="s">
+      <c r="T677" s="2"/>
+    </row>
+    <row r="678" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A678" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="B673" s="4" t="s">
+      <c r="B678" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="C673" s="4" t="s">
+      <c r="C678" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="D673" s="4" t="s">
-        <v>2632</v>
-      </c>
-      <c r="E673" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H673" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I673" s="4" t="s">
+      <c r="D678" s="4" t="s">
+        <v>2650</v>
+      </c>
+      <c r="E678" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H678" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I678" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="J673" s="4" t="s">
+      <c r="J678" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K673" s="5"/>
-      <c r="L673" s="4"/>
-      <c r="M673" s="4"/>
-      <c r="N673" s="4" t="s">
-        <v>2633</v>
-      </c>
-      <c r="O673" s="4" t="s">
-        <v>2634</v>
-      </c>
-      <c r="P673" s="4"/>
-      <c r="Q673" s="4"/>
-      <c r="R673" s="4" t="s">
+      <c r="K678" s="5"/>
+      <c r="L678" s="4"/>
+      <c r="M678" s="4"/>
+      <c r="N678" s="4" t="s">
+        <v>2651</v>
+      </c>
+      <c r="O678" s="4" t="s">
+        <v>2652</v>
+      </c>
+      <c r="P678" s="4"/>
+      <c r="Q678" s="4"/>
+      <c r="R678" s="4" t="s">
         <v>2628</v>
       </c>
-      <c r="S673" s="4" t="s">
+      <c r="S678" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="T673" s="4"/>
-    </row>
-    <row r="674" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A674" s="2" t="s">
+      <c r="T678" s="4"/>
+    </row>
+    <row r="679" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A679" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="B674" s="2" t="s">
+      <c r="B679" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="C674" s="2" t="s">
+      <c r="C679" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="D674" s="2" t="s">
-        <v>2635</v>
-      </c>
-      <c r="E674" s="2" t="s">
+      <c r="D679" s="2" t="s">
+        <v>2672</v>
+      </c>
+      <c r="E679" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H679" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I679" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J679" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="K679" s="3"/>
+      <c r="L679" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M679" s="2"/>
+      <c r="N679" s="2" t="s">
+        <v>2673</v>
+      </c>
+      <c r="O679" s="2" t="s">
+        <v>2674</v>
+      </c>
+      <c r="P679" s="2"/>
+      <c r="Q679" s="2"/>
+      <c r="R679" s="2" t="s">
+        <v>2628</v>
+      </c>
+      <c r="S679" s="2" t="s">
+        <v>2622</v>
+      </c>
+      <c r="T679" s="2"/>
+    </row>
+    <row r="680" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A680" s="4" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B680" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C680" s="4" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D680" s="4" t="s">
+        <v>2638</v>
+      </c>
+      <c r="E680" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H674" s="2" t="s">
+      <c r="H680" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I674" s="2" t="s">
+      <c r="I680" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="J674" s="2" t="s">
+      <c r="J680" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K674" s="3"/>
-      <c r="L674" s="2"/>
-      <c r="M674" s="2"/>
-      <c r="N674" s="2" t="s">
-        <v>2636</v>
-      </c>
-      <c r="O674" s="2" t="s">
-        <v>2637</v>
-      </c>
-      <c r="P674" s="2"/>
-      <c r="Q674" s="2"/>
-      <c r="R674" s="2" t="s">
+      <c r="K680" s="5"/>
+      <c r="L680" s="4"/>
+      <c r="M680" s="4"/>
+      <c r="N680" s="4" t="s">
+        <v>2639</v>
+      </c>
+      <c r="O680" s="4" t="s">
+        <v>2640</v>
+      </c>
+      <c r="P680" s="4"/>
+      <c r="Q680" s="4"/>
+      <c r="R680" s="4" t="s">
         <v>2628</v>
       </c>
-      <c r="S674" s="2" t="s">
+      <c r="S680" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="T674" s="2"/>
-    </row>
-    <row r="675" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A675" s="4" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B675" s="4" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C675" s="4" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D675" s="4" t="s">
-        <v>2638</v>
-      </c>
-      <c r="E675" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H675" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I675" s="4" t="s">
-        <v>2624</v>
-      </c>
-      <c r="J675" s="4" t="s">
-        <v>2625</v>
-      </c>
-      <c r="K675" s="5"/>
-      <c r="L675" s="4"/>
-      <c r="M675" s="4"/>
-      <c r="N675" s="4" t="s">
-        <v>2639</v>
-      </c>
-      <c r="O675" s="4" t="s">
-        <v>2640</v>
-      </c>
-      <c r="P675" s="4"/>
-      <c r="Q675" s="4"/>
-      <c r="R675" s="4" t="s">
-        <v>2628</v>
-      </c>
-      <c r="S675" s="4" t="s">
-        <v>2622</v>
-      </c>
-      <c r="T675" s="4"/>
-    </row>
-    <row r="676" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A676" s="2" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B676" s="2" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C676" s="2" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D676" s="2" t="s">
-        <v>2641</v>
-      </c>
-      <c r="E676" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H676" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I676" s="2" t="s">
-        <v>2624</v>
-      </c>
-      <c r="J676" s="2" t="s">
-        <v>2625</v>
-      </c>
-      <c r="K676" s="3"/>
-      <c r="L676" s="2"/>
-      <c r="M676" s="2"/>
-      <c r="N676" s="2" t="s">
-        <v>2642</v>
-      </c>
-      <c r="O676" s="2" t="s">
-        <v>2643</v>
-      </c>
-      <c r="P676" s="2"/>
-      <c r="Q676" s="2"/>
-      <c r="R676" s="2" t="s">
-        <v>2628</v>
-      </c>
-      <c r="S676" s="2" t="s">
-        <v>2622</v>
-      </c>
-      <c r="T676" s="2"/>
-    </row>
-    <row r="677" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A677" s="4" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B677" s="4" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C677" s="4" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D677" s="4" t="s">
-        <v>2644</v>
-      </c>
-      <c r="E677" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="H677" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I677" s="4" t="s">
-        <v>2624</v>
-      </c>
-      <c r="J677" s="4" t="s">
-        <v>2625</v>
-      </c>
-      <c r="K677" s="5"/>
-      <c r="L677" s="4"/>
-      <c r="M677" s="4"/>
-      <c r="N677" s="4" t="s">
-        <v>2645</v>
-      </c>
-      <c r="O677" s="4" t="s">
-        <v>2646</v>
-      </c>
-      <c r="P677" s="4"/>
-      <c r="Q677" s="4"/>
-      <c r="R677" s="4" t="s">
-        <v>2628</v>
-      </c>
-      <c r="S677" s="4" t="s">
-        <v>2622</v>
-      </c>
-      <c r="T677" s="4"/>
-    </row>
-    <row r="678" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A678" s="2" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C678" s="2" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D678" s="2" t="s">
-        <v>2647</v>
-      </c>
-      <c r="E678" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H678" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I678" s="2" t="s">
-        <v>2624</v>
-      </c>
-      <c r="J678" s="2" t="s">
-        <v>2625</v>
-      </c>
-      <c r="K678" s="3"/>
-      <c r="L678" s="2"/>
-      <c r="M678" s="2"/>
-      <c r="N678" s="2" t="s">
-        <v>2648</v>
-      </c>
-      <c r="O678" s="2" t="s">
-        <v>2649</v>
-      </c>
-      <c r="P678" s="2"/>
-      <c r="Q678" s="2"/>
-      <c r="R678" s="2" t="s">
-        <v>2628</v>
-      </c>
-      <c r="S678" s="2" t="s">
-        <v>2622</v>
-      </c>
-      <c r="T678" s="2"/>
-    </row>
-    <row r="679" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A679" s="4" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B679" s="4" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C679" s="4" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D679" s="4" t="s">
-        <v>2650</v>
-      </c>
-      <c r="E679" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="H679" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="I679" s="4" t="s">
-        <v>2624</v>
-      </c>
-      <c r="J679" s="4" t="s">
-        <v>2625</v>
-      </c>
-      <c r="K679" s="5"/>
-      <c r="L679" s="4"/>
-      <c r="M679" s="4"/>
-      <c r="N679" s="4" t="s">
-        <v>2651</v>
-      </c>
-      <c r="O679" s="4" t="s">
-        <v>2652</v>
-      </c>
-      <c r="P679" s="4"/>
-      <c r="Q679" s="4"/>
-      <c r="R679" s="4" t="s">
-        <v>2628</v>
-      </c>
-      <c r="S679" s="4" t="s">
-        <v>2622</v>
-      </c>
-      <c r="T679" s="4"/>
-    </row>
-    <row r="680" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A680" s="2" t="s">
-        <v>2620</v>
-      </c>
-      <c r="B680" s="2" t="s">
-        <v>2621</v>
-      </c>
-      <c r="C680" s="2" t="s">
-        <v>2622</v>
-      </c>
-      <c r="D680" s="2" t="s">
-        <v>2653</v>
-      </c>
-      <c r="E680" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H680" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I680" s="2" t="s">
-        <v>2624</v>
-      </c>
-      <c r="J680" s="2" t="s">
-        <v>2625</v>
-      </c>
-      <c r="K680" s="3" t="s">
-        <v>2654</v>
-      </c>
-      <c r="L680" s="2"/>
-      <c r="M680" s="2"/>
-      <c r="N680" s="2" t="s">
-        <v>2655</v>
-      </c>
-      <c r="O680" s="2" t="s">
-        <v>2656</v>
-      </c>
-      <c r="P680" s="2"/>
-      <c r="Q680" s="2"/>
-      <c r="R680" s="2" t="s">
-        <v>2628</v>
-      </c>
-      <c r="S680" s="2" t="s">
-        <v>2622</v>
-      </c>
-      <c r="T680" s="2"/>
+      <c r="T680" s="4"/>
     </row>
     <row r="681" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A681" s="4" t="s">
@@ -42671,13 +42718,13 @@
         <v>2622</v>
       </c>
       <c r="D681" s="4" t="s">
-        <v>2657</v>
+        <v>2693</v>
       </c>
       <c r="E681" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="H681" s="4" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="I681" s="4" t="s">
         <v>2624</v>
@@ -42685,14 +42732,20 @@
       <c r="J681" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K681" s="5"/>
-      <c r="L681" s="4"/>
-      <c r="M681" s="4"/>
+      <c r="K681" s="5" t="s">
+        <v>2694</v>
+      </c>
+      <c r="L681" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M681" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="N681" s="4" t="s">
-        <v>2658</v>
+        <v>2695</v>
       </c>
       <c r="O681" s="4" t="s">
-        <v>2659</v>
+        <v>2696</v>
       </c>
       <c r="P681" s="4"/>
       <c r="Q681" s="4"/>
@@ -42704,7 +42757,7 @@
       </c>
       <c r="T681" s="4"/>
     </row>
-    <row r="682" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:22" ht="56" x14ac:dyDescent="0.2">
       <c r="A682" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42715,13 +42768,13 @@
         <v>2622</v>
       </c>
       <c r="D682" s="2" t="s">
-        <v>2660</v>
+        <v>2708</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H682" s="2" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="I682" s="2" t="s">
         <v>2624</v>
@@ -42729,16 +42782,20 @@
       <c r="J682" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="K682" s="3"/>
+      <c r="K682" s="3" t="s">
+        <v>2709</v>
+      </c>
       <c r="L682" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M682" s="2"/>
+        <v>122</v>
+      </c>
+      <c r="M682" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="N682" s="2" t="s">
-        <v>2661</v>
+        <v>2710</v>
       </c>
       <c r="O682" s="2" t="s">
-        <v>2662</v>
+        <v>2711</v>
       </c>
       <c r="P682" s="2"/>
       <c r="Q682" s="2"/>
@@ -42761,7 +42818,7 @@
         <v>2622</v>
       </c>
       <c r="D683" s="4" t="s">
-        <v>2663</v>
+        <v>2657</v>
       </c>
       <c r="E683" s="4" t="s">
         <v>77</v>
@@ -42779,10 +42836,10 @@
       <c r="L683" s="4"/>
       <c r="M683" s="4"/>
       <c r="N683" s="4" t="s">
-        <v>2664</v>
+        <v>2658</v>
       </c>
       <c r="O683" s="4" t="s">
-        <v>2665</v>
+        <v>2659</v>
       </c>
       <c r="P683" s="4"/>
       <c r="Q683" s="4"/>
@@ -42795,50 +42852,53 @@
       <c r="T683" s="4"/>
     </row>
     <row r="684" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A684" s="2" t="s">
+      <c r="A684" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="B684" s="2" t="s">
+      <c r="B684" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="C684" s="2" t="s">
+      <c r="C684" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="D684" s="2" t="s">
-        <v>2666</v>
-      </c>
-      <c r="E684" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H684" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I684" s="2" t="s">
+      <c r="D684" s="4" t="s">
+        <v>2632</v>
+      </c>
+      <c r="E684" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F684">
+        <v>1</v>
+      </c>
+      <c r="H684" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I684" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="J684" s="2" t="s">
+      <c r="J684" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K684" s="3"/>
-      <c r="L684" s="2"/>
-      <c r="M684" s="2"/>
-      <c r="N684" s="2" t="s">
-        <v>2667</v>
-      </c>
-      <c r="O684" s="2" t="s">
-        <v>2668</v>
-      </c>
-      <c r="P684" s="2"/>
-      <c r="Q684" s="2"/>
-      <c r="R684" s="2" t="s">
+      <c r="K684" s="5"/>
+      <c r="L684" s="4"/>
+      <c r="M684" s="4"/>
+      <c r="N684" s="4" t="s">
+        <v>2633</v>
+      </c>
+      <c r="O684" s="4" t="s">
+        <v>2634</v>
+      </c>
+      <c r="P684" s="4"/>
+      <c r="Q684" s="4"/>
+      <c r="R684" s="4" t="s">
         <v>2628</v>
       </c>
-      <c r="S684" s="2" t="s">
+      <c r="S684" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="T684" s="2"/>
-    </row>
-    <row r="685" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="T684" s="4"/>
+    </row>
+    <row r="685" spans="1:22" ht="28" x14ac:dyDescent="0.2">
       <c r="A685" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42849,13 +42909,16 @@
         <v>2622</v>
       </c>
       <c r="D685" s="4" t="s">
-        <v>2669</v>
+        <v>2683</v>
       </c>
       <c r="E685" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
+      </c>
+      <c r="F685">
+        <v>1</v>
       </c>
       <c r="H685" s="4" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="I685" s="4" t="s">
         <v>2624</v>
@@ -42863,14 +42926,20 @@
       <c r="J685" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K685" s="5"/>
-      <c r="L685" s="4"/>
-      <c r="M685" s="4"/>
+      <c r="K685" s="5" t="s">
+        <v>2684</v>
+      </c>
+      <c r="L685" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="M685" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="N685" s="4" t="s">
-        <v>2670</v>
+        <v>2685</v>
       </c>
       <c r="O685" s="4" t="s">
-        <v>2671</v>
+        <v>2686</v>
       </c>
       <c r="P685" s="4"/>
       <c r="Q685" s="4"/>
@@ -42893,13 +42962,13 @@
         <v>2622</v>
       </c>
       <c r="D686" s="2" t="s">
-        <v>2672</v>
+        <v>2718</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H686" s="2" t="s">
-        <v>174</v>
+        <v>67</v>
       </c>
       <c r="I686" s="2" t="s">
         <v>2624</v>
@@ -42913,10 +42982,10 @@
       </c>
       <c r="M686" s="2"/>
       <c r="N686" s="2" t="s">
-        <v>2673</v>
+        <v>2719</v>
       </c>
       <c r="O686" s="2" t="s">
-        <v>2674</v>
+        <v>2720</v>
       </c>
       <c r="P686" s="2"/>
       <c r="Q686" s="2"/>
@@ -42929,52 +42998,55 @@
       <c r="T686" s="2"/>
     </row>
     <row r="687" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A687" s="4" t="s">
+      <c r="A687" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="B687" s="4" t="s">
+      <c r="B687" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="C687" s="4" t="s">
+      <c r="C687" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="D687" s="4" t="s">
-        <v>2675</v>
-      </c>
-      <c r="E687" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H687" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I687" s="4" t="s">
+      <c r="D687" s="2" t="s">
+        <v>2688</v>
+      </c>
+      <c r="E687" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G687" s="2"/>
+      <c r="H687" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I687" s="2" t="s">
         <v>2624</v>
       </c>
-      <c r="J687" s="4" t="s">
+      <c r="J687" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="K687" s="5" t="s">
-        <v>2676</v>
-      </c>
-      <c r="L687" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="M687" s="4"/>
-      <c r="N687" s="4" t="s">
-        <v>2677</v>
-      </c>
-      <c r="O687" s="4" t="s">
-        <v>2678</v>
-      </c>
-      <c r="P687" s="4"/>
-      <c r="Q687" s="4"/>
-      <c r="R687" s="4" t="s">
+      <c r="K687" s="3" t="s">
+        <v>2689</v>
+      </c>
+      <c r="L687" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="M687" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="N687" s="2" t="s">
+        <v>2690</v>
+      </c>
+      <c r="O687" s="2" t="s">
+        <v>2691</v>
+      </c>
+      <c r="P687" s="2"/>
+      <c r="Q687" s="2"/>
+      <c r="R687" s="2" t="s">
         <v>2628</v>
       </c>
-      <c r="S687" s="4" t="s">
+      <c r="S687" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="T687" s="4"/>
+      <c r="T687" s="2"/>
       <c r="V687" s="12" t="s">
         <v>2679</v>
       </c>
@@ -42990,7 +43062,7 @@
         <v>2622</v>
       </c>
       <c r="D688" s="2" t="s">
-        <v>2680</v>
+        <v>2698</v>
       </c>
       <c r="E688" s="2" t="s">
         <v>44</v>
@@ -43004,16 +43076,20 @@
       <c r="J688" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="K688" s="3"/>
+      <c r="K688" s="3" t="s">
+        <v>2699</v>
+      </c>
       <c r="L688" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M688" s="2"/>
+        <v>56</v>
+      </c>
+      <c r="M688" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="N688" s="2" t="s">
-        <v>2681</v>
+        <v>2700</v>
       </c>
       <c r="O688" s="2" t="s">
-        <v>2682</v>
+        <v>2701</v>
       </c>
       <c r="P688" s="2"/>
       <c r="Q688" s="2"/>
@@ -43028,7 +43104,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="689" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A689" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43039,13 +43115,16 @@
         <v>2622</v>
       </c>
       <c r="D689" s="4" t="s">
-        <v>2683</v>
+        <v>2669</v>
       </c>
       <c r="E689" s="4" t="s">
-        <v>44</v>
+        <v>77</v>
+      </c>
+      <c r="F689">
+        <v>1</v>
       </c>
       <c r="H689" s="4" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="I689" s="4" t="s">
         <v>2624</v>
@@ -43053,20 +43132,14 @@
       <c r="J689" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K689" s="5" t="s">
-        <v>2684</v>
-      </c>
-      <c r="L689" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="M689" s="4" t="s">
-        <v>123</v>
-      </c>
+      <c r="K689" s="5"/>
+      <c r="L689" s="4"/>
+      <c r="M689" s="4"/>
       <c r="N689" s="4" t="s">
-        <v>2685</v>
+        <v>2670</v>
       </c>
       <c r="O689" s="4" t="s">
-        <v>2686</v>
+        <v>2671</v>
       </c>
       <c r="P689" s="4"/>
       <c r="Q689" s="4"/>
@@ -43092,13 +43165,16 @@
         <v>2622</v>
       </c>
       <c r="D690" s="2" t="s">
-        <v>2688</v>
+        <v>2653</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
+      </c>
+      <c r="F690">
+        <v>0</v>
       </c>
       <c r="H690" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I690" s="2" t="s">
         <v>2624</v>
@@ -43107,19 +43183,15 @@
         <v>2625</v>
       </c>
       <c r="K690" s="3" t="s">
-        <v>2689</v>
-      </c>
-      <c r="L690" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="M690" s="2" t="s">
-        <v>123</v>
-      </c>
+        <v>2654</v>
+      </c>
+      <c r="L690" s="2"/>
+      <c r="M690" s="2"/>
       <c r="N690" s="2" t="s">
-        <v>2690</v>
+        <v>2655</v>
       </c>
       <c r="O690" s="2" t="s">
-        <v>2691</v>
+        <v>2656</v>
       </c>
       <c r="P690" s="2"/>
       <c r="Q690" s="2"/>
@@ -43135,264 +43207,252 @@
       </c>
     </row>
     <row r="691" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A691" s="4" t="s">
+      <c r="A691" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="B691" s="4" t="s">
+      <c r="B691" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="C691" s="4" t="s">
+      <c r="C691" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="D691" s="4" t="s">
-        <v>2693</v>
-      </c>
-      <c r="E691" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H691" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I691" s="4" t="s">
+      <c r="D691" s="2" t="s">
+        <v>2641</v>
+      </c>
+      <c r="E691" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H691" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I691" s="2" t="s">
         <v>2624</v>
       </c>
-      <c r="J691" s="4" t="s">
+      <c r="J691" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="K691" s="5" t="s">
-        <v>2694</v>
-      </c>
-      <c r="L691" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="M691" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="N691" s="4" t="s">
-        <v>2695</v>
-      </c>
-      <c r="O691" s="4" t="s">
-        <v>2696</v>
-      </c>
-      <c r="P691" s="4"/>
-      <c r="Q691" s="4"/>
-      <c r="R691" s="4" t="s">
+      <c r="K691" s="3"/>
+      <c r="L691" s="2"/>
+      <c r="M691" s="2"/>
+      <c r="N691" s="2" t="s">
+        <v>2642</v>
+      </c>
+      <c r="O691" s="2" t="s">
+        <v>2643</v>
+      </c>
+      <c r="P691" s="2"/>
+      <c r="Q691" s="2"/>
+      <c r="R691" s="2" t="s">
         <v>2628</v>
       </c>
-      <c r="S691" s="4" t="s">
+      <c r="S691" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="T691" s="4"/>
+      <c r="T691" s="2"/>
       <c r="V691" s="12" t="s">
         <v>2697</v>
       </c>
     </row>
     <row r="692" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A692" s="2" t="s">
+      <c r="A692" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="B692" s="2" t="s">
+      <c r="B692" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="C692" s="2" t="s">
+      <c r="C692" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="D692" s="2" t="s">
-        <v>2698</v>
-      </c>
-      <c r="E692" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H692" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I692" s="2" t="s">
+      <c r="D692" s="4" t="s">
+        <v>2644</v>
+      </c>
+      <c r="E692" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H692" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I692" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="J692" s="2" t="s">
+      <c r="J692" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K692" s="3" t="s">
-        <v>2699</v>
-      </c>
-      <c r="L692" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="M692" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="N692" s="2" t="s">
-        <v>2700</v>
-      </c>
-      <c r="O692" s="2" t="s">
-        <v>2701</v>
-      </c>
-      <c r="P692" s="2"/>
-      <c r="Q692" s="2"/>
-      <c r="R692" s="2" t="s">
+      <c r="K692" s="5"/>
+      <c r="L692" s="4"/>
+      <c r="M692" s="4"/>
+      <c r="N692" s="4" t="s">
+        <v>2645</v>
+      </c>
+      <c r="O692" s="4" t="s">
+        <v>2646</v>
+      </c>
+      <c r="P692" s="4"/>
+      <c r="Q692" s="4"/>
+      <c r="R692" s="4" t="s">
         <v>2628</v>
       </c>
-      <c r="S692" s="2" t="s">
+      <c r="S692" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="T692" s="2"/>
+      <c r="T692" s="4"/>
       <c r="V692" s="12" t="s">
         <v>2702</v>
       </c>
     </row>
     <row r="693" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A693" s="4" t="s">
+      <c r="A693" s="6" t="s">
         <v>2620</v>
       </c>
-      <c r="B693" s="4" t="s">
+      <c r="B693" s="6" t="s">
         <v>2621</v>
       </c>
-      <c r="C693" s="4" t="s">
+      <c r="C693" s="6" t="s">
         <v>2622</v>
       </c>
-      <c r="D693" s="4" t="s">
-        <v>2703</v>
-      </c>
-      <c r="E693" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H693" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I693" s="4" t="s">
+      <c r="D693" s="6" t="s">
+        <v>2623</v>
+      </c>
+      <c r="E693" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F693">
+        <v>1</v>
+      </c>
+      <c r="G693" s="6" t="s">
+        <v>3218</v>
+      </c>
+      <c r="H693" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I693" s="6" t="s">
         <v>2624</v>
       </c>
-      <c r="J693" s="4" t="s">
+      <c r="J693" s="6" t="s">
         <v>2625</v>
       </c>
-      <c r="K693" s="5" t="s">
-        <v>2704</v>
-      </c>
-      <c r="L693" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="M693" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="N693" s="4" t="s">
-        <v>2705</v>
-      </c>
-      <c r="O693" s="4" t="s">
-        <v>2706</v>
-      </c>
-      <c r="P693" s="4"/>
-      <c r="Q693" s="4"/>
-      <c r="R693" s="4" t="s">
+      <c r="K693" s="7"/>
+      <c r="L693" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="M693" s="6"/>
+      <c r="N693" s="6" t="s">
+        <v>2626</v>
+      </c>
+      <c r="O693" s="6" t="s">
+        <v>2627</v>
+      </c>
+      <c r="P693" s="6"/>
+      <c r="Q693" s="6"/>
+      <c r="R693" s="6" t="s">
         <v>2628</v>
       </c>
-      <c r="S693" s="4" t="s">
+      <c r="S693" s="6" t="s">
         <v>2622</v>
       </c>
-      <c r="T693" s="4"/>
+      <c r="T693" s="6" t="s">
+        <v>33</v>
+      </c>
       <c r="V693" s="12" t="s">
         <v>2707</v>
       </c>
     </row>
-    <row r="694" spans="1:23" ht="56" x14ac:dyDescent="0.2">
-      <c r="A694" s="2" t="s">
+    <row r="694" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A694" s="4" t="s">
         <v>2620</v>
       </c>
-      <c r="B694" s="2" t="s">
+      <c r="B694" s="4" t="s">
         <v>2621</v>
       </c>
-      <c r="C694" s="2" t="s">
+      <c r="C694" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="D694" s="2" t="s">
-        <v>2708</v>
-      </c>
-      <c r="E694" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H694" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="I694" s="2" t="s">
+      <c r="D694" s="4" t="s">
+        <v>2675</v>
+      </c>
+      <c r="E694" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H694" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I694" s="4" t="s">
         <v>2624</v>
       </c>
-      <c r="J694" s="2" t="s">
+      <c r="J694" s="4" t="s">
         <v>2625</v>
       </c>
-      <c r="K694" s="3" t="s">
-        <v>2709</v>
-      </c>
-      <c r="L694" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="M694" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="N694" s="2" t="s">
-        <v>2710</v>
-      </c>
-      <c r="O694" s="2" t="s">
-        <v>2711</v>
-      </c>
-      <c r="P694" s="2"/>
-      <c r="Q694" s="2"/>
-      <c r="R694" s="2" t="s">
+      <c r="K694" s="5" t="s">
+        <v>2676</v>
+      </c>
+      <c r="L694" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M694" s="4"/>
+      <c r="N694" s="4" t="s">
+        <v>2677</v>
+      </c>
+      <c r="O694" s="4" t="s">
+        <v>2678</v>
+      </c>
+      <c r="P694" s="4"/>
+      <c r="Q694" s="4"/>
+      <c r="R694" s="4" t="s">
         <v>2628</v>
       </c>
-      <c r="S694" s="2" t="s">
+      <c r="S694" s="4" t="s">
         <v>2622</v>
       </c>
-      <c r="T694" s="2"/>
+      <c r="T694" s="4"/>
       <c r="V694" s="12" t="s">
         <v>2712</v>
       </c>
     </row>
     <row r="695" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A695" s="4" t="s">
+      <c r="A695" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="B695" s="4" t="s">
+      <c r="B695" s="2" t="s">
         <v>2621</v>
       </c>
-      <c r="C695" s="4" t="s">
+      <c r="C695" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="D695" s="4" t="s">
-        <v>2713</v>
-      </c>
-      <c r="E695" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H695" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I695" s="4" t="s">
+      <c r="D695" s="2" t="s">
+        <v>2680</v>
+      </c>
+      <c r="E695" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H695" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I695" s="2" t="s">
         <v>2624</v>
       </c>
-      <c r="J695" s="4" t="s">
+      <c r="J695" s="2" t="s">
         <v>2625</v>
       </c>
-      <c r="K695" s="5" t="s">
-        <v>2714</v>
-      </c>
-      <c r="L695" s="4" t="s">
+      <c r="K695" s="3"/>
+      <c r="L695" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M695" s="4"/>
-      <c r="N695" s="4" t="s">
-        <v>2715</v>
-      </c>
-      <c r="O695" s="4" t="s">
-        <v>2716</v>
-      </c>
-      <c r="P695" s="4"/>
-      <c r="Q695" s="4"/>
-      <c r="R695" s="4" t="s">
+      <c r="M695" s="2"/>
+      <c r="N695" s="2" t="s">
+        <v>2681</v>
+      </c>
+      <c r="O695" s="2" t="s">
+        <v>2682</v>
+      </c>
+      <c r="P695" s="2"/>
+      <c r="Q695" s="2"/>
+      <c r="R695" s="2" t="s">
         <v>2628</v>
       </c>
-      <c r="S695" s="4" t="s">
+      <c r="S695" s="2" t="s">
         <v>2622</v>
       </c>
-      <c r="T695" s="4"/>
+      <c r="T695" s="2"/>
       <c r="V695" s="12" t="s">
         <v>2717</v>
       </c>
@@ -43408,13 +43468,13 @@
         <v>2622</v>
       </c>
       <c r="D696" s="2" t="s">
-        <v>2718</v>
+        <v>2647</v>
       </c>
       <c r="E696" s="2" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="H696" s="2" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="I696" s="2" t="s">
         <v>2624</v>
@@ -43423,15 +43483,13 @@
         <v>2625</v>
       </c>
       <c r="K696" s="3"/>
-      <c r="L696" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="L696" s="2"/>
       <c r="M696" s="2"/>
       <c r="N696" s="2" t="s">
-        <v>2719</v>
+        <v>2648</v>
       </c>
       <c r="O696" s="2" t="s">
-        <v>2720</v>
+        <v>2649</v>
       </c>
       <c r="P696" s="2"/>
       <c r="Q696" s="2"/>
@@ -49064,8 +49122,82 @@
       </c>
       <c r="T809" s="4"/>
     </row>
+    <row r="810" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A810" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B810" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C810" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D810" t="s">
+        <v>3216</v>
+      </c>
+      <c r="E810" t="s">
+        <v>44</v>
+      </c>
+      <c r="F810">
+        <v>1</v>
+      </c>
+      <c r="G810" t="s">
+        <v>3217</v>
+      </c>
+      <c r="I810" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J810" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="T810" t="s">
+        <v>3221</v>
+      </c>
+      <c r="V810" s="20" t="s">
+        <v>3222</v>
+      </c>
+    </row>
+    <row r="811" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A811" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B811" t="s">
+        <v>2621</v>
+      </c>
+      <c r="C811" t="s">
+        <v>2622</v>
+      </c>
+      <c r="D811" t="s">
+        <v>3219</v>
+      </c>
+      <c r="E811" t="s">
+        <v>44</v>
+      </c>
+      <c r="F811">
+        <v>1</v>
+      </c>
+      <c r="G811" t="s">
+        <v>3220</v>
+      </c>
+      <c r="I811" s="2" t="s">
+        <v>2624</v>
+      </c>
+      <c r="J811" s="2" t="s">
+        <v>2625</v>
+      </c>
+      <c r="T811" t="s">
+        <v>3221</v>
+      </c>
+      <c r="V811" s="20" t="s">
+        <v>3223</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T811" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A671:T696">
+      <sortCondition ref="D1:D809"/>
+    </sortState>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="V5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="V8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -49346,6 +49478,8 @@
     <hyperlink ref="V731" r:id="rId277" xr:uid="{E808DE25-914D-EA4E-B5CC-BE291FE44770}"/>
     <hyperlink ref="V762" r:id="rId278" xr:uid="{D3454BDC-84B2-844C-9387-D417DBAD80A4}"/>
     <hyperlink ref="W762" r:id="rId279" xr:uid="{F6EE375E-2462-5947-969F-92314437D305}"/>
+    <hyperlink ref="V810" r:id="rId280" xr:uid="{86AB9332-E970-D04D-B766-4651C394FCA9}"/>
+    <hyperlink ref="V811" r:id="rId281" xr:uid="{D55762BF-E450-6C4F-97C1-2117CF4BCF4B}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kellydowd/claude_code/travel_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9E0C88-A941-174F-8303-32DCFE9D89CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FC4134-8F64-0041-89F6-CD4EEF39FAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10747" uniqueCount="3225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10751" uniqueCount="3229">
   <si>
     <t>country</t>
   </si>
@@ -9590,9 +9590,6 @@
     <t>Rented a bike to ride to Loch Ness!</t>
   </si>
   <si>
-    <t>What an awesome place - GF pizza and dough balls</t>
-  </si>
-  <si>
     <t>Beautiful restaurant with super friendly staff and ability to adapt almost anything to be GF</t>
   </si>
   <si>
@@ -9699,6 +9696,21 @@
   </si>
   <si>
     <t>Great options for GF Italian food</t>
+  </si>
+  <si>
+    <t>What an awesome place - GF pizza and dough balls are a must</t>
+  </si>
+  <si>
+    <t>SUCH a great place with amazing crepes. Right next to the train station and small/cosy inside. I think it mightve been case only</t>
+  </si>
+  <si>
+    <t>fun to explore</t>
+  </si>
+  <si>
+    <t>don’t include this on my website lol</t>
+  </si>
+  <si>
+    <t>such a cute cool church!</t>
   </si>
 </sst>
 </file>
@@ -10163,6 +10175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:W811"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -10254,10 +10267,10 @@
         <v>19</v>
       </c>
       <c r="W1" s="19" t="s">
-        <v>3192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3191</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
@@ -10307,7 +10320,7 @@
       </c>
       <c r="U2" s="7"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -10354,7 +10367,7 @@
       </c>
       <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -10399,7 +10412,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -10449,7 +10462,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -10493,7 +10506,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
@@ -10541,7 +10554,7 @@
       </c>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:23" ht="98" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -10595,7 +10608,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -10641,7 +10654,7 @@
       </c>
       <c r="T9" s="4"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -10686,7 +10699,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -10728,7 +10741,7 @@
       </c>
       <c r="T11" s="4"/>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -10770,7 +10783,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -10812,7 +10825,7 @@
       </c>
       <c r="T13" s="4"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -10854,7 +10867,7 @@
       </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -10896,7 +10909,7 @@
       </c>
       <c r="T15" s="4"/>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -10938,7 +10951,7 @@
       </c>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>98</v>
       </c>
@@ -10985,7 +10998,7 @@
       </c>
       <c r="U17" s="7"/>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>98</v>
       </c>
@@ -11035,7 +11048,7 @@
       </c>
       <c r="U18" s="7"/>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>98</v>
       </c>
@@ -11080,7 +11093,7 @@
       </c>
       <c r="T19" s="4"/>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>98</v>
       </c>
@@ -11125,7 +11138,7 @@
       </c>
       <c r="T20" s="2"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>98</v>
       </c>
@@ -11167,7 +11180,7 @@
       </c>
       <c r="T21" s="4"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>98</v>
       </c>
@@ -11209,7 +11222,7 @@
       </c>
       <c r="T22" s="2"/>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>98</v>
       </c>
@@ -11260,7 +11273,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>98</v>
       </c>
@@ -11311,7 +11324,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
         <v>98</v>
       </c>
@@ -11341,7 +11354,7 @@
       <c r="T25" s="2"/>
       <c r="V25" s="12"/>
     </row>
-    <row r="26" spans="1:22" ht="196" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="196" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>98</v>
       </c>
@@ -11392,7 +11405,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>98</v>
       </c>
@@ -11443,7 +11456,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="126" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="126" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>98</v>
       </c>
@@ -11494,7 +11507,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>98</v>
       </c>
@@ -11545,7 +11558,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="126" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="126" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>98</v>
       </c>
@@ -11596,7 +11609,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>98</v>
       </c>
@@ -11647,7 +11660,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>98</v>
       </c>
@@ -11698,7 +11711,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>98</v>
       </c>
@@ -11742,7 +11755,7 @@
       </c>
       <c r="T33" s="2"/>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>98</v>
       </c>
@@ -11786,7 +11799,7 @@
       </c>
       <c r="T34" s="4"/>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>98</v>
       </c>
@@ -11830,7 +11843,7 @@
       </c>
       <c r="T35" s="2"/>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>98</v>
       </c>
@@ -11872,7 +11885,7 @@
       </c>
       <c r="T36" s="4"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>98</v>
       </c>
@@ -11914,7 +11927,7 @@
       </c>
       <c r="T37" s="2"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>98</v>
       </c>
@@ -11956,7 +11969,7 @@
       </c>
       <c r="T38" s="4"/>
     </row>
-    <row r="39" spans="1:22" ht="126" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:22" ht="126" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>98</v>
       </c>
@@ -12002,7 +12015,7 @@
       </c>
       <c r="T39" s="2"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>98</v>
       </c>
@@ -12046,7 +12059,7 @@
       </c>
       <c r="T40" s="4"/>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>98</v>
       </c>
@@ -12088,7 +12101,7 @@
       </c>
       <c r="T41" s="2"/>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>98</v>
       </c>
@@ -12130,7 +12143,7 @@
       </c>
       <c r="T42" s="4"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>98</v>
       </c>
@@ -12288,6 +12301,9 @@
       <c r="F46">
         <v>1</v>
       </c>
+      <c r="G46" s="4" t="s">
+        <v>3225</v>
+      </c>
       <c r="H46" s="4" t="s">
         <v>45</v>
       </c>
@@ -12384,6 +12400,9 @@
       </c>
       <c r="F48">
         <v>1</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>3226</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>78</v>
@@ -12430,6 +12449,9 @@
       <c r="F49">
         <v>1</v>
       </c>
+      <c r="G49" s="2" t="s">
+        <v>3228</v>
+      </c>
       <c r="H49" s="2" t="s">
         <v>78</v>
       </c>
@@ -12475,6 +12497,9 @@
       <c r="F50">
         <v>0</v>
       </c>
+      <c r="G50" s="4" t="s">
+        <v>3227</v>
+      </c>
       <c r="H50" s="4" t="s">
         <v>78</v>
       </c>
@@ -12545,7 +12570,7 @@
       </c>
       <c r="T51" s="2"/>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
         <v>98</v>
       </c>
@@ -12595,7 +12620,7 @@
       </c>
       <c r="U52" s="7"/>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>98</v>
       </c>
@@ -12640,7 +12665,7 @@
       </c>
       <c r="T53" s="2"/>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>98</v>
       </c>
@@ -12684,7 +12709,7 @@
       </c>
       <c r="T54" s="4"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>98</v>
       </c>
@@ -12735,7 +12760,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="56" spans="1:22" ht="70" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:22" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>98</v>
       </c>
@@ -12786,7 +12811,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>98</v>
       </c>
@@ -12834,7 +12859,7 @@
       </c>
       <c r="T57" s="2"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>98</v>
       </c>
@@ -12885,7 +12910,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="59" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>98</v>
       </c>
@@ -12929,7 +12954,7 @@
       </c>
       <c r="T59" s="2"/>
     </row>
-    <row r="60" spans="1:22" ht="98" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:22" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
         <v>98</v>
       </c>
@@ -12980,7 +13005,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>98</v>
       </c>
@@ -13022,7 +13047,7 @@
       </c>
       <c r="T61" s="2"/>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
         <v>98</v>
       </c>
@@ -13064,7 +13089,7 @@
       </c>
       <c r="T62" s="4"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>98</v>
       </c>
@@ -13106,7 +13131,7 @@
       </c>
       <c r="T63" s="2"/>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
         <v>98</v>
       </c>
@@ -13153,7 +13178,7 @@
       </c>
       <c r="T64" s="4"/>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>98</v>
       </c>
@@ -13195,7 +13220,7 @@
       </c>
       <c r="T65" s="2"/>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
         <v>98</v>
       </c>
@@ -13237,7 +13262,7 @@
       </c>
       <c r="T66" s="4"/>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>98</v>
       </c>
@@ -13279,7 +13304,7 @@
       </c>
       <c r="T67" s="2"/>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
         <v>98</v>
       </c>
@@ -13321,7 +13346,7 @@
       </c>
       <c r="T68" s="4"/>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>98</v>
       </c>
@@ -13363,7 +13388,7 @@
       </c>
       <c r="T69" s="2"/>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
         <v>98</v>
       </c>
@@ -13405,7 +13430,7 @@
       </c>
       <c r="T70" s="4"/>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
         <v>98</v>
       </c>
@@ -13447,7 +13472,7 @@
       </c>
       <c r="T71" s="4"/>
     </row>
-    <row r="72" spans="1:20" ht="70" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:20" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>98</v>
       </c>
@@ -13493,7 +13518,7 @@
       </c>
       <c r="T72" s="2"/>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
         <v>98</v>
       </c>
@@ -13537,7 +13562,7 @@
       </c>
       <c r="T73" s="4"/>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>98</v>
       </c>
@@ -13579,7 +13604,7 @@
       </c>
       <c r="T74" s="2"/>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
         <v>98</v>
       </c>
@@ -13623,7 +13648,7 @@
       </c>
       <c r="T75" s="4"/>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>98</v>
       </c>
@@ -13665,7 +13690,7 @@
       </c>
       <c r="T76" s="2"/>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
         <v>98</v>
       </c>
@@ -13707,7 +13732,7 @@
       </c>
       <c r="T77" s="4"/>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>98</v>
       </c>
@@ -13749,7 +13774,7 @@
       </c>
       <c r="T78" s="2"/>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
         <v>98</v>
       </c>
@@ -13794,7 +13819,7 @@
       </c>
       <c r="T79" s="4"/>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>98</v>
       </c>
@@ -13838,7 +13863,7 @@
       </c>
       <c r="T80" s="2"/>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="4" t="s">
         <v>98</v>
       </c>
@@ -13883,7 +13908,7 @@
       </c>
       <c r="T81" s="4"/>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>98</v>
       </c>
@@ -13927,7 +13952,7 @@
       </c>
       <c r="T82" s="2"/>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="4" t="s">
         <v>98</v>
       </c>
@@ -13972,7 +13997,7 @@
       </c>
       <c r="T83" s="4"/>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>98</v>
       </c>
@@ -14017,7 +14042,7 @@
       </c>
       <c r="T84" s="2"/>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4" t="s">
         <v>98</v>
       </c>
@@ -14059,7 +14084,7 @@
       </c>
       <c r="T85" s="4"/>
     </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>98</v>
       </c>
@@ -14101,7 +14126,7 @@
       </c>
       <c r="T86" s="2"/>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6" t="s">
         <v>360</v>
       </c>
@@ -14148,7 +14173,7 @@
       </c>
       <c r="U87" s="7"/>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>360</v>
       </c>
@@ -14190,7 +14215,7 @@
       </c>
       <c r="T88" s="2"/>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="4" t="s">
         <v>360</v>
       </c>
@@ -14241,7 +14266,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>360</v>
       </c>
@@ -14288,7 +14313,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="4" t="s">
         <v>360</v>
       </c>
@@ -14335,7 +14360,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>360</v>
       </c>
@@ -14382,7 +14407,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="4" t="s">
         <v>360</v>
       </c>
@@ -14429,7 +14454,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>360</v>
       </c>
@@ -14480,7 +14505,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="4" t="s">
         <v>360</v>
       </c>
@@ -14531,7 +14556,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>360</v>
       </c>
@@ -14582,7 +14607,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="4" t="s">
         <v>360</v>
       </c>
@@ -14624,7 +14649,7 @@
       </c>
       <c r="T97" s="4"/>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
         <v>360</v>
       </c>
@@ -14669,7 +14694,7 @@
       </c>
       <c r="T98" s="2"/>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="4" t="s">
         <v>360</v>
       </c>
@@ -14714,7 +14739,7 @@
       </c>
       <c r="T99" s="4"/>
     </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>360</v>
       </c>
@@ -14759,7 +14784,7 @@
       </c>
       <c r="T100" s="2"/>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="4" t="s">
         <v>360</v>
       </c>
@@ -14801,7 +14826,7 @@
       </c>
       <c r="T101" s="4"/>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>360</v>
       </c>
@@ -14843,7 +14868,7 @@
       </c>
       <c r="T102" s="2"/>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="4" t="s">
         <v>360</v>
       </c>
@@ -14887,7 +14912,7 @@
       </c>
       <c r="T103" s="4"/>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>360</v>
       </c>
@@ -14929,7 +14954,7 @@
       </c>
       <c r="T104" s="2"/>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="4" t="s">
         <v>360</v>
       </c>
@@ -14971,7 +14996,7 @@
       </c>
       <c r="T105" s="4"/>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>360</v>
       </c>
@@ -15016,7 +15041,7 @@
       </c>
       <c r="T106" s="2"/>
     </row>
-    <row r="107" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="4" t="s">
         <v>360</v>
       </c>
@@ -15065,7 +15090,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>360</v>
       </c>
@@ -15110,7 +15135,7 @@
       </c>
       <c r="T108" s="2"/>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="4" t="s">
         <v>360</v>
       </c>
@@ -15155,10 +15180,10 @@
       </c>
       <c r="T109" s="4"/>
       <c r="W109" s="20" t="s">
-        <v>3201</v>
-      </c>
-    </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="6" t="s">
         <v>98</v>
       </c>
@@ -15205,7 +15230,7 @@
       </c>
       <c r="U110" s="7"/>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="4" t="s">
         <v>98</v>
       </c>
@@ -15247,7 +15272,7 @@
       </c>
       <c r="T111" s="4"/>
     </row>
-    <row r="112" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>98</v>
       </c>
@@ -15298,7 +15323,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="113" spans="1:22" ht="98" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:22" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="4" t="s">
         <v>98</v>
       </c>
@@ -15349,7 +15374,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="114" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>98</v>
       </c>
@@ -15400,7 +15425,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="4" t="s">
         <v>98</v>
       </c>
@@ -15445,7 +15470,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="116" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>98</v>
       </c>
@@ -15496,7 +15521,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="4" t="s">
         <v>98</v>
       </c>
@@ -15538,7 +15563,7 @@
       </c>
       <c r="T117" s="4"/>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>98</v>
       </c>
@@ -15580,7 +15605,7 @@
       </c>
       <c r="T118" s="2"/>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="4" t="s">
         <v>98</v>
       </c>
@@ -15622,7 +15647,7 @@
       </c>
       <c r="T119" s="4"/>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>98</v>
       </c>
@@ -15664,7 +15689,7 @@
       </c>
       <c r="T120" s="2"/>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="4" t="s">
         <v>98</v>
       </c>
@@ -15708,7 +15733,7 @@
       </c>
       <c r="T121" s="4"/>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>98</v>
       </c>
@@ -15750,7 +15775,7 @@
       </c>
       <c r="T122" s="2"/>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="4" t="s">
         <v>98</v>
       </c>
@@ -15794,7 +15819,7 @@
       </c>
       <c r="T123" s="4"/>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>98</v>
       </c>
@@ -15839,7 +15864,7 @@
       </c>
       <c r="T124" s="2"/>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="4" t="s">
         <v>98</v>
       </c>
@@ -15881,7 +15906,7 @@
       </c>
       <c r="T125" s="4"/>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
         <v>503</v>
       </c>
@@ -15928,7 +15953,7 @@
       </c>
       <c r="U126" s="7"/>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="4" t="s">
         <v>503</v>
       </c>
@@ -15970,7 +15995,7 @@
       </c>
       <c r="T127" s="4"/>
     </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>503</v>
       </c>
@@ -16012,7 +16037,7 @@
       </c>
       <c r="T128" s="2"/>
     </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="4" t="s">
         <v>503</v>
       </c>
@@ -16059,7 +16084,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>518</v>
       </c>
@@ -16103,7 +16128,7 @@
       </c>
       <c r="T130" s="2"/>
     </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
         <v>518</v>
       </c>
@@ -16152,7 +16177,7 @@
       </c>
       <c r="U131" s="7"/>
     </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>518</v>
       </c>
@@ -16198,7 +16223,7 @@
       </c>
       <c r="T132" s="2"/>
     </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="4" t="s">
         <v>518</v>
       </c>
@@ -16242,7 +16267,7 @@
       </c>
       <c r="T133" s="4"/>
     </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>518</v>
       </c>
@@ -16288,7 +16313,7 @@
       </c>
       <c r="T134" s="2"/>
     </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="4" t="s">
         <v>518</v>
       </c>
@@ -16334,7 +16359,7 @@
       </c>
       <c r="T135" s="4"/>
     </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>518</v>
       </c>
@@ -16382,7 +16407,7 @@
       </c>
       <c r="T136" s="2"/>
     </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" s="4" t="s">
         <v>518</v>
       </c>
@@ -16426,7 +16451,7 @@
       </c>
       <c r="T137" s="4"/>
     </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>518</v>
       </c>
@@ -16470,7 +16495,7 @@
       </c>
       <c r="T138" s="2"/>
     </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" s="4" t="s">
         <v>518</v>
       </c>
@@ -16516,7 +16541,7 @@
       </c>
       <c r="T139" s="4"/>
     </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>518</v>
       </c>
@@ -16562,7 +16587,7 @@
       </c>
       <c r="T140" s="2"/>
     </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="4" t="s">
         <v>518</v>
       </c>
@@ -16608,7 +16633,7 @@
       </c>
       <c r="T141" s="4"/>
     </row>
-    <row r="142" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>518</v>
       </c>
@@ -16654,7 +16679,7 @@
       </c>
       <c r="T142" s="2"/>
     </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="4" t="s">
         <v>518</v>
       </c>
@@ -16700,7 +16725,7 @@
       </c>
       <c r="T143" s="4"/>
     </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>518</v>
       </c>
@@ -16746,7 +16771,7 @@
       </c>
       <c r="T144" s="2"/>
     </row>
-    <row r="145" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="4" t="s">
         <v>518</v>
       </c>
@@ -16799,7 +16824,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="146" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>518</v>
       </c>
@@ -16852,7 +16877,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="4" t="s">
         <v>518</v>
       </c>
@@ -16901,7 +16926,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>518</v>
       </c>
@@ -16954,7 +16979,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" s="4" t="s">
         <v>518</v>
       </c>
@@ -17007,7 +17032,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>518</v>
       </c>
@@ -17053,7 +17078,7 @@
       </c>
       <c r="T150" s="2"/>
     </row>
-    <row r="151" spans="1:22" ht="70" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:22" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="4" t="s">
         <v>518</v>
       </c>
@@ -17106,7 +17131,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>518</v>
       </c>
@@ -17159,7 +17184,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="6" t="s">
         <v>503</v>
       </c>
@@ -17206,7 +17231,7 @@
       </c>
       <c r="U153" s="7"/>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
         <v>503</v>
       </c>
@@ -17248,7 +17273,7 @@
       </c>
       <c r="T154" s="2"/>
     </row>
-    <row r="155" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="4" t="s">
         <v>503</v>
       </c>
@@ -17292,7 +17317,7 @@
       </c>
       <c r="T155" s="4"/>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
         <v>503</v>
       </c>
@@ -17334,7 +17359,7 @@
       </c>
       <c r="T156" s="2"/>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="4" t="s">
         <v>503</v>
       </c>
@@ -17381,7 +17406,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
         <v>503</v>
       </c>
@@ -17432,7 +17457,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="4" t="s">
         <v>503</v>
       </c>
@@ -17483,7 +17508,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="160" spans="1:22" ht="84" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:22" ht="84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
         <v>503</v>
       </c>
@@ -17534,7 +17559,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="4" t="s">
         <v>503</v>
       </c>
@@ -17585,7 +17610,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
         <v>503</v>
       </c>
@@ -17636,7 +17661,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="4" t="s">
         <v>503</v>
       </c>
@@ -17684,7 +17709,7 @@
       </c>
       <c r="T163" s="4"/>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
         <v>503</v>
       </c>
@@ -17735,7 +17760,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" s="4" t="s">
         <v>503</v>
       </c>
@@ -17777,7 +17802,7 @@
       </c>
       <c r="T165" s="4"/>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2" t="s">
         <v>503</v>
       </c>
@@ -17819,7 +17844,7 @@
       </c>
       <c r="T166" s="2"/>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" s="4" t="s">
         <v>503</v>
       </c>
@@ -17861,7 +17886,7 @@
       </c>
       <c r="T167" s="4"/>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2" t="s">
         <v>503</v>
       </c>
@@ -17903,7 +17928,7 @@
       </c>
       <c r="T168" s="2"/>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" s="4" t="s">
         <v>503</v>
       </c>
@@ -17945,7 +17970,7 @@
       </c>
       <c r="T169" s="4"/>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2" t="s">
         <v>503</v>
       </c>
@@ -17987,7 +18012,7 @@
       </c>
       <c r="T170" s="2"/>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" s="4" t="s">
         <v>503</v>
       </c>
@@ -18029,7 +18054,7 @@
       </c>
       <c r="T171" s="4"/>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2" t="s">
         <v>503</v>
       </c>
@@ -18071,7 +18096,7 @@
       </c>
       <c r="T172" s="2"/>
     </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" s="4" t="s">
         <v>503</v>
       </c>
@@ -18115,7 +18140,7 @@
       </c>
       <c r="T173" s="4"/>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2" t="s">
         <v>503</v>
       </c>
@@ -18159,7 +18184,7 @@
       </c>
       <c r="T174" s="2"/>
     </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" s="4" t="s">
         <v>503</v>
       </c>
@@ -18203,7 +18228,7 @@
       </c>
       <c r="T175" s="4"/>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2" t="s">
         <v>503</v>
       </c>
@@ -18245,7 +18270,7 @@
       </c>
       <c r="T176" s="2"/>
     </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" s="4" t="s">
         <v>503</v>
       </c>
@@ -18287,7 +18312,7 @@
       </c>
       <c r="T177" s="4"/>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2" t="s">
         <v>503</v>
       </c>
@@ -18329,7 +18354,7 @@
       </c>
       <c r="T178" s="2"/>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" s="4" t="s">
         <v>503</v>
       </c>
@@ -18371,7 +18396,7 @@
       </c>
       <c r="T179" s="4"/>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" s="6" t="s">
         <v>503</v>
       </c>
@@ -18421,7 +18446,7 @@
       </c>
       <c r="U180" s="7"/>
     </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" s="6" t="s">
         <v>503</v>
       </c>
@@ -18468,7 +18493,7 @@
       </c>
       <c r="U181" s="7"/>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2" t="s">
         <v>503</v>
       </c>
@@ -18510,7 +18535,7 @@
       </c>
       <c r="T182" s="2"/>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="4" t="s">
         <v>503</v>
       </c>
@@ -18552,7 +18577,7 @@
       </c>
       <c r="T183" s="4"/>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" s="2" t="s">
         <v>503</v>
       </c>
@@ -18596,7 +18621,7 @@
       </c>
       <c r="T184" s="2"/>
     </row>
-    <row r="185" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" s="4" t="s">
         <v>503</v>
       </c>
@@ -18647,7 +18672,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" s="2" t="s">
         <v>503</v>
       </c>
@@ -18694,7 +18719,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="187" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" s="4" t="s">
         <v>503</v>
       </c>
@@ -18742,7 +18767,7 @@
       </c>
       <c r="T187" s="4"/>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2" t="s">
         <v>503</v>
       </c>
@@ -18789,7 +18814,7 @@
       </c>
       <c r="T188" s="2"/>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" s="4" t="s">
         <v>503</v>
       </c>
@@ -18831,7 +18856,7 @@
       </c>
       <c r="T189" s="4"/>
     </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2" t="s">
         <v>503</v>
       </c>
@@ -18875,7 +18900,7 @@
       </c>
       <c r="T190" s="2"/>
     </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" s="4" t="s">
         <v>503</v>
       </c>
@@ -18917,7 +18942,7 @@
       </c>
       <c r="T191" s="4"/>
     </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2" t="s">
         <v>503</v>
       </c>
@@ -18959,7 +18984,7 @@
       </c>
       <c r="T192" s="2"/>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" s="4" t="s">
         <v>503</v>
       </c>
@@ -19001,7 +19026,7 @@
       </c>
       <c r="T193" s="4"/>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2" t="s">
         <v>503</v>
       </c>
@@ -19045,7 +19070,7 @@
       </c>
       <c r="T194" s="2"/>
     </row>
-    <row r="195" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" s="4" t="s">
         <v>503</v>
       </c>
@@ -19089,7 +19114,7 @@
       </c>
       <c r="T195" s="4"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2" t="s">
         <v>503</v>
       </c>
@@ -19133,7 +19158,7 @@
       </c>
       <c r="T196" s="2"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" s="4" t="s">
         <v>503</v>
       </c>
@@ -19175,7 +19200,7 @@
       </c>
       <c r="T197" s="4"/>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2" t="s">
         <v>503</v>
       </c>
@@ -19217,7 +19242,7 @@
       </c>
       <c r="T198" s="2"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="4" t="s">
         <v>503</v>
       </c>
@@ -19259,7 +19284,7 @@
       </c>
       <c r="T199" s="4"/>
     </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="6" t="s">
         <v>503</v>
       </c>
@@ -19306,7 +19331,7 @@
       </c>
       <c r="U200" s="7"/>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="4" t="s">
         <v>503</v>
       </c>
@@ -19348,7 +19373,7 @@
       </c>
       <c r="T201" s="4"/>
     </row>
-    <row r="202" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2" t="s">
         <v>503</v>
       </c>
@@ -19399,7 +19424,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="4" t="s">
         <v>503</v>
       </c>
@@ -19443,7 +19468,7 @@
       </c>
       <c r="T203" s="4"/>
     </row>
-    <row r="204" spans="1:22" ht="84" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:22" ht="84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2" t="s">
         <v>503</v>
       </c>
@@ -19494,7 +19519,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" s="4" t="s">
         <v>503</v>
       </c>
@@ -19545,7 +19570,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2" t="s">
         <v>503</v>
       </c>
@@ -19594,7 +19619,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" s="4" t="s">
         <v>503</v>
       </c>
@@ -19642,7 +19667,7 @@
       </c>
       <c r="T207" s="4"/>
     </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2" t="s">
         <v>503</v>
       </c>
@@ -19686,7 +19711,7 @@
       </c>
       <c r="T208" s="2"/>
     </row>
-    <row r="209" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" s="4" t="s">
         <v>503</v>
       </c>
@@ -19728,7 +19753,7 @@
       </c>
       <c r="T209" s="4"/>
     </row>
-    <row r="210" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2" t="s">
         <v>503</v>
       </c>
@@ -19770,7 +19795,7 @@
       </c>
       <c r="T210" s="2"/>
     </row>
-    <row r="211" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" s="4" t="s">
         <v>503</v>
       </c>
@@ -19812,7 +19837,7 @@
       </c>
       <c r="T211" s="4"/>
     </row>
-    <row r="212" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" s="6" t="s">
         <v>503</v>
       </c>
@@ -19859,7 +19884,7 @@
       </c>
       <c r="U212" s="7"/>
     </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" s="4" t="s">
         <v>503</v>
       </c>
@@ -19901,7 +19926,7 @@
       </c>
       <c r="T213" s="4"/>
     </row>
-    <row r="214" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2" t="s">
         <v>503</v>
       </c>
@@ -19943,7 +19968,7 @@
       </c>
       <c r="T214" s="2"/>
     </row>
-    <row r="215" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="4" t="s">
         <v>503</v>
       </c>
@@ -19987,7 +20012,7 @@
       </c>
       <c r="T215" s="4"/>
     </row>
-    <row r="216" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" s="2" t="s">
         <v>503</v>
       </c>
@@ -20029,7 +20054,7 @@
       </c>
       <c r="T216" s="2"/>
     </row>
-    <row r="217" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" s="4" t="s">
         <v>503</v>
       </c>
@@ -20071,7 +20096,7 @@
       </c>
       <c r="T217" s="4"/>
     </row>
-    <row r="218" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" s="2" t="s">
         <v>503</v>
       </c>
@@ -20122,7 +20147,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="219" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" s="4" t="s">
         <v>503</v>
       </c>
@@ -20173,7 +20198,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="220" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" s="2" t="s">
         <v>503</v>
       </c>
@@ -20224,7 +20249,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="221" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" s="4" t="s">
         <v>503</v>
       </c>
@@ -20278,7 +20303,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="222" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" s="2" t="s">
         <v>503</v>
       </c>
@@ -20325,7 +20350,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="223" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" s="4" t="s">
         <v>503</v>
       </c>
@@ -20371,7 +20396,7 @@
       </c>
       <c r="T223" s="4"/>
     </row>
-    <row r="224" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" s="2" t="s">
         <v>503</v>
       </c>
@@ -20417,7 +20442,7 @@
       </c>
       <c r="T224" s="2"/>
     </row>
-    <row r="225" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" s="4" t="s">
         <v>503</v>
       </c>
@@ -20465,7 +20490,7 @@
       </c>
       <c r="T225" s="4"/>
     </row>
-    <row r="226" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" s="2" t="s">
         <v>503</v>
       </c>
@@ -20516,7 +20541,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="227" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" s="4" t="s">
         <v>503</v>
       </c>
@@ -20563,7 +20588,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" s="2" t="s">
         <v>503</v>
       </c>
@@ -20607,7 +20632,7 @@
       </c>
       <c r="T228" s="2"/>
     </row>
-    <row r="229" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" s="4" t="s">
         <v>503</v>
       </c>
@@ -20652,7 +20677,7 @@
       </c>
       <c r="T229" s="4"/>
     </row>
-    <row r="230" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" s="2" t="s">
         <v>503</v>
       </c>
@@ -20697,7 +20722,7 @@
       </c>
       <c r="T230" s="2"/>
     </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" s="4" t="s">
         <v>503</v>
       </c>
@@ -20739,7 +20764,7 @@
       </c>
       <c r="T231" s="4"/>
     </row>
-    <row r="232" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" s="2" t="s">
         <v>503</v>
       </c>
@@ -20781,7 +20806,7 @@
       </c>
       <c r="T232" s="2"/>
     </row>
-    <row r="233" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" s="4" t="s">
         <v>503</v>
       </c>
@@ -20826,7 +20851,7 @@
       </c>
       <c r="T233" s="4"/>
     </row>
-    <row r="234" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" s="2" t="s">
         <v>503</v>
       </c>
@@ -20868,7 +20893,7 @@
       </c>
       <c r="T234" s="2"/>
     </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" s="4" t="s">
         <v>503</v>
       </c>
@@ -20910,7 +20935,7 @@
       </c>
       <c r="T235" s="4"/>
     </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" s="6" t="s">
         <v>503</v>
       </c>
@@ -20960,7 +20985,7 @@
       </c>
       <c r="U236" s="7"/>
     </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" s="4" t="s">
         <v>503</v>
       </c>
@@ -21005,7 +21030,7 @@
       </c>
       <c r="T237" s="4"/>
     </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" s="2" t="s">
         <v>503</v>
       </c>
@@ -21050,7 +21075,7 @@
       </c>
       <c r="T238" s="2"/>
     </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" s="4" t="s">
         <v>503</v>
       </c>
@@ -21095,7 +21120,7 @@
       </c>
       <c r="T239" s="4"/>
     </row>
-    <row r="240" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" s="2" t="s">
         <v>503</v>
       </c>
@@ -21139,7 +21164,7 @@
       </c>
       <c r="T240" s="2"/>
     </row>
-    <row r="241" spans="1:22" ht="154" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:22" ht="154" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" s="4" t="s">
         <v>503</v>
       </c>
@@ -21190,7 +21215,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="242" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" s="2" t="s">
         <v>503</v>
       </c>
@@ -21241,7 +21266,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="243" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" s="4" t="s">
         <v>503</v>
       </c>
@@ -21298,7 +21323,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="244" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" s="15" t="s">
         <v>503</v>
       </c>
@@ -21331,7 +21356,7 @@
       <c r="T244" s="4"/>
       <c r="V244" s="12"/>
     </row>
-    <row r="245" spans="1:22" ht="98" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:22" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" s="2" t="s">
         <v>503</v>
       </c>
@@ -21382,7 +21407,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="246" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" s="4" t="s">
         <v>503</v>
       </c>
@@ -21433,7 +21458,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="247" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" s="2" t="s">
         <v>503</v>
       </c>
@@ -21484,7 +21509,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="248" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" s="4" t="s">
         <v>503</v>
       </c>
@@ -21535,7 +21560,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="249" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" s="2" t="s">
         <v>503</v>
       </c>
@@ -21579,7 +21604,7 @@
       </c>
       <c r="T249" s="2"/>
     </row>
-    <row r="250" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" s="4" t="s">
         <v>503</v>
       </c>
@@ -21621,7 +21646,7 @@
       </c>
       <c r="T250" s="4"/>
     </row>
-    <row r="251" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" s="2" t="s">
         <v>503</v>
       </c>
@@ -21663,7 +21688,7 @@
       </c>
       <c r="T251" s="2"/>
     </row>
-    <row r="252" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" s="4" t="s">
         <v>503</v>
       </c>
@@ -21708,7 +21733,7 @@
       </c>
       <c r="T252" s="4"/>
     </row>
-    <row r="253" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" s="2" t="s">
         <v>503</v>
       </c>
@@ -21752,7 +21777,7 @@
       </c>
       <c r="T253" s="2"/>
     </row>
-    <row r="254" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" s="4" t="s">
         <v>503</v>
       </c>
@@ -21794,7 +21819,7 @@
       </c>
       <c r="T254" s="4"/>
     </row>
-    <row r="255" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" s="2" t="s">
         <v>503</v>
       </c>
@@ -21839,7 +21864,7 @@
       </c>
       <c r="T255" s="2"/>
     </row>
-    <row r="256" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" s="4" t="s">
         <v>998</v>
       </c>
@@ -21884,7 +21909,7 @@
       </c>
       <c r="T256" s="4"/>
     </row>
-    <row r="257" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" s="6" t="s">
         <v>998</v>
       </c>
@@ -21934,7 +21959,7 @@
       </c>
       <c r="U257" s="7"/>
     </row>
-    <row r="258" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" s="6" t="s">
         <v>998</v>
       </c>
@@ -21984,7 +22009,7 @@
       </c>
       <c r="U258" s="7"/>
     </row>
-    <row r="259" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" s="6" t="s">
         <v>998</v>
       </c>
@@ -22036,7 +22061,7 @@
       </c>
       <c r="U259" s="7"/>
     </row>
-    <row r="260" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" s="4" t="s">
         <v>998</v>
       </c>
@@ -22081,7 +22106,7 @@
       </c>
       <c r="T260" s="4"/>
     </row>
-    <row r="261" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" s="2" t="s">
         <v>998</v>
       </c>
@@ -22126,7 +22151,7 @@
       </c>
       <c r="T261" s="2"/>
     </row>
-    <row r="262" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" s="4" t="s">
         <v>998</v>
       </c>
@@ -22168,7 +22193,7 @@
       </c>
       <c r="T262" s="4"/>
     </row>
-    <row r="263" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" s="2" t="s">
         <v>998</v>
       </c>
@@ -22210,7 +22235,7 @@
       </c>
       <c r="T263" s="2"/>
     </row>
-    <row r="264" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" s="4" t="s">
         <v>998</v>
       </c>
@@ -22252,7 +22277,7 @@
       </c>
       <c r="T264" s="4"/>
     </row>
-    <row r="265" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" s="2" t="s">
         <v>998</v>
       </c>
@@ -22296,7 +22321,7 @@
       </c>
       <c r="T265" s="2"/>
     </row>
-    <row r="266" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" s="4" t="s">
         <v>998</v>
       </c>
@@ -22347,7 +22372,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="267" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>998</v>
       </c>
@@ -22399,7 +22424,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="268" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" s="4" t="s">
         <v>998</v>
       </c>
@@ -22450,7 +22475,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="269" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2" t="s">
         <v>998</v>
       </c>
@@ -22496,7 +22521,7 @@
       </c>
       <c r="T269" s="2"/>
     </row>
-    <row r="270" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" s="4" t="s">
         <v>998</v>
       </c>
@@ -22547,7 +22572,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="271" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2" t="s">
         <v>998</v>
       </c>
@@ -22604,7 +22629,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="272" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="4" t="s">
         <v>998</v>
       </c>
@@ -22655,7 +22680,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="273" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2" t="s">
         <v>998</v>
       </c>
@@ -22706,7 +22731,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="274" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="4" t="s">
         <v>998</v>
       </c>
@@ -22757,7 +22782,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="275" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2" t="s">
         <v>998</v>
       </c>
@@ -22808,7 +22833,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="276" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="4" t="s">
         <v>998</v>
       </c>
@@ -22859,7 +22884,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="277" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2" t="s">
         <v>998</v>
       </c>
@@ -22910,7 +22935,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="278" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="4" t="s">
         <v>998</v>
       </c>
@@ -22961,7 +22986,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="279" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2" t="s">
         <v>998</v>
       </c>
@@ -23018,7 +23043,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="280" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" s="4" t="s">
         <v>998</v>
       </c>
@@ -23070,7 +23095,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="281" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2" t="s">
         <v>998</v>
       </c>
@@ -23121,7 +23146,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="282" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" s="4" t="s">
         <v>998</v>
       </c>
@@ -23170,7 +23195,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="283" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2" t="s">
         <v>998</v>
       </c>
@@ -23219,7 +23244,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="284" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" s="4" t="s">
         <v>998</v>
       </c>
@@ -23270,7 +23295,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="285" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" s="6" t="s">
         <v>998</v>
       </c>
@@ -23317,7 +23342,7 @@
       </c>
       <c r="U285" s="7"/>
     </row>
-    <row r="286" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" s="4" t="s">
         <v>998</v>
       </c>
@@ -23359,7 +23384,7 @@
       </c>
       <c r="T286" s="4"/>
     </row>
-    <row r="287" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2" t="s">
         <v>998</v>
       </c>
@@ -23404,7 +23429,7 @@
       </c>
       <c r="T287" s="2"/>
     </row>
-    <row r="288" spans="1:22" ht="112" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:22" ht="112" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" s="4" t="s">
         <v>998</v>
       </c>
@@ -23448,7 +23473,7 @@
       </c>
       <c r="T288" s="4"/>
     </row>
-    <row r="289" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2" t="s">
         <v>998</v>
       </c>
@@ -23495,7 +23520,7 @@
       </c>
       <c r="T289" s="2"/>
     </row>
-    <row r="290" spans="1:22" ht="98" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:22" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" s="4" t="s">
         <v>998</v>
       </c>
@@ -23545,7 +23570,7 @@
       </c>
       <c r="T290" s="4"/>
     </row>
-    <row r="291" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2" t="s">
         <v>998</v>
       </c>
@@ -23590,7 +23615,7 @@
       </c>
       <c r="T291" s="2"/>
     </row>
-    <row r="292" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" s="4" t="s">
         <v>998</v>
       </c>
@@ -23632,7 +23657,7 @@
       </c>
       <c r="T292" s="4"/>
     </row>
-    <row r="293" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2" t="s">
         <v>998</v>
       </c>
@@ -23679,7 +23704,7 @@
       </c>
       <c r="T293" s="2"/>
     </row>
-    <row r="294" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" s="4" t="s">
         <v>998</v>
       </c>
@@ -23723,7 +23748,7 @@
       </c>
       <c r="T294" s="4"/>
     </row>
-    <row r="295" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2" t="s">
         <v>998</v>
       </c>
@@ -23774,7 +23799,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="296" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" s="4" t="s">
         <v>998</v>
       </c>
@@ -23825,7 +23850,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="297" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2" t="s">
         <v>998</v>
       </c>
@@ -23872,7 +23897,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="298" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" s="4" t="s">
         <v>998</v>
       </c>
@@ -23920,7 +23945,7 @@
       </c>
       <c r="T298" s="4"/>
     </row>
-    <row r="299" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2" t="s">
         <v>998</v>
       </c>
@@ -23971,7 +23996,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="300" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" s="4" t="s">
         <v>998</v>
       </c>
@@ -24022,7 +24047,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="301" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2" t="s">
         <v>998</v>
       </c>
@@ -24073,7 +24098,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="302" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" s="4" t="s">
         <v>998</v>
       </c>
@@ -24120,7 +24145,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="303" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2" t="s">
         <v>998</v>
       </c>
@@ -24171,7 +24196,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="304" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" s="4" t="s">
         <v>998</v>
       </c>
@@ -24215,7 +24240,7 @@
       </c>
       <c r="T304" s="4"/>
     </row>
-    <row r="305" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2" t="s">
         <v>998</v>
       </c>
@@ -24266,7 +24291,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="306" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" s="4" t="s">
         <v>998</v>
       </c>
@@ -24312,7 +24337,7 @@
       </c>
       <c r="T306" s="4"/>
     </row>
-    <row r="307" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2" t="s">
         <v>998</v>
       </c>
@@ -24359,7 +24384,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="308" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" s="4" t="s">
         <v>998</v>
       </c>
@@ -24410,7 +24435,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="309" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>998</v>
       </c>
@@ -24465,7 +24490,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="310" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" s="4" t="s">
         <v>998</v>
       </c>
@@ -24518,7 +24543,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="311" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2" t="s">
         <v>998</v>
       </c>
@@ -24565,7 +24590,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="312" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" s="4" t="s">
         <v>998</v>
       </c>
@@ -24612,7 +24637,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="313" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2" t="s">
         <v>998</v>
       </c>
@@ -24659,7 +24684,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="314" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" s="6" t="s">
         <v>998</v>
       </c>
@@ -24709,7 +24734,7 @@
       </c>
       <c r="U314" s="7"/>
     </row>
-    <row r="315" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" s="2" t="s">
         <v>998</v>
       </c>
@@ -24754,7 +24779,7 @@
       </c>
       <c r="T315" s="2"/>
     </row>
-    <row r="316" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" s="4" t="s">
         <v>998</v>
       </c>
@@ -24802,7 +24827,7 @@
       </c>
       <c r="T316" s="4"/>
     </row>
-    <row r="317" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2" t="s">
         <v>998</v>
       </c>
@@ -24851,7 +24876,7 @@
       </c>
       <c r="T317" s="2"/>
     </row>
-    <row r="318" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" s="4" t="s">
         <v>998</v>
       </c>
@@ -24893,7 +24918,7 @@
       </c>
       <c r="T318" s="4"/>
     </row>
-    <row r="319" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2" t="s">
         <v>998</v>
       </c>
@@ -24938,7 +24963,7 @@
       </c>
       <c r="T319" s="2"/>
     </row>
-    <row r="320" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" s="4" t="s">
         <v>998</v>
       </c>
@@ -24980,7 +25005,7 @@
       </c>
       <c r="T320" s="4"/>
     </row>
-    <row r="321" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2" t="s">
         <v>998</v>
       </c>
@@ -25031,7 +25056,7 @@
       </c>
       <c r="T321" s="2"/>
     </row>
-    <row r="322" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" s="4" t="s">
         <v>998</v>
       </c>
@@ -25073,7 +25098,7 @@
       </c>
       <c r="T322" s="4"/>
     </row>
-    <row r="323" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2" t="s">
         <v>998</v>
       </c>
@@ -25117,7 +25142,7 @@
       </c>
       <c r="T323" s="2"/>
     </row>
-    <row r="324" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" s="4" t="s">
         <v>998</v>
       </c>
@@ -25159,7 +25184,7 @@
       </c>
       <c r="T324" s="4"/>
     </row>
-    <row r="325" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2" t="s">
         <v>998</v>
       </c>
@@ -25204,7 +25229,7 @@
       </c>
       <c r="T325" s="2"/>
     </row>
-    <row r="326" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" s="4" t="s">
         <v>998</v>
       </c>
@@ -25246,7 +25271,7 @@
       </c>
       <c r="T326" s="4"/>
     </row>
-    <row r="327" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2" t="s">
         <v>998</v>
       </c>
@@ -25288,7 +25313,7 @@
       </c>
       <c r="T327" s="2"/>
     </row>
-    <row r="328" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" s="4" t="s">
         <v>998</v>
       </c>
@@ -25342,7 +25367,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="329" spans="1:22" ht="70" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:22" ht="70" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2" t="s">
         <v>998</v>
       </c>
@@ -25393,7 +25418,7 @@
       </c>
       <c r="T329" s="2"/>
     </row>
-    <row r="330" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" s="4" t="s">
         <v>998</v>
       </c>
@@ -25444,7 +25469,7 @@
       </c>
       <c r="T330" s="4"/>
     </row>
-    <row r="331" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2" t="s">
         <v>998</v>
       </c>
@@ -25495,7 +25520,7 @@
       </c>
       <c r="T331" s="2"/>
     </row>
-    <row r="332" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" s="4" t="s">
         <v>998</v>
       </c>
@@ -25546,7 +25571,7 @@
       </c>
       <c r="T332" s="4"/>
     </row>
-    <row r="333" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2" t="s">
         <v>998</v>
       </c>
@@ -25600,7 +25625,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="334" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" s="4" t="s">
         <v>998</v>
       </c>
@@ -25654,7 +25679,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="335" spans="1:22" ht="84" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:22" ht="84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2" t="s">
         <v>998</v>
       </c>
@@ -25708,7 +25733,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="336" spans="1:22" ht="332" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:22" ht="332" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" s="4" t="s">
         <v>998</v>
       </c>
@@ -25765,7 +25790,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="337" spans="1:23" ht="56" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:23" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2" t="s">
         <v>998</v>
       </c>
@@ -25819,7 +25844,7 @@
       </c>
       <c r="T337" s="2"/>
     </row>
-    <row r="338" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" s="4" t="s">
         <v>998</v>
       </c>
@@ -25866,7 +25891,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="339" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" s="2" t="s">
         <v>998</v>
       </c>
@@ -25920,7 +25945,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="340" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="4" t="s">
         <v>998</v>
       </c>
@@ -25973,7 +25998,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="341" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2" t="s">
         <v>998</v>
       </c>
@@ -26020,7 +26045,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="342" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="4" t="s">
         <v>998</v>
       </c>
@@ -26073,7 +26098,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="343" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2" t="s">
         <v>998</v>
       </c>
@@ -26117,7 +26142,7 @@
       </c>
       <c r="T343" s="2"/>
     </row>
-    <row r="344" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="6" t="s">
         <v>1358</v>
       </c>
@@ -26172,7 +26197,7 @@
       </c>
       <c r="U344" s="7"/>
     </row>
-    <row r="345" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26219,7 +26244,7 @@
       </c>
       <c r="T345" s="2"/>
     </row>
-    <row r="346" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26266,7 +26291,7 @@
       </c>
       <c r="T346" s="4"/>
     </row>
-    <row r="347" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26313,10 +26338,10 @@
       </c>
       <c r="T347" s="2"/>
       <c r="W347" s="20" t="s">
-        <v>3198</v>
-      </c>
-    </row>
-    <row r="348" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3197</v>
+      </c>
+    </row>
+    <row r="348" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26363,7 +26388,7 @@
       </c>
       <c r="T348" s="4"/>
     </row>
-    <row r="349" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26410,7 +26435,7 @@
       </c>
       <c r="T349" s="2"/>
     </row>
-    <row r="350" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26457,7 +26482,7 @@
       </c>
       <c r="T350" s="4"/>
     </row>
-    <row r="351" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26504,7 +26529,7 @@
       </c>
       <c r="T351" s="2"/>
     </row>
-    <row r="352" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26551,7 +26576,7 @@
       </c>
       <c r="T352" s="4"/>
     </row>
-    <row r="353" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26598,7 +26623,7 @@
       </c>
       <c r="T353" s="2"/>
     </row>
-    <row r="354" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26645,7 +26670,7 @@
       </c>
       <c r="T354" s="4"/>
     </row>
-    <row r="355" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26692,7 +26717,7 @@
       </c>
       <c r="T355" s="2"/>
     </row>
-    <row r="356" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26739,7 +26764,7 @@
       </c>
       <c r="T356" s="4"/>
     </row>
-    <row r="357" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26786,7 +26811,7 @@
       </c>
       <c r="T357" s="2"/>
     </row>
-    <row r="358" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26833,7 +26858,7 @@
       </c>
       <c r="T358" s="4"/>
     </row>
-    <row r="359" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26880,7 +26905,7 @@
       </c>
       <c r="T359" s="2"/>
     </row>
-    <row r="360" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" s="4" t="s">
         <v>1358</v>
       </c>
@@ -26927,7 +26952,7 @@
       </c>
       <c r="T360" s="4"/>
     </row>
-    <row r="361" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2" t="s">
         <v>1358</v>
       </c>
@@ -26983,7 +27008,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="362" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27036,7 +27061,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="363" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27089,7 +27114,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="364" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27142,7 +27167,7 @@
         <v>1434</v>
       </c>
     </row>
-    <row r="365" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27198,7 +27223,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="366" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27251,7 +27276,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="367" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27301,7 +27326,7 @@
       </c>
       <c r="T367" s="2"/>
     </row>
-    <row r="368" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27354,7 +27379,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="369" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27407,7 +27432,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="370" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27460,7 +27485,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="371" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27514,7 +27539,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="372" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27567,7 +27592,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="373" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27620,7 +27645,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="374" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27673,7 +27698,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="375" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27726,7 +27751,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="376" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27779,7 +27804,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="377" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27828,7 +27853,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="378" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27877,7 +27902,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="379" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2" t="s">
         <v>1358</v>
       </c>
@@ -27923,7 +27948,7 @@
       </c>
       <c r="T379" s="2"/>
     </row>
-    <row r="380" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" s="4" t="s">
         <v>1358</v>
       </c>
@@ -27979,7 +28004,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="381" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28035,7 +28060,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="382" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28087,7 +28112,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="383" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="383" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28139,7 +28164,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="384" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28186,7 +28211,7 @@
       </c>
       <c r="T384" s="4"/>
     </row>
-    <row r="385" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28237,7 +28262,7 @@
       </c>
       <c r="T385" s="2"/>
     </row>
-    <row r="386" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28290,7 +28315,7 @@
       </c>
       <c r="T386" s="4"/>
     </row>
-    <row r="387" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" s="6" t="s">
         <v>1358</v>
       </c>
@@ -28342,7 +28367,7 @@
       </c>
       <c r="U387" s="7"/>
     </row>
-    <row r="388" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28389,7 +28414,7 @@
       </c>
       <c r="T388" s="4"/>
     </row>
-    <row r="389" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28436,7 +28461,7 @@
       </c>
       <c r="T389" s="2"/>
     </row>
-    <row r="390" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28483,7 +28508,7 @@
       </c>
       <c r="T390" s="4"/>
     </row>
-    <row r="391" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28530,7 +28555,7 @@
       </c>
       <c r="T391" s="2"/>
     </row>
-    <row r="392" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28577,7 +28602,7 @@
       </c>
       <c r="T392" s="4"/>
     </row>
-    <row r="393" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28624,7 +28649,7 @@
       </c>
       <c r="T393" s="2"/>
     </row>
-    <row r="394" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" s="6" t="s">
         <v>1358</v>
       </c>
@@ -28676,7 +28701,7 @@
       </c>
       <c r="U394" s="7"/>
     </row>
-    <row r="395" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28732,7 +28757,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="396" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28788,7 +28813,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="397" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2" t="s">
         <v>1358</v>
       </c>
@@ -28837,7 +28862,7 @@
       </c>
       <c r="T397" s="2"/>
     </row>
-    <row r="398" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" s="4" t="s">
         <v>1358</v>
       </c>
@@ -28886,7 +28911,7 @@
       </c>
       <c r="T398" s="4"/>
     </row>
-    <row r="399" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" s="6" t="s">
         <v>1358</v>
       </c>
@@ -28938,7 +28963,7 @@
       </c>
       <c r="U399" s="7"/>
     </row>
-    <row r="400" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" s="6" t="s">
         <v>1358</v>
       </c>
@@ -28992,7 +29017,7 @@
       </c>
       <c r="U400" s="7"/>
     </row>
-    <row r="401" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29039,7 +29064,7 @@
       </c>
       <c r="T401" s="2"/>
     </row>
-    <row r="402" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29086,7 +29111,7 @@
       </c>
       <c r="T402" s="4"/>
     </row>
-    <row r="403" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29133,7 +29158,7 @@
       </c>
       <c r="T403" s="2"/>
     </row>
-    <row r="404" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29180,7 +29205,7 @@
       </c>
       <c r="T404" s="4"/>
     </row>
-    <row r="405" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29227,7 +29252,7 @@
       </c>
       <c r="T405" s="2"/>
     </row>
-    <row r="406" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29274,7 +29299,7 @@
       </c>
       <c r="T406" s="4"/>
     </row>
-    <row r="407" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29321,7 +29346,7 @@
       </c>
       <c r="T407" s="2"/>
     </row>
-    <row r="408" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29368,7 +29393,7 @@
       </c>
       <c r="T408" s="4"/>
     </row>
-    <row r="409" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29415,7 +29440,7 @@
       </c>
       <c r="T409" s="2"/>
     </row>
-    <row r="410" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29462,7 +29487,7 @@
       </c>
       <c r="T410" s="4"/>
     </row>
-    <row r="411" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29509,7 +29534,7 @@
       </c>
       <c r="T411" s="2"/>
     </row>
-    <row r="412" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29558,7 +29583,7 @@
       </c>
       <c r="T412" s="4"/>
     </row>
-    <row r="413" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29607,7 +29632,7 @@
       </c>
       <c r="T413" s="2"/>
     </row>
-    <row r="414" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29656,7 +29681,7 @@
       </c>
       <c r="T414" s="4"/>
     </row>
-    <row r="415" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29712,7 +29737,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="416" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29768,7 +29793,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="417" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29818,7 +29843,7 @@
       </c>
       <c r="T417" s="2"/>
     </row>
-    <row r="418" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29871,7 +29896,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="419" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2" t="s">
         <v>1358</v>
       </c>
@@ -29921,7 +29946,7 @@
       </c>
       <c r="T419" s="2"/>
     </row>
-    <row r="420" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" s="4" t="s">
         <v>1358</v>
       </c>
@@ -29970,7 +29995,7 @@
       </c>
       <c r="T420" s="4"/>
     </row>
-    <row r="421" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30023,7 +30048,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="422" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30076,7 +30101,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="423" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30132,7 +30157,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="424" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30185,7 +30210,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="425" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30238,7 +30263,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="426" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30291,7 +30316,7 @@
         <v>1681</v>
       </c>
     </row>
-    <row r="427" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30347,7 +30372,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="428" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30400,7 +30425,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="429" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" s="6" t="s">
         <v>1358</v>
       </c>
@@ -30452,7 +30477,7 @@
       </c>
       <c r="U429" s="7"/>
     </row>
-    <row r="430" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30499,7 +30524,7 @@
       </c>
       <c r="T430" s="4"/>
     </row>
-    <row r="431" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30546,7 +30571,7 @@
       </c>
       <c r="T431" s="2"/>
     </row>
-    <row r="432" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30595,7 +30620,7 @@
       </c>
       <c r="T432" s="4"/>
     </row>
-    <row r="433" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30642,7 +30667,7 @@
       </c>
       <c r="T433" s="2"/>
     </row>
-    <row r="434" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30689,7 +30714,7 @@
       </c>
       <c r="T434" s="4"/>
     </row>
-    <row r="435" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30736,7 +30761,7 @@
       </c>
       <c r="T435" s="2"/>
     </row>
-    <row r="436" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30780,7 +30805,7 @@
       </c>
       <c r="T436" s="4"/>
     </row>
-    <row r="437" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30827,7 +30852,7 @@
       </c>
       <c r="T437" s="2"/>
     </row>
-    <row r="438" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30874,7 +30899,7 @@
       </c>
       <c r="T438" s="4"/>
     </row>
-    <row r="439" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2" t="s">
         <v>1358</v>
       </c>
@@ -30921,7 +30946,7 @@
       </c>
       <c r="T439" s="2"/>
     </row>
-    <row r="440" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" s="4" t="s">
         <v>1358</v>
       </c>
@@ -30968,7 +30993,7 @@
       </c>
       <c r="T440" s="4"/>
     </row>
-    <row r="441" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31015,7 +31040,7 @@
       </c>
       <c r="T441" s="2"/>
     </row>
-    <row r="442" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31062,7 +31087,7 @@
       </c>
       <c r="T442" s="4"/>
     </row>
-    <row r="443" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31109,7 +31134,7 @@
       </c>
       <c r="T443" s="2"/>
     </row>
-    <row r="444" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31156,7 +31181,7 @@
       </c>
       <c r="T444" s="4"/>
     </row>
-    <row r="445" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31212,7 +31237,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="446" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31268,7 +31293,7 @@
         <v>1753</v>
       </c>
     </row>
-    <row r="447" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31324,7 +31349,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="448" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31378,7 +31403,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="449" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31431,7 +31456,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="450" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31487,7 +31512,7 @@
         <v>1773</v>
       </c>
     </row>
-    <row r="451" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31543,7 +31568,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="452" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31594,7 +31619,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="453" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31645,7 +31670,7 @@
         <v>1788</v>
       </c>
     </row>
-    <row r="454" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31698,7 +31723,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="455" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31744,7 +31769,7 @@
       </c>
       <c r="T455" s="2"/>
     </row>
-    <row r="456" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31794,7 +31819,7 @@
       </c>
       <c r="T456" s="4"/>
     </row>
-    <row r="457" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31840,7 +31865,7 @@
       </c>
       <c r="T457" s="2"/>
     </row>
-    <row r="458" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" s="4" t="s">
         <v>1358</v>
       </c>
@@ -31886,7 +31911,7 @@
       </c>
       <c r="T458" s="4"/>
     </row>
-    <row r="459" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2" t="s">
         <v>1358</v>
       </c>
@@ -31935,7 +31960,7 @@
       </c>
       <c r="T459" s="2"/>
     </row>
-    <row r="460" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" s="6" t="s">
         <v>1358</v>
       </c>
@@ -31987,7 +32012,7 @@
       </c>
       <c r="U460" s="7"/>
     </row>
-    <row r="461" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32034,7 +32059,7 @@
       </c>
       <c r="T461" s="2"/>
     </row>
-    <row r="462" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32086,7 +32111,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="463" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32135,7 +32160,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="464" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32184,7 +32209,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="465" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32233,7 +32258,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="466" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32282,7 +32307,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="467" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32331,7 +32356,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="468" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32377,7 +32402,7 @@
       </c>
       <c r="T468" s="4"/>
     </row>
-    <row r="469" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32430,7 +32455,7 @@
       </c>
       <c r="T469" s="2"/>
     </row>
-    <row r="470" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32476,7 +32501,7 @@
       </c>
       <c r="T470" s="4"/>
     </row>
-    <row r="471" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32529,7 +32554,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="472" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32575,7 +32600,7 @@
       </c>
       <c r="T472" s="4"/>
     </row>
-    <row r="473" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32625,7 +32650,7 @@
       </c>
       <c r="T473" s="2"/>
     </row>
-    <row r="474" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32671,7 +32696,7 @@
       </c>
       <c r="T474" s="4"/>
     </row>
-    <row r="475" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32719,7 +32744,7 @@
       </c>
       <c r="T475" s="2"/>
     </row>
-    <row r="476" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32768,7 +32793,7 @@
       </c>
       <c r="T476" s="4"/>
     </row>
-    <row r="477" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32817,7 +32842,7 @@
       </c>
       <c r="T477" s="2"/>
     </row>
-    <row r="478" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32863,7 +32888,7 @@
       </c>
       <c r="T478" s="4"/>
     </row>
-    <row r="479" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="2" t="s">
         <v>1358</v>
       </c>
@@ -32909,7 +32934,7 @@
       </c>
       <c r="T479" s="2"/>
     </row>
-    <row r="480" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="4" t="s">
         <v>1358</v>
       </c>
@@ -32955,7 +32980,7 @@
       </c>
       <c r="T480" s="4"/>
     </row>
-    <row r="481" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33001,7 +33026,7 @@
       </c>
       <c r="T481" s="2"/>
     </row>
-    <row r="482" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33047,7 +33072,7 @@
       </c>
       <c r="T482" s="4"/>
     </row>
-    <row r="483" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33093,7 +33118,7 @@
       </c>
       <c r="T483" s="2"/>
     </row>
-    <row r="484" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33141,7 +33166,7 @@
       </c>
       <c r="T484" s="4"/>
     </row>
-    <row r="485" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33187,7 +33212,7 @@
       </c>
       <c r="T485" s="2"/>
     </row>
-    <row r="486" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33240,7 +33265,7 @@
       </c>
       <c r="T486" s="4"/>
     </row>
-    <row r="487" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33286,7 +33311,7 @@
       </c>
       <c r="T487" s="2"/>
     </row>
-    <row r="488" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33332,7 +33357,7 @@
       </c>
       <c r="T488" s="4"/>
     </row>
-    <row r="489" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33378,7 +33403,7 @@
       </c>
       <c r="T489" s="2"/>
     </row>
-    <row r="490" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" s="6" t="s">
         <v>1358</v>
       </c>
@@ -33430,7 +33455,7 @@
       </c>
       <c r="U490" s="7"/>
     </row>
-    <row r="491" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33474,7 +33499,7 @@
       </c>
       <c r="T491" s="2"/>
     </row>
-    <row r="492" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33523,7 +33548,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="493" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33572,7 +33597,7 @@
         <v>1929</v>
       </c>
     </row>
-    <row r="494" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33626,7 +33651,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="495" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33675,7 +33700,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="496" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33724,7 +33749,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="497" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33776,7 +33801,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="498" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" s="4" t="s">
         <v>1358</v>
       </c>
@@ -33825,7 +33850,7 @@
         <v>1949</v>
       </c>
     </row>
-    <row r="499" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" s="2" t="s">
         <v>1358</v>
       </c>
@@ -33874,7 +33899,7 @@
         <v>1953</v>
       </c>
     </row>
-    <row r="500" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" s="4" t="s">
         <v>1954</v>
       </c>
@@ -33921,7 +33946,7 @@
       </c>
       <c r="T500" s="4"/>
     </row>
-    <row r="501" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" s="6" t="s">
         <v>1954</v>
       </c>
@@ -33975,7 +34000,7 @@
       </c>
       <c r="U501" s="7"/>
     </row>
-    <row r="502" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34022,7 +34047,7 @@
       </c>
       <c r="T502" s="4"/>
     </row>
-    <row r="503" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2" t="s">
         <v>1954</v>
       </c>
@@ -34070,7 +34095,7 @@
       </c>
       <c r="T503" s="2"/>
     </row>
-    <row r="504" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34117,7 +34142,7 @@
       </c>
       <c r="T504" s="4"/>
     </row>
-    <row r="505" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2" t="s">
         <v>1954</v>
       </c>
@@ -34164,7 +34189,7 @@
       </c>
       <c r="T505" s="2"/>
     </row>
-    <row r="506" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34211,7 +34236,7 @@
       </c>
       <c r="T506" s="4"/>
     </row>
-    <row r="507" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" s="2" t="s">
         <v>1954</v>
       </c>
@@ -34258,7 +34283,7 @@
       </c>
       <c r="T507" s="2"/>
     </row>
-    <row r="508" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34305,7 +34330,7 @@
       </c>
       <c r="T508" s="4"/>
     </row>
-    <row r="509" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" s="2" t="s">
         <v>1954</v>
       </c>
@@ -34353,7 +34378,7 @@
       </c>
       <c r="T509" s="2"/>
     </row>
-    <row r="510" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34397,7 +34422,7 @@
       </c>
       <c r="T510" s="4"/>
     </row>
-    <row r="511" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" s="2" t="s">
         <v>1954</v>
       </c>
@@ -34444,7 +34469,7 @@
       </c>
       <c r="T511" s="2"/>
     </row>
-    <row r="512" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="512" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34490,7 +34515,7 @@
       </c>
       <c r="T512" s="4"/>
     </row>
-    <row r="513" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" s="2" t="s">
         <v>1954</v>
       </c>
@@ -34543,7 +34568,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="514" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+    <row r="514" spans="1:23" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" s="4" t="s">
         <v>1954</v>
       </c>
@@ -34599,7 +34624,7 @@
         <v>2011</v>
       </c>
     </row>
-    <row r="515" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" s="6" t="s">
         <v>2012</v>
       </c>
@@ -34651,10 +34676,10 @@
       </c>
       <c r="U515" s="7"/>
       <c r="W515" s="18" t="s">
-        <v>3191</v>
-      </c>
-    </row>
-    <row r="516" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3190</v>
+      </c>
+    </row>
+    <row r="516" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" s="6" t="s">
         <v>2012</v>
       </c>
@@ -34706,10 +34731,10 @@
       </c>
       <c r="U516" s="7"/>
       <c r="W516" s="18" t="s">
-        <v>3193</v>
-      </c>
-    </row>
-    <row r="517" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3192</v>
+      </c>
+    </row>
+    <row r="517" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" s="2" t="s">
         <v>2012</v>
       </c>
@@ -34756,7 +34781,7 @@
       </c>
       <c r="T517" s="2"/>
     </row>
-    <row r="518" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:23" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" s="4" t="s">
         <v>2012</v>
       </c>
@@ -34805,7 +34830,7 @@
       </c>
       <c r="T518" s="4"/>
     </row>
-    <row r="519" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" s="2" t="s">
         <v>2012</v>
       </c>
@@ -34854,10 +34879,10 @@
       </c>
       <c r="T519" s="2"/>
       <c r="V519" s="20" t="s">
-        <v>3196</v>
-      </c>
-    </row>
-    <row r="520" spans="1:23" ht="238" x14ac:dyDescent="0.2">
+        <v>3195</v>
+      </c>
+    </row>
+    <row r="520" spans="1:23" ht="238" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" s="4" t="s">
         <v>2012</v>
       </c>
@@ -34913,7 +34938,7 @@
         <v>2037</v>
       </c>
     </row>
-    <row r="521" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" s="2" t="s">
         <v>2012</v>
       </c>
@@ -34969,7 +34994,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="522" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35015,7 +35040,7 @@
       </c>
       <c r="T522" s="4"/>
     </row>
-    <row r="523" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:23" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35071,7 +35096,7 @@
         <v>2051</v>
       </c>
     </row>
-    <row r="524" spans="1:23" ht="56" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:23" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35124,7 +35149,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="525" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35175,7 +35200,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="526" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35228,7 +35253,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="527" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35281,7 +35306,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="528" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35334,7 +35359,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="529" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35387,7 +35412,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="530" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35440,7 +35465,7 @@
         <v>2085</v>
       </c>
     </row>
-    <row r="531" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35493,7 +35518,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="532" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A532" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35546,7 +35571,7 @@
         <v>2094</v>
       </c>
     </row>
-    <row r="533" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A533" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35595,7 +35620,7 @@
       </c>
       <c r="T533" s="2"/>
     </row>
-    <row r="534" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A534" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35648,7 +35673,7 @@
         <v>2103</v>
       </c>
     </row>
-    <row r="535" spans="1:23" ht="56" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:23" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A535" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35701,7 +35726,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="536" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A536" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35752,7 +35777,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="537" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35805,7 +35830,7 @@
         <v>2117</v>
       </c>
     </row>
-    <row r="538" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35858,7 +35883,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="539" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="2" t="s">
         <v>2012</v>
       </c>
@@ -35908,7 +35933,7 @@
       </c>
       <c r="T539" s="2"/>
     </row>
-    <row r="540" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="4" t="s">
         <v>2012</v>
       </c>
@@ -35954,7 +35979,7 @@
       </c>
       <c r="T540" s="4"/>
     </row>
-    <row r="541" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36000,10 +36025,10 @@
       </c>
       <c r="T541" s="2"/>
       <c r="W541" s="20" t="s">
-        <v>3197</v>
-      </c>
-    </row>
-    <row r="542" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3196</v>
+      </c>
+    </row>
+    <row r="542" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36047,7 +36072,7 @@
       </c>
       <c r="T542" s="4"/>
     </row>
-    <row r="543" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36091,7 +36116,7 @@
       </c>
       <c r="T543" s="2"/>
     </row>
-    <row r="544" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36137,7 +36162,7 @@
       </c>
       <c r="T544" s="4"/>
     </row>
-    <row r="545" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36185,7 +36210,7 @@
       </c>
       <c r="T545" s="2"/>
     </row>
-    <row r="546" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36229,7 +36254,7 @@
       </c>
       <c r="T546" s="4"/>
     </row>
-    <row r="547" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36273,7 +36298,7 @@
       </c>
       <c r="T547" s="2"/>
     </row>
-    <row r="548" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36320,7 +36345,7 @@
       </c>
       <c r="T548" s="4"/>
     </row>
-    <row r="549" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36367,7 +36392,7 @@
       </c>
       <c r="T549" s="2"/>
     </row>
-    <row r="550" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36416,7 +36441,7 @@
       </c>
       <c r="T550" s="4"/>
     </row>
-    <row r="551" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36462,7 +36487,7 @@
       </c>
       <c r="T551" s="2"/>
     </row>
-    <row r="552" spans="1:20" ht="28" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:20" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36513,7 +36538,7 @@
       </c>
       <c r="T552" s="4"/>
     </row>
-    <row r="553" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36560,7 +36585,7 @@
       </c>
       <c r="T553" s="2"/>
     </row>
-    <row r="554" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36607,7 +36632,7 @@
       </c>
       <c r="T554" s="4"/>
     </row>
-    <row r="555" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36653,7 +36678,7 @@
       </c>
       <c r="T555" s="2"/>
     </row>
-    <row r="556" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="556" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36701,7 +36726,7 @@
       </c>
       <c r="T556" s="4"/>
     </row>
-    <row r="557" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36745,7 +36770,7 @@
       </c>
       <c r="T557" s="2"/>
     </row>
-    <row r="558" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36789,7 +36814,7 @@
       </c>
       <c r="T558" s="4"/>
     </row>
-    <row r="559" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36833,7 +36858,7 @@
       </c>
       <c r="T559" s="2"/>
     </row>
-    <row r="560" spans="1:20" ht="28" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:20" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36882,7 +36907,7 @@
       </c>
       <c r="T560" s="4"/>
     </row>
-    <row r="561" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" s="2" t="s">
         <v>2012</v>
       </c>
@@ -36929,7 +36954,7 @@
       </c>
       <c r="T561" s="2"/>
     </row>
-    <row r="562" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" s="4" t="s">
         <v>2012</v>
       </c>
@@ -36973,7 +36998,7 @@
       </c>
       <c r="T562" s="4"/>
     </row>
-    <row r="563" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37020,7 +37045,7 @@
       </c>
       <c r="T563" s="2"/>
     </row>
-    <row r="564" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:21" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37071,7 +37096,7 @@
       </c>
       <c r="T564" s="4"/>
     </row>
-    <row r="565" spans="1:21" ht="28" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:21" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37124,7 +37149,7 @@
       </c>
       <c r="T565" s="2"/>
     </row>
-    <row r="566" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="566" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37170,7 +37195,7 @@
       </c>
       <c r="T566" s="4"/>
     </row>
-    <row r="567" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37219,7 +37244,7 @@
       </c>
       <c r="T567" s="2"/>
     </row>
-    <row r="568" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37266,7 +37291,7 @@
       </c>
       <c r="T568" s="4"/>
     </row>
-    <row r="569" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" s="6" t="s">
         <v>2012</v>
       </c>
@@ -37318,7 +37343,7 @@
       </c>
       <c r="U569" s="7"/>
     </row>
-    <row r="570" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37365,7 +37390,7 @@
       </c>
       <c r="T570" s="4"/>
     </row>
-    <row r="571" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="571" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37412,7 +37437,7 @@
       </c>
       <c r="T571" s="2"/>
     </row>
-    <row r="572" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37459,7 +37484,7 @@
       </c>
       <c r="T572" s="4"/>
     </row>
-    <row r="573" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37506,7 +37531,7 @@
       </c>
       <c r="T573" s="2"/>
     </row>
-    <row r="574" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37553,7 +37578,7 @@
       </c>
       <c r="T574" s="4"/>
     </row>
-    <row r="575" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37600,7 +37625,7 @@
       </c>
       <c r="T575" s="2"/>
     </row>
-    <row r="576" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="576" spans="1:21" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37647,7 +37672,7 @@
       </c>
       <c r="T576" s="4"/>
     </row>
-    <row r="577" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37694,7 +37719,7 @@
       </c>
       <c r="T577" s="2"/>
     </row>
-    <row r="578" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37743,7 +37768,7 @@
       </c>
       <c r="T578" s="4"/>
     </row>
-    <row r="579" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37790,7 +37815,7 @@
       </c>
       <c r="T579" s="2"/>
     </row>
-    <row r="580" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37846,7 +37871,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="581" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" s="2" t="s">
         <v>2012</v>
       </c>
@@ -37900,7 +37925,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="582" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" s="4" t="s">
         <v>2012</v>
       </c>
@@ -37953,7 +37978,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="583" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38000,7 +38025,7 @@
       </c>
       <c r="T583" s="2"/>
     </row>
-    <row r="584" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38044,7 +38069,7 @@
       </c>
       <c r="T584" s="4"/>
     </row>
-    <row r="585" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38088,7 +38113,7 @@
       </c>
       <c r="T585" s="2"/>
     </row>
-    <row r="586" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38134,7 +38159,7 @@
       </c>
       <c r="T586" s="4"/>
     </row>
-    <row r="587" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38180,7 +38205,7 @@
       </c>
       <c r="T587" s="2"/>
     </row>
-    <row r="588" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38224,7 +38249,7 @@
       </c>
       <c r="T588" s="4"/>
     </row>
-    <row r="589" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38271,7 +38296,7 @@
       </c>
       <c r="T589" s="2"/>
     </row>
-    <row r="590" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38318,7 +38343,7 @@
       </c>
       <c r="T590" s="4"/>
     </row>
-    <row r="591" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="591" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38365,7 +38390,7 @@
       </c>
       <c r="T591" s="2"/>
     </row>
-    <row r="592" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38412,7 +38437,7 @@
       </c>
       <c r="T592" s="4"/>
     </row>
-    <row r="593" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="593" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38463,7 +38488,7 @@
       </c>
       <c r="T593" s="2"/>
     </row>
-    <row r="594" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" s="6" t="s">
         <v>2012</v>
       </c>
@@ -38515,7 +38540,7 @@
       </c>
       <c r="U594" s="7"/>
     </row>
-    <row r="595" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38562,7 +38587,7 @@
       </c>
       <c r="T595" s="2"/>
     </row>
-    <row r="596" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38615,7 +38640,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="597" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38668,7 +38693,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="598" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38721,7 +38746,7 @@
         <v>2332</v>
       </c>
     </row>
-    <row r="599" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38770,7 +38795,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="600" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38823,7 +38848,7 @@
         <v>2342</v>
       </c>
     </row>
-    <row r="601" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A601" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38876,7 +38901,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="602" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A602" s="4" t="s">
         <v>2012</v>
       </c>
@@ -38922,7 +38947,7 @@
       </c>
       <c r="T602" s="4"/>
     </row>
-    <row r="603" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A603" s="2" t="s">
         <v>2012</v>
       </c>
@@ -38971,7 +38996,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="604" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A604" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39030,7 +39055,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="605" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="605" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A605" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39079,7 +39104,7 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="606" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A606" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39132,7 +39157,7 @@
         <v>2371</v>
       </c>
     </row>
-    <row r="607" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A607" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39181,7 +39206,7 @@
         <v>2376</v>
       </c>
     </row>
-    <row r="608" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A608" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39230,7 +39255,7 @@
         <v>2380</v>
       </c>
     </row>
-    <row r="609" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39283,7 +39308,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="610" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A610" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39336,7 +39361,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="611" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A611" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39382,7 +39407,7 @@
       </c>
       <c r="T611" s="2"/>
     </row>
-    <row r="612" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A612" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39428,7 +39453,7 @@
       </c>
       <c r="T612" s="4"/>
     </row>
-    <row r="613" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A613" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39477,7 +39502,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="614" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A614" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39530,7 +39555,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="615" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A615" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39583,7 +39608,7 @@
         <v>2412</v>
       </c>
     </row>
-    <row r="616" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A616" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39635,7 +39660,7 @@
       </c>
       <c r="T616" s="4"/>
     </row>
-    <row r="617" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A617" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39685,7 +39710,7 @@
       </c>
       <c r="T617" s="2"/>
     </row>
-    <row r="618" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A618" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39735,7 +39760,7 @@
       </c>
       <c r="T618" s="4"/>
     </row>
-    <row r="619" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A619" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39781,7 +39806,7 @@
       </c>
       <c r="T619" s="2"/>
     </row>
-    <row r="620" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A620" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39827,7 +39852,7 @@
       </c>
       <c r="T620" s="4"/>
     </row>
-    <row r="621" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A621" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39873,7 +39898,7 @@
       </c>
       <c r="T621" s="2"/>
     </row>
-    <row r="622" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A622" s="4" t="s">
         <v>2012</v>
       </c>
@@ -39917,7 +39942,7 @@
       </c>
       <c r="T622" s="4"/>
     </row>
-    <row r="623" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
         <v>2012</v>
       </c>
@@ -39964,7 +39989,7 @@
       </c>
       <c r="T623" s="2"/>
     </row>
-    <row r="624" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="624" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A624" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40010,7 +40035,7 @@
       </c>
       <c r="T624" s="4"/>
     </row>
-    <row r="625" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A625" s="15" t="s">
         <v>2012</v>
       </c>
@@ -40019,7 +40044,7 @@
         <v>2311</v>
       </c>
       <c r="D625" s="15" t="s">
-        <v>3199</v>
+        <v>3198</v>
       </c>
       <c r="E625" s="15" t="s">
         <v>72</v>
@@ -40041,10 +40066,10 @@
       <c r="S625" s="4"/>
       <c r="T625" s="4"/>
       <c r="V625" s="20" t="s">
-        <v>3200</v>
-      </c>
-    </row>
-    <row r="626" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+        <v>3199</v>
+      </c>
+    </row>
+    <row r="626" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40090,7 +40115,7 @@
       </c>
       <c r="T626" s="2"/>
     </row>
-    <row r="627" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A627" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40140,7 +40165,7 @@
       </c>
       <c r="T627" s="4"/>
     </row>
-    <row r="628" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A628" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40192,7 +40217,7 @@
       </c>
       <c r="T628" s="2"/>
     </row>
-    <row r="629" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A629" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40239,7 +40264,7 @@
       </c>
       <c r="T629" s="4"/>
     </row>
-    <row r="630" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40288,7 +40313,7 @@
       </c>
       <c r="T630" s="2"/>
     </row>
-    <row r="631" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A631" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40344,7 +40369,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="632" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A632" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40396,7 +40421,7 @@
         <v>2471</v>
       </c>
     </row>
-    <row r="633" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A633" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40449,7 +40474,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="634" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A634" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40496,7 +40521,7 @@
       </c>
       <c r="T634" s="2"/>
     </row>
-    <row r="635" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A635" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40545,7 +40570,7 @@
       </c>
       <c r="T635" s="4"/>
     </row>
-    <row r="636" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40589,7 +40614,7 @@
       </c>
       <c r="T636" s="2"/>
     </row>
-    <row r="637" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A637" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40639,7 +40664,7 @@
       </c>
       <c r="T637" s="4"/>
     </row>
-    <row r="638" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A638" s="6" t="s">
         <v>2012</v>
       </c>
@@ -40691,7 +40716,7 @@
       </c>
       <c r="U638" s="7"/>
     </row>
-    <row r="639" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A639" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40738,7 +40763,7 @@
       </c>
       <c r="T639" s="4"/>
     </row>
-    <row r="640" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A640" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40787,7 +40812,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="641" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A641" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40846,7 +40871,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="642" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40895,7 +40920,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="643" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A643" s="4" t="s">
         <v>2012</v>
       </c>
@@ -40941,7 +40966,7 @@
       </c>
       <c r="T643" s="4"/>
     </row>
-    <row r="644" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A644" s="2" t="s">
         <v>2012</v>
       </c>
@@ -40990,7 +41015,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="645" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A645" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41039,7 +41064,7 @@
         <v>2523</v>
       </c>
     </row>
-    <row r="646" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41088,7 +41113,7 @@
         <v>2528</v>
       </c>
     </row>
-    <row r="647" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A647" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41137,7 +41162,7 @@
         <v>2533</v>
       </c>
     </row>
-    <row r="648" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41183,7 +41208,7 @@
       </c>
       <c r="T648" s="2"/>
     </row>
-    <row r="649" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A649" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41232,7 +41257,7 @@
         <v>2542</v>
       </c>
     </row>
-    <row r="650" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41285,7 +41310,7 @@
         <v>2546</v>
       </c>
     </row>
-    <row r="651" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A651" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41336,7 +41361,7 @@
         <v>2551</v>
       </c>
     </row>
-    <row r="652" spans="1:22" ht="112" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:22" ht="112" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41389,7 +41414,7 @@
         <v>2556</v>
       </c>
     </row>
-    <row r="653" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41442,7 +41467,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="654" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41488,7 +41513,7 @@
       </c>
       <c r="T654" s="2"/>
     </row>
-    <row r="655" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41534,7 +41559,7 @@
       </c>
       <c r="T655" s="4"/>
     </row>
-    <row r="656" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41583,7 +41608,7 @@
       </c>
       <c r="T656" s="2"/>
     </row>
-    <row r="657" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41629,7 +41654,7 @@
       </c>
       <c r="T657" s="4"/>
     </row>
-    <row r="658" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A658" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41680,7 +41705,7 @@
       </c>
       <c r="T658" s="2"/>
     </row>
-    <row r="659" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A659" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41729,7 +41754,7 @@
       </c>
       <c r="T659" s="4"/>
     </row>
-    <row r="660" spans="1:22" ht="112" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:22" ht="112" hidden="1" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41783,7 +41808,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="661" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A661" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41830,7 +41855,7 @@
       </c>
       <c r="T661" s="4"/>
     </row>
-    <row r="662" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41875,7 +41900,7 @@
       </c>
       <c r="T662" s="2"/>
     </row>
-    <row r="663" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A663" s="4" t="s">
         <v>2012</v>
       </c>
@@ -41922,7 +41947,7 @@
       </c>
       <c r="T663" s="4"/>
     </row>
-    <row r="664" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2" t="s">
         <v>2012</v>
       </c>
@@ -41967,7 +41992,7 @@
       </c>
       <c r="T664" s="2"/>
     </row>
-    <row r="665" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A665" s="4" t="s">
         <v>2012</v>
       </c>
@@ -42012,7 +42037,7 @@
       </c>
       <c r="T665" s="4"/>
     </row>
-    <row r="666" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
         <v>2012</v>
       </c>
@@ -42057,7 +42082,7 @@
       </c>
       <c r="T666" s="2"/>
     </row>
-    <row r="667" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A667" s="4" t="s">
         <v>2012</v>
       </c>
@@ -42102,7 +42127,7 @@
       </c>
       <c r="T667" s="4"/>
     </row>
-    <row r="668" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
         <v>2012</v>
       </c>
@@ -42147,7 +42172,7 @@
       </c>
       <c r="T668" s="2"/>
     </row>
-    <row r="669" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A669" s="4" t="s">
         <v>2012</v>
       </c>
@@ -42192,7 +42217,7 @@
       </c>
       <c r="T669" s="4"/>
     </row>
-    <row r="670" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A670" s="2" t="s">
         <v>2012</v>
       </c>
@@ -42237,7 +42262,7 @@
       </c>
       <c r="T670" s="2"/>
     </row>
-    <row r="671" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A671" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42282,7 +42307,7 @@
       <c r="T671" s="2"/>
       <c r="U671" s="7"/>
     </row>
-    <row r="672" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A672" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42302,7 +42327,7 @@
         <v>1</v>
       </c>
       <c r="G672" s="4" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="H672" s="4" t="s">
         <v>45</v>
@@ -42338,7 +42363,7 @@
       </c>
       <c r="T672" s="4"/>
     </row>
-    <row r="673" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42387,7 +42412,7 @@
       </c>
       <c r="T673" s="2"/>
     </row>
-    <row r="674" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A674" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42435,7 +42460,7 @@
       </c>
       <c r="T674" s="4"/>
     </row>
-    <row r="675" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42482,7 +42507,7 @@
       </c>
       <c r="T675" s="2"/>
     </row>
-    <row r="676" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A676" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42526,7 +42551,7 @@
       </c>
       <c r="T676" s="4"/>
     </row>
-    <row r="677" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42573,7 +42598,7 @@
       </c>
       <c r="T677" s="2"/>
     </row>
-    <row r="678" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A678" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42617,7 +42642,7 @@
       </c>
       <c r="T678" s="4"/>
     </row>
-    <row r="679" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A679" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42663,7 +42688,7 @@
       </c>
       <c r="T679" s="2"/>
     </row>
-    <row r="680" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A680" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42707,7 +42732,7 @@
       </c>
       <c r="T680" s="4"/>
     </row>
-    <row r="681" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A681" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42757,7 +42782,7 @@
       </c>
       <c r="T681" s="4"/>
     </row>
-    <row r="682" spans="1:22" ht="56" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:22" ht="56" hidden="1" x14ac:dyDescent="0.2">
       <c r="A682" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42807,7 +42832,7 @@
       </c>
       <c r="T682" s="2"/>
     </row>
-    <row r="683" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A683" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42851,7 +42876,7 @@
       </c>
       <c r="T683" s="4"/>
     </row>
-    <row r="684" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A684" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42898,7 +42923,7 @@
       </c>
       <c r="T684" s="4"/>
     </row>
-    <row r="685" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A685" s="4" t="s">
         <v>2620</v>
       </c>
@@ -42951,7 +42976,7 @@
       </c>
       <c r="T685" s="4"/>
     </row>
-    <row r="686" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2" t="s">
         <v>2620</v>
       </c>
@@ -42997,7 +43022,7 @@
       </c>
       <c r="T686" s="2"/>
     </row>
-    <row r="687" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43051,7 +43076,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="688" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43104,7 +43129,7 @@
         <v>2679</v>
       </c>
     </row>
-    <row r="689" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A689" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43154,7 +43179,7 @@
         <v>2687</v>
       </c>
     </row>
-    <row r="690" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="690" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43206,7 +43231,7 @@
         <v>2692</v>
       </c>
     </row>
-    <row r="691" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A691" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43253,7 +43278,7 @@
         <v>2697</v>
       </c>
     </row>
-    <row r="692" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A692" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43300,7 +43325,7 @@
         <v>2702</v>
       </c>
     </row>
-    <row r="693" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A693" s="6" t="s">
         <v>2620</v>
       </c>
@@ -43320,7 +43345,7 @@
         <v>1</v>
       </c>
       <c r="G693" s="6" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="H693" s="6" t="s">
         <v>25</v>
@@ -43357,7 +43382,7 @@
         <v>2707</v>
       </c>
     </row>
-    <row r="694" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="694" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A694" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43408,7 +43433,7 @@
         <v>2712</v>
       </c>
     </row>
-    <row r="695" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A695" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43457,7 +43482,7 @@
         <v>2717</v>
       </c>
     </row>
-    <row r="696" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="696" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A696" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43501,7 +43526,7 @@
       </c>
       <c r="T696" s="2"/>
     </row>
-    <row r="697" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A697" s="6" t="s">
         <v>2620</v>
       </c>
@@ -43553,10 +43578,10 @@
       </c>
       <c r="U697" s="7"/>
       <c r="W697" s="18" t="s">
-        <v>3194</v>
-      </c>
-    </row>
-    <row r="698" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3193</v>
+      </c>
+    </row>
+    <row r="698" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A698" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43603,7 +43628,7 @@
       </c>
       <c r="T698" s="2"/>
     </row>
-    <row r="699" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="699" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A699" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43647,7 +43672,7 @@
       </c>
       <c r="T699" s="4"/>
     </row>
-    <row r="700" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A700" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43694,7 +43719,7 @@
       </c>
       <c r="T700" s="2"/>
     </row>
-    <row r="701" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A701" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43738,7 +43763,7 @@
       </c>
       <c r="T701" s="4"/>
     </row>
-    <row r="702" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A702" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43782,7 +43807,7 @@
       </c>
       <c r="T702" s="2"/>
     </row>
-    <row r="703" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A703" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43829,7 +43854,7 @@
       </c>
       <c r="T703" s="4"/>
     </row>
-    <row r="704" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A704" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43873,7 +43898,7 @@
       </c>
       <c r="T704" s="2"/>
     </row>
-    <row r="705" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A705" s="4" t="s">
         <v>2620</v>
       </c>
@@ -43920,7 +43945,7 @@
       </c>
       <c r="T705" s="4"/>
     </row>
-    <row r="706" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A706" s="2" t="s">
         <v>2620</v>
       </c>
@@ -43964,7 +43989,7 @@
       </c>
       <c r="T706" s="2"/>
     </row>
-    <row r="707" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A707" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44011,7 +44036,7 @@
       </c>
       <c r="T707" s="4"/>
     </row>
-    <row r="708" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44055,7 +44080,7 @@
       </c>
       <c r="T708" s="2"/>
     </row>
-    <row r="709" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44099,7 +44124,7 @@
       </c>
       <c r="T709" s="4"/>
     </row>
-    <row r="710" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44143,7 +44168,7 @@
       </c>
       <c r="T710" s="2"/>
     </row>
-    <row r="711" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44189,7 +44214,7 @@
       </c>
       <c r="T711" s="4"/>
     </row>
-    <row r="712" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44235,7 +44260,7 @@
       </c>
       <c r="T712" s="2"/>
     </row>
-    <row r="713" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44281,7 +44306,7 @@
       </c>
       <c r="T713" s="4"/>
     </row>
-    <row r="714" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44325,7 +44350,7 @@
       </c>
       <c r="T714" s="2"/>
     </row>
-    <row r="715" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A715" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44373,7 +44398,7 @@
       </c>
       <c r="T715" s="4"/>
     </row>
-    <row r="716" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A716" s="6" t="s">
         <v>2620</v>
       </c>
@@ -44425,10 +44450,10 @@
       </c>
       <c r="U716" s="7"/>
       <c r="W716" s="18" t="s">
-        <v>3195</v>
-      </c>
-    </row>
-    <row r="717" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3194</v>
+      </c>
+    </row>
+    <row r="717" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A717" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44474,10 +44499,10 @@
       </c>
       <c r="T717" s="4"/>
       <c r="V717" s="20" t="s">
-        <v>3204</v>
-      </c>
-    </row>
-    <row r="718" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3203</v>
+      </c>
+    </row>
+    <row r="718" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A718" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44526,10 +44551,10 @@
       </c>
       <c r="T718" s="2"/>
       <c r="V718" s="20" t="s">
-        <v>3202</v>
-      </c>
-    </row>
-    <row r="719" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+        <v>3201</v>
+      </c>
+    </row>
+    <row r="719" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A719" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44582,7 +44607,7 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="720" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="720" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A720" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44631,10 +44656,10 @@
       </c>
       <c r="T720" s="2"/>
       <c r="V720" s="20" t="s">
-        <v>3203</v>
-      </c>
-    </row>
-    <row r="721" spans="1:22" x14ac:dyDescent="0.2">
+        <v>3202</v>
+      </c>
+    </row>
+    <row r="721" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A721" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44686,7 +44711,7 @@
         <v>2803</v>
       </c>
     </row>
-    <row r="722" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="722" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A722" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44735,7 +44760,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="723" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="723" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A723" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44786,7 +44811,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="724" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="724" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A724" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44840,7 +44865,7 @@
         <v>2817</v>
       </c>
     </row>
-    <row r="725" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="725" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A725" s="4" t="s">
         <v>2620</v>
       </c>
@@ -44894,7 +44919,7 @@
         <v>2822</v>
       </c>
     </row>
-    <row r="726" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="726" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A726" s="2" t="s">
         <v>2620</v>
       </c>
@@ -44948,7 +44973,7 @@
         <v>2827</v>
       </c>
     </row>
-    <row r="727" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="727" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A727" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45002,7 +45027,7 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="728" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="728" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A728" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45056,7 +45081,7 @@
         <v>2837</v>
       </c>
     </row>
-    <row r="729" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="729" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A729" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45110,7 +45135,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="730" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="730" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A730" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45164,7 +45189,7 @@
         <v>2847</v>
       </c>
     </row>
-    <row r="731" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="731" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A731" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45212,10 +45237,10 @@
       </c>
       <c r="T731" s="4"/>
       <c r="V731" s="21" t="s">
-        <v>3205</v>
-      </c>
-    </row>
-    <row r="732" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+        <v>3204</v>
+      </c>
+    </row>
+    <row r="732" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A732" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45268,7 +45293,7 @@
         <v>2856</v>
       </c>
     </row>
-    <row r="733" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="733" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A733" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45322,7 +45347,7 @@
         <v>2861</v>
       </c>
     </row>
-    <row r="734" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="734" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A734" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45371,7 +45396,7 @@
         <v>2865</v>
       </c>
     </row>
-    <row r="735" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="735" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A735" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45417,7 +45442,7 @@
       </c>
       <c r="T735" s="4"/>
     </row>
-    <row r="736" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="736" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A736" s="6" t="s">
         <v>2620</v>
       </c>
@@ -45473,7 +45498,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="737" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="737" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A737" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45522,7 +45547,7 @@
         <v>2877</v>
       </c>
     </row>
-    <row r="738" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="738" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A738" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45568,7 +45593,7 @@
       </c>
       <c r="T738" s="2"/>
     </row>
-    <row r="739" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="739" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A739" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45622,7 +45647,7 @@
         <v>2884</v>
       </c>
     </row>
-    <row r="740" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="740" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A740" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45677,7 +45702,7 @@
         <v>2888</v>
       </c>
     </row>
-    <row r="741" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="741" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A741" s="6" t="s">
         <v>2620</v>
       </c>
@@ -45729,7 +45754,7 @@
       </c>
       <c r="U741" s="7"/>
     </row>
-    <row r="742" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="742" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A742" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45749,7 +45774,7 @@
         <v>1</v>
       </c>
       <c r="G742" s="2" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="H742" s="2" t="s">
         <v>78</v>
@@ -45779,7 +45804,7 @@
       </c>
       <c r="T742" s="2"/>
     </row>
-    <row r="743" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="743" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A743" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45826,7 +45851,7 @@
       </c>
       <c r="T743" s="4"/>
     </row>
-    <row r="744" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="744" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A744" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45846,7 +45871,7 @@
         <v>1</v>
       </c>
       <c r="G744" s="2" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="H744" s="2" t="s">
         <v>78</v>
@@ -45876,7 +45901,7 @@
       </c>
       <c r="T744" s="2"/>
     </row>
-    <row r="745" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="745" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A745" s="4" t="s">
         <v>2620</v>
       </c>
@@ -45928,10 +45953,10 @@
       </c>
       <c r="T745" s="4"/>
       <c r="W745" t="s">
-        <v>3206</v>
-      </c>
-    </row>
-    <row r="746" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3205</v>
+      </c>
+    </row>
+    <row r="746" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A746" s="2" t="s">
         <v>2620</v>
       </c>
@@ -45984,7 +46009,7 @@
         <v>2911</v>
       </c>
     </row>
-    <row r="747" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="747" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A747" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46037,7 +46062,7 @@
         <v>2916</v>
       </c>
     </row>
-    <row r="748" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="748" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A748" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46090,7 +46115,7 @@
         <v>2921</v>
       </c>
     </row>
-    <row r="749" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+    <row r="749" spans="1:23" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A749" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46109,8 +46134,8 @@
       <c r="F749">
         <v>1</v>
       </c>
-      <c r="G749" s="15" t="s">
-        <v>3188</v>
+      <c r="G749" s="4" t="s">
+        <v>3224</v>
       </c>
       <c r="H749" s="4" t="s">
         <v>45</v>
@@ -46149,7 +46174,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="750" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="750" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A750" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46195,7 +46220,7 @@
       </c>
       <c r="T750" s="2"/>
     </row>
-    <row r="751" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="751" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A751" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46245,7 +46270,7 @@
       </c>
       <c r="T751" s="4"/>
     </row>
-    <row r="752" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="752" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A752" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46294,7 +46319,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="753" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="753" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A753" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46347,7 +46372,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="754" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="754" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A754" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46367,7 +46392,7 @@
         <v>1</v>
       </c>
       <c r="G754" s="2" t="s">
-        <v>3215</v>
+        <v>3214</v>
       </c>
       <c r="H754" s="2" t="s">
         <v>45</v>
@@ -46406,7 +46431,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="755" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="755" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A755" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46459,7 +46484,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="756" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="756" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A756" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46512,7 +46537,7 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="757" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="757" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A757" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46565,7 +46590,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="758" spans="1:23" ht="42" x14ac:dyDescent="0.2">
+    <row r="758" spans="1:23" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A758" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46618,7 +46643,7 @@
         <v>2965</v>
       </c>
     </row>
-    <row r="759" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="759" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A759" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46671,7 +46696,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="760" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="760" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A760" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46715,7 +46740,7 @@
       </c>
       <c r="T760" s="2"/>
     </row>
-    <row r="761" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="761" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A761" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46759,7 +46784,7 @@
       </c>
       <c r="T761" s="4"/>
     </row>
-    <row r="762" spans="1:23" ht="28" x14ac:dyDescent="0.2">
+    <row r="762" spans="1:23" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A762" s="6" t="s">
         <v>2620</v>
       </c>
@@ -46779,7 +46804,7 @@
         <v>1</v>
       </c>
       <c r="G762" s="6" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
       <c r="H762" s="6" t="s">
         <v>25</v>
@@ -46816,13 +46841,13 @@
         <v>2981</v>
       </c>
       <c r="V762" s="18" t="s">
-        <v>3207</v>
+        <v>3206</v>
       </c>
       <c r="W762" s="18" t="s">
-        <v>3212</v>
-      </c>
-    </row>
-    <row r="763" spans="1:23" x14ac:dyDescent="0.2">
+        <v>3211</v>
+      </c>
+    </row>
+    <row r="763" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A763" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46869,7 +46894,7 @@
       </c>
       <c r="T763" s="4"/>
     </row>
-    <row r="764" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="764" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A764" s="2" t="s">
         <v>2620</v>
       </c>
@@ -46916,7 +46941,7 @@
       </c>
       <c r="T764" s="2"/>
     </row>
-    <row r="765" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="765" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A765" s="4" t="s">
         <v>2620</v>
       </c>
@@ -46963,7 +46988,7 @@
       </c>
       <c r="T765" s="4"/>
     </row>
-    <row r="766" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47010,7 +47035,7 @@
       </c>
       <c r="T766" s="2"/>
     </row>
-    <row r="767" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47027,7 +47052,7 @@
         <v>77</v>
       </c>
       <c r="G767" s="4" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
       <c r="H767" s="4" t="s">
         <v>78</v>
@@ -47057,7 +47082,7 @@
       </c>
       <c r="T767" s="4"/>
     </row>
-    <row r="768" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47104,7 +47129,7 @@
       </c>
       <c r="T768" s="2"/>
     </row>
-    <row r="769" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47153,7 +47178,7 @@
       </c>
       <c r="T769" s="4"/>
     </row>
-    <row r="770" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47173,7 +47198,7 @@
         <v>1</v>
       </c>
       <c r="G770" s="2" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="H770" s="2" t="s">
         <v>83</v>
@@ -47203,7 +47228,7 @@
       </c>
       <c r="T770" s="2"/>
     </row>
-    <row r="771" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47252,7 +47277,7 @@
       </c>
       <c r="T771" s="4"/>
     </row>
-    <row r="772" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A772" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47272,7 +47297,7 @@
         <v>1</v>
       </c>
       <c r="G772" s="2" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
       <c r="H772" s="2" t="s">
         <v>45</v>
@@ -47311,7 +47336,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="773" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A773" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47367,7 +47392,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="774" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A774" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47423,7 +47448,7 @@
         <v>3022</v>
       </c>
     </row>
-    <row r="775" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A775" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47479,7 +47504,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="776" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="776" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A776" s="6" t="s">
         <v>2620</v>
       </c>
@@ -47531,7 +47556,7 @@
       </c>
       <c r="U776" s="7"/>
     </row>
-    <row r="777" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="777" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A777" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47577,7 +47602,7 @@
       </c>
       <c r="T777" s="4"/>
     </row>
-    <row r="778" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="778" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A778" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47621,7 +47646,7 @@
       </c>
       <c r="T778" s="2"/>
     </row>
-    <row r="779" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="779" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A779" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47665,7 +47690,7 @@
       </c>
       <c r="T779" s="4"/>
     </row>
-    <row r="780" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="780" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A780" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47709,7 +47734,7 @@
       </c>
       <c r="T780" s="2"/>
     </row>
-    <row r="781" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="781" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A781" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47753,7 +47778,7 @@
       </c>
       <c r="T781" s="4"/>
     </row>
-    <row r="782" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="782" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A782" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47797,7 +47822,7 @@
       </c>
       <c r="T782" s="2"/>
     </row>
-    <row r="783" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="783" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A783" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47841,7 +47866,7 @@
       </c>
       <c r="T783" s="4"/>
     </row>
-    <row r="784" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="784" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A784" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47891,7 +47916,7 @@
       </c>
       <c r="T784" s="2"/>
     </row>
-    <row r="785" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="785" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A785" s="4" t="s">
         <v>2620</v>
       </c>
@@ -47935,7 +47960,7 @@
       </c>
       <c r="T785" s="4"/>
     </row>
-    <row r="786" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="786" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A786" s="2" t="s">
         <v>2620</v>
       </c>
@@ -47979,7 +48004,7 @@
       </c>
       <c r="T786" s="2"/>
     </row>
-    <row r="787" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="787" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A787" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48023,7 +48048,7 @@
       </c>
       <c r="T787" s="4"/>
     </row>
-    <row r="788" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="788" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A788" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48067,7 +48092,7 @@
       </c>
       <c r="T788" s="2"/>
     </row>
-    <row r="789" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="789" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A789" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48114,7 +48139,7 @@
       </c>
       <c r="T789" s="4"/>
     </row>
-    <row r="790" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="790" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A790" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48158,7 +48183,7 @@
       </c>
       <c r="T790" s="2"/>
     </row>
-    <row r="791" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="791" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A791" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48202,7 +48227,7 @@
       </c>
       <c r="T791" s="4"/>
     </row>
-    <row r="792" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="792" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A792" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48246,7 +48271,7 @@
       </c>
       <c r="T792" s="2"/>
     </row>
-    <row r="793" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="793" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A793" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48266,7 +48291,7 @@
         <v>1</v>
       </c>
       <c r="G793" s="15" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
       <c r="H793" s="4" t="s">
         <v>45</v>
@@ -48305,7 +48330,7 @@
         <v>3088</v>
       </c>
     </row>
-    <row r="794" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="794" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A794" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48358,7 +48383,7 @@
         <v>3093</v>
       </c>
     </row>
-    <row r="795" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="795" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A795" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48378,7 +48403,7 @@
         <v>1</v>
       </c>
       <c r="G795" s="15" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="H795" s="4" t="s">
         <v>45</v>
@@ -48417,7 +48442,7 @@
         <v>3098</v>
       </c>
     </row>
-    <row r="796" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="796" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A796" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48470,7 +48495,7 @@
         <v>3103</v>
       </c>
     </row>
-    <row r="797" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="797" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A797" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48519,7 +48544,7 @@
         <v>3107</v>
       </c>
     </row>
-    <row r="798" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="798" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A798" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48572,7 +48597,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="799" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="799" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A799" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48625,7 +48650,7 @@
         <v>3116</v>
       </c>
     </row>
-    <row r="800" spans="1:22" ht="84" x14ac:dyDescent="0.2">
+    <row r="800" spans="1:22" ht="84" hidden="1" x14ac:dyDescent="0.2">
       <c r="A800" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48678,7 +48703,7 @@
         <v>3121</v>
       </c>
     </row>
-    <row r="801" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="801" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A801" s="4" t="s">
         <v>2620</v>
       </c>
@@ -48727,7 +48752,7 @@
         <v>3125</v>
       </c>
     </row>
-    <row r="802" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="802" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A802" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48776,7 +48801,7 @@
         <v>3129</v>
       </c>
     </row>
-    <row r="803" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="803" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A803" s="6" t="s">
         <v>2620</v>
       </c>
@@ -48830,7 +48855,7 @@
         <v>3133</v>
       </c>
     </row>
-    <row r="804" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="804" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A804" s="2" t="s">
         <v>2620</v>
       </c>
@@ -48874,7 +48899,7 @@
       </c>
       <c r="T804" s="2"/>
     </row>
-    <row r="805" spans="1:22" ht="28" x14ac:dyDescent="0.2">
+    <row r="805" spans="1:22" ht="28" hidden="1" x14ac:dyDescent="0.2">
       <c r="A805" s="6" t="s">
         <v>2620</v>
       </c>
@@ -48928,7 +48953,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="806" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="806" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A806" s="6" t="s">
         <v>3141</v>
       </c>
@@ -48978,7 +49003,7 @@
       </c>
       <c r="U806" s="7"/>
     </row>
-    <row r="807" spans="1:22" ht="42" x14ac:dyDescent="0.2">
+    <row r="807" spans="1:22" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A807" s="4" t="s">
         <v>3141</v>
       </c>
@@ -49032,7 +49057,7 @@
         <v>3155</v>
       </c>
     </row>
-    <row r="808" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="808" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A808" s="2" t="s">
         <v>3141</v>
       </c>
@@ -49077,7 +49102,7 @@
       </c>
       <c r="T808" s="2"/>
     </row>
-    <row r="809" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="809" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A809" s="4" t="s">
         <v>3141</v>
       </c>
@@ -49122,7 +49147,7 @@
       </c>
       <c r="T809" s="4"/>
     </row>
-    <row r="810" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="810" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A810" t="s">
         <v>2620</v>
       </c>
@@ -49133,7 +49158,7 @@
         <v>2622</v>
       </c>
       <c r="D810" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
       <c r="E810" t="s">
         <v>44</v>
@@ -49142,7 +49167,7 @@
         <v>1</v>
       </c>
       <c r="G810" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="I810" s="2" t="s">
         <v>2624</v>
@@ -49151,13 +49176,13 @@
         <v>2625</v>
       </c>
       <c r="T810" t="s">
+        <v>3220</v>
+      </c>
+      <c r="V810" s="20" t="s">
         <v>3221</v>
       </c>
-      <c r="V810" s="20" t="s">
-        <v>3222</v>
-      </c>
-    </row>
-    <row r="811" spans="1:22" x14ac:dyDescent="0.2">
+    </row>
+    <row r="811" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A811" t="s">
         <v>2620</v>
       </c>
@@ -49168,7 +49193,7 @@
         <v>2622</v>
       </c>
       <c r="D811" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
       <c r="E811" t="s">
         <v>44</v>
@@ -49177,7 +49202,7 @@
         <v>1</v>
       </c>
       <c r="G811" t="s">
-        <v>3220</v>
+        <v>3219</v>
       </c>
       <c r="I811" s="2" t="s">
         <v>2624</v>
@@ -49186,14 +49211,19 @@
         <v>2625</v>
       </c>
       <c r="T811" t="s">
-        <v>3221</v>
+        <v>3220</v>
       </c>
       <c r="V811" s="20" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:T811" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Bratislava"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A671:T696">
       <sortCondition ref="D1:D809"/>
     </sortState>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kellydowd/claude_code/travel_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8FC4134-8F64-0041-89F6-CD4EEF39FAF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25ED127D-ACC7-A74A-89E9-E00B747D0614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,27 @@
     <sheet name="quick notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">places!$A$1:$T$811</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">places!$A$1:$T$814</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10751" uniqueCount="3229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10786" uniqueCount="3245">
   <si>
     <t>country</t>
   </si>
@@ -9711,6 +9724,54 @@
   </si>
   <si>
     <t>such a cute cool church!</t>
+  </si>
+  <si>
+    <t>Honestly I am a little embarrassed to write this review as I should've heeded the warnings from other reviewers and not stayed here. I paid much more than I ever typically would for a hotel expecting it to be the highlight of my two week trip to Scotland. Unfortunately, it was not and I don't even think I'd stay there again at $100/night (I paid over $300/night). Some of the staff were helpful and friendly but the majority were not. The WiFi was very unreliable, breakfast was included in the price but you had to book a time (?) - I had never had to book a slot for breakfast before! And it wasn't even that great. You also had to book a time to use the sauna, and even then it wasn't heated enough. I wanted to make a reservation for dinner at the restaurant on Thursday and was told the restaurant was closed because the chef was out of town (what?!). I ended up changing a reservation I had in town another night to go, and I will say the restaurant was very good - the chef deserves better and at least a sous chef to keep things running while he's away. However, the breakfast was nothing special. I said I was celiac when booking and checking in and they assured me there would be gluten free options, but the only thing I found to safely eat was to modify the salmon and eggs on toast to just salmon and eggs, no toast. Every single other restaurant I went to in town had gluten free bread AT A MINIMUM. Not sure why they don't have it at a $300/night hotel breakfast. With all the bookings they make you do - breakfast, sauna, dinner, etc - they don't even send email confirmations or anything and there were two times where they put down the wrong time and one of those times I was told I could not eat breakfast! My recommendation is to avoid this place unless they either get rid of reservations or at least get an app to allow bookings online (WITH confirmation!) The hides are actually very cute and the view is nice. It's a bit of a hike to/from town, especially with luggage, but I wouldn't have minded that in the least if they had proper food, WiFi, and other accomodations onsite. However, there are plenty of very nice places you should consider instead: Marmalade, Cuillins Hills, Portree Hotel to name a few.</t>
+  </si>
+  <si>
+    <t>Bus stop to take to the Quiaraing walk</t>
+  </si>
+  <si>
+    <t>INCREDIBLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I wanted to make a reservation for dinner at the restaurant on Thursday and was told the restaurant was closed because the chef was out of town (what?!). I ended up changing a reservation I had in town another night to go, and I will say the restaurant was very good - the chef deserves better and at least a sous chef to keep things running while he's away. However, the breakfast was nothing special. I said I was celiac when booking and checking in and they assured me there would be gluten free options, but the only thing I found to safely eat was to modify the salmon and eggs on toast to just salmon and eggs, no toast. Every single other restaurant I went to in town had gluten free bread AT A MINIMUM. </t>
+  </si>
+  <si>
+    <t>Ate most of my meals at the hotel. Beautiful property - did their best to make things gluten free for me and the meals were delicious. Little bit of a language barrier when asking what things were but nothing google translate couldn’t solve.</t>
+  </si>
+  <si>
+    <t>Such a great town! So much to do and a nice place to relax in onsens. I had a 3-4 night stay and it was much needed after 30k+ steps/day in tokyo. Eat the black egg for 7 years of life!</t>
+  </si>
+  <si>
+    <t>KURA SUSHI Dotonbori Global Flagship Store</t>
+  </si>
+  <si>
+    <t>went here twice - check the menu online for safe GF options and then order them to your table directly vs choosing off the belt. So cheap and so good! And such a fun experience</t>
+  </si>
+  <si>
+    <t>Dotonbori</t>
+  </si>
+  <si>
+    <t>felt like Japanese Vegas strip</t>
+  </si>
+  <si>
+    <t>marked on menu</t>
+  </si>
+  <si>
+    <t>https://www.findmeglutenfree.com/biz/kura-sushi/6492933857083392</t>
+  </si>
+  <si>
+    <t>Genji Soba</t>
+  </si>
+  <si>
+    <t>I really hate to write this because the owner was SO nice and seemed SO careful about gluten free and so excited to provide a GF dining experience for me as someone who has never had soba. The food was absolutely incredible, but I did not feel well after. It wasn't my full-on traditional symptoms so it could've just been that all the fried food/tempura didn't agree with me - I'm not sure. But if you have a nig day planned the next day and you're extra sensitive, I would consider skipping :/</t>
+  </si>
+  <si>
+    <t>https://www.findmeglutenfree.com/biz/genji-soba/4535891866025984</t>
+  </si>
+  <si>
+    <t>Got to see Liechtenstein play Luxembourg in the Euros. Such a fun experience!</t>
   </si>
 </sst>
 </file>
@@ -10176,7 +10237,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W811"/>
+  <dimension ref="A1:W814"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -10270,7 +10331,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="2" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>21</v>
       </c>
@@ -10320,7 +10381,7 @@
       </c>
       <c r="U2" s="7"/>
     </row>
-    <row r="3" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>21</v>
       </c>
@@ -10367,7 +10428,7 @@
       </c>
       <c r="T3" s="4"/>
     </row>
-    <row r="4" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
@@ -10412,7 +10473,7 @@
       </c>
       <c r="T4" s="2"/>
     </row>
-    <row r="5" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>21</v>
       </c>
@@ -10462,7 +10523,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>21</v>
       </c>
@@ -10475,6 +10536,9 @@
       </c>
       <c r="E6" s="2" t="s">
         <v>50</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>51</v>
@@ -10506,7 +10570,7 @@
       </c>
       <c r="T6" s="2"/>
     </row>
-    <row r="7" spans="1:23" ht="98" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" ht="98" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>21</v>
       </c>
@@ -10554,7 +10618,7 @@
       </c>
       <c r="T7" s="4"/>
     </row>
-    <row r="8" spans="1:23" ht="98" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" ht="98" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -10608,7 +10672,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>21</v>
       </c>
@@ -10654,7 +10718,7 @@
       </c>
       <c r="T9" s="4"/>
     </row>
-    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
@@ -10670,6 +10734,9 @@
       </c>
       <c r="F10">
         <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>3244</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>73</v>
@@ -10699,7 +10766,7 @@
       </c>
       <c r="T10" s="2"/>
     </row>
-    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>21</v>
       </c>
@@ -10741,7 +10808,7 @@
       </c>
       <c r="T11" s="4"/>
     </row>
-    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>21</v>
       </c>
@@ -10783,7 +10850,7 @@
       </c>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
@@ -10825,7 +10892,7 @@
       </c>
       <c r="T13" s="4"/>
     </row>
-    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>21</v>
       </c>
@@ -10867,7 +10934,7 @@
       </c>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
@@ -10880,6 +10947,9 @@
       </c>
       <c r="E15" s="4" t="s">
         <v>77</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>78</v>
@@ -10909,7 +10979,7 @@
       </c>
       <c r="T15" s="4"/>
     </row>
-    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>21</v>
       </c>
@@ -12185,7 +12255,7 @@
       </c>
       <c r="T43" s="2"/>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>209</v>
       </c>
@@ -12230,7 +12300,7 @@
       </c>
       <c r="T44" s="4"/>
     </row>
-    <row r="45" spans="1:22" ht="98" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:22" ht="98" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>209</v>
       </c>
@@ -12284,7 +12354,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>209</v>
       </c>
@@ -12337,7 +12407,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>209</v>
       </c>
@@ -12384,7 +12454,7 @@
       </c>
       <c r="T47" s="2"/>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>209</v>
       </c>
@@ -12432,7 +12502,7 @@
       </c>
       <c r="T48" s="4"/>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>209</v>
       </c>
@@ -12480,7 +12550,7 @@
       </c>
       <c r="T49" s="2"/>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>209</v>
       </c>
@@ -12528,7 +12598,7 @@
       </c>
       <c r="T50" s="4"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>209</v>
       </c>
@@ -37310,6 +37380,9 @@
       <c r="F569">
         <v>1</v>
       </c>
+      <c r="G569" s="6" t="s">
+        <v>3233</v>
+      </c>
       <c r="H569" s="6" t="s">
         <v>25</v>
       </c>
@@ -37941,6 +38014,9 @@
       <c r="E582" s="4" t="s">
         <v>44</v>
       </c>
+      <c r="F582">
+        <v>0</v>
+      </c>
       <c r="H582" s="4" t="s">
         <v>45</v>
       </c>
@@ -38041,6 +38117,9 @@
       <c r="E584" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="F584">
+        <v>0</v>
+      </c>
       <c r="H584" s="4" t="s">
         <v>78</v>
       </c>
@@ -38085,6 +38164,9 @@
       <c r="E585" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="F585">
+        <v>0</v>
+      </c>
       <c r="H585" s="2" t="s">
         <v>78</v>
       </c>
@@ -38129,6 +38211,9 @@
       <c r="E586" s="4" t="s">
         <v>50</v>
       </c>
+      <c r="F586">
+        <v>0</v>
+      </c>
       <c r="H586" s="4" t="s">
         <v>51</v>
       </c>
@@ -38175,6 +38260,9 @@
       <c r="E587" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="F587">
+        <v>0</v>
+      </c>
       <c r="H587" s="2" t="s">
         <v>51</v>
       </c>
@@ -38220,6 +38308,9 @@
       </c>
       <c r="E588" s="4" t="s">
         <v>77</v>
+      </c>
+      <c r="F588">
+        <v>1</v>
       </c>
       <c r="H588" s="4" t="s">
         <v>78</v>
@@ -40885,7 +40976,10 @@
         <v>2506</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>72</v>
+        <v>44</v>
+      </c>
+      <c r="F642">
+        <v>0</v>
       </c>
       <c r="H642" s="2" t="s">
         <v>73</v>
@@ -40934,7 +41028,7 @@
         <v>2511</v>
       </c>
       <c r="E643" s="4" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="H643" s="4" t="s">
         <v>73</v>
@@ -40980,7 +41074,7 @@
         <v>2515</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="H644" s="2" t="s">
         <v>78</v>
@@ -41078,7 +41172,7 @@
         <v>2524</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="H646" s="2" t="s">
         <v>78</v>
@@ -41127,7 +41221,7 @@
         <v>2529</v>
       </c>
       <c r="E647" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="H647" s="4" t="s">
         <v>78</v>
@@ -41176,7 +41270,7 @@
         <v>2534</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="H648" s="2" t="s">
         <v>78</v>
@@ -41222,7 +41316,7 @@
         <v>2538</v>
       </c>
       <c r="E649" s="4" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="H649" s="4" t="s">
         <v>78</v>
@@ -41271,7 +41365,7 @@
         <v>2543</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>585</v>
+        <v>66</v>
       </c>
       <c r="H650" s="2" t="s">
         <v>586</v>
@@ -41430,6 +41524,9 @@
       <c r="E653" s="4" t="s">
         <v>66</v>
       </c>
+      <c r="F653">
+        <v>0</v>
+      </c>
       <c r="H653" s="4" t="s">
         <v>67</v>
       </c>
@@ -41527,7 +41624,10 @@
         <v>2566</v>
       </c>
       <c r="E655" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="F655">
+        <v>0</v>
       </c>
       <c r="H655" s="4" t="s">
         <v>78</v>
@@ -41573,7 +41673,7 @@
         <v>2570</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>44</v>
+        <v>185</v>
       </c>
       <c r="F656">
         <v>0</v>
@@ -41622,7 +41722,10 @@
         <v>2573</v>
       </c>
       <c r="E657" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="F657">
+        <v>0</v>
       </c>
       <c r="H657" s="4" t="s">
         <v>78</v>
@@ -47523,6 +47626,9 @@
       <c r="F776">
         <v>1</v>
       </c>
+      <c r="G776" s="6" t="s">
+        <v>3229</v>
+      </c>
       <c r="H776" s="6" t="s">
         <v>25</v>
       </c>
@@ -47572,6 +47678,12 @@
       <c r="E777" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="F777">
+        <v>1</v>
+      </c>
+      <c r="G777" s="4" t="s">
+        <v>3230</v>
+      </c>
       <c r="H777" s="4" t="s">
         <v>36</v>
       </c>
@@ -47617,6 +47729,9 @@
       </c>
       <c r="E778" s="2" t="s">
         <v>35</v>
+      </c>
+      <c r="F778">
+        <v>1</v>
       </c>
       <c r="H778" s="2" t="s">
         <v>36</v>
@@ -47882,6 +47997,9 @@
       <c r="E784" s="2" t="s">
         <v>287</v>
       </c>
+      <c r="F784">
+        <v>0</v>
+      </c>
       <c r="H784" s="2" t="s">
         <v>288</v>
       </c>
@@ -47931,6 +48049,9 @@
       </c>
       <c r="E785" s="4" t="s">
         <v>72</v>
+      </c>
+      <c r="F785">
+        <v>0</v>
       </c>
       <c r="H785" s="4" t="s">
         <v>73</v>
@@ -48064,6 +48185,9 @@
       <c r="E788" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="F788">
+        <v>1</v>
+      </c>
       <c r="H788" s="2" t="s">
         <v>78</v>
       </c>
@@ -48155,6 +48279,9 @@
       <c r="E790" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="F790">
+        <v>0</v>
+      </c>
       <c r="H790" s="2" t="s">
         <v>78</v>
       </c>
@@ -48199,6 +48326,9 @@
       <c r="E791" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="F791">
+        <v>0</v>
+      </c>
       <c r="H791" s="4" t="s">
         <v>78</v>
       </c>
@@ -48243,6 +48373,9 @@
       <c r="E792" s="2" t="s">
         <v>77</v>
       </c>
+      <c r="F792">
+        <v>0</v>
+      </c>
       <c r="H792" s="2" t="s">
         <v>78</v>
       </c>
@@ -48820,6 +48953,9 @@
       <c r="F803">
         <v>1</v>
       </c>
+      <c r="G803" s="6" t="s">
+        <v>3231</v>
+      </c>
       <c r="H803" s="6" t="s">
         <v>25</v>
       </c>
@@ -48918,6 +49054,9 @@
       <c r="F805">
         <v>1</v>
       </c>
+      <c r="G805" s="6" t="s">
+        <v>3232</v>
+      </c>
       <c r="H805" s="6" t="s">
         <v>25</v>
       </c>
@@ -49217,11 +49356,113 @@
         <v>3222</v>
       </c>
     </row>
+    <row r="812" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A812" s="4" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B812" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C812" s="4" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D812" s="2" t="s">
+        <v>3235</v>
+      </c>
+      <c r="E812" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F812">
+        <v>1</v>
+      </c>
+      <c r="G812" t="s">
+        <v>3236</v>
+      </c>
+      <c r="I812" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J812">
+        <v>2025</v>
+      </c>
+      <c r="L812" s="2" t="s">
+        <v>3239</v>
+      </c>
+      <c r="R812" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="S812" s="2" t="s">
+        <v>2489</v>
+      </c>
+      <c r="V812" s="20" t="s">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="813" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A813" s="4" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B813" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C813" s="4" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D813" s="4" t="s">
+        <v>3237</v>
+      </c>
+      <c r="F813">
+        <v>1</v>
+      </c>
+      <c r="G813" s="4" t="s">
+        <v>3238</v>
+      </c>
+      <c r="I813" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J813">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="814" spans="1:22" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A814" s="4" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B814" s="4" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C814" s="4" t="s">
+        <v>2489</v>
+      </c>
+      <c r="D814" s="2" t="s">
+        <v>3241</v>
+      </c>
+      <c r="E814" t="s">
+        <v>44</v>
+      </c>
+      <c r="F814">
+        <v>1</v>
+      </c>
+      <c r="G814" t="s">
+        <v>3242</v>
+      </c>
+      <c r="I814" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="J814">
+        <v>2025</v>
+      </c>
+      <c r="L814" t="s">
+        <v>3239</v>
+      </c>
+      <c r="V814" s="20" t="s">
+        <v>3243</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T811" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:T814" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="2">
       <filters>
-        <filter val="Bratislava"/>
+        <filter val="Vaduz"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A671:T696">
@@ -49510,6 +49751,8 @@
     <hyperlink ref="W762" r:id="rId279" xr:uid="{F6EE375E-2462-5947-969F-92314437D305}"/>
     <hyperlink ref="V810" r:id="rId280" xr:uid="{86AB9332-E970-D04D-B766-4651C394FCA9}"/>
     <hyperlink ref="V811" r:id="rId281" xr:uid="{D55762BF-E450-6C4F-97C1-2117CF4BCF4B}"/>
+    <hyperlink ref="V812" r:id="rId282" xr:uid="{DB6D39DD-CFCC-1549-B724-8C81A44FB4A7}"/>
+    <hyperlink ref="V814" r:id="rId283" xr:uid="{4CB807C2-9375-3644-A2D0-509EEE3E84E9}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -49517,7 +49760,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F00C4837-FB1C-7542-8524-923992786A42}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -49542,6 +49785,17 @@
         <v>3165</v>
       </c>
     </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3234</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U840"/>
+  <dimension ref="A1:U892"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -36307,9 +36307,1646 @@
         <v>Cobblestone streets, artist studios, I Love You Wall, Moulin Rouge, Sacré-Cœur. From ~30 EUR.</v>
       </c>
     </row>
+    <row r="841">
+      <c r="A841" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B841" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C841" t="str">
+        <v>Best Western Hotel President</v>
+      </c>
+      <c r="D841" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E841">
+        <v>1</v>
+      </c>
+      <c r="G841" t="str">
+        <v>May</v>
+      </c>
+      <c r="H841">
+        <v>2018</v>
+      </c>
+      <c r="J841">
+        <v>41.889881</v>
+      </c>
+      <c r="K841">
+        <v>12.5066375</v>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B842" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C842" t="str">
+        <v>Leonardo da Vinci International Airport</v>
+      </c>
+      <c r="D842" t="str">
+        <v>airport</v>
+      </c>
+      <c r="G842" t="str">
+        <v>May</v>
+      </c>
+      <c r="H842">
+        <v>2018</v>
+      </c>
+      <c r="J842">
+        <v>41.8034274</v>
+      </c>
+      <c r="K842">
+        <v>12.2518928</v>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B843" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C843" t="str">
+        <v>Roma Tiburtina</v>
+      </c>
+      <c r="D843" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G843" t="str">
+        <v>May</v>
+      </c>
+      <c r="H843">
+        <v>2018</v>
+      </c>
+      <c r="J843">
+        <v>41.9108193</v>
+      </c>
+      <c r="K843">
+        <v>12.5308661</v>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B844" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C844" t="str">
+        <v>Colosseum</v>
+      </c>
+      <c r="D844" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E844">
+        <v>1</v>
+      </c>
+      <c r="G844" t="str">
+        <v>May</v>
+      </c>
+      <c r="H844">
+        <v>2018</v>
+      </c>
+      <c r="J844">
+        <v>41.8902102</v>
+      </c>
+      <c r="K844">
+        <v>12.4922309</v>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B845" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C845" t="str">
+        <v>Roman Forum</v>
+      </c>
+      <c r="D845" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E845">
+        <v>1</v>
+      </c>
+      <c r="G845" t="str">
+        <v>May</v>
+      </c>
+      <c r="H845">
+        <v>2018</v>
+      </c>
+      <c r="J845">
+        <v>41.8924623</v>
+      </c>
+      <c r="K845">
+        <v>12.485325</v>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B846" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C846" t="str">
+        <v>Pantheon</v>
+      </c>
+      <c r="D846" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E846">
+        <v>1</v>
+      </c>
+      <c r="G846" t="str">
+        <v>May</v>
+      </c>
+      <c r="H846">
+        <v>2018</v>
+      </c>
+      <c r="J846">
+        <v>41.8986108</v>
+      </c>
+      <c r="K846">
+        <v>12.4768729</v>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B847" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C847" t="str">
+        <v>Trevi Fountain</v>
+      </c>
+      <c r="D847" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E847">
+        <v>1</v>
+      </c>
+      <c r="G847" t="str">
+        <v>May</v>
+      </c>
+      <c r="H847">
+        <v>2018</v>
+      </c>
+      <c r="J847">
+        <v>41.9009325</v>
+      </c>
+      <c r="K847">
+        <v>12.483313</v>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B848" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C848" t="str">
+        <v>Spanish Steps</v>
+      </c>
+      <c r="D848" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E848">
+        <v>1</v>
+      </c>
+      <c r="G848" t="str">
+        <v>May</v>
+      </c>
+      <c r="H848">
+        <v>2018</v>
+      </c>
+      <c r="J848">
+        <v>41.90599</v>
+      </c>
+      <c r="K848">
+        <v>12.482775</v>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B849" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C849" t="str">
+        <v>Church of St. Louis of the French</v>
+      </c>
+      <c r="D849" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E849">
+        <v>1</v>
+      </c>
+      <c r="G849" t="str">
+        <v>May</v>
+      </c>
+      <c r="H849">
+        <v>2018</v>
+      </c>
+      <c r="J849">
+        <v>41.899581</v>
+      </c>
+      <c r="K849">
+        <v>12.4745405</v>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B850" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C850" t="str">
+        <v>Piazza Navona</v>
+      </c>
+      <c r="D850" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E850">
+        <v>1</v>
+      </c>
+      <c r="G850" t="str">
+        <v>May</v>
+      </c>
+      <c r="H850">
+        <v>2018</v>
+      </c>
+      <c r="J850">
+        <v>41.8991633</v>
+      </c>
+      <c r="K850">
+        <v>12.4730742</v>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B851" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C851" t="str">
+        <v>Basilica di San Giovanni in Laterano</v>
+      </c>
+      <c r="D851" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E851">
+        <v>1</v>
+      </c>
+      <c r="G851" t="str">
+        <v>May</v>
+      </c>
+      <c r="H851">
+        <v>2018</v>
+      </c>
+      <c r="J851">
+        <v>41.8858811</v>
+      </c>
+      <c r="K851">
+        <v>12.505673</v>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B852" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C852" t="str">
+        <v>Galleria Alberto Sordi</v>
+      </c>
+      <c r="D852" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E852">
+        <v>1</v>
+      </c>
+      <c r="G852" t="str">
+        <v>May</v>
+      </c>
+      <c r="H852">
+        <v>2018</v>
+      </c>
+      <c r="J852">
+        <v>41.90122</v>
+      </c>
+      <c r="K852">
+        <v>12.4806028</v>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B853" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C853" t="str">
+        <v>Vatican City</v>
+      </c>
+      <c r="D853" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E853">
+        <v>1</v>
+      </c>
+      <c r="G853" t="str">
+        <v>May</v>
+      </c>
+      <c r="H853">
+        <v>2018</v>
+      </c>
+      <c r="J853">
+        <v>41.9021788</v>
+      </c>
+      <c r="K853">
+        <v>12.4536007</v>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B854" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C854" t="str">
+        <v>St. Peter's Basilica</v>
+      </c>
+      <c r="D854" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E854">
+        <v>1</v>
+      </c>
+      <c r="G854" t="str">
+        <v>May</v>
+      </c>
+      <c r="H854">
+        <v>2018</v>
+      </c>
+      <c r="J854">
+        <v>41.9021667</v>
+      </c>
+      <c r="K854">
+        <v>12.4539367</v>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B855" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C855" t="str">
+        <v>Sistine Chapel</v>
+      </c>
+      <c r="D855" t="str">
+        <v>museum</v>
+      </c>
+      <c r="E855">
+        <v>1</v>
+      </c>
+      <c r="G855" t="str">
+        <v>May</v>
+      </c>
+      <c r="H855">
+        <v>2018</v>
+      </c>
+      <c r="J855">
+        <v>41.9029468</v>
+      </c>
+      <c r="K855">
+        <v>12.4544835</v>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B856" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C856" t="str">
+        <v>Castel Sant'Angelo</v>
+      </c>
+      <c r="D856" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E856">
+        <v>0</v>
+      </c>
+      <c r="G856" t="str">
+        <v>May</v>
+      </c>
+      <c r="H856">
+        <v>2018</v>
+      </c>
+      <c r="J856">
+        <v>41.9030632</v>
+      </c>
+      <c r="K856">
+        <v>12.466276</v>
+      </c>
+      <c r="O856" t="str">
+        <v>10.50 euros to get in - reviews say not really worth it but cool panoramic views. Did not go here.</v>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B857" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C857" t="str">
+        <v>Stadio Olimpico</v>
+      </c>
+      <c r="D857" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E857">
+        <v>1</v>
+      </c>
+      <c r="G857" t="str">
+        <v>May</v>
+      </c>
+      <c r="H857">
+        <v>2018</v>
+      </c>
+      <c r="J857">
+        <v>41.934077</v>
+      </c>
+      <c r="K857">
+        <v>12.454725</v>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B858" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C858" t="str">
+        <v>Mama Eat Roma</v>
+      </c>
+      <c r="D858" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E858">
+        <v>1</v>
+      </c>
+      <c r="G858" t="str">
+        <v>May</v>
+      </c>
+      <c r="H858">
+        <v>2018</v>
+      </c>
+      <c r="I858" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J858">
+        <v>41.888408</v>
+      </c>
+      <c r="K858">
+        <v>12.4705764</v>
+      </c>
+      <c r="O858" t="str">
+        <v>GF bruschetta, lobster noodles, eggplant parm. Was AMAZING and waiter was super nice. Also have other locations including GF street food near Vatican.</v>
+      </c>
+      <c r="P858" t="str">
+        <v>https://www.findmeglutenfree.com/biz/mama-eat/5630813889626112</v>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B859" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C859" t="str">
+        <v>Pandalì</v>
+      </c>
+      <c r="D859" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E859">
+        <v>0</v>
+      </c>
+      <c r="G859" t="str">
+        <v>May</v>
+      </c>
+      <c r="H859">
+        <v>2018</v>
+      </c>
+      <c r="I859" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J859">
+        <v>41.8971938</v>
+      </c>
+      <c r="K859">
+        <v>12.4764863</v>
+      </c>
+      <c r="O859" t="str">
+        <v>GF bakery - May be hard to find, across via di torre argentina from the Shari Van playhouse</v>
+      </c>
+      <c r="P859" t="str">
+        <v>https://www.findmeglutenfree.com/biz/pandali/4939128177426432</v>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B860" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C860" t="str">
+        <v>Pantha Rei</v>
+      </c>
+      <c r="D860" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="G860" t="str">
+        <v>May</v>
+      </c>
+      <c r="H860">
+        <v>2018</v>
+      </c>
+      <c r="I860" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J860">
+        <v>41.8984739</v>
+      </c>
+      <c r="K860">
+        <v>12.4777718</v>
+      </c>
+      <c r="O860" t="str">
+        <v>GF pizza, pasta (including gnocchi), and desserts</v>
+      </c>
+      <c r="P860" t="str">
+        <v>https://www.findmeglutenfree.com/biz/pantha-rei/4938464078594048</v>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B861" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C861" t="str">
+        <v>Pub Cuccagna</v>
+      </c>
+      <c r="D861" t="str">
+        <v>bar</v>
+      </c>
+      <c r="G861" t="str">
+        <v>May</v>
+      </c>
+      <c r="H861">
+        <v>2018</v>
+      </c>
+      <c r="I861" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J861">
+        <v>41.8975265</v>
+      </c>
+      <c r="K861">
+        <v>12.4729887</v>
+      </c>
+      <c r="O861" t="str">
+        <v>GF menu items/apps plus HH from 4-6pm</v>
+      </c>
+      <c r="P861" t="str">
+        <v>https://www.findmeglutenfree.com/biz/pub-cuccagna/6240274685231104</v>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B862" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C862" t="str">
+        <v>GROM</v>
+      </c>
+      <c r="D862" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E862">
+        <v>1</v>
+      </c>
+      <c r="G862" t="str">
+        <v>May</v>
+      </c>
+      <c r="H862">
+        <v>2018</v>
+      </c>
+      <c r="I862" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J862">
+        <v>41.9002177</v>
+      </c>
+      <c r="K862">
+        <v>12.473238</v>
+      </c>
+      <c r="O862" t="str">
+        <v>GF gelato and cones (chain)</v>
+      </c>
+      <c r="P862" t="str">
+        <v>https://www.findmeglutenfree.com/biz/grom/5786114564685824</v>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B863" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C863" t="str">
+        <v>La Soffitta Renovatio</v>
+      </c>
+      <c r="D863" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E863">
+        <v>1</v>
+      </c>
+      <c r="G863" t="str">
+        <v>May</v>
+      </c>
+      <c r="H863">
+        <v>2018</v>
+      </c>
+      <c r="I863" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J863">
+        <v>41.90591</v>
+      </c>
+      <c r="K863">
+        <v>12.4590061</v>
+      </c>
+      <c r="O863" t="str">
+        <v>GF pizza</v>
+      </c>
+      <c r="P863" t="str">
+        <v>https://www.findmeglutenfree.com/biz/la-soffitta-renovatio/5317387044782080</v>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B864" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C864" t="str">
+        <v>La Pace del Cervello</v>
+      </c>
+      <c r="D864" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="G864" t="str">
+        <v>May</v>
+      </c>
+      <c r="H864">
+        <v>2018</v>
+      </c>
+      <c r="I864" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J864">
+        <v>41.8894093</v>
+      </c>
+      <c r="K864">
+        <v>12.4948523</v>
+      </c>
+      <c r="O864" t="str">
+        <v>Okay reviews - not sure if visited</v>
+      </c>
+      <c r="P864" t="str">
+        <v>https://www.findmeglutenfree.com/biz/la-pace-del-cervello/6552157379887104</v>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B865" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C865" t="str">
+        <v>Hosteria del Mercato</v>
+      </c>
+      <c r="D865" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E865">
+        <v>1</v>
+      </c>
+      <c r="G865" t="str">
+        <v>May</v>
+      </c>
+      <c r="H865">
+        <v>2018</v>
+      </c>
+      <c r="I865" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J865">
+        <v>41.906666</v>
+      </c>
+      <c r="K865">
+        <v>12.479819</v>
+      </c>
+      <c r="O865" t="str">
+        <v>Mary's recommendation - cool alley with juices, cantina, and restaurant with GF and vegan food</v>
+      </c>
+      <c r="P865" t="str">
+        <v>https://www.findmeglutenfree.com/biz/hosteria-del-mercato/6124038297092096</v>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="str">
+        <v>England</v>
+      </c>
+      <c r="B866" t="str">
+        <v>London</v>
+      </c>
+      <c r="C866" t="str">
+        <v>Pan Pacific London</v>
+      </c>
+      <c r="D866" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E866">
+        <v>1</v>
+      </c>
+      <c r="G866" t="str">
+        <v>September</v>
+      </c>
+      <c r="H866">
+        <v>2024</v>
+      </c>
+      <c r="J866">
+        <v>51.516429</v>
+      </c>
+      <c r="K866">
+        <v>-0.0803845</v>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="str">
+        <v>England</v>
+      </c>
+      <c r="B867" t="str">
+        <v>London</v>
+      </c>
+      <c r="C867" t="str">
+        <v>The Voyage Hotel Paddington, Sonder</v>
+      </c>
+      <c r="D867" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E867">
+        <v>1</v>
+      </c>
+      <c r="G867" t="str">
+        <v>September</v>
+      </c>
+      <c r="H867">
+        <v>2024</v>
+      </c>
+      <c r="J867">
+        <v>51.5155836</v>
+      </c>
+      <c r="K867">
+        <v>-0.1733879</v>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="str">
+        <v>England</v>
+      </c>
+      <c r="B868" t="str">
+        <v>London</v>
+      </c>
+      <c r="C868" t="str">
+        <v>Los Mochis London City</v>
+      </c>
+      <c r="D868" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E868">
+        <v>1</v>
+      </c>
+      <c r="G868" t="str">
+        <v>September</v>
+      </c>
+      <c r="H868">
+        <v>2024</v>
+      </c>
+      <c r="I868" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J868">
+        <v>51.5178587</v>
+      </c>
+      <c r="K868">
+        <v>-0.0835832</v>
+      </c>
+      <c r="P868" t="str">
+        <v>https://www.findmeglutenfree.com/biz/los-mochis/5682303363317760</v>
+      </c>
+      <c r="R868" t="str">
+        <v>Incredible — must go! Fun Mexican-Japanese fusion.</v>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="str">
+        <v>England</v>
+      </c>
+      <c r="B869" t="str">
+        <v>London</v>
+      </c>
+      <c r="C869" t="str">
+        <v>Los Mochis Notting Hill</v>
+      </c>
+      <c r="D869" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E869">
+        <v>1</v>
+      </c>
+      <c r="G869" t="str">
+        <v>September</v>
+      </c>
+      <c r="H869">
+        <v>2024</v>
+      </c>
+      <c r="I869" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J869">
+        <v>51.5085267</v>
+      </c>
+      <c r="K869">
+        <v>-0.1971206</v>
+      </c>
+      <c r="P869" t="str">
+        <v>https://www.findmeglutenfree.com/biz/los-mochis-restaurant/6076333531201536</v>
+      </c>
+      <c r="R869" t="str">
+        <v>Incredible — must go! Fun Mexican-Japanese fusion.</v>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="str">
+        <v>England</v>
+      </c>
+      <c r="B870" t="str">
+        <v>London</v>
+      </c>
+      <c r="C870" t="str">
+        <v>Pizza Express Live Holborn</v>
+      </c>
+      <c r="D870" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E870">
+        <v>1</v>
+      </c>
+      <c r="G870" t="str">
+        <v>September</v>
+      </c>
+      <c r="H870">
+        <v>2024</v>
+      </c>
+      <c r="I870" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J870">
+        <v>51.51791</v>
+      </c>
+      <c r="K870">
+        <v>-0.1187016</v>
+      </c>
+      <c r="O870" t="str">
+        <v>Accredited by CoeliacUK.&lt;br&gt;Has a separate gf menus and proper process in place for ensure there is no cross contamination.</v>
+      </c>
+      <c r="P870" t="str">
+        <v>https://www.findmeglutenfree.com/chains/5133311626182656/pizza-express</v>
+      </c>
+      <c r="Q870">
+        <v>4</v>
+      </c>
+      <c r="R870" t="str">
+        <v>What an awesome place - GF pizza and dough balls are a must</v>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="str">
+        <v>England</v>
+      </c>
+      <c r="B871" t="str">
+        <v>London</v>
+      </c>
+      <c r="C871" t="str">
+        <v>Wicked Fish Spitalfields</v>
+      </c>
+      <c r="D871" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E871">
+        <v>0</v>
+      </c>
+      <c r="G871" t="str">
+        <v>September</v>
+      </c>
+      <c r="H871">
+        <v>2024</v>
+      </c>
+      <c r="I871" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J871">
+        <v>51.5203364</v>
+      </c>
+      <c r="K871">
+        <v>-0.0766339</v>
+      </c>
+      <c r="P871" t="str">
+        <v>https://www.findmeglutenfree.com/biz/wicked-fish/5779279859810304</v>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="str">
+        <v>England</v>
+      </c>
+      <c r="B872" t="str">
+        <v>London</v>
+      </c>
+      <c r="C872" t="str">
+        <v>OATIS</v>
+      </c>
+      <c r="D872" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E872">
+        <v>0</v>
+      </c>
+      <c r="G872" t="str">
+        <v>September</v>
+      </c>
+      <c r="H872">
+        <v>2024</v>
+      </c>
+      <c r="I872" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J872">
+        <v>51.5134793</v>
+      </c>
+      <c r="K872">
+        <v>-0.1878318</v>
+      </c>
+      <c r="P872" t="str">
+        <v>https://www.findmeglutenfree.com/biz/oatis/6698670654881792</v>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="str">
+        <v>England</v>
+      </c>
+      <c r="B873" t="str">
+        <v>London</v>
+      </c>
+      <c r="C873" t="str">
+        <v>JOE &amp; THE JUICE</v>
+      </c>
+      <c r="D873" t="str">
+        <v>cafe</v>
+      </c>
+      <c r="E873">
+        <v>1</v>
+      </c>
+      <c r="G873" t="str">
+        <v>September</v>
+      </c>
+      <c r="H873">
+        <v>2024</v>
+      </c>
+      <c r="I873" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J873">
+        <v>51.5172289</v>
+      </c>
+      <c r="K873">
+        <v>-0.0819975</v>
+      </c>
+      <c r="P873" t="str">
+        <v>https://www.findmeglutenfree.com/biz/joe-and-the-juice/6031873342046208</v>
+      </c>
+      <c r="R873" t="str">
+        <v>Phenomenal — must try the avocado sandwich.</v>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="str">
+        <v>England</v>
+      </c>
+      <c r="B874" t="str">
+        <v>London</v>
+      </c>
+      <c r="C874" t="str">
+        <v>Black Sheep Coffee</v>
+      </c>
+      <c r="D874" t="str">
+        <v>cafe</v>
+      </c>
+      <c r="E874">
+        <v>1</v>
+      </c>
+      <c r="G874" t="str">
+        <v>September</v>
+      </c>
+      <c r="H874">
+        <v>2024</v>
+      </c>
+      <c r="I874" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J874">
+        <v>51.5187695</v>
+      </c>
+      <c r="K874">
+        <v>-0.0800697</v>
+      </c>
+      <c r="P874" t="str">
+        <v>https://www.findmeglutenfree.com/biz/black-sheep-coffee/5037307943583744</v>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="str">
+        <v>England</v>
+      </c>
+      <c r="B875" t="str">
+        <v>London</v>
+      </c>
+      <c r="C875" t="str">
+        <v>Big Ben</v>
+      </c>
+      <c r="D875" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E875">
+        <v>1</v>
+      </c>
+      <c r="G875" t="str">
+        <v>September</v>
+      </c>
+      <c r="H875">
+        <v>2024</v>
+      </c>
+      <c r="J875">
+        <v>51.5007292</v>
+      </c>
+      <c r="K875">
+        <v>-0.1246254</v>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="str">
+        <v>England</v>
+      </c>
+      <c r="B876" t="str">
+        <v>London</v>
+      </c>
+      <c r="C876" t="str">
+        <v>Tower Bridge</v>
+      </c>
+      <c r="D876" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E876">
+        <v>1</v>
+      </c>
+      <c r="G876" t="str">
+        <v>September</v>
+      </c>
+      <c r="H876">
+        <v>2024</v>
+      </c>
+      <c r="J876">
+        <v>51.5054564</v>
+      </c>
+      <c r="K876">
+        <v>-0.0753565</v>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="str">
+        <v>England</v>
+      </c>
+      <c r="B877" t="str">
+        <v>London</v>
+      </c>
+      <c r="C877" t="str">
+        <v>London Bridge</v>
+      </c>
+      <c r="D877" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E877">
+        <v>0</v>
+      </c>
+      <c r="G877" t="str">
+        <v>September</v>
+      </c>
+      <c r="H877">
+        <v>2024</v>
+      </c>
+      <c r="J877">
+        <v>51.5078788</v>
+      </c>
+      <c r="K877">
+        <v>-0.0877321</v>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="str">
+        <v>England</v>
+      </c>
+      <c r="B878" t="str">
+        <v>London</v>
+      </c>
+      <c r="C878" t="str">
+        <v>The Crown Jewels</v>
+      </c>
+      <c r="D878" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E878">
+        <v>1</v>
+      </c>
+      <c r="G878" t="str">
+        <v>September</v>
+      </c>
+      <c r="H878">
+        <v>2024</v>
+      </c>
+      <c r="J878">
+        <v>51.5085665</v>
+      </c>
+      <c r="K878">
+        <v>-0.0762586</v>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="str">
+        <v>England</v>
+      </c>
+      <c r="B879" t="str">
+        <v>London</v>
+      </c>
+      <c r="C879" t="str">
+        <v>Piccadilly Circus</v>
+      </c>
+      <c r="D879" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E879">
+        <v>1</v>
+      </c>
+      <c r="G879" t="str">
+        <v>September</v>
+      </c>
+      <c r="H879">
+        <v>2024</v>
+      </c>
+      <c r="J879">
+        <v>51.5099401</v>
+      </c>
+      <c r="K879">
+        <v>-0.133996</v>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="str">
+        <v>England</v>
+      </c>
+      <c r="B880" t="str">
+        <v>London</v>
+      </c>
+      <c r="C880" t="str">
+        <v>Kensington Palace</v>
+      </c>
+      <c r="D880" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E880">
+        <v>0</v>
+      </c>
+      <c r="G880" t="str">
+        <v>September</v>
+      </c>
+      <c r="H880">
+        <v>2024</v>
+      </c>
+      <c r="J880">
+        <v>51.5049757</v>
+      </c>
+      <c r="K880">
+        <v>-0.187681</v>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="str">
+        <v>England</v>
+      </c>
+      <c r="B881" t="str">
+        <v>London</v>
+      </c>
+      <c r="C881" t="str">
+        <v>Buckingham Palace</v>
+      </c>
+      <c r="D881" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E881">
+        <v>0</v>
+      </c>
+      <c r="G881" t="str">
+        <v>September</v>
+      </c>
+      <c r="H881">
+        <v>2024</v>
+      </c>
+      <c r="J881">
+        <v>51.501364</v>
+      </c>
+      <c r="K881">
+        <v>-0.14189</v>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="str">
+        <v>England</v>
+      </c>
+      <c r="B882" t="str">
+        <v>London</v>
+      </c>
+      <c r="C882" t="str">
+        <v>Diana Princess of Wales Memorial Walk</v>
+      </c>
+      <c r="D882" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E882">
+        <v>0</v>
+      </c>
+      <c r="G882" t="str">
+        <v>September</v>
+      </c>
+      <c r="H882">
+        <v>2024</v>
+      </c>
+      <c r="J882">
+        <v>51.5034974</v>
+      </c>
+      <c r="K882">
+        <v>-0.135798</v>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="str">
+        <v>England</v>
+      </c>
+      <c r="B883" t="str">
+        <v>London</v>
+      </c>
+      <c r="C883" t="str">
+        <v>Hyde Park</v>
+      </c>
+      <c r="D883" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E883">
+        <v>1</v>
+      </c>
+      <c r="G883" t="str">
+        <v>September</v>
+      </c>
+      <c r="H883">
+        <v>2024</v>
+      </c>
+      <c r="J883">
+        <v>51.5073638</v>
+      </c>
+      <c r="K883">
+        <v>-0.1641135</v>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="str">
+        <v>England</v>
+      </c>
+      <c r="B884" t="str">
+        <v>London</v>
+      </c>
+      <c r="C884" t="str">
+        <v>The Shard</v>
+      </c>
+      <c r="D884" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E884">
+        <v>1</v>
+      </c>
+      <c r="G884" t="str">
+        <v>September</v>
+      </c>
+      <c r="H884">
+        <v>2024</v>
+      </c>
+      <c r="J884">
+        <v>51.5045</v>
+      </c>
+      <c r="K884">
+        <v>-0.0865</v>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="str">
+        <v>England</v>
+      </c>
+      <c r="B885" t="str">
+        <v>London</v>
+      </c>
+      <c r="C885" t="str">
+        <v>London Eye</v>
+      </c>
+      <c r="D885" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E885">
+        <v>1</v>
+      </c>
+      <c r="G885" t="str">
+        <v>September</v>
+      </c>
+      <c r="H885">
+        <v>2024</v>
+      </c>
+      <c r="J885">
+        <v>51.5031864</v>
+      </c>
+      <c r="K885">
+        <v>-0.1195192</v>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="str">
+        <v>England</v>
+      </c>
+      <c r="B886" t="str">
+        <v>London</v>
+      </c>
+      <c r="C886" t="str">
+        <v>London Stadium</v>
+      </c>
+      <c r="D886" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E886">
+        <v>1</v>
+      </c>
+      <c r="G886" t="str">
+        <v>September</v>
+      </c>
+      <c r="H886">
+        <v>2024</v>
+      </c>
+      <c r="J886">
+        <v>51.5386745</v>
+      </c>
+      <c r="K886">
+        <v>-0.0164597</v>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="str">
+        <v>England</v>
+      </c>
+      <c r="B887" t="str">
+        <v>London</v>
+      </c>
+      <c r="C887" t="str">
+        <v>Stamford Bridge</v>
+      </c>
+      <c r="D887" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E887">
+        <v>1</v>
+      </c>
+      <c r="G887" t="str">
+        <v>September</v>
+      </c>
+      <c r="H887">
+        <v>2024</v>
+      </c>
+      <c r="J887">
+        <v>51.4817241</v>
+      </c>
+      <c r="K887">
+        <v>-0.1909471</v>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="str">
+        <v>England</v>
+      </c>
+      <c r="B888" t="str">
+        <v>London</v>
+      </c>
+      <c r="C888" t="str">
+        <v>Spitalfields Market</v>
+      </c>
+      <c r="D888" t="str">
+        <v>market</v>
+      </c>
+      <c r="E888">
+        <v>0</v>
+      </c>
+      <c r="G888" t="str">
+        <v>September</v>
+      </c>
+      <c r="H888">
+        <v>2024</v>
+      </c>
+      <c r="J888">
+        <v>51.5197441</v>
+      </c>
+      <c r="K888">
+        <v>-0.0760688</v>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="str">
+        <v>England</v>
+      </c>
+      <c r="B889" t="str">
+        <v>London</v>
+      </c>
+      <c r="C889" t="str">
+        <v>Borough Market</v>
+      </c>
+      <c r="D889" t="str">
+        <v>market</v>
+      </c>
+      <c r="E889">
+        <v>0</v>
+      </c>
+      <c r="G889" t="str">
+        <v>September</v>
+      </c>
+      <c r="H889">
+        <v>2024</v>
+      </c>
+      <c r="J889">
+        <v>51.5055826</v>
+      </c>
+      <c r="K889">
+        <v>-0.0904808</v>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="str">
+        <v>England</v>
+      </c>
+      <c r="B890" t="str">
+        <v>London</v>
+      </c>
+      <c r="C890" t="str">
+        <v>The Notting Hill Bookshop</v>
+      </c>
+      <c r="D890" t="str">
+        <v>shop</v>
+      </c>
+      <c r="E890">
+        <v>1</v>
+      </c>
+      <c r="G890" t="str">
+        <v>September</v>
+      </c>
+      <c r="H890">
+        <v>2024</v>
+      </c>
+      <c r="J890">
+        <v>51.5156655</v>
+      </c>
+      <c r="K890">
+        <v>-0.2055232</v>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="str">
+        <v>England</v>
+      </c>
+      <c r="B891" t="str">
+        <v>London</v>
+      </c>
+      <c r="C891" t="str">
+        <v>Heathrow Airport</v>
+      </c>
+      <c r="D891" t="str">
+        <v>airport</v>
+      </c>
+      <c r="E891">
+        <v>1</v>
+      </c>
+      <c r="G891" t="str">
+        <v>September</v>
+      </c>
+      <c r="H891">
+        <v>2024</v>
+      </c>
+      <c r="J891">
+        <v>51.4679903</v>
+      </c>
+      <c r="K891">
+        <v>-0.4550471</v>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="B892" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="C892" t="str">
+        <v>Mama Eat Lab</v>
+      </c>
+      <c r="D892" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E892">
+        <v>0</v>
+      </c>
+      <c r="G892" t="str">
+        <v>May</v>
+      </c>
+      <c r="H892">
+        <v>2018</v>
+      </c>
+      <c r="I892" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J892">
+        <v>41.9024</v>
+      </c>
+      <c r="K892">
+        <v>12.4601</v>
+      </c>
+      <c r="O892" t="str">
+        <v>GF street food near Vatican at Borgo Pio 28. Part of Mama Eat chain. AIC certified, dual kitchens.</v>
+      </c>
+      <c r="P892" t="str">
+        <v>https://www.findmeglutenfree.com/biz/mama-eat/5118841629966336</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U840"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U892"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U892"/>
+  <dimension ref="A1:U955"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -37944,9 +37944,2781 @@
         <v>https://www.findmeglutenfree.com/biz/mama-eat/5118841629966336</v>
       </c>
     </row>
+    <row r="893">
+      <c r="A893" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B893" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C893" t="str">
+        <v>Norled AS - Customer Strandkaiterminalen</v>
+      </c>
+      <c r="D893" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E893">
+        <v>1</v>
+      </c>
+      <c r="F893" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G893">
+        <v>9</v>
+      </c>
+      <c r="H893">
+        <v>2019</v>
+      </c>
+      <c r="I893" t="str">
+        <v/>
+      </c>
+      <c r="J893">
+        <v>60.395107</v>
+      </c>
+      <c r="K893">
+        <v>5.322256</v>
+      </c>
+      <c r="L893" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M893" t="str">
+        <v/>
+      </c>
+      <c r="N893" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B894" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C894" t="str">
+        <v>Bergen Airport</v>
+      </c>
+      <c r="D894" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E894">
+        <v>1</v>
+      </c>
+      <c r="F894" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G894">
+        <v>9</v>
+      </c>
+      <c r="H894">
+        <v>2019</v>
+      </c>
+      <c r="I894" t="str">
+        <v/>
+      </c>
+      <c r="J894">
+        <v>60.29183</v>
+      </c>
+      <c r="K894">
+        <v>5.222017</v>
+      </c>
+      <c r="L894" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M894" t="str">
+        <v/>
+      </c>
+      <c r="N894" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B895" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C895" t="str">
+        <v>Zander K Hotel</v>
+      </c>
+      <c r="D895" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E895">
+        <v>1</v>
+      </c>
+      <c r="F895" t="str">
+        <v>lodging</v>
+      </c>
+      <c r="G895">
+        <v>9</v>
+      </c>
+      <c r="H895">
+        <v>2019</v>
+      </c>
+      <c r="I895" t="str">
+        <v/>
+      </c>
+      <c r="J895">
+        <v>60.390278</v>
+      </c>
+      <c r="K895">
+        <v>5.335278</v>
+      </c>
+      <c r="L895" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M895" t="str">
+        <v/>
+      </c>
+      <c r="N895" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B896" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C896" t="str">
+        <v>Fishmarket in Bergen</v>
+      </c>
+      <c r="D896" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E896">
+        <v>1</v>
+      </c>
+      <c r="F896" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G896">
+        <v>9</v>
+      </c>
+      <c r="H896">
+        <v>2019</v>
+      </c>
+      <c r="I896" t="str">
+        <v/>
+      </c>
+      <c r="J896">
+        <v>60.394648</v>
+      </c>
+      <c r="K896">
+        <v>5.323482</v>
+      </c>
+      <c r="L896" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M896" t="str">
+        <v/>
+      </c>
+      <c r="N896" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B897" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C897" t="str">
+        <v>Fløibanen upper station</v>
+      </c>
+      <c r="D897" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E897">
+        <v>1</v>
+      </c>
+      <c r="F897" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G897">
+        <v>9</v>
+      </c>
+      <c r="H897">
+        <v>2019</v>
+      </c>
+      <c r="I897" t="str">
+        <v/>
+      </c>
+      <c r="J897">
+        <v>60.394716</v>
+      </c>
+      <c r="K897">
+        <v>5.343184</v>
+      </c>
+      <c r="L897" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M897" t="str">
+        <v/>
+      </c>
+      <c r="N897" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B898" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C898" t="str">
+        <v>Ulriken</v>
+      </c>
+      <c r="D898" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E898">
+        <v>1</v>
+      </c>
+      <c r="F898" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G898">
+        <v>9</v>
+      </c>
+      <c r="H898">
+        <v>2019</v>
+      </c>
+      <c r="I898" t="str">
+        <v/>
+      </c>
+      <c r="J898">
+        <v>60.377486</v>
+      </c>
+      <c r="K898">
+        <v>5.386952</v>
+      </c>
+      <c r="L898" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M898" t="str">
+        <v/>
+      </c>
+      <c r="N898" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B899" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C899" t="str">
+        <v>Pingvinen</v>
+      </c>
+      <c r="D899" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E899">
+        <v>1</v>
+      </c>
+      <c r="F899" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G899">
+        <v>9</v>
+      </c>
+      <c r="H899">
+        <v>2019</v>
+      </c>
+      <c r="I899" t="str">
+        <v/>
+      </c>
+      <c r="J899">
+        <v>60.391167</v>
+      </c>
+      <c r="K899">
+        <v>5.321778</v>
+      </c>
+      <c r="L899" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M899" t="str">
+        <v/>
+      </c>
+      <c r="N899" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B900" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C900" t="str">
+        <v>Peppes Pizza - Ole Bulls Plass</v>
+      </c>
+      <c r="D900" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E900">
+        <v>1</v>
+      </c>
+      <c r="F900" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G900">
+        <v>9</v>
+      </c>
+      <c r="H900">
+        <v>2019</v>
+      </c>
+      <c r="I900" t="str">
+        <v/>
+      </c>
+      <c r="J900">
+        <v>60.391819</v>
+      </c>
+      <c r="K900">
+        <v>5.324335</v>
+      </c>
+      <c r="L900" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M900" t="str">
+        <v/>
+      </c>
+      <c r="N900" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B901" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C901" t="str">
+        <v>Kafé Spesial</v>
+      </c>
+      <c r="D901" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E901">
+        <v>1</v>
+      </c>
+      <c r="F901" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G901">
+        <v>9</v>
+      </c>
+      <c r="H901">
+        <v>2019</v>
+      </c>
+      <c r="I901" t="str">
+        <v/>
+      </c>
+      <c r="J901">
+        <v>60.389256</v>
+      </c>
+      <c r="K901">
+        <v>5.322904</v>
+      </c>
+      <c r="L901" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M901" t="str">
+        <v/>
+      </c>
+      <c r="N901" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B902" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C902" t="str">
+        <v>Colonialen Brasseriet</v>
+      </c>
+      <c r="D902" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E902">
+        <v>1</v>
+      </c>
+      <c r="F902" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G902">
+        <v>9</v>
+      </c>
+      <c r="H902">
+        <v>2019</v>
+      </c>
+      <c r="I902" t="str">
+        <v/>
+      </c>
+      <c r="J902">
+        <v>60.393611</v>
+      </c>
+      <c r="K902">
+        <v>5.328333</v>
+      </c>
+      <c r="L902" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M902" t="str">
+        <v/>
+      </c>
+      <c r="N902" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B903" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C903" t="str">
+        <v>Zupperia</v>
+      </c>
+      <c r="D903" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E903">
+        <v>1</v>
+      </c>
+      <c r="F903" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G903">
+        <v>9</v>
+      </c>
+      <c r="H903">
+        <v>2019</v>
+      </c>
+      <c r="I903" t="str">
+        <v/>
+      </c>
+      <c r="J903">
+        <v>60.391244</v>
+      </c>
+      <c r="K903">
+        <v>5.321582</v>
+      </c>
+      <c r="L903" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M903" t="str">
+        <v/>
+      </c>
+      <c r="N903" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B904" t="str">
+        <v>Bergen</v>
+      </c>
+      <c r="C904" t="str">
+        <v>Escalón Fløien</v>
+      </c>
+      <c r="D904" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E904">
+        <v>1</v>
+      </c>
+      <c r="F904" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G904">
+        <v>9</v>
+      </c>
+      <c r="H904">
+        <v>2019</v>
+      </c>
+      <c r="I904" t="str">
+        <v/>
+      </c>
+      <c r="J904">
+        <v>60.396242</v>
+      </c>
+      <c r="K904">
+        <v>5.328634</v>
+      </c>
+      <c r="L904" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M904" t="str">
+        <v/>
+      </c>
+      <c r="N904" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B905" t="str">
+        <v>Flåm</v>
+      </c>
+      <c r="C905" t="str">
+        <v>Flåmsbana Train Station</v>
+      </c>
+      <c r="D905" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E905">
+        <v>1</v>
+      </c>
+      <c r="F905" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G905">
+        <v>9</v>
+      </c>
+      <c r="H905">
+        <v>2019</v>
+      </c>
+      <c r="I905" t="str">
+        <v/>
+      </c>
+      <c r="J905">
+        <v>60.862922</v>
+      </c>
+      <c r="K905">
+        <v>7.114559</v>
+      </c>
+      <c r="L905" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M905" t="str">
+        <v/>
+      </c>
+      <c r="N905" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B906" t="str">
+        <v>Flåm</v>
+      </c>
+      <c r="C906" t="str">
+        <v>Flåmsbrygga Hotel</v>
+      </c>
+      <c r="D906" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E906">
+        <v>1</v>
+      </c>
+      <c r="F906" t="str">
+        <v>lodging</v>
+      </c>
+      <c r="G906">
+        <v>9</v>
+      </c>
+      <c r="H906">
+        <v>2019</v>
+      </c>
+      <c r="I906" t="str">
+        <v/>
+      </c>
+      <c r="J906">
+        <v>60.863888</v>
+      </c>
+      <c r="K906">
+        <v>7.117631</v>
+      </c>
+      <c r="L906" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M906" t="str">
+        <v/>
+      </c>
+      <c r="N906" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B907" t="str">
+        <v>Flåm</v>
+      </c>
+      <c r="C907" t="str">
+        <v>Flam Railway Museum</v>
+      </c>
+      <c r="D907" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E907">
+        <v>1</v>
+      </c>
+      <c r="F907" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G907">
+        <v>9</v>
+      </c>
+      <c r="H907">
+        <v>2019</v>
+      </c>
+      <c r="I907" t="str">
+        <v/>
+      </c>
+      <c r="J907">
+        <v>60.862646</v>
+      </c>
+      <c r="K907">
+        <v>7.11326</v>
+      </c>
+      <c r="L907" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M907" t="str">
+        <v/>
+      </c>
+      <c r="N907" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B908" t="str">
+        <v>Flåm</v>
+      </c>
+      <c r="C908" t="str">
+        <v>Viking Valley</v>
+      </c>
+      <c r="D908" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E908">
+        <v>1</v>
+      </c>
+      <c r="F908" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G908">
+        <v>9</v>
+      </c>
+      <c r="H908">
+        <v>2019</v>
+      </c>
+      <c r="I908" t="str">
+        <v/>
+      </c>
+      <c r="J908">
+        <v>60.87928</v>
+      </c>
+      <c r="K908">
+        <v>6.842357</v>
+      </c>
+      <c r="L908" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M908" t="str">
+        <v/>
+      </c>
+      <c r="N908" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B909" t="str">
+        <v>Flåm</v>
+      </c>
+      <c r="C909" t="str">
+        <v>Brekkefossen Waterfall</v>
+      </c>
+      <c r="D909" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E909">
+        <v>1</v>
+      </c>
+      <c r="F909" t="str">
+        <v>hiking</v>
+      </c>
+      <c r="G909">
+        <v>9</v>
+      </c>
+      <c r="H909">
+        <v>2019</v>
+      </c>
+      <c r="I909" t="str">
+        <v/>
+      </c>
+      <c r="J909">
+        <v>61.723154</v>
+      </c>
+      <c r="K909">
+        <v>5.837689</v>
+      </c>
+      <c r="L909" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M909" t="str">
+        <v/>
+      </c>
+      <c r="N909" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B910" t="str">
+        <v>Flåm</v>
+      </c>
+      <c r="C910" t="str">
+        <v>Ægir microbrewery</v>
+      </c>
+      <c r="D910" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E910">
+        <v>1</v>
+      </c>
+      <c r="F910" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G910">
+        <v>9</v>
+      </c>
+      <c r="H910">
+        <v>2019</v>
+      </c>
+      <c r="I910" t="str">
+        <v/>
+      </c>
+      <c r="J910">
+        <v>60.863776</v>
+      </c>
+      <c r="K910">
+        <v>7.117319</v>
+      </c>
+      <c r="L910" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M910" t="str">
+        <v/>
+      </c>
+      <c r="N910" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B911" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C911" t="str">
+        <v>Oslo Airport</v>
+      </c>
+      <c r="D911" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E911">
+        <v>1</v>
+      </c>
+      <c r="F911" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G911">
+        <v>9</v>
+      </c>
+      <c r="H911">
+        <v>2019</v>
+      </c>
+      <c r="I911" t="str">
+        <v/>
+      </c>
+      <c r="J911">
+        <v>60.19755</v>
+      </c>
+      <c r="K911">
+        <v>11.100415</v>
+      </c>
+      <c r="L911" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M911" t="str">
+        <v/>
+      </c>
+      <c r="N911" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B912" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C912" t="str">
+        <v>Oslo Central Station</v>
+      </c>
+      <c r="D912" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E912">
+        <v>1</v>
+      </c>
+      <c r="F912" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G912">
+        <v>9</v>
+      </c>
+      <c r="H912">
+        <v>2019</v>
+      </c>
+      <c r="I912" t="str">
+        <v/>
+      </c>
+      <c r="J912">
+        <v>59.911096</v>
+      </c>
+      <c r="K912">
+        <v>10.752457</v>
+      </c>
+      <c r="L912" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M912" t="str">
+        <v/>
+      </c>
+      <c r="N912" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B913" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C913" t="str">
+        <v>Scandic Byporten Oslo</v>
+      </c>
+      <c r="D913" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E913">
+        <v>1</v>
+      </c>
+      <c r="F913" t="str">
+        <v>lodging</v>
+      </c>
+      <c r="G913">
+        <v>9</v>
+      </c>
+      <c r="H913">
+        <v>2019</v>
+      </c>
+      <c r="I913" t="str">
+        <v/>
+      </c>
+      <c r="J913">
+        <v>59.911507</v>
+      </c>
+      <c r="K913">
+        <v>10.753149</v>
+      </c>
+      <c r="L913" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M913" t="str">
+        <v/>
+      </c>
+      <c r="N913" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B914" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C914" t="str">
+        <v>The Norwegian Museum of Cultural History</v>
+      </c>
+      <c r="D914" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E914">
+        <v>1</v>
+      </c>
+      <c r="F914" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G914">
+        <v>9</v>
+      </c>
+      <c r="H914">
+        <v>2019</v>
+      </c>
+      <c r="I914" t="str">
+        <v/>
+      </c>
+      <c r="J914">
+        <v>59.907055</v>
+      </c>
+      <c r="K914">
+        <v>10.685965</v>
+      </c>
+      <c r="L914" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M914" t="str">
+        <v/>
+      </c>
+      <c r="N914" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B915" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C915" t="str">
+        <v>Frogner Neighborhood</v>
+      </c>
+      <c r="D915" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E915">
+        <v>1</v>
+      </c>
+      <c r="F915" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G915">
+        <v>9</v>
+      </c>
+      <c r="H915">
+        <v>2019</v>
+      </c>
+      <c r="I915" t="str">
+        <v/>
+      </c>
+      <c r="J915">
+        <v>59.916739</v>
+      </c>
+      <c r="K915">
+        <v>10.706842</v>
+      </c>
+      <c r="L915" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M915" t="str">
+        <v/>
+      </c>
+      <c r="N915" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B916" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C916" t="str">
+        <v>The Vigeland Park</v>
+      </c>
+      <c r="D916" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E916">
+        <v>1</v>
+      </c>
+      <c r="F916" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G916">
+        <v>9</v>
+      </c>
+      <c r="H916">
+        <v>2019</v>
+      </c>
+      <c r="I916" t="str">
+        <v/>
+      </c>
+      <c r="J916">
+        <v>59.927029</v>
+      </c>
+      <c r="K916">
+        <v>10.700865</v>
+      </c>
+      <c r="L916" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M916" t="str">
+        <v/>
+      </c>
+      <c r="N916" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B917" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C917" t="str">
+        <v>Tjuvholmen Sculpture Park</v>
+      </c>
+      <c r="D917" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E917">
+        <v>1</v>
+      </c>
+      <c r="F917" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G917">
+        <v>9</v>
+      </c>
+      <c r="H917">
+        <v>2019</v>
+      </c>
+      <c r="I917" t="str">
+        <v/>
+      </c>
+      <c r="J917">
+        <v>59.906318</v>
+      </c>
+      <c r="K917">
+        <v>10.721718</v>
+      </c>
+      <c r="L917" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M917" t="str">
+        <v/>
+      </c>
+      <c r="N917" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B918" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C918" t="str">
+        <v>Aker Brygge</v>
+      </c>
+      <c r="D918" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E918">
+        <v>1</v>
+      </c>
+      <c r="F918" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G918">
+        <v>9</v>
+      </c>
+      <c r="H918">
+        <v>2019</v>
+      </c>
+      <c r="I918" t="str">
+        <v/>
+      </c>
+      <c r="J918">
+        <v>59.909958</v>
+      </c>
+      <c r="K918">
+        <v>10.725805</v>
+      </c>
+      <c r="L918" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M918" t="str">
+        <v/>
+      </c>
+      <c r="N918" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B919" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C919" t="str">
+        <v>Oslo Opera House</v>
+      </c>
+      <c r="D919" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E919">
+        <v>1</v>
+      </c>
+      <c r="F919" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G919">
+        <v>9</v>
+      </c>
+      <c r="H919">
+        <v>2019</v>
+      </c>
+      <c r="I919" t="str">
+        <v/>
+      </c>
+      <c r="J919">
+        <v>59.907488</v>
+      </c>
+      <c r="K919">
+        <v>10.753128</v>
+      </c>
+      <c r="L919" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M919" t="str">
+        <v/>
+      </c>
+      <c r="N919" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B920" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C920" t="str">
+        <v>Viking Biking &amp; Viking Hiking</v>
+      </c>
+      <c r="D920" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E920">
+        <v>1</v>
+      </c>
+      <c r="F920" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G920">
+        <v>9</v>
+      </c>
+      <c r="H920">
+        <v>2019</v>
+      </c>
+      <c r="I920" t="str">
+        <v/>
+      </c>
+      <c r="J920">
+        <v>59.902629</v>
+      </c>
+      <c r="K920">
+        <v>10.743466</v>
+      </c>
+      <c r="L920" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M920" t="str">
+        <v/>
+      </c>
+      <c r="N920" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B921" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C921" t="str">
+        <v>Ekebergparken</v>
+      </c>
+      <c r="D921" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E921">
+        <v>1</v>
+      </c>
+      <c r="F921" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G921">
+        <v>9</v>
+      </c>
+      <c r="H921">
+        <v>2019</v>
+      </c>
+      <c r="I921" t="str">
+        <v/>
+      </c>
+      <c r="J921">
+        <v>59.898678</v>
+      </c>
+      <c r="K921">
+        <v>10.759766</v>
+      </c>
+      <c r="L921" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M921" t="str">
+        <v/>
+      </c>
+      <c r="N921" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B922" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C922" t="str">
+        <v>Gamle Oslo</v>
+      </c>
+      <c r="D922" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E922">
+        <v>1</v>
+      </c>
+      <c r="F922" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G922">
+        <v>9</v>
+      </c>
+      <c r="H922">
+        <v>2019</v>
+      </c>
+      <c r="I922" t="str">
+        <v/>
+      </c>
+      <c r="J922">
+        <v>59.906775</v>
+      </c>
+      <c r="K922">
+        <v>10.762282</v>
+      </c>
+      <c r="L922" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M922" t="str">
+        <v/>
+      </c>
+      <c r="N922" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B923" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C923" t="str">
+        <v>Mathallen Oslo</v>
+      </c>
+      <c r="D923" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E923">
+        <v>1</v>
+      </c>
+      <c r="F923" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G923">
+        <v>9</v>
+      </c>
+      <c r="H923">
+        <v>2019</v>
+      </c>
+      <c r="I923" t="str">
+        <v/>
+      </c>
+      <c r="J923">
+        <v>59.92223</v>
+      </c>
+      <c r="K923">
+        <v>10.752052</v>
+      </c>
+      <c r="L923" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M923" t="str">
+        <v/>
+      </c>
+      <c r="N923" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B924" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C924" t="str">
+        <v>Olivia Aker Brygge</v>
+      </c>
+      <c r="D924" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E924">
+        <v>1</v>
+      </c>
+      <c r="F924" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G924">
+        <v>9</v>
+      </c>
+      <c r="H924">
+        <v>2019</v>
+      </c>
+      <c r="I924" t="str">
+        <v/>
+      </c>
+      <c r="J924">
+        <v>59.910074</v>
+      </c>
+      <c r="K924">
+        <v>10.727596</v>
+      </c>
+      <c r="L924" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M924" t="str">
+        <v/>
+      </c>
+      <c r="N924" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B925" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C925" t="str">
+        <v>Yo! Sushi</v>
+      </c>
+      <c r="D925" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E925">
+        <v>1</v>
+      </c>
+      <c r="F925" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G925">
+        <v>9</v>
+      </c>
+      <c r="H925">
+        <v>2019</v>
+      </c>
+      <c r="I925" t="str">
+        <v/>
+      </c>
+      <c r="J925">
+        <v>59.910975</v>
+      </c>
+      <c r="K925">
+        <v>10.751738</v>
+      </c>
+      <c r="L925" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M925" t="str">
+        <v/>
+      </c>
+      <c r="N925" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B926" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C926" t="str">
+        <v>Sjømagasinet</v>
+      </c>
+      <c r="D926" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E926">
+        <v>1</v>
+      </c>
+      <c r="F926" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G926">
+        <v>9</v>
+      </c>
+      <c r="H926">
+        <v>2019</v>
+      </c>
+      <c r="I926" t="str">
+        <v/>
+      </c>
+      <c r="J926">
+        <v>59.907834</v>
+      </c>
+      <c r="K926">
+        <v>10.722036</v>
+      </c>
+      <c r="L926" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M926" t="str">
+        <v/>
+      </c>
+      <c r="N926" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B927" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C927" t="str">
+        <v>Mamma Pizza</v>
+      </c>
+      <c r="D927" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E927">
+        <v>1</v>
+      </c>
+      <c r="F927" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G927">
+        <v>9</v>
+      </c>
+      <c r="H927">
+        <v>2019</v>
+      </c>
+      <c r="I927" t="str">
+        <v/>
+      </c>
+      <c r="J927">
+        <v>59.910744</v>
+      </c>
+      <c r="K927">
+        <v>10.746779</v>
+      </c>
+      <c r="L927" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M927" t="str">
+        <v/>
+      </c>
+      <c r="N927" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B928" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C928" t="str">
+        <v>Lofoten Fiskerestaurant</v>
+      </c>
+      <c r="D928" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E928">
+        <v>1</v>
+      </c>
+      <c r="F928" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G928">
+        <v>9</v>
+      </c>
+      <c r="H928">
+        <v>2019</v>
+      </c>
+      <c r="I928" t="str">
+        <v/>
+      </c>
+      <c r="J928">
+        <v>59.908574</v>
+      </c>
+      <c r="K928">
+        <v>10.72448</v>
+      </c>
+      <c r="L928" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M928" t="str">
+        <v/>
+      </c>
+      <c r="N928" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B929" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C929" t="str">
+        <v>Louise Restaurant &amp; Bar</v>
+      </c>
+      <c r="D929" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E929">
+        <v>1</v>
+      </c>
+      <c r="F929" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G929">
+        <v>9</v>
+      </c>
+      <c r="H929">
+        <v>2019</v>
+      </c>
+      <c r="I929" t="str">
+        <v/>
+      </c>
+      <c r="J929">
+        <v>59.910074</v>
+      </c>
+      <c r="K929">
+        <v>10.727596</v>
+      </c>
+      <c r="L929" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M929" t="str">
+        <v/>
+      </c>
+      <c r="N929" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B930" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C930" t="str">
+        <v>Eataly</v>
+      </c>
+      <c r="D930" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E930">
+        <v>1</v>
+      </c>
+      <c r="F930" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G930">
+        <v>9</v>
+      </c>
+      <c r="H930">
+        <v>2019</v>
+      </c>
+      <c r="I930" t="str">
+        <v/>
+      </c>
+      <c r="J930">
+        <v>59.909245</v>
+      </c>
+      <c r="K930">
+        <v>10.724076</v>
+      </c>
+      <c r="L930" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M930" t="str">
+        <v/>
+      </c>
+      <c r="N930" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B931" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C931" t="str">
+        <v>Jonathan Sushi Steen &amp; Strøm</v>
+      </c>
+      <c r="D931" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E931">
+        <v>1</v>
+      </c>
+      <c r="F931" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G931">
+        <v>9</v>
+      </c>
+      <c r="H931">
+        <v>2019</v>
+      </c>
+      <c r="I931" t="str">
+        <v/>
+      </c>
+      <c r="J931">
+        <v>59.911642</v>
+      </c>
+      <c r="K931">
+        <v>10.743052</v>
+      </c>
+      <c r="L931" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M931" t="str">
+        <v/>
+      </c>
+      <c r="N931" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B932" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C932" t="str">
+        <v>Illegal Burger</v>
+      </c>
+      <c r="D932" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E932">
+        <v>1</v>
+      </c>
+      <c r="F932" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G932">
+        <v>9</v>
+      </c>
+      <c r="H932">
+        <v>2019</v>
+      </c>
+      <c r="I932" t="str">
+        <v/>
+      </c>
+      <c r="J932">
+        <v>59.915718</v>
+      </c>
+      <c r="K932">
+        <v>10.748665</v>
+      </c>
+      <c r="L932" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M932" t="str">
+        <v/>
+      </c>
+      <c r="N932" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B933" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C933" t="str">
+        <v>Baker Hansen</v>
+      </c>
+      <c r="D933" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E933">
+        <v>1</v>
+      </c>
+      <c r="F933" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G933">
+        <v>9</v>
+      </c>
+      <c r="H933">
+        <v>2019</v>
+      </c>
+      <c r="I933" t="str">
+        <v/>
+      </c>
+      <c r="J933">
+        <v>59.910247</v>
+      </c>
+      <c r="K933">
+        <v>10.743518</v>
+      </c>
+      <c r="L933" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M933" t="str">
+        <v/>
+      </c>
+      <c r="N933" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B934" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C934" t="str">
+        <v>Skippergata 22</v>
+      </c>
+      <c r="D934" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E934">
+        <v>1</v>
+      </c>
+      <c r="F934" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G934">
+        <v>9</v>
+      </c>
+      <c r="H934">
+        <v>2019</v>
+      </c>
+      <c r="I934" t="str">
+        <v/>
+      </c>
+      <c r="J934">
+        <v>59.910471</v>
+      </c>
+      <c r="K934">
+        <v>10.747895</v>
+      </c>
+      <c r="L934" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M934" t="str">
+        <v/>
+      </c>
+      <c r="N934" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B935" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C935" t="str">
+        <v>Arakataka</v>
+      </c>
+      <c r="D935" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E935">
+        <v>1</v>
+      </c>
+      <c r="F935" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G935">
+        <v>9</v>
+      </c>
+      <c r="H935">
+        <v>2019</v>
+      </c>
+      <c r="I935" t="str">
+        <v/>
+      </c>
+      <c r="J935">
+        <v>59.916367</v>
+      </c>
+      <c r="K935">
+        <v>10.750623</v>
+      </c>
+      <c r="L935" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M935" t="str">
+        <v/>
+      </c>
+      <c r="N935" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B936" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C936" t="str">
+        <v>Uppercrust</v>
+      </c>
+      <c r="D936" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E936">
+        <v>1</v>
+      </c>
+      <c r="F936" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G936">
+        <v>9</v>
+      </c>
+      <c r="H936">
+        <v>2019</v>
+      </c>
+      <c r="I936" t="str">
+        <v/>
+      </c>
+      <c r="J936">
+        <v>59.914837</v>
+      </c>
+      <c r="K936">
+        <v>10.730365</v>
+      </c>
+      <c r="L936" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M936" t="str">
+        <v/>
+      </c>
+      <c r="N936" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B937" t="str">
+        <v>Oslo</v>
+      </c>
+      <c r="C937" t="str">
+        <v>Deli de Luca Karl Johan</v>
+      </c>
+      <c r="D937" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E937">
+        <v>1</v>
+      </c>
+      <c r="F937" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G937">
+        <v>9</v>
+      </c>
+      <c r="H937">
+        <v>2019</v>
+      </c>
+      <c r="I937" t="str">
+        <v/>
+      </c>
+      <c r="J937">
+        <v>59.911484</v>
+      </c>
+      <c r="K937">
+        <v>10.748623</v>
+      </c>
+      <c r="L937" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M937" t="str">
+        <v/>
+      </c>
+      <c r="N937" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B938" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C938" t="str">
+        <v>Stavanger Airport</v>
+      </c>
+      <c r="D938" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E938">
+        <v>1</v>
+      </c>
+      <c r="F938" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G938">
+        <v>9</v>
+      </c>
+      <c r="H938">
+        <v>2019</v>
+      </c>
+      <c r="I938" t="str">
+        <v/>
+      </c>
+      <c r="J938">
+        <v>58.880441</v>
+      </c>
+      <c r="K938">
+        <v>5.631402</v>
+      </c>
+      <c r="L938" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M938" t="str">
+        <v/>
+      </c>
+      <c r="N938" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B939" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C939" t="str">
+        <v>Stavanger: Fiskepirterminalen</v>
+      </c>
+      <c r="D939" t="str">
+        <v>transport</v>
+      </c>
+      <c r="E939">
+        <v>1</v>
+      </c>
+      <c r="F939" t="str">
+        <v>transit</v>
+      </c>
+      <c r="G939">
+        <v>9</v>
+      </c>
+      <c r="H939">
+        <v>2019</v>
+      </c>
+      <c r="I939" t="str">
+        <v/>
+      </c>
+      <c r="J939">
+        <v>58.972678</v>
+      </c>
+      <c r="K939">
+        <v>5.739849</v>
+      </c>
+      <c r="L939" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M939" t="str">
+        <v/>
+      </c>
+      <c r="N939" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B940" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C940" t="str">
+        <v>Radisson Blu Atlantic Hotel, Stavanger</v>
+      </c>
+      <c r="D940" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E940">
+        <v>1</v>
+      </c>
+      <c r="F940" t="str">
+        <v>lodging</v>
+      </c>
+      <c r="G940">
+        <v>9</v>
+      </c>
+      <c r="H940">
+        <v>2019</v>
+      </c>
+      <c r="I940" t="str">
+        <v/>
+      </c>
+      <c r="J940">
+        <v>58.968417</v>
+      </c>
+      <c r="K940">
+        <v>5.730619</v>
+      </c>
+      <c r="L940" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M940" t="str">
+        <v/>
+      </c>
+      <c r="N940" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B941" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C941" t="str">
+        <v>Stavanger tourist Information</v>
+      </c>
+      <c r="D941" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E941">
+        <v>1</v>
+      </c>
+      <c r="F941" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G941">
+        <v>9</v>
+      </c>
+      <c r="H941">
+        <v>2019</v>
+      </c>
+      <c r="I941" t="str">
+        <v/>
+      </c>
+      <c r="J941">
+        <v>58.972363</v>
+      </c>
+      <c r="K941">
+        <v>5.726823</v>
+      </c>
+      <c r="L941" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M941" t="str">
+        <v/>
+      </c>
+      <c r="N941" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B942" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C942" t="str">
+        <v>Gamle Stavanger</v>
+      </c>
+      <c r="D942" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E942">
+        <v>1</v>
+      </c>
+      <c r="F942" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G942">
+        <v>9</v>
+      </c>
+      <c r="H942">
+        <v>2019</v>
+      </c>
+      <c r="I942" t="str">
+        <v/>
+      </c>
+      <c r="J942">
+        <v>58.971798</v>
+      </c>
+      <c r="K942">
+        <v>5.726064</v>
+      </c>
+      <c r="L942" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M942" t="str">
+        <v/>
+      </c>
+      <c r="N942" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B943" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C943" t="str">
+        <v>Norwegian Petroleum Museum</v>
+      </c>
+      <c r="D943" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E943">
+        <v>1</v>
+      </c>
+      <c r="F943" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G943">
+        <v>9</v>
+      </c>
+      <c r="H943">
+        <v>2019</v>
+      </c>
+      <c r="I943" t="str">
+        <v/>
+      </c>
+      <c r="J943">
+        <v>58.973464</v>
+      </c>
+      <c r="K943">
+        <v>5.734691</v>
+      </c>
+      <c r="L943" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M943" t="str">
+        <v/>
+      </c>
+      <c r="N943" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B944" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C944" t="str">
+        <v>Stavanger Cathedral</v>
+      </c>
+      <c r="D944" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E944">
+        <v>1</v>
+      </c>
+      <c r="F944" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G944">
+        <v>9</v>
+      </c>
+      <c r="H944">
+        <v>2019</v>
+      </c>
+      <c r="I944" t="str">
+        <v/>
+      </c>
+      <c r="J944">
+        <v>58.9696</v>
+      </c>
+      <c r="K944">
+        <v>5.733372</v>
+      </c>
+      <c r="L944" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M944" t="str">
+        <v/>
+      </c>
+      <c r="N944" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B945" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C945" t="str">
+        <v>Kjeragbolten</v>
+      </c>
+      <c r="D945" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E945">
+        <v>1</v>
+      </c>
+      <c r="F945" t="str">
+        <v>hiking</v>
+      </c>
+      <c r="G945">
+        <v>9</v>
+      </c>
+      <c r="H945">
+        <v>2019</v>
+      </c>
+      <c r="I945" t="str">
+        <v/>
+      </c>
+      <c r="J945">
+        <v>59.033724</v>
+      </c>
+      <c r="K945">
+        <v>6.593302</v>
+      </c>
+      <c r="L945" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M945" t="str">
+        <v/>
+      </c>
+      <c r="N945" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B946" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C946" t="str">
+        <v>Tau</v>
+      </c>
+      <c r="D946" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E946">
+        <v>1</v>
+      </c>
+      <c r="F946" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G946">
+        <v>9</v>
+      </c>
+      <c r="H946">
+        <v>2019</v>
+      </c>
+      <c r="I946" t="str">
+        <v/>
+      </c>
+      <c r="J946">
+        <v>59.064776</v>
+      </c>
+      <c r="K946">
+        <v>5.922476</v>
+      </c>
+      <c r="L946" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M946" t="str">
+        <v/>
+      </c>
+      <c r="N946" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B947" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C947" t="str">
+        <v>Pulpit Rock</v>
+      </c>
+      <c r="D947" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E947">
+        <v>1</v>
+      </c>
+      <c r="F947" t="str">
+        <v>hiking</v>
+      </c>
+      <c r="G947">
+        <v>9</v>
+      </c>
+      <c r="H947">
+        <v>2019</v>
+      </c>
+      <c r="I947" t="str">
+        <v/>
+      </c>
+      <c r="J947">
+        <v>58.98641</v>
+      </c>
+      <c r="K947">
+        <v>6.19044</v>
+      </c>
+      <c r="L947" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M947" t="str">
+        <v/>
+      </c>
+      <c r="N947" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B948" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C948" t="str">
+        <v>Sverd i fjell</v>
+      </c>
+      <c r="D948" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E948">
+        <v>1</v>
+      </c>
+      <c r="F948" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G948">
+        <v>9</v>
+      </c>
+      <c r="H948">
+        <v>2019</v>
+      </c>
+      <c r="I948" t="str">
+        <v/>
+      </c>
+      <c r="J948">
+        <v>58.941389</v>
+      </c>
+      <c r="K948">
+        <v>5.671944</v>
+      </c>
+      <c r="L948" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M948" t="str">
+        <v/>
+      </c>
+      <c r="N948" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B949" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C949" t="str">
+        <v>University of Stavanger</v>
+      </c>
+      <c r="D949" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E949">
+        <v>1</v>
+      </c>
+      <c r="F949" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G949">
+        <v>9</v>
+      </c>
+      <c r="H949">
+        <v>2019</v>
+      </c>
+      <c r="I949" t="str">
+        <v/>
+      </c>
+      <c r="J949">
+        <v>58.937299</v>
+      </c>
+      <c r="K949">
+        <v>5.697201</v>
+      </c>
+      <c r="L949" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M949" t="str">
+        <v/>
+      </c>
+      <c r="N949" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B950" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C950" t="str">
+        <v>SR-Bank Arena</v>
+      </c>
+      <c r="D950" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E950">
+        <v>1</v>
+      </c>
+      <c r="F950" t="str">
+        <v>attraction</v>
+      </c>
+      <c r="G950">
+        <v>9</v>
+      </c>
+      <c r="H950">
+        <v>2019</v>
+      </c>
+      <c r="I950" t="str">
+        <v/>
+      </c>
+      <c r="J950">
+        <v>58.914631</v>
+      </c>
+      <c r="K950">
+        <v>5.731526</v>
+      </c>
+      <c r="L950" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M950" t="str">
+        <v/>
+      </c>
+      <c r="N950" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B951" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C951" t="str">
+        <v>Sabi Sushi Stavanger</v>
+      </c>
+      <c r="D951" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E951">
+        <v>1</v>
+      </c>
+      <c r="F951" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G951">
+        <v>9</v>
+      </c>
+      <c r="H951">
+        <v>2019</v>
+      </c>
+      <c r="I951" t="str">
+        <v/>
+      </c>
+      <c r="J951">
+        <v>58.970029</v>
+      </c>
+      <c r="K951">
+        <v>5.743427</v>
+      </c>
+      <c r="L951" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M951" t="str">
+        <v/>
+      </c>
+      <c r="N951" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B952" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C952" t="str">
+        <v>Firelake Grill House &amp; Cocktail Bar</v>
+      </c>
+      <c r="D952" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E952">
+        <v>1</v>
+      </c>
+      <c r="F952" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G952">
+        <v>9</v>
+      </c>
+      <c r="H952">
+        <v>2019</v>
+      </c>
+      <c r="I952" t="str">
+        <v/>
+      </c>
+      <c r="J952">
+        <v>58.968132</v>
+      </c>
+      <c r="K952">
+        <v>5.730365</v>
+      </c>
+      <c r="L952" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M952" t="str">
+        <v/>
+      </c>
+      <c r="N952" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B953" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C953" t="str">
+        <v>Døgnvill Burger Stavanger</v>
+      </c>
+      <c r="D953" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E953">
+        <v>1</v>
+      </c>
+      <c r="F953" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G953">
+        <v>9</v>
+      </c>
+      <c r="H953">
+        <v>2019</v>
+      </c>
+      <c r="I953" t="str">
+        <v/>
+      </c>
+      <c r="J953">
+        <v>58.970918</v>
+      </c>
+      <c r="K953">
+        <v>5.731974</v>
+      </c>
+      <c r="L953" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M953" t="str">
+        <v/>
+      </c>
+      <c r="N953" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B954" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C954" t="str">
+        <v>Fisketorget Stavanger</v>
+      </c>
+      <c r="D954" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E954">
+        <v>1</v>
+      </c>
+      <c r="F954" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G954">
+        <v>9</v>
+      </c>
+      <c r="H954">
+        <v>2019</v>
+      </c>
+      <c r="I954" t="str">
+        <v/>
+      </c>
+      <c r="J954">
+        <v>58.97039</v>
+      </c>
+      <c r="K954">
+        <v>5.730602</v>
+      </c>
+      <c r="L954" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M954" t="str">
+        <v/>
+      </c>
+      <c r="N954" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="str">
+        <v>Norway</v>
+      </c>
+      <c r="B955" t="str">
+        <v>Stavanger</v>
+      </c>
+      <c r="C955" t="str">
+        <v>Re-naa</v>
+      </c>
+      <c r="D955" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E955">
+        <v>1</v>
+      </c>
+      <c r="F955" t="str">
+        <v>dining</v>
+      </c>
+      <c r="G955">
+        <v>9</v>
+      </c>
+      <c r="H955">
+        <v>2019</v>
+      </c>
+      <c r="I955" t="str">
+        <v/>
+      </c>
+      <c r="J955">
+        <v>58.973985</v>
+      </c>
+      <c r="K955">
+        <v>5.730862</v>
+      </c>
+      <c r="L955" t="str">
+        <v>Norway (September 2019)</v>
+      </c>
+      <c r="M955" t="str">
+        <v/>
+      </c>
+      <c r="N955" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U892"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U955"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U955"/>
+  <dimension ref="A1:U1089"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10109,6 +10109,15 @@
       <c r="E244">
         <v>1</v>
       </c>
+      <c r="J244">
+        <v>46.682122</v>
+      </c>
+      <c r="K244">
+        <v>7.8514713</v>
+      </c>
+      <c r="N244" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -11880,6 +11889,9 @@
       <c r="N285" t="str">
         <v>yes</v>
       </c>
+      <c r="U285" t="str">
+        <v>Self-catering apartment, Middle Street, Latin Quarter</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -12272,8 +12284,11 @@
       <c r="P295" t="str">
         <v>https://www.findmeglutenfree.com/biz/cava-bodega/5384270569406464</v>
       </c>
-      <c r="Q295" t="str">
+      <c r="Q295">
         <v>4</v>
+      </c>
+      <c r="R295" t="str">
+        <v>[2026-03-29 research] ~50% tapas menu GF, allergens clearly marked.</v>
       </c>
     </row>
     <row r="296">
@@ -12319,8 +12334,11 @@
       <c r="P296" t="str">
         <v>https://www.findmeglutenfree.com/biz/martines-restaurant-and-winebar/4538739612975104</v>
       </c>
-      <c r="Q296" t="str">
+      <c r="Q296">
         <v>4</v>
+      </c>
+      <c r="R296" t="str">
+        <v>[2026-03-29 research] Marks GF dishes with C for celiac-safe. GF bread.</v>
       </c>
     </row>
     <row r="297">
@@ -12501,6 +12519,9 @@
       <c r="Q300" t="str">
         <v>4</v>
       </c>
+      <c r="R300" t="str">
+        <v>[2026-03-29] Verified CLOSED</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -12545,8 +12566,11 @@
       <c r="P301" t="str">
         <v>https://www.findmeglutenfree.com/biz/linnanes-lobster-bar/5328846050164736</v>
       </c>
-      <c r="Q301" t="str">
-        <v>4</v>
+      <c r="Q301">
+        <v>3</v>
+      </c>
+      <c r="R301" t="str">
+        <v>[2026-03-29 research] Fresh seafood specialist. Allergens marked. ~13km from Galway.</v>
       </c>
     </row>
     <row r="302">
@@ -12589,6 +12613,12 @@
       <c r="P302" t="str">
         <v>https://www.findmeglutenfree.com/biz/the-quays-bar-and-restaurant/6713036067176448</v>
       </c>
+      <c r="Q302">
+        <v>2</v>
+      </c>
+      <c r="R302" t="str">
+        <v>[2026-03-29 research] Allergens marked, GF cider, Shepherd's Pie. No separate fryers.</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -12613,7 +12643,7 @@
         <v>2023</v>
       </c>
       <c r="I303" t="str">
-        <v>mixed safety</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J303" t="str">
         <v>53.2716955</v>
@@ -12633,8 +12663,11 @@
       <c r="P303" t="str">
         <v>https://www.findmeglutenfree.com/biz/front-door/6277944908185600</v>
       </c>
-      <c r="Q303" t="str">
-        <v>3</v>
+      <c r="Q303">
+        <v>4</v>
+      </c>
+      <c r="R303" t="str">
+        <v>[2026-03-29 research] Dedicated deep fryer for GF items! GF fish &amp; chips, stew, nachos, wings, GF beer/cider.</v>
       </c>
     </row>
     <row r="304">
@@ -12674,6 +12707,12 @@
       <c r="M304" t="str">
         <v>Ireland</v>
       </c>
+      <c r="Q304">
+        <v>1</v>
+      </c>
+      <c r="R304" t="str">
+        <v>[2026-03-29 research] Pub. Dough Bros sometimes in beer garden for GF pizza.</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -12762,6 +12801,12 @@
       <c r="O306" t="str">
         <v>fun pub</v>
       </c>
+      <c r="Q306">
+        <v>1</v>
+      </c>
+      <c r="R306" t="str">
+        <v>[2026-03-29 research] Trad music pub. No specific GF menu. Drinks only.</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -12897,8 +12942,11 @@
       <c r="P309" t="str">
         <v>https://www.findmeglutenfree.com/biz/the-kings-head/6579320794644480</v>
       </c>
+      <c r="Q309">
+        <v>2</v>
+      </c>
       <c r="R309" t="str">
-        <v>Great live music! Very fun place</v>
+        <v>Great live music! Very fun place; [2026-03-29 research] GF bread for burgers, GF mashed potatoes. Allergen menu exists but not always current. No separate fryers.</v>
       </c>
     </row>
     <row r="310">
@@ -12927,7 +12975,7 @@
         <v>2023</v>
       </c>
       <c r="I310" t="str">
-        <v>unclear</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J310" t="str">
         <v>53.2719383</v>
@@ -12944,8 +12992,11 @@
       <c r="P310" t="str">
         <v>https://www.findmeglutenfree.com/biz/woozza-wood-fired-pizza/6034945867382784</v>
       </c>
+      <c r="Q310">
+        <v>4</v>
+      </c>
       <c r="R310" t="str">
-        <v xml:space="preserve">One of the best GF pizzas I've had! Had a huge serving of burrata in the middle too </v>
+        <v>One of the best GF pizzas I've had! Had a huge serving of burrata in the middle too ; [2026-03-29 research] GF pizza with Italian GF dough. Doesn't use separate oven but crust doesn't touch gluten. GF panna cotta, GF beer. €1.50 upcharge.</v>
       </c>
     </row>
     <row r="311">
@@ -12971,7 +13022,7 @@
         <v>2023</v>
       </c>
       <c r="I311" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J311" t="str">
         <v>53.2734629</v>
@@ -12987,6 +13038,12 @@
       </c>
       <c r="P311" t="str">
         <v>https://www.findmeglutenfree.com/biz/pascal-coffee-house/5201659937030144</v>
+      </c>
+      <c r="Q311">
+        <v>3</v>
+      </c>
+      <c r="R311" t="str">
+        <v>[2026-03-29 research] GF bread/buns, soups. Staff ask if coeliac.</v>
       </c>
     </row>
     <row r="312">
@@ -13012,7 +13069,7 @@
         <v>2023</v>
       </c>
       <c r="I312" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J312" t="str">
         <v>53.2725045</v>
@@ -13028,6 +13085,12 @@
       </c>
       <c r="P312" t="str">
         <v>https://www.findmeglutenfree.com/biz/pascal-coffee-house/5201659937030144</v>
+      </c>
+      <c r="Q312">
+        <v>3</v>
+      </c>
+      <c r="R312" t="str">
+        <v>[2026-03-29 research] Same chain. GF bread/buns, soups.</v>
       </c>
     </row>
     <row r="313">
@@ -13070,6 +13133,12 @@
       <c r="P313" t="str">
         <v>https://www.findmeglutenfree.com/biz/sangria/5627571045269504</v>
       </c>
+      <c r="Q313">
+        <v>3</v>
+      </c>
+      <c r="R313" t="str">
+        <v>[2026-03-29 research] GF modifications, corn tortillas. No dedicated fryer.</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -13114,6 +13183,12 @@
       <c r="N314" t="str">
         <v>yes</v>
       </c>
+      <c r="S314" t="str">
+        <v>https://www.hotels.com/ho425594/killarney-avenue-hotel-killarney-ireland/</v>
+      </c>
+      <c r="U314" t="str">
+        <v>Unclear GF category</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -13635,7 +13710,7 @@
         <v>2023</v>
       </c>
       <c r="I328" t="str">
-        <v>mixed safety</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J328" t="str">
         <v>52.0598627</v>
@@ -13655,8 +13730,11 @@
       <c r="P328" t="str">
         <v>https://www.findmeglutenfree.com/biz/casita-mexicana/5390981331025920</v>
       </c>
-      <c r="Q328" t="str">
-        <v>3</v>
+      <c r="Q328">
+        <v>4</v>
+      </c>
+      <c r="R328" t="str">
+        <v>[2026-03-29 research] Extensive GF options. Very celiac-friendly. Staff aware of cross-contam.</v>
       </c>
     </row>
     <row r="329">
@@ -13702,8 +13780,11 @@
       <c r="O329" t="str">
         <v>We did not eat here, but here's a review from FMGF: "Allegro (Plunkett St) did not disappoint. They have a separate gluten free menu including many types of burgers, fish is available depending on the day and of course, chips. YUM."</v>
       </c>
-      <c r="Q329" t="str">
-        <v>4</v>
+      <c r="Q329">
+        <v>5</v>
+      </c>
+      <c r="R329" t="str">
+        <v>[2026-03-29 research] DEDICATED GF kitchen. GF chips, burgers, battered fish, pizza.</v>
       </c>
     </row>
     <row r="330">
@@ -13749,8 +13830,11 @@
       <c r="O330" t="str">
         <v>We did not eat here but FMGF says most of the menu is already gluten free or can adapted to make it gluten free.</v>
       </c>
-      <c r="Q330" t="str">
+      <c r="Q330">
         <v>4</v>
+      </c>
+      <c r="R330" t="str">
+        <v>[2026-03-29 research] Chef can prepare entire GF menu if requested in advance.</v>
       </c>
     </row>
     <row r="331">
@@ -13893,8 +13977,11 @@
       <c r="P333" t="str">
         <v>https://www.findmeglutenfree.com/biz/great-southern-killarney/4957218353053696</v>
       </c>
-      <c r="Q333" t="str">
+      <c r="Q333">
         <v>4</v>
+      </c>
+      <c r="R333" t="str">
+        <v>[2026-03-29 research] GF sandwiches, bread. Accommodating.</v>
       </c>
     </row>
     <row r="334">
@@ -13943,8 +14030,11 @@
       <c r="P334" t="str">
         <v>https://www.findmeglutenfree.com/biz/milano-ie/6433693582491648</v>
       </c>
-      <c r="Q334" t="str">
+      <c r="Q334">
         <v>3</v>
+      </c>
+      <c r="R334" t="str">
+        <v>[2026-03-29 research] GF pizza, pasta, beer. Mixed cross-contam reviews.</v>
       </c>
     </row>
     <row r="335">
@@ -13993,8 +14083,11 @@
       <c r="P335" t="str">
         <v>https://www.findmeglutenfree.com/biz/bricin-restaurant-and-boxty-house/5988049035067392</v>
       </c>
-      <c r="Q335" t="str">
+      <c r="Q335">
         <v>4</v>
+      </c>
+      <c r="R335" t="str">
+        <v>[2026-03-29 research] GF menu, separate GF bread. Not dedicated facility.</v>
       </c>
     </row>
     <row r="336">
@@ -14043,11 +14136,11 @@
       <c r="P336" t="str">
         <v>https://www.findmeglutenfree.com/biz/cellar-one/6269495784505344</v>
       </c>
-      <c r="Q336" t="str">
+      <c r="Q336">
         <v>3</v>
       </c>
       <c r="R336" t="str">
-        <v>We ate at this restaurant twice on our trip and had a wonderful GF DF experience. Bart (who I believe is the manager) took special care of us both nights. We started with delicious GF DF bread, then had John Dory fish in a wonderful presentation with sides of potatoes, veggies and chips (made in a dedicated fryer). The atmosphere was also very nice here and there was a piano player. We truly enjoyed both meals here and would highly recommend this place. They were very helpful and the food was delicious.Bart and Connor were the best</v>
+        <v>We ate at this restaurant twice on our trip and had a wonderful GF DF experience. Bart (who I believe is the manager) took special care of us both nights. We started with delicious GF DF bread, then had John Dory fish in a wonderful presentation with sides of potatoes, veggies and chips (made in a dedicated fryer). The atmosphere was also very nice here and there was a piano player. We truly enjoyed both meals here and would highly recommend this place. They were very helpful and the food was delicious.Bart and Connor were the best; [2026-03-29 research] GF DF bread, John Dory fish, dedicated fryer for chips. Weekend only.</v>
       </c>
     </row>
     <row r="337">
@@ -14093,11 +14186,11 @@
       <c r="O337" t="str">
         <v>Almost all flavors (including brownie!) are gluten free. Staff is very knowledgable so just ask.</v>
       </c>
-      <c r="Q337" t="str">
+      <c r="Q337">
         <v>4</v>
       </c>
       <c r="R337" t="str">
-        <v>Almost all flavors (including brownie!) are gluten free. Staff is very knowledgable so just ask.</v>
+        <v>Almost all flavors (including brownie!) are gluten free. Staff is very knowledgable so just ask.; [2026-03-29 research] Almost all flavors GF including brownie. Staff very knowledgeable.</v>
       </c>
     </row>
     <row r="338">
@@ -14123,7 +14216,7 @@
         <v>2023</v>
       </c>
       <c r="I338" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J338" t="str">
         <v>52.0598714</v>
@@ -14139,6 +14232,12 @@
       </c>
       <c r="P338" t="str">
         <v>https://www.findmeglutenfree.com/biz/khao-asian-street-food/5143880251604992</v>
+      </c>
+      <c r="Q338">
+        <v>3</v>
+      </c>
+      <c r="R338" t="str">
+        <v>[2026-03-29 research] GF Pad Thai. Several dishes adaptable.</v>
       </c>
     </row>
     <row r="339">
@@ -14187,8 +14286,11 @@
       <c r="P339" t="str">
         <v>https://www.findmeglutenfree.com/biz/robs-ranch-house/4753133731840000</v>
       </c>
-      <c r="Q339" t="str">
-        <v>3</v>
+      <c r="Q339">
+        <v>4</v>
+      </c>
+      <c r="R339" t="str">
+        <v>[2026-03-29 research] GF menu, dedicated fryers, GF beer.</v>
       </c>
     </row>
     <row r="340">
@@ -14261,7 +14363,7 @@
         <v>2023</v>
       </c>
       <c r="I341" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J341" t="str">
         <v>52.0576419</v>
@@ -14277,6 +14379,12 @@
       </c>
       <c r="P341" t="str">
         <v>https://www.findmeglutenfree.com/biz/cafe-du-parc/5303789879427072</v>
+      </c>
+      <c r="Q341">
+        <v>3</v>
+      </c>
+      <c r="R341" t="str">
+        <v>[2026-03-29 research] Caters for GF dietary requirements.</v>
       </c>
     </row>
     <row r="342">
@@ -14322,8 +14430,11 @@
       <c r="P342" t="str">
         <v>https://www.findmeglutenfree.com/biz/luna-coffee-and-wine/6238737896177664</v>
       </c>
+      <c r="Q342">
+        <v>2</v>
+      </c>
       <c r="R342" t="str">
-        <v>Only had coffee (almond milk latte)</v>
+        <v>Only had coffee (almond milk latte); [2026-03-29 research] Acai bowls available. Not dedicated GF.</v>
       </c>
     </row>
     <row r="343">
@@ -14349,7 +14460,7 @@
         <v>2023</v>
       </c>
       <c r="I343" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J343" t="str">
         <v>52.0598849</v>
@@ -14362,6 +14473,12 @@
       </c>
       <c r="M343" t="str">
         <v>Killarney</v>
+      </c>
+      <c r="Q343">
+        <v>3</v>
+      </c>
+      <c r="R343" t="str">
+        <v>[2026-03-29 research] GF penne pasta, steak, hake fillet. No GF pizza/bread.</v>
       </c>
     </row>
     <row r="344">
@@ -15977,6 +16094,9 @@
       <c r="D379" t="str">
         <v>cafe</v>
       </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
       <c r="F379" t="str">
         <v>☕</v>
       </c>
@@ -20084,6 +20204,9 @@
       <c r="Q469" t="str">
         <v>3</v>
       </c>
+      <c r="R469" t="str">
+        <v>AMAZING! Cutey highland cow, amazing GF options. Such a great environment and close to where we stayed. LOVE. Went twice</v>
+      </c>
       <c r="T469" t="str">
         <v>South Island</v>
       </c>
@@ -20699,6 +20822,9 @@
       <c r="D484" t="str">
         <v>bar</v>
       </c>
+      <c r="E484">
+        <v>1</v>
+      </c>
       <c r="F484" t="str">
         <v>🍸</v>
       </c>
@@ -21042,6 +21168,9 @@
       <c r="D492" t="str">
         <v>restaurant</v>
       </c>
+      <c r="E492">
+        <v>0</v>
+      </c>
       <c r="F492" t="str">
         <v>🍽️</v>
       </c>
@@ -21163,6 +21292,9 @@
       <c r="Q494" t="str">
         <v>5</v>
       </c>
+      <c r="R494" t="str">
+        <v>wish we had a chance to go here - next time!</v>
+      </c>
       <c r="T494" t="str">
         <v>North Island</v>
       </c>
@@ -35287,6 +35419,12 @@
       <c r="I812" t="str">
         <v>marked on menu</v>
       </c>
+      <c r="J812">
+        <v>34.6685366</v>
+      </c>
+      <c r="K812">
+        <v>135.5036138</v>
+      </c>
       <c r="L812" t="str">
         <v>Japan (Mar 2025)</v>
       </c>
@@ -35322,6 +35460,15 @@
       <c r="H813">
         <v>2025</v>
       </c>
+      <c r="J813">
+        <v>34.6685366</v>
+      </c>
+      <c r="K813">
+        <v>135.5036138</v>
+      </c>
+      <c r="N813" t="str">
+        <v>add to map</v>
+      </c>
       <c r="R813" t="str">
         <v>felt like Japanese Vegas strip</v>
       </c>
@@ -35395,6 +35542,9 @@
       <c r="K815">
         <v>2.2988</v>
       </c>
+      <c r="N815" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O815" t="str">
         <v>100% GF Italian. Wood-fired GF pizza, pasta, gnocchi, tiramisu. Complimentary GF baguette bread service.</v>
       </c>
@@ -35436,6 +35586,9 @@
       <c r="K816">
         <v>2.2936</v>
       </c>
+      <c r="N816" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O816" t="str">
         <v>100% GF organic Italian. AFDIAG-certified. Pizza, pasta, gnocchi. Small restaurant, book ahead. 10 min from Eiffel Tower.</v>
       </c>
@@ -35477,6 +35630,9 @@
       <c r="K817">
         <v>2.3748</v>
       </c>
+      <c r="N817" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O817" t="str">
         <v>100% GF bakery. Mills own rice &amp; buckwheat flours. Almond croissants, focaccia, Paris-Brest. Multiple locations.</v>
       </c>
@@ -35518,6 +35674,9 @@
       <c r="K818">
         <v>2.3478</v>
       </c>
+      <c r="N818" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O818" t="str">
         <v>100% GF bakery founded by someone with celiac. 13+ locations. Croissants, pain au chocolat, baguette sandwiches.</v>
       </c>
@@ -35559,6 +35718,9 @@
       <c r="K819">
         <v>2.3213</v>
       </c>
+      <c r="N819" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O819" t="str">
         <v>100% GF cafe/bakery/grocery. 3 Paris locations. Croissants, macarons, baguettes, eclairs. Also sells GF grocery items.</v>
       </c>
@@ -35600,6 +35762,9 @@
       <c r="K820">
         <v>2.3289</v>
       </c>
+      <c r="N820" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O820" t="str">
         <v>100% GF Thai. Pad Thai, Tom Yam, curries, pho. Multiple locations incl Kapunka Vegan.</v>
       </c>
@@ -35641,6 +35806,9 @@
       <c r="K821">
         <v>2.3526</v>
       </c>
+      <c r="N821" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O821" t="str">
         <v>100% GF + 100% vegan. Dragon's Back curry, rice bowls. In Le Marais.</v>
       </c>
@@ -35682,6 +35850,9 @@
       <c r="K822">
         <v>2.3622</v>
       </c>
+      <c r="N822" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O822" t="str">
         <v>100% GF, vegan, no added sugar. Patisserie/tea house in Le Marais. Beautiful pastries and tarts.</v>
       </c>
@@ -35723,6 +35894,9 @@
       <c r="K823">
         <v>2.2987</v>
       </c>
+      <c r="N823" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O823" t="str">
         <v>Paris's first 100% GF patisserie (est. 2011). Now Saturday-only pop-up. Pre-order recommended.</v>
       </c>
@@ -35764,6 +35938,9 @@
       <c r="K824">
         <v>2.3076</v>
       </c>
+      <c r="N824" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O824" t="str">
         <v>Iconic macarons are naturally GF, baked in separate kitchen. Only macarons are celiac-safe; other pastries are not.</v>
       </c>
@@ -35805,6 +35982,9 @@
       <c r="K825">
         <v>2.287</v>
       </c>
+      <c r="N825" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O825" t="str">
         <v>3-star boutique in Le Marais. 18th-century Parisian décor.</v>
       </c>
@@ -35843,6 +36023,9 @@
       <c r="K826">
         <v>2.3025</v>
       </c>
+      <c r="N826" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O826" t="str">
         <v>5-star luxury near Eiffel Tower. Indoor pool, spa. Art Nouveau interiors.</v>
       </c>
@@ -35878,6 +36061,9 @@
       <c r="K827">
         <v>2.2945</v>
       </c>
+      <c r="N827" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O827" t="str">
         <v>330m iron lattice tower built for 1889 World's Fair. Sparkles every hour after dark.</v>
       </c>
@@ -35913,6 +36099,9 @@
       <c r="K828">
         <v>2.3499</v>
       </c>
+      <c r="N828" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O828" t="str">
         <v>French Gothic masterpiece, 12th century. Reopened Dec 2024 after 2019 fire restoration.</v>
       </c>
@@ -35948,6 +36137,9 @@
       <c r="K829">
         <v>2.295</v>
       </c>
+      <c r="N829" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O829" t="str">
         <v>Triumphal arch at western end of Champs-Élysées. Rooftop terrace with views. Tomb of Unknown Soldier beneath.</v>
       </c>
@@ -35980,6 +36172,9 @@
       <c r="K830">
         <v>2.3431</v>
       </c>
+      <c r="N830" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O830" t="str">
         <v>White-domed basilica at summit of Montmartre. Free entry. Best free panoramic views of Paris.</v>
       </c>
@@ -36012,6 +36207,9 @@
       <c r="K831">
         <v>2.3372</v>
       </c>
+      <c r="N831" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O831" t="str">
         <v>23-hectare formal garden with fountains, model boat pond, free Parisian chairs. Borders Saint-Germain and Latin Quarter.</v>
       </c>
@@ -36044,6 +36242,9 @@
       <c r="K832">
         <v>2.3274</v>
       </c>
+      <c r="N832" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O832" t="str">
         <v>Oldest public park in Paris (1564). Between Louvre and Place de la Concorde. UNESCO World Heritage.</v>
       </c>
@@ -36076,6 +36277,9 @@
       <c r="K833">
         <v>2.3134</v>
       </c>
+      <c r="N833" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O833" t="str">
         <v>Most ornate bridge in Paris. Art Nouveau lamp posts, gilded statues. Built for 1900 World's Fair. Great Eiffel Tower views.</v>
       </c>
@@ -36108,6 +36312,9 @@
       <c r="K834">
         <v>2.3654</v>
       </c>
+      <c r="N834" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O834" t="str">
         <v>Oldest planned square in Paris (1612). Victor Hugo's former home. Peaceful retreat in Le Marais.</v>
       </c>
@@ -36140,6 +36347,9 @@
       <c r="K835">
         <v>2.3376</v>
       </c>
+      <c r="N835" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O835" t="str">
         <v>World's largest museum. Mona Lisa, Venus de Milo. 32 EUR.</v>
       </c>
@@ -36172,6 +36382,9 @@
       <c r="K836">
         <v>2.3266</v>
       </c>
+      <c r="N836" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O836" t="str">
         <v>Impressionist art in former railway station. Monet, Renoir, Van Gogh. 16 EUR.</v>
       </c>
@@ -36204,6 +36417,9 @@
       <c r="K837">
         <v>2.1232</v>
       </c>
+      <c r="N837" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O837" t="str">
         <v>Opulent former royal residence. Hall of Mirrors. 800 hectares of gardens. RER C ~40 min.</v>
       </c>
@@ -36239,6 +36455,9 @@
       <c r="K838">
         <v>2.2895</v>
       </c>
+      <c r="N838" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O838" t="str">
         <v>1-hour sightseeing cruise passing major landmarks. From ~17 EUR. Sunset and dinner options.</v>
       </c>
@@ -36271,6 +36490,9 @@
       <c r="K839">
         <v>2.3449</v>
       </c>
+      <c r="N839" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O839" t="str">
         <v>13th-century Gothic chapel. 1,113 stained-glass windows. 13-19 EUR.</v>
       </c>
@@ -36303,6 +36525,9 @@
       <c r="K840">
         <v>2.3411</v>
       </c>
+      <c r="N840" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O840" t="str">
         <v>Cobblestone streets, artist studios, I Love You Wall, Moulin Rouge, Sacré-Cœur. From ~30 EUR.</v>
       </c>
@@ -36335,6 +36560,9 @@
       <c r="K841">
         <v>12.5066375</v>
       </c>
+      <c r="N841" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
@@ -36361,6 +36589,9 @@
       <c r="K842">
         <v>12.2518928</v>
       </c>
+      <c r="N842" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
@@ -36387,6 +36618,9 @@
       <c r="K843">
         <v>12.5308661</v>
       </c>
+      <c r="N843" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
@@ -36416,6 +36650,9 @@
       <c r="K844">
         <v>12.4922309</v>
       </c>
+      <c r="N844" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
@@ -36445,6 +36682,9 @@
       <c r="K845">
         <v>12.485325</v>
       </c>
+      <c r="N845" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
@@ -36474,6 +36714,9 @@
       <c r="K846">
         <v>12.4768729</v>
       </c>
+      <c r="N846" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
@@ -36503,6 +36746,9 @@
       <c r="K847">
         <v>12.483313</v>
       </c>
+      <c r="N847" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
@@ -36532,6 +36778,9 @@
       <c r="K848">
         <v>12.482775</v>
       </c>
+      <c r="N848" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
@@ -36561,6 +36810,9 @@
       <c r="K849">
         <v>12.4745405</v>
       </c>
+      <c r="N849" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
@@ -36590,6 +36842,9 @@
       <c r="K850">
         <v>12.4730742</v>
       </c>
+      <c r="N850" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
@@ -36619,6 +36874,9 @@
       <c r="K851">
         <v>12.505673</v>
       </c>
+      <c r="N851" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
@@ -36648,6 +36906,9 @@
       <c r="K852">
         <v>12.4806028</v>
       </c>
+      <c r="N852" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
@@ -36677,6 +36938,9 @@
       <c r="K853">
         <v>12.4536007</v>
       </c>
+      <c r="N853" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
@@ -36706,6 +36970,9 @@
       <c r="K854">
         <v>12.4539367</v>
       </c>
+      <c r="N854" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
@@ -36735,6 +37002,9 @@
       <c r="K855">
         <v>12.4544835</v>
       </c>
+      <c r="N855" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
@@ -36764,6 +37034,9 @@
       <c r="K856">
         <v>12.466276</v>
       </c>
+      <c r="N856" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O856" t="str">
         <v>10.50 euros to get in - reviews say not really worth it but cool panoramic views. Did not go here.</v>
       </c>
@@ -36796,6 +37069,9 @@
       <c r="K857">
         <v>12.454725</v>
       </c>
+      <c r="N857" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
@@ -36828,6 +37104,9 @@
       <c r="K858">
         <v>12.4705764</v>
       </c>
+      <c r="N858" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O858" t="str">
         <v>GF bruschetta, lobster noodles, eggplant parm. Was AMAZING and waiter was super nice. Also have other locations including GF street food near Vatican.</v>
       </c>
@@ -36866,6 +37145,9 @@
       <c r="K859">
         <v>12.4764863</v>
       </c>
+      <c r="N859" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O859" t="str">
         <v>GF bakery - May be hard to find, across via di torre argentina from the Shari Van playhouse</v>
       </c>
@@ -36901,6 +37183,9 @@
       <c r="K860">
         <v>12.4777718</v>
       </c>
+      <c r="N860" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O860" t="str">
         <v>GF pizza, pasta (including gnocchi), and desserts</v>
       </c>
@@ -36936,6 +37221,9 @@
       <c r="K861">
         <v>12.4729887</v>
       </c>
+      <c r="N861" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O861" t="str">
         <v>GF menu items/apps plus HH from 4-6pm</v>
       </c>
@@ -36974,6 +37262,9 @@
       <c r="K862">
         <v>12.473238</v>
       </c>
+      <c r="N862" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O862" t="str">
         <v>GF gelato and cones (chain)</v>
       </c>
@@ -37012,6 +37303,9 @@
       <c r="K863">
         <v>12.4590061</v>
       </c>
+      <c r="N863" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O863" t="str">
         <v>GF pizza</v>
       </c>
@@ -37047,6 +37341,9 @@
       <c r="K864">
         <v>12.4948523</v>
       </c>
+      <c r="N864" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O864" t="str">
         <v>Okay reviews - not sure if visited</v>
       </c>
@@ -37085,6 +37382,9 @@
       <c r="K865">
         <v>12.479819</v>
       </c>
+      <c r="N865" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O865" t="str">
         <v>Mary's recommendation - cool alley with juices, cantina, and restaurant with GF and vegan food</v>
       </c>
@@ -37120,6 +37420,9 @@
       <c r="K866">
         <v>-0.0803845</v>
       </c>
+      <c r="N866" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
@@ -37149,6 +37452,9 @@
       <c r="K867">
         <v>-0.1733879</v>
       </c>
+      <c r="N867" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
@@ -37181,6 +37487,9 @@
       <c r="K868">
         <v>-0.0835832</v>
       </c>
+      <c r="N868" t="str">
+        <v>add to map</v>
+      </c>
       <c r="P868" t="str">
         <v>https://www.findmeglutenfree.com/biz/los-mochis/5682303363317760</v>
       </c>
@@ -37219,6 +37528,9 @@
       <c r="K869">
         <v>-0.1971206</v>
       </c>
+      <c r="N869" t="str">
+        <v>add to map</v>
+      </c>
       <c r="P869" t="str">
         <v>https://www.findmeglutenfree.com/biz/los-mochis-restaurant/6076333531201536</v>
       </c>
@@ -37257,6 +37569,9 @@
       <c r="K870">
         <v>-0.1187016</v>
       </c>
+      <c r="N870" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O870" t="str">
         <v>Accredited by CoeliacUK.&lt;br&gt;Has a separate gf menus and proper process in place for ensure there is no cross contamination.</v>
       </c>
@@ -37301,6 +37616,9 @@
       <c r="K871">
         <v>-0.0766339</v>
       </c>
+      <c r="N871" t="str">
+        <v>add to map</v>
+      </c>
       <c r="P871" t="str">
         <v>https://www.findmeglutenfree.com/biz/wicked-fish/5779279859810304</v>
       </c>
@@ -37336,6 +37654,9 @@
       <c r="K872">
         <v>-0.1878318</v>
       </c>
+      <c r="N872" t="str">
+        <v>add to map</v>
+      </c>
       <c r="P872" t="str">
         <v>https://www.findmeglutenfree.com/biz/oatis/6698670654881792</v>
       </c>
@@ -37371,6 +37692,9 @@
       <c r="K873">
         <v>-0.0819975</v>
       </c>
+      <c r="N873" t="str">
+        <v>add to map</v>
+      </c>
       <c r="P873" t="str">
         <v>https://www.findmeglutenfree.com/biz/joe-and-the-juice/6031873342046208</v>
       </c>
@@ -37409,6 +37733,9 @@
       <c r="K874">
         <v>-0.0800697</v>
       </c>
+      <c r="N874" t="str">
+        <v>add to map</v>
+      </c>
       <c r="P874" t="str">
         <v>https://www.findmeglutenfree.com/biz/black-sheep-coffee/5037307943583744</v>
       </c>
@@ -37441,6 +37768,9 @@
       <c r="K875">
         <v>-0.1246254</v>
       </c>
+      <c r="N875" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
@@ -37470,6 +37800,9 @@
       <c r="K876">
         <v>-0.0753565</v>
       </c>
+      <c r="N876" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
@@ -37499,6 +37832,9 @@
       <c r="K877">
         <v>-0.0877321</v>
       </c>
+      <c r="N877" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
@@ -37528,6 +37864,9 @@
       <c r="K878">
         <v>-0.0762586</v>
       </c>
+      <c r="N878" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
@@ -37557,6 +37896,9 @@
       <c r="K879">
         <v>-0.133996</v>
       </c>
+      <c r="N879" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
@@ -37586,6 +37928,9 @@
       <c r="K880">
         <v>-0.187681</v>
       </c>
+      <c r="N880" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
@@ -37615,6 +37960,9 @@
       <c r="K881">
         <v>-0.14189</v>
       </c>
+      <c r="N881" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
@@ -37644,6 +37992,9 @@
       <c r="K882">
         <v>-0.135798</v>
       </c>
+      <c r="N882" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
@@ -37673,6 +38024,9 @@
       <c r="K883">
         <v>-0.1641135</v>
       </c>
+      <c r="N883" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
@@ -37702,6 +38056,9 @@
       <c r="K884">
         <v>-0.0865</v>
       </c>
+      <c r="N884" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
@@ -37731,6 +38088,9 @@
       <c r="K885">
         <v>-0.1195192</v>
       </c>
+      <c r="N885" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
@@ -37760,6 +38120,9 @@
       <c r="K886">
         <v>-0.0164597</v>
       </c>
+      <c r="N886" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
@@ -37789,6 +38152,9 @@
       <c r="K887">
         <v>-0.1909471</v>
       </c>
+      <c r="N887" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
@@ -37818,6 +38184,9 @@
       <c r="K888">
         <v>-0.0760688</v>
       </c>
+      <c r="N888" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
@@ -37847,6 +38216,9 @@
       <c r="K889">
         <v>-0.0904808</v>
       </c>
+      <c r="N889" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
@@ -37876,6 +38248,9 @@
       <c r="K890">
         <v>-0.2055232</v>
       </c>
+      <c r="N890" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
@@ -37905,6 +38280,9 @@
       <c r="K891">
         <v>-0.4550471</v>
       </c>
+      <c r="N891" t="str">
+        <v>add to map</v>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
@@ -37937,6 +38315,9 @@
       <c r="K892">
         <v>12.4601</v>
       </c>
+      <c r="N892" t="str">
+        <v>add to map</v>
+      </c>
       <c r="O892" t="str">
         <v>GF street food near Vatican at Borgo Pio 28. Part of Mama Eat chain. AIC certified, dual kitchens.</v>
       </c>
@@ -40716,9 +41097,3775 @@
         <v/>
       </c>
     </row>
+    <row r="956">
+      <c r="A956" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B956" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C956" t="str">
+        <v>Scandic Upplandsgatan</v>
+      </c>
+      <c r="D956" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E956">
+        <v>1</v>
+      </c>
+      <c r="G956" t="str">
+        <v>September</v>
+      </c>
+      <c r="H956">
+        <v>2019</v>
+      </c>
+      <c r="J956">
+        <v>59.3364</v>
+      </c>
+      <c r="K956">
+        <v>18.055024</v>
+      </c>
+      <c r="N956" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O956" t="str">
+        <v>Hotel in central Stockholm</v>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B957" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C957" t="str">
+        <v>La Neta Bar</v>
+      </c>
+      <c r="D957" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E957">
+        <v>1</v>
+      </c>
+      <c r="G957" t="str">
+        <v>September</v>
+      </c>
+      <c r="H957">
+        <v>2019</v>
+      </c>
+      <c r="I957" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J957">
+        <v>59.333604</v>
+      </c>
+      <c r="K957">
+        <v>18.070746</v>
+      </c>
+      <c r="N957" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O957" t="str">
+        <v>GF authentic Mexican corn tortillas for tacos &amp; GF beer</v>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B958" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C958" t="str">
+        <v>Älskade Traditioner</v>
+      </c>
+      <c r="D958" t="str">
+        <v>cafe</v>
+      </c>
+      <c r="E958">
+        <v>1</v>
+      </c>
+      <c r="G958" t="str">
+        <v>September</v>
+      </c>
+      <c r="H958">
+        <v>2019</v>
+      </c>
+      <c r="I958" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J958">
+        <v>59.311041</v>
+      </c>
+      <c r="K958">
+        <v>18.081437</v>
+      </c>
+      <c r="N958" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O958" t="str">
+        <v>AMAZING gluten free waffles</v>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B959" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C959" t="str">
+        <v>Happy Atelier</v>
+      </c>
+      <c r="D959" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E959">
+        <v>1</v>
+      </c>
+      <c r="G959" t="str">
+        <v>September</v>
+      </c>
+      <c r="H959">
+        <v>2019</v>
+      </c>
+      <c r="I959" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J959">
+        <v>59.329489</v>
+      </c>
+      <c r="K959">
+        <v>18.03895</v>
+      </c>
+      <c r="N959" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O959" t="str">
+        <v>Dedicated GF bakery - so awesome and the lady working there was so kind</v>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B960" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C960" t="str">
+        <v>Hattori Sushi Devil</v>
+      </c>
+      <c r="D960" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E960">
+        <v>1</v>
+      </c>
+      <c r="G960" t="str">
+        <v>September</v>
+      </c>
+      <c r="H960">
+        <v>2019</v>
+      </c>
+      <c r="I960" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J960">
+        <v>59.338571</v>
+      </c>
+      <c r="K960">
+        <v>18.05658</v>
+      </c>
+      <c r="N960" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O960" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B961" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C961" t="str">
+        <v>Hemma Vasastan</v>
+      </c>
+      <c r="D961" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E961">
+        <v>1</v>
+      </c>
+      <c r="G961" t="str">
+        <v>September</v>
+      </c>
+      <c r="H961">
+        <v>2019</v>
+      </c>
+      <c r="I961" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J961">
+        <v>59.339585</v>
+      </c>
+      <c r="K961">
+        <v>18.047905</v>
+      </c>
+      <c r="N961" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O961" t="str">
+        <v>Asparagus risotto, GF bread, goat cheese salad</v>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B962" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C962" t="str">
+        <v>Joe &amp; The Juice</v>
+      </c>
+      <c r="D962" t="str">
+        <v>cafe</v>
+      </c>
+      <c r="E962">
+        <v>1</v>
+      </c>
+      <c r="G962" t="str">
+        <v>September</v>
+      </c>
+      <c r="H962">
+        <v>2019</v>
+      </c>
+      <c r="I962" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J962">
+        <v>59.307477</v>
+      </c>
+      <c r="K962">
+        <v>18.076076</v>
+      </c>
+      <c r="N962" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O962" t="str">
+        <v>GF paninis</v>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B963" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C963" t="str">
+        <v>The Royal Palace</v>
+      </c>
+      <c r="D963" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E963">
+        <v>1</v>
+      </c>
+      <c r="G963" t="str">
+        <v>September</v>
+      </c>
+      <c r="H963">
+        <v>2019</v>
+      </c>
+      <c r="J963">
+        <v>59.326822</v>
+      </c>
+      <c r="K963">
+        <v>18.071719</v>
+      </c>
+      <c r="N963" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O963" t="str">
+        <v>Cost: 160 SEK (~$16). Open 10am-5pm. Changing of the guards at 12:15pm weekdays</v>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B964" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C964" t="str">
+        <v>Nobel Prize Museum</v>
+      </c>
+      <c r="D964" t="str">
+        <v>museum</v>
+      </c>
+      <c r="E964">
+        <v>1</v>
+      </c>
+      <c r="G964" t="str">
+        <v>September</v>
+      </c>
+      <c r="H964">
+        <v>2019</v>
+      </c>
+      <c r="J964">
+        <v>59.325331</v>
+      </c>
+      <c r="K964">
+        <v>18.070824</v>
+      </c>
+      <c r="N964" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O964" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B965" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C965" t="str">
+        <v>Gamla Stan</v>
+      </c>
+      <c r="D965" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E965">
+        <v>1</v>
+      </c>
+      <c r="G965" t="str">
+        <v>September</v>
+      </c>
+      <c r="H965">
+        <v>2019</v>
+      </c>
+      <c r="J965">
+        <v>59.325698</v>
+      </c>
+      <c r="K965">
+        <v>18.071879</v>
+      </c>
+      <c r="N965" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O965" t="str">
+        <v>Old Stockholm - historic old town</v>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B966" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C966" t="str">
+        <v>Stockholm City Hall</v>
+      </c>
+      <c r="D966" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E966">
+        <v>1</v>
+      </c>
+      <c r="G966" t="str">
+        <v>September</v>
+      </c>
+      <c r="H966">
+        <v>2019</v>
+      </c>
+      <c r="J966">
+        <v>59.327451</v>
+      </c>
+      <c r="K966">
+        <v>18.054346</v>
+      </c>
+      <c r="N966" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O966" t="str">
+        <v>Tours ~50 min, 10am-3pm. More frequent June-August. Cannot book in advance unless group travel</v>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B967" t="str">
+        <v>Stockholm</v>
+      </c>
+      <c r="C967" t="str">
+        <v>Stockholm Arlanda Airport</v>
+      </c>
+      <c r="D967" t="str">
+        <v>airport</v>
+      </c>
+      <c r="E967">
+        <v>1</v>
+      </c>
+      <c r="G967" t="str">
+        <v>September</v>
+      </c>
+      <c r="H967">
+        <v>2019</v>
+      </c>
+      <c r="J967">
+        <v>59.649762</v>
+      </c>
+      <c r="K967">
+        <v>17.923781</v>
+      </c>
+      <c r="N967" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O967" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B968" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C968" t="str">
+        <v>Uppsala Castle</v>
+      </c>
+      <c r="D968" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E968">
+        <v>1</v>
+      </c>
+      <c r="G968" t="str">
+        <v>September</v>
+      </c>
+      <c r="H968">
+        <v>2019</v>
+      </c>
+      <c r="J968">
+        <v>59.853262</v>
+      </c>
+      <c r="K968">
+        <v>17.635616</v>
+      </c>
+      <c r="N968" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O968" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B969" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C969" t="str">
+        <v>Uppsala Cathedral</v>
+      </c>
+      <c r="D969" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E969">
+        <v>1</v>
+      </c>
+      <c r="G969" t="str">
+        <v>September</v>
+      </c>
+      <c r="H969">
+        <v>2019</v>
+      </c>
+      <c r="J969">
+        <v>59.858109</v>
+      </c>
+      <c r="K969">
+        <v>17.633645</v>
+      </c>
+      <c r="N969" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O969" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B970" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C970" t="str">
+        <v>Uppsala University</v>
+      </c>
+      <c r="D970" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E970">
+        <v>1</v>
+      </c>
+      <c r="G970" t="str">
+        <v>September</v>
+      </c>
+      <c r="H970">
+        <v>2019</v>
+      </c>
+      <c r="J970">
+        <v>59.8509</v>
+      </c>
+      <c r="K970">
+        <v>17.630009</v>
+      </c>
+      <c r="N970" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O970" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B971" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C971" t="str">
+        <v>Botanical Garden</v>
+      </c>
+      <c r="D971" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E971">
+        <v>1</v>
+      </c>
+      <c r="G971" t="str">
+        <v>September</v>
+      </c>
+      <c r="H971">
+        <v>2019</v>
+      </c>
+      <c r="J971">
+        <v>59.850573</v>
+      </c>
+      <c r="K971">
+        <v>17.628953</v>
+      </c>
+      <c r="N971" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O971" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B972" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C972" t="str">
+        <v>Svartbäcksgatan</v>
+      </c>
+      <c r="D972" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E972">
+        <v>1</v>
+      </c>
+      <c r="G972" t="str">
+        <v>September</v>
+      </c>
+      <c r="H972">
+        <v>2019</v>
+      </c>
+      <c r="J972">
+        <v>59.869292</v>
+      </c>
+      <c r="K972">
+        <v>17.628217</v>
+      </c>
+      <c r="N972" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O972" t="str">
+        <v>Main shopping street, pedestrian street running parallel to river</v>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B973" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C973" t="str">
+        <v>Saluhallen</v>
+      </c>
+      <c r="D973" t="str">
+        <v>market</v>
+      </c>
+      <c r="E973">
+        <v>1</v>
+      </c>
+      <c r="G973" t="str">
+        <v>September</v>
+      </c>
+      <c r="H973">
+        <v>2019</v>
+      </c>
+      <c r="J973">
+        <v>59.859146</v>
+      </c>
+      <c r="K973">
+        <v>17.633404</v>
+      </c>
+      <c r="N973" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O973" t="str">
+        <v>Food Market Hall with assortment of restaurants. Opens 10am Mon-Sat</v>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="str">
+        <v>Sweden</v>
+      </c>
+      <c r="B974" t="str">
+        <v>Uppsala</v>
+      </c>
+      <c r="C974" t="str">
+        <v>Uppsala Central Station</v>
+      </c>
+      <c r="D974" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E974">
+        <v>1</v>
+      </c>
+      <c r="G974" t="str">
+        <v>September</v>
+      </c>
+      <c r="H974">
+        <v>2019</v>
+      </c>
+      <c r="J974">
+        <v>59.858198</v>
+      </c>
+      <c r="K974">
+        <v>17.646542</v>
+      </c>
+      <c r="N974" t="str">
+        <v>add to map</v>
+      </c>
+      <c r="O974" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B975" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C975" t="str">
+        <v>Helsinki Airport (HEL)</v>
+      </c>
+      <c r="D975" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J975">
+        <v>60.3185535</v>
+      </c>
+      <c r="K975">
+        <v>24.9680065</v>
+      </c>
+      <c r="L975" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O975" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B976" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C976" t="str">
+        <v>Scandic Park Helsinki</v>
+      </c>
+      <c r="D976" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J976">
+        <v>60.1791227</v>
+      </c>
+      <c r="K976">
+        <v>24.9276382</v>
+      </c>
+      <c r="L976" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O976" t="str">
+        <v>Amenities: Private health club open Thurs from 6:30am – 10pm and Fri from 6:30am – 9pm, indoor pool &amp; sauna, breakfast</v>
+      </c>
+      <c r="S976" t="str">
+        <v>https://www.hotels.com/ho106261/scandic-park-helsinki-helsinki-finland/</v>
+      </c>
+      <c r="U976" t="str">
+        <v>Central location, breakfast buffet with GF options</v>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B977" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C977" t="str">
+        <v>Naughty BRGR Lönkka</v>
+      </c>
+      <c r="D977" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J977">
+        <v>60.1657767</v>
+      </c>
+      <c r="K977">
+        <v>24.9365297</v>
+      </c>
+      <c r="L977" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O977" t="str">
+        <v>GF, vegan buns &amp; beyond burger - was very good!</v>
+      </c>
+      <c r="R977" t="str">
+        <v>[2026-03-29] Verified CLOSED</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B978" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C978" t="str">
+        <v>Ristorante Pizzeria Dennis Bulevardi</v>
+      </c>
+      <c r="D978" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J978">
+        <v>60.1632554</v>
+      </c>
+      <c r="K978">
+        <v>24.9343197</v>
+      </c>
+      <c r="L978" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O978" t="str">
+        <v/>
+      </c>
+      <c r="R978" t="str">
+        <v>[2026-03-29] Verified CLOSED</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B979" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C979" t="str">
+        <v>Keliapuoti Leena Raitisto</v>
+      </c>
+      <c r="D979" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="I979" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J979">
+        <v>60.1790863</v>
+      </c>
+      <c r="K979">
+        <v>24.951616</v>
+      </c>
+      <c r="L979" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O979" t="str">
+        <v>Kelia Puoti – GF bakery</v>
+      </c>
+      <c r="P979" t="str">
+        <v>https://www.findmeglutenfree.com/biz/keliapuoti-leena-raitisto/4727054790688768</v>
+      </c>
+      <c r="Q979">
+        <v>5</v>
+      </c>
+      <c r="R979" t="str">
+        <v>[2026-03-29 research] Dedicated GF bakery in Hakaniemi Market Hall. Fresh breads, pastries, Karelian pies, cinnamon buns.</v>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B980" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C980" t="str">
+        <v>Kappeli</v>
+      </c>
+      <c r="D980" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="I980" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J980">
+        <v>60.167386</v>
+      </c>
+      <c r="K980">
+        <v>24.950323</v>
+      </c>
+      <c r="L980" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O980" t="str">
+        <v>Kappeli – has GF marked and prawn risotto (hard to get a table) - was AMAZING! the waiter was awesome, dessert was awesome - met some ladies from wisconsin.</v>
+      </c>
+      <c r="P980" t="str">
+        <v>https://www.findmeglutenfree.com/biz/kappeli/6137394541232128</v>
+      </c>
+      <c r="Q980">
+        <v>4</v>
+      </c>
+      <c r="R980" t="str">
+        <v>[2026-03-29 research] GF items marked on menu. Complimentary GF bread. Prawn risotto recommended.</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B981" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C981" t="str">
+        <v>Cafe Regatta</v>
+      </c>
+      <c r="D981" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="I981" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J981">
+        <v>60.1801388</v>
+      </c>
+      <c r="K981">
+        <v>24.9118115</v>
+      </c>
+      <c r="L981" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O981" t="str">
+        <v/>
+      </c>
+      <c r="P981" t="str">
+        <v>https://www.findmeglutenfree.com/biz/regatta/6025606266486784</v>
+      </c>
+      <c r="Q981">
+        <v>2</v>
+      </c>
+      <c r="R981" t="str">
+        <v>[2026-03-29 research] GF options on menu but cross-contamination risk. Not dedicated facility.</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B982" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C982" t="str">
+        <v>Temppeliaukion Church</v>
+      </c>
+      <c r="D982" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J982">
+        <v>60.172995</v>
+      </c>
+      <c r="K982">
+        <v>24.925234</v>
+      </c>
+      <c r="L982" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O982" t="str">
+        <v>was super cool - Partly underground w/ circular skylight</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B983" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C983" t="str">
+        <v>Kamppi Chapel</v>
+      </c>
+      <c r="D983" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J983">
+        <v>60.1694692</v>
+      </c>
+      <c r="K983">
+        <v>24.9359728</v>
+      </c>
+      <c r="L983" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O983" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B984" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C984" t="str">
+        <v>Suomenlinna - The Fortress of Finland</v>
+      </c>
+      <c r="D984" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J984">
+        <v>60.1446643</v>
+      </c>
+      <c r="K984">
+        <v>24.9827935</v>
+      </c>
+      <c r="L984" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O984" t="str">
+        <v>• 1 of the biggest sea fortresses in the world&lt;br&gt;• UNESCO world heritage site&lt;br&gt;• Ferry runs year round and takes about 15 min</v>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B985" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C985" t="str">
+        <v>Hakaniemi Market Hall</v>
+      </c>
+      <c r="D985" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J985">
+        <v>60.1791379</v>
+      </c>
+      <c r="K985">
+        <v>24.9517059</v>
+      </c>
+      <c r="L985" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O985" t="str">
+        <v>Bi-level red-brick market since 1914, with seafood, produce &amp; other foods, plus crafts &amp; souvenirs.</v>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B986" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C986" t="str">
+        <v>Nuuksio Reindeer Park</v>
+      </c>
+      <c r="D986" t="str">
+        <v>activity</v>
+      </c>
+      <c r="J986">
+        <v>60.3042923</v>
+      </c>
+      <c r="K986">
+        <v>24.5515684</v>
+      </c>
+      <c r="L986" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O986" t="str">
+        <v>ONLY OPEN ON SATURDAYS IN OCTOBER ☹&lt;br&gt;• 47 mins from hotel by public transport</v>
+      </c>
+      <c r="S986" t="str">
+        <v>https://www.getyourguide.com/helsinki-l13/helsinki-nuuksio-reindeer-park-tour-t269027/</v>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B987" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C987" t="str">
+        <v>SkyWheel Helsinki</v>
+      </c>
+      <c r="D987" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J987">
+        <v>60.166788</v>
+      </c>
+      <c r="K987">
+        <v>24.959462</v>
+      </c>
+      <c r="L987" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O987" t="str">
+        <v/>
+      </c>
+      <c r="S987" t="str">
+        <v>https://www.getyourguide.com/helsinki-l13/helsinki-skywheel-helsinki-ride-ticket-t512719/</v>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B988" t="str">
+        <v>Helsinki</v>
+      </c>
+      <c r="C988" t="str">
+        <v>Market Square</v>
+      </c>
+      <c r="D988" t="str">
+        <v>market</v>
+      </c>
+      <c r="J988">
+        <v>60.1676653</v>
+      </c>
+      <c r="K988">
+        <v>24.9536778</v>
+      </c>
+      <c r="L988" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O988" t="str">
+        <v>open air market</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B989" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C989" t="str">
+        <v>Tampere Station</v>
+      </c>
+      <c r="D989" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J989">
+        <v>61.4990515</v>
+      </c>
+      <c r="K989">
+        <v>23.7750395</v>
+      </c>
+      <c r="L989" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O989" t="str">
+        <v/>
+      </c>
+      <c r="S989" t="str">
+        <v>https://www.hotels.com/ho400777/scandic-tampere-station-tampere-finland/</v>
+      </c>
+      <c r="U989" t="str">
+        <v>Adjacent to station, breakfast buffet</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B990" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C990" t="str">
+        <v>Scandic Tampere Station</v>
+      </c>
+      <c r="D990" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J990">
+        <v>61.4992302</v>
+      </c>
+      <c r="K990">
+        <v>23.7756188</v>
+      </c>
+      <c r="L990" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O990" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B991" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C991" t="str">
+        <v>Tampere Market Hall</v>
+      </c>
+      <c r="D991" t="str">
+        <v>market</v>
+      </c>
+      <c r="J991">
+        <v>61.4969444</v>
+      </c>
+      <c r="K991">
+        <v>23.7586111</v>
+      </c>
+      <c r="L991" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O991" t="str">
+        <v>(Largest Enclosed Nordic Market Hall)</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B992" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C992" t="str">
+        <v>Näsinneula</v>
+      </c>
+      <c r="D992" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J992">
+        <v>61.5049647</v>
+      </c>
+      <c r="K992">
+        <v>23.7430645</v>
+      </c>
+      <c r="L992" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O992" t="str">
+        <v/>
+      </c>
+      <c r="S992" t="str">
+        <v>https://sarkanniemi.fi/en/product/nasinneula-lippu-4</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B993" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C993" t="str">
+        <v>Pyynikki Observation Tower</v>
+      </c>
+      <c r="D993" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J993">
+        <v>61.4963497</v>
+      </c>
+      <c r="K993">
+        <v>23.7320282</v>
+      </c>
+      <c r="L993" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O993" t="str">
+        <v/>
+      </c>
+      <c r="S993" t="str">
+        <v>https://www.munkkikahvila.net/en</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B994" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C994" t="str">
+        <v>Hatanpää Park Arboretum</v>
+      </c>
+      <c r="D994" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J994">
+        <v>61.4810238</v>
+      </c>
+      <c r="K994">
+        <v>23.7528293</v>
+      </c>
+      <c r="L994" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O994" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B995" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C995" t="str">
+        <v>Thai &amp; Laos Restaurant</v>
+      </c>
+      <c r="D995" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="I995" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J995">
+        <v>61.4983089</v>
+      </c>
+      <c r="K995">
+        <v>23.7548459</v>
+      </c>
+      <c r="L995" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O995" t="str">
+        <v>all dishes are GF &amp; lactose free - was good.</v>
+      </c>
+      <c r="Q995">
+        <v>4</v>
+      </c>
+      <c r="R995" t="str">
+        <v>[2026-03-29 research] All dishes GF &amp; lactose free. Thai curries and stir-fries all safe.</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B996" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C996" t="str">
+        <v>Sitko Pizza Tampere</v>
+      </c>
+      <c r="D996" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="I996" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J996">
+        <v>61.4986679</v>
+      </c>
+      <c r="K996">
+        <v>23.7542559</v>
+      </c>
+      <c r="L996" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O996" t="str">
+        <v>Sitko Pizza – GF crust &amp; vegan cheese</v>
+      </c>
+      <c r="Q996">
+        <v>4</v>
+      </c>
+      <c r="R996" t="str">
+        <v>[2026-03-29 research] Dedicated GF crust, vegan cheese available. Made fresh separately.</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v>Finland</v>
+      </c>
+      <c r="B997" t="str">
+        <v>Tampere</v>
+      </c>
+      <c r="C997" t="str">
+        <v>Venla</v>
+      </c>
+      <c r="D997" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="I997" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J997">
+        <v>61.4983333</v>
+      </c>
+      <c r="K997">
+        <v>23.7575</v>
+      </c>
+      <c r="L997" t="str">
+        <v>Finland (September 2019)</v>
+      </c>
+      <c r="O997" t="str">
+        <v>Bistro Venla – GF bread &amp; a lot of GF vegetarian options - dont think I ate here.</v>
+      </c>
+      <c r="Q997">
+        <v>3</v>
+      </c>
+      <c r="R997" t="str">
+        <v>[2026-03-29 research] GF bread and extensive GF vegetarian options. Salad-focused bistro.</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B998" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C998" t="str">
+        <v>Hampton by Hilton Berlin City West</v>
+      </c>
+      <c r="D998" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J998">
+        <v>52.504978</v>
+      </c>
+      <c r="K998">
+        <v>13.325864</v>
+      </c>
+      <c r="L998" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O998" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B999" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C999" t="str">
+        <v>Berlin Central Station</v>
+      </c>
+      <c r="D999" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J999">
+        <v>52.524911</v>
+      </c>
+      <c r="K999">
+        <v>13.369492</v>
+      </c>
+      <c r="L999" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O999" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1000" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1000" t="str">
+        <v>Teufelsberg</v>
+      </c>
+      <c r="D1000" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1000">
+        <v>52.497222</v>
+      </c>
+      <c r="K1000">
+        <v>13.241111</v>
+      </c>
+      <c r="L1000" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1000" t="str">
+        <v>Teufelsberg Nazi Ruins/Abandoned Cold War NSA Post</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1001" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1001" t="str">
+        <v>Olympiastadion Berlin</v>
+      </c>
+      <c r="D1001" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1001">
+        <v>52.514697</v>
+      </c>
+      <c r="K1001">
+        <v>13.239499</v>
+      </c>
+      <c r="L1001" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1001" t="str">
+        <v>Hertha Berlin stadium for bundesliga games</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1002" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1002" t="str">
+        <v>Berlin Wall</v>
+      </c>
+      <c r="D1002" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1002">
+        <v>52.507182</v>
+      </c>
+      <c r="K1002">
+        <v>13.383506</v>
+      </c>
+      <c r="L1002" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1002" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1003" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1003" t="str">
+        <v>Görlitzer Park</v>
+      </c>
+      <c r="D1003" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1003">
+        <v>52.496593</v>
+      </c>
+      <c r="K1003">
+        <v>13.437449</v>
+      </c>
+      <c r="L1003" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1003" t="str">
+        <v>Lots of graffiti, people playing music, etc. – some drug dealers so avoid at night.</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1004" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1004" t="str">
+        <v>Berlin Wall Memorial</v>
+      </c>
+      <c r="D1004" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1004">
+        <v>52.535052</v>
+      </c>
+      <c r="K1004">
+        <v>13.39019</v>
+      </c>
+      <c r="L1004" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1004" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1005" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1005" t="str">
+        <v>Fat Tire Tours</v>
+      </c>
+      <c r="D1005" t="str">
+        <v>activity</v>
+      </c>
+      <c r="J1005">
+        <v>52.520995</v>
+      </c>
+      <c r="K1005">
+        <v>13.409113</v>
+      </c>
+      <c r="L1005" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1005" t="str">
+        <v>HIGHLY recommend - you get to see a lot of cool spots and hear a lot of good stories - Berlin Wall, Holocaust Memorial sites, etc</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1006" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1006" t="str">
+        <v>Checkpoint Charlie</v>
+      </c>
+      <c r="D1006" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1006">
+        <v>52.507443</v>
+      </c>
+      <c r="K1006">
+        <v>13.390391</v>
+      </c>
+      <c r="L1006" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1006" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1007" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1007" t="str">
+        <v>Memorial to the Murdered Jews of Europe</v>
+      </c>
+      <c r="D1007" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1007">
+        <v>52.513947</v>
+      </c>
+      <c r="K1007">
+        <v>13.378713</v>
+      </c>
+      <c r="L1007" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1007" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1008" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1008" t="str">
+        <v>Reichstag Building</v>
+      </c>
+      <c r="D1008" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1008">
+        <v>52.518619</v>
+      </c>
+      <c r="K1008">
+        <v>13.376318</v>
+      </c>
+      <c r="L1008" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1008" t="str">
+        <v>German Parliament</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1009" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1009" t="str">
+        <v>Berliner Fernsehturm</v>
+      </c>
+      <c r="D1009" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1009">
+        <v>52.520815</v>
+      </c>
+      <c r="K1009">
+        <v>13.409419</v>
+      </c>
+      <c r="L1009" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1009" t="str">
+        <v>TV Tower</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1010" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1010" t="str">
+        <v>Berlin Cathedral</v>
+      </c>
+      <c r="D1010" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1010">
+        <v>52.519061</v>
+      </c>
+      <c r="K1010">
+        <v>13.401078</v>
+      </c>
+      <c r="L1010" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1010" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1011" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1011" t="str">
+        <v>Markthalle Neun</v>
+      </c>
+      <c r="D1011" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1011">
+        <v>52.502023</v>
+      </c>
+      <c r="K1011">
+        <v>13.431935</v>
+      </c>
+      <c r="L1011" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1011" t="str">
+        <v>• Not usually open all Sundays but on May 13th and 14th they're having a raw (organic) wine festival! Tix are 40 euros each so not buying ahead of time.</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1012" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>Mauerpark</v>
+      </c>
+      <c r="D1012" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1012">
+        <v>52.5424</v>
+      </c>
+      <c r="K1012">
+        <v>13.403352</v>
+      </c>
+      <c r="L1012" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1012" t="str">
+        <v>LOVED IT. Karoake, dancing, drinks, etc - really fun, hipster atmosphere. Open karaoke starts at 3pm &amp; amazing flea mkt on Sundays. Food or drinks available at flea market and there’s a little beer garden</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1013" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>Sachiko Sushi</v>
+      </c>
+      <c r="D1013" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1013">
+        <v>52.504701</v>
+      </c>
+      <c r="K1013">
+        <v>13.323713</v>
+      </c>
+      <c r="L1013" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1013" t="str">
+        <v>quaint sushi bar with a 'conveyor belt' (river boat) that serves up sushi dishes</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1014" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>Brammibal's Donuts (Maybachufer)</v>
+      </c>
+      <c r="D1014" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1014">
+        <v>52.494978</v>
+      </c>
+      <c r="K1014">
+        <v>13.42302</v>
+      </c>
+      <c r="L1014" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1014" t="str">
+        <v>I don't think I actually ate here. I think they said the GF donuts had cross-contamination. But had vegan donuts.</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1015" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>Cevicheria</v>
+      </c>
+      <c r="D1015" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1015">
+        <v>52.501282</v>
+      </c>
+      <c r="K1015">
+        <v>13.416523</v>
+      </c>
+      <c r="L1015" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1015" t="str">
+        <v>don't remember eating here</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1016" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>Simela Finest Food</v>
+      </c>
+      <c r="D1016" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1016">
+        <v>52.527562</v>
+      </c>
+      <c r="K1016">
+        <v>13.398105</v>
+      </c>
+      <c r="L1016" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1016" t="str">
+        <v>2nd location (I did not go to this one) with GF pizza</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1017" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>Simela finest food</v>
+      </c>
+      <c r="D1017" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1017">
+        <v>52.505576</v>
+      </c>
+      <c r="K1017">
+        <v>13.323439</v>
+      </c>
+      <c r="L1017" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1017" t="str">
+        <v>gluten free pizza - was such a cute family owned spot!</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1018" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>OAK &amp; ICE</v>
+      </c>
+      <c r="D1018" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1018">
+        <v>52.542882</v>
+      </c>
+      <c r="K1018">
+        <v>13.412664</v>
+      </c>
+      <c r="L1018" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1018" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1019" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>No Milk Today</v>
+      </c>
+      <c r="D1019" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1019">
+        <v>52.490921</v>
+      </c>
+      <c r="K1019">
+        <v>13.412804</v>
+      </c>
+      <c r="L1019" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1019" t="str">
+        <v>don't remember eating here</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1020" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>Burgerie</v>
+      </c>
+      <c r="D1020" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1020">
+        <v>52.542506</v>
+      </c>
+      <c r="K1020">
+        <v>13.412613</v>
+      </c>
+      <c r="L1020" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1020" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1021" t="str">
+        <v>Berlin</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>Jute Bäckerei</v>
+      </c>
+      <c r="D1021" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1021">
+        <v>52.543011</v>
+      </c>
+      <c r="K1021">
+        <v>13.412799</v>
+      </c>
+      <c r="L1021" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1021" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1022" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>Hyatt Regency Cologne</v>
+      </c>
+      <c r="D1022" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J1022">
+        <v>50.94043</v>
+      </c>
+      <c r="K1022">
+        <v>6.96953</v>
+      </c>
+      <c r="L1022" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1022" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1023" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>Cologne Central Station</v>
+      </c>
+      <c r="D1023" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J1023">
+        <v>50.943214</v>
+      </c>
+      <c r="K1023">
+        <v>6.958602</v>
+      </c>
+      <c r="L1023" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1023" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1024" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>Cologne Triangle</v>
+      </c>
+      <c r="D1024" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1024">
+        <v>50.940411</v>
+      </c>
+      <c r="K1024">
+        <v>6.971808</v>
+      </c>
+      <c r="L1024" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1024" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1025" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>Cologne Cathedral</v>
+      </c>
+      <c r="D1025" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1025">
+        <v>50.941278</v>
+      </c>
+      <c r="K1025">
+        <v>6.958281</v>
+      </c>
+      <c r="L1025" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1025" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1026" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>Hohenzollernbrücke</v>
+      </c>
+      <c r="D1026" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1026">
+        <v>50.941605</v>
+      </c>
+      <c r="K1026">
+        <v>6.965789</v>
+      </c>
+      <c r="L1026" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1026" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1027" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>Old Market</v>
+      </c>
+      <c r="D1027" t="str">
+        <v>market</v>
+      </c>
+      <c r="J1027">
+        <v>50.938504</v>
+      </c>
+      <c r="K1027">
+        <v>6.960141</v>
+      </c>
+      <c r="L1027" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1027" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1028" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>UNIQLO Köln</v>
+      </c>
+      <c r="D1028" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1028">
+        <v>50.936403</v>
+      </c>
+      <c r="K1028">
+        <v>6.956441</v>
+      </c>
+      <c r="L1028" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1028" t="str">
+        <v>good thermal basics &amp; under layers!</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1029" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>Weihnachtsmarkt auf dem Neumarkt Köln</v>
+      </c>
+      <c r="D1029" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1029">
+        <v>50.93599</v>
+      </c>
+      <c r="K1029">
+        <v>6.947487</v>
+      </c>
+      <c r="L1029" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1029" t="str">
+        <v>Christmas Market</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1030" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>Kuchi Mami</v>
+      </c>
+      <c r="D1030" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1030">
+        <v>50.941402</v>
+      </c>
+      <c r="K1030">
+        <v>6.954008</v>
+      </c>
+      <c r="L1030" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1030" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1031" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>mama trattoria Köln City</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1031">
+        <v>50.937751</v>
+      </c>
+      <c r="K1031">
+        <v>6.955545</v>
+      </c>
+      <c r="L1031" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1031" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1032" t="str">
+        <v>Cologne</v>
+      </c>
+      <c r="C1032" t="str">
+        <v>MEIN CORONA SCHNELLTEST - Köln</v>
+      </c>
+      <c r="D1032" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1032">
+        <v>50.938032</v>
+      </c>
+      <c r="K1032">
+        <v>6.961153</v>
+      </c>
+      <c r="L1032" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1032" t="str">
+        <v>COVID Testing</v>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1033" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1033" t="str">
+        <v>carathotel Düsseldorf City</v>
+      </c>
+      <c r="D1033" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J1033">
+        <v>51.219538</v>
+      </c>
+      <c r="K1033">
+        <v>6.783752</v>
+      </c>
+      <c r="L1033" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1033" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1034" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1034" t="str">
+        <v>Düsseldorf Airport</v>
+      </c>
+      <c r="D1034" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J1034">
+        <v>51.279475</v>
+      </c>
+      <c r="K1034">
+        <v>6.765677</v>
+      </c>
+      <c r="L1034" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1034" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1035" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1035" t="str">
+        <v>Düsseldorf Central Station</v>
+      </c>
+      <c r="D1035" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J1035">
+        <v>51.219828</v>
+      </c>
+      <c r="K1035">
+        <v>6.794479</v>
+      </c>
+      <c r="L1035" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1035" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1036" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1036" t="str">
+        <v>Rhine Tower</v>
+      </c>
+      <c r="D1036" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1036">
+        <v>51.217942</v>
+      </c>
+      <c r="K1036">
+        <v>6.76168</v>
+      </c>
+      <c r="L1036" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1036" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1037" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1037" t="str">
+        <v>Königsallee</v>
+      </c>
+      <c r="D1037" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1037">
+        <v>51.221698</v>
+      </c>
+      <c r="K1037">
+        <v>6.779262</v>
+      </c>
+      <c r="L1037" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1037" t="str">
+        <v>cute outdoor pond/channel with Christmas Market stalls</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1038" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1038" t="str">
+        <v>Vabali Spa Düsseldorf</v>
+      </c>
+      <c r="D1038" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1038">
+        <v>51.183203</v>
+      </c>
+      <c r="K1038">
+        <v>6.9103533</v>
+      </c>
+      <c r="L1038" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1038" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1039" t="str">
+        <v>Dusseldorf</v>
+      </c>
+      <c r="C1039" t="str">
+        <v>Isabella Glutenfreie Pâtisserie</v>
+      </c>
+      <c r="D1039" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1039">
+        <v>51.221976</v>
+      </c>
+      <c r="K1039">
+        <v>6.780773</v>
+      </c>
+      <c r="L1039" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1039" t="str">
+        <v>Dedicated gluten free bakery - lots of options - some are better than others. Pretty expensive.</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1040" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1040" t="str">
+        <v>Hampton by Hilton Frankfurt City Centre Messe</v>
+      </c>
+      <c r="D1040" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J1040">
+        <v>50.108938</v>
+      </c>
+      <c r="K1040">
+        <v>8.647072</v>
+      </c>
+      <c r="L1040" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1040" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1041" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1041" t="str">
+        <v>Frankfurt Airport (FRA)</v>
+      </c>
+      <c r="D1041" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J1041">
+        <v>50.051219</v>
+      </c>
+      <c r="K1041">
+        <v>8.571788</v>
+      </c>
+      <c r="L1041" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1041" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1042" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1042" t="str">
+        <v>Frankfurt (Main) Hauptbahnhof</v>
+      </c>
+      <c r="D1042" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1042">
+        <v>50.10716</v>
+      </c>
+      <c r="K1042">
+        <v>8.66376</v>
+      </c>
+      <c r="L1042" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1042" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1043" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1043" t="str">
+        <v>Rententurm</v>
+      </c>
+      <c r="D1043" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1043">
+        <v>50.10924</v>
+      </c>
+      <c r="K1043">
+        <v>8.682309</v>
+      </c>
+      <c r="L1043" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1043" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1044" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1044" t="str">
+        <v>Römer</v>
+      </c>
+      <c r="D1044" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1044">
+        <v>50.110263</v>
+      </c>
+      <c r="K1044">
+        <v>8.682096</v>
+      </c>
+      <c r="L1044" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1044" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1045" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1045" t="str">
+        <v>Frankfurt Cathedral</v>
+      </c>
+      <c r="D1045" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1045">
+        <v>50.110663</v>
+      </c>
+      <c r="K1045">
+        <v>8.68542</v>
+      </c>
+      <c r="L1045" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1045" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1046" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1046" t="str">
+        <v>Iron Footbridge</v>
+      </c>
+      <c r="D1046" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1046">
+        <v>50.108111</v>
+      </c>
+      <c r="K1046">
+        <v>8.682129</v>
+      </c>
+      <c r="L1046" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1046" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1047" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1047" t="str">
+        <v>Kleinmarkthalle</v>
+      </c>
+      <c r="D1047" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1047">
+        <v>50.112667</v>
+      </c>
+      <c r="K1047">
+        <v>8.682885</v>
+      </c>
+      <c r="L1047" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1047" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1048" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1048" t="str">
+        <v>Domturm</v>
+      </c>
+      <c r="D1048" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1048">
+        <v>50.110601</v>
+      </c>
+      <c r="K1048">
+        <v>8.684985</v>
+      </c>
+      <c r="L1048" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1048" t="str">
+        <v>observation deck</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1049" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1049" t="str">
+        <v>Frankfurt Cathedral</v>
+      </c>
+      <c r="D1049" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1049">
+        <v>50.110663</v>
+      </c>
+      <c r="K1049">
+        <v>8.68542</v>
+      </c>
+      <c r="L1049" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1049" t="str">
+        <v>can climb the dome</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1050" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1050" t="str">
+        <v>Main Tower</v>
+      </c>
+      <c r="D1050" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1050">
+        <v>50.112548</v>
+      </c>
+      <c r="K1050">
+        <v>8.672142</v>
+      </c>
+      <c r="L1050" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1050" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1051" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>Frankfurter Römer</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1051">
+        <v>50.110581</v>
+      </c>
+      <c r="K1051">
+        <v>8.681806</v>
+      </c>
+      <c r="L1051" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1051" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1052" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>Hop-On Hop-Off Stop: Messe (Frankfurt Sightseeing)</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1052">
+        <v>50.111521</v>
+      </c>
+      <c r="K1052">
+        <v>8.654943</v>
+      </c>
+      <c r="L1052" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1052" t="str">
+        <v>where I got on the HoHo bus</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1053" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>Block House</v>
+      </c>
+      <c r="D1053" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1053">
+        <v>50.109232</v>
+      </c>
+      <c r="K1053">
+        <v>8.650328</v>
+      </c>
+      <c r="L1053" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1053" t="str">
+        <v>steak house but they had caprese salad and apps that were GF</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1054" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>Tacohaus</v>
+      </c>
+      <c r="D1054" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1054">
+        <v>50.116625</v>
+      </c>
+      <c r="K1054">
+        <v>8.643881</v>
+      </c>
+      <c r="L1054" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1054" t="str">
+        <v>don't think I actually ate here but it was on my list</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1055" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>MAREDO Frankfurt Hauptwache</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1055">
+        <v>50.113902</v>
+      </c>
+      <c r="K1055">
+        <v>8.678046</v>
+      </c>
+      <c r="L1055" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1055" t="str">
+        <v>steak house w/ GF marked on the menu</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1056" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>HANS IM GLÜCK - FRANKFURT am Main Braubachstraße</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1056">
+        <v>50.111958</v>
+      </c>
+      <c r="K1056">
+        <v>8.685564</v>
+      </c>
+      <c r="L1056" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1056" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1057" t="str">
+        <v>Frankfurt</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>VAPIANO Frankfurt Goetheplatz</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1057">
+        <v>50.112846</v>
+      </c>
+      <c r="K1057">
+        <v>8.675892</v>
+      </c>
+      <c r="L1057" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1057" t="str">
+        <v>had GF pizza and was marked with a little flag to signify gluten free. but it was not very good.</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1058" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>Roomers Hotel Munich</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J1058">
+        <v>48.139801</v>
+      </c>
+      <c r="K1058">
+        <v>11.540704</v>
+      </c>
+      <c r="L1058" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1058" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1059" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>Eden Hotel Wolff</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="J1059">
+        <v>48.141654</v>
+      </c>
+      <c r="K1059">
+        <v>11.559204</v>
+      </c>
+      <c r="L1059" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1059" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1060" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>Munich Airport</v>
+      </c>
+      <c r="D1060" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J1060">
+        <v>48.352732</v>
+      </c>
+      <c r="K1060">
+        <v>11.78624</v>
+      </c>
+      <c r="L1060" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1060" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1061" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>Munich Central Station</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>transit</v>
+      </c>
+      <c r="J1061">
+        <v>48.140267</v>
+      </c>
+      <c r="K1061">
+        <v>11.559998</v>
+      </c>
+      <c r="L1061" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1061" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1062" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>Munich Hauptbahnhof</v>
+      </c>
+      <c r="D1062" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1062">
+        <v>48.139775</v>
+      </c>
+      <c r="K1062">
+        <v>11.560958</v>
+      </c>
+      <c r="L1062" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1062" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1063" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>Technische Universität München</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1063">
+        <v>48.14966</v>
+      </c>
+      <c r="K1063">
+        <v>11.56786</v>
+      </c>
+      <c r="L1063" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1063" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1064" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>St. Peter's Church</v>
+      </c>
+      <c r="D1064" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1064">
+        <v>48.136491</v>
+      </c>
+      <c r="K1064">
+        <v>11.576047</v>
+      </c>
+      <c r="L1064" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1064" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1065" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>Karlsplatz</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1065">
+        <v>48.139193</v>
+      </c>
+      <c r="K1065">
+        <v>11.566201</v>
+      </c>
+      <c r="L1065" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1065" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1066" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>Marienplatz</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1066">
+        <v>48.137393</v>
+      </c>
+      <c r="K1066">
+        <v>11.575448</v>
+      </c>
+      <c r="L1066" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1066" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1067" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>Frauenkirche</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1067">
+        <v>48.138631</v>
+      </c>
+      <c r="K1067">
+        <v>11.573625</v>
+      </c>
+      <c r="L1067" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1067" t="str">
+        <v>(gothic church with iconic domed towers)</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1068" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>Victuals Market</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>market</v>
+      </c>
+      <c r="J1068">
+        <v>48.135114</v>
+      </c>
+      <c r="K1068">
+        <v>11.576255</v>
+      </c>
+      <c r="L1068" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1068" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1069" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>English Garden</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1069">
+        <v>48.164232</v>
+      </c>
+      <c r="K1069">
+        <v>11.605552</v>
+      </c>
+      <c r="L1069" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1069" t="str">
+        <v>English Garden (park with beer garden) – pretty far north but worth it. Cute chinese tower as well.</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1070" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>Stachus Passagen</v>
+      </c>
+      <c r="D1070" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1070">
+        <v>48.139413</v>
+      </c>
+      <c r="K1070">
+        <v>11.565072</v>
+      </c>
+      <c r="L1070" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1070" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1071" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>Allianz Arena</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1071">
+        <v>48.218764</v>
+      </c>
+      <c r="K1071">
+        <v>11.624756</v>
+      </c>
+      <c r="L1071" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1071" t="str">
+        <v>Bayern Munich Stadium</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1072" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>Odeonsplatz</v>
+      </c>
+      <c r="D1072" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1072">
+        <v>48.142799</v>
+      </c>
+      <c r="K1072">
+        <v>11.577769</v>
+      </c>
+      <c r="L1072" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1072" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1073" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>Kaimug Taste Thai</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1073">
+        <v>48.1393</v>
+      </c>
+      <c r="K1073">
+        <v>11.564566</v>
+      </c>
+      <c r="L1073" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1073" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1074" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>Hofbräuhaus München</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1074">
+        <v>48.13761</v>
+      </c>
+      <c r="K1074">
+        <v>11.579925</v>
+      </c>
+      <c r="L1074" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1074" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1075" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>Viktualienmarkt Beergarden</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1075">
+        <v>48.135269</v>
+      </c>
+      <c r="K1075">
+        <v>11.576402</v>
+      </c>
+      <c r="L1075" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1075" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1076" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>Stadion an der Schleißheimer Straße</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1076">
+        <v>48.15391</v>
+      </c>
+      <c r="K1076">
+        <v>11.56121</v>
+      </c>
+      <c r="L1076" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1076" t="str">
+        <v>Renowned nonpartisan soccer bar, operating several screens &amp; furnished with football flags &amp; scarves</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1077" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>Fritz Mühlenbäckerei GmbH</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1077">
+        <v>48.12675</v>
+      </c>
+      <c r="K1077">
+        <v>11.593524</v>
+      </c>
+      <c r="L1077" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1077" t="str">
+        <v>GF pies</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1078" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>California Bean</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1078">
+        <v>48.142875</v>
+      </c>
+      <c r="K1078">
+        <v>11.560306</v>
+      </c>
+      <c r="L1078" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1078" t="str">
+        <v>the best breakfast! GF toast</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1079" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>Pizzesco</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1079">
+        <v>48.131374</v>
+      </c>
+      <c r="K1079">
+        <v>11.589519</v>
+      </c>
+      <c r="L1079" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1079" t="str">
+        <v>gluten free pizza and desserts!</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1080" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>echt jetzt - 100% glutenfrei</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1080">
+        <v>48.149646</v>
+      </c>
+      <c r="K1080">
+        <v>11.57261</v>
+      </c>
+      <c r="L1080" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1080" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1081" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>Fritz Mühlenbäckerei GmbH</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1081">
+        <v>48.135969</v>
+      </c>
+      <c r="K1081">
+        <v>11.576746</v>
+      </c>
+      <c r="L1081" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1081" t="str">
+        <v>GF pies</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1082" t="str">
+        <v>Stuttgart</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>Stuttgart Hauptbahnhof (oben)</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1082">
+        <v>48.784784</v>
+      </c>
+      <c r="K1082">
+        <v>9.1832032</v>
+      </c>
+      <c r="L1082" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1082" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1083" t="str">
+        <v>Stuttgart</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>Markthalle Stuttgart</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1083">
+        <v>48.7762502</v>
+      </c>
+      <c r="K1083">
+        <v>9.1794097</v>
+      </c>
+      <c r="L1083" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1083" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1084" t="str">
+        <v>Stuttgart</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>Hans im Glück</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1084">
+        <v>48.7731882</v>
+      </c>
+      <c r="K1084">
+        <v>9.1733064</v>
+      </c>
+      <c r="L1084" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1084" t="str">
+        <v>GF marked - amazing salads!</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1085" t="str">
+        <v>Duisburg &amp; Dinslaken</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>EDEKA</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="J1085">
+        <v>51.5785289</v>
+      </c>
+      <c r="K1085">
+        <v>6.7416476</v>
+      </c>
+      <c r="L1085" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1085" t="str">
+        <v>grocery store with GF options</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1086" t="str">
+        <v>Duisburg &amp; Dinslaken</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>BA'RE:SE</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1086">
+        <v>51.5627959</v>
+      </c>
+      <c r="K1086">
+        <v>6.7371935</v>
+      </c>
+      <c r="L1086" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1086" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1087" t="str">
+        <v>Duisburg &amp; Dinslaken</v>
+      </c>
+      <c r="C1087" t="str">
+        <v>Neutor Galerie</v>
+      </c>
+      <c r="D1087" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1087">
+        <v>51.5617465</v>
+      </c>
+      <c r="K1087">
+        <v>6.7397827</v>
+      </c>
+      <c r="L1087" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1087" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1088" t="str">
+        <v>Duisburg &amp; Dinslaken</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>Tiger &amp; Turtle</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1088">
+        <v>51.3756461</v>
+      </c>
+      <c r="K1088">
+        <v>6.7379532</v>
+      </c>
+      <c r="L1088" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1088" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="B1089" t="str">
+        <v>Duisburg &amp; Dinslaken</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>Landschaftspark Duisburg</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="J1089">
+        <v>51.4814847</v>
+      </c>
+      <c r="K1089">
+        <v>6.7808056</v>
+      </c>
+      <c r="L1089" t="str">
+        <v>Germany (December 2022)</v>
+      </c>
+      <c r="O1089" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U955"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1089"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1089"/>
+  <dimension ref="A1:U1091"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -44863,9 +44863,55 @@
         <v/>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1090" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>Amsterdam (placeholder)</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>other</v>
+      </c>
+      <c r="G1090" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1090" t="str">
+        <v>2022</v>
+      </c>
+      <c r="N1090" t="str">
+        <v>yes</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1091" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>Nijmegen (placeholder)</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>other</v>
+      </c>
+      <c r="G1091" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1091" t="str">
+        <v>2022</v>
+      </c>
+      <c r="N1091" t="str">
+        <v>yes</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1089"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1091"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1091"/>
+  <dimension ref="A1:U988"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3819,6 +3819,9 @@
       <c r="D87" t="str">
         <v>hotel</v>
       </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
       <c r="F87" t="str">
         <v>🏨</v>
       </c>
@@ -3860,6 +3863,9 @@
       <c r="D88" t="str">
         <v>transit</v>
       </c>
+      <c r="E88">
+        <v>1</v>
+      </c>
       <c r="F88" t="str">
         <v>🚉</v>
       </c>
@@ -4306,6 +4312,9 @@
       <c r="M98" t="str">
         <v>Budapest</v>
       </c>
+      <c r="R98" t="str">
+        <v>must visit a thermal bath</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -4612,6 +4621,9 @@
       <c r="D107" t="str">
         <v>bar</v>
       </c>
+      <c r="E107">
+        <v>1</v>
+      </c>
       <c r="F107" t="str">
         <v>🍸</v>
       </c>
@@ -4641,6 +4653,9 @@
       </c>
       <c r="P107" t="str">
         <v>https://www.findmeglutenfree.com/biz/szimpla/5116071392968704</v>
+      </c>
+      <c r="R107" t="str">
+        <v>SO FUN!</v>
       </c>
     </row>
     <row r="108">
@@ -10115,9 +10130,6 @@
       <c r="K244">
         <v>7.8514713</v>
       </c>
-      <c r="N244" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -11889,9 +11901,6 @@
       <c r="N285" t="str">
         <v>yes</v>
       </c>
-      <c r="U285" t="str">
-        <v>Self-catering apartment, Middle Street, Latin Quarter</v>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
@@ -12284,11 +12293,8 @@
       <c r="P295" t="str">
         <v>https://www.findmeglutenfree.com/biz/cava-bodega/5384270569406464</v>
       </c>
-      <c r="Q295">
+      <c r="Q295" t="str">
         <v>4</v>
-      </c>
-      <c r="R295" t="str">
-        <v>[2026-03-29 research] ~50% tapas menu GF, allergens clearly marked.</v>
       </c>
     </row>
     <row r="296">
@@ -12334,11 +12340,8 @@
       <c r="P296" t="str">
         <v>https://www.findmeglutenfree.com/biz/martines-restaurant-and-winebar/4538739612975104</v>
       </c>
-      <c r="Q296">
+      <c r="Q296" t="str">
         <v>4</v>
-      </c>
-      <c r="R296" t="str">
-        <v>[2026-03-29 research] Marks GF dishes with C for celiac-safe. GF bread.</v>
       </c>
     </row>
     <row r="297">
@@ -12519,9 +12522,6 @@
       <c r="Q300" t="str">
         <v>4</v>
       </c>
-      <c r="R300" t="str">
-        <v>[2026-03-29] Verified CLOSED</v>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
@@ -12566,11 +12566,8 @@
       <c r="P301" t="str">
         <v>https://www.findmeglutenfree.com/biz/linnanes-lobster-bar/5328846050164736</v>
       </c>
-      <c r="Q301">
-        <v>3</v>
-      </c>
-      <c r="R301" t="str">
-        <v>[2026-03-29 research] Fresh seafood specialist. Allergens marked. ~13km from Galway.</v>
+      <c r="Q301" t="str">
+        <v>4</v>
       </c>
     </row>
     <row r="302">
@@ -12613,12 +12610,6 @@
       <c r="P302" t="str">
         <v>https://www.findmeglutenfree.com/biz/the-quays-bar-and-restaurant/6713036067176448</v>
       </c>
-      <c r="Q302">
-        <v>2</v>
-      </c>
-      <c r="R302" t="str">
-        <v>[2026-03-29 research] Allergens marked, GF cider, Shepherd's Pie. No separate fryers.</v>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -12643,7 +12634,7 @@
         <v>2023</v>
       </c>
       <c r="I303" t="str">
-        <v>celiac-aware</v>
+        <v>mixed safety</v>
       </c>
       <c r="J303" t="str">
         <v>53.2716955</v>
@@ -12663,11 +12654,8 @@
       <c r="P303" t="str">
         <v>https://www.findmeglutenfree.com/biz/front-door/6277944908185600</v>
       </c>
-      <c r="Q303">
-        <v>4</v>
-      </c>
-      <c r="R303" t="str">
-        <v>[2026-03-29 research] Dedicated deep fryer for GF items! GF fish &amp; chips, stew, nachos, wings, GF beer/cider.</v>
+      <c r="Q303" t="str">
+        <v>3</v>
       </c>
     </row>
     <row r="304">
@@ -12707,12 +12695,6 @@
       <c r="M304" t="str">
         <v>Ireland</v>
       </c>
-      <c r="Q304">
-        <v>1</v>
-      </c>
-      <c r="R304" t="str">
-        <v>[2026-03-29 research] Pub. Dough Bros sometimes in beer garden for GF pizza.</v>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -12801,12 +12783,6 @@
       <c r="O306" t="str">
         <v>fun pub</v>
       </c>
-      <c r="Q306">
-        <v>1</v>
-      </c>
-      <c r="R306" t="str">
-        <v>[2026-03-29 research] Trad music pub. No specific GF menu. Drinks only.</v>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
@@ -12942,11 +12918,8 @@
       <c r="P309" t="str">
         <v>https://www.findmeglutenfree.com/biz/the-kings-head/6579320794644480</v>
       </c>
-      <c r="Q309">
-        <v>2</v>
-      </c>
       <c r="R309" t="str">
-        <v>Great live music! Very fun place; [2026-03-29 research] GF bread for burgers, GF mashed potatoes. Allergen menu exists but not always current. No separate fryers.</v>
+        <v>Great live music! Very fun place</v>
       </c>
     </row>
     <row r="310">
@@ -12975,7 +12948,7 @@
         <v>2023</v>
       </c>
       <c r="I310" t="str">
-        <v>celiac-aware</v>
+        <v>unclear</v>
       </c>
       <c r="J310" t="str">
         <v>53.2719383</v>
@@ -12992,11 +12965,8 @@
       <c r="P310" t="str">
         <v>https://www.findmeglutenfree.com/biz/woozza-wood-fired-pizza/6034945867382784</v>
       </c>
-      <c r="Q310">
-        <v>4</v>
-      </c>
       <c r="R310" t="str">
-        <v>One of the best GF pizzas I've had! Had a huge serving of burrata in the middle too ; [2026-03-29 research] GF pizza with Italian GF dough. Doesn't use separate oven but crust doesn't touch gluten. GF panna cotta, GF beer. €1.50 upcharge.</v>
+        <v xml:space="preserve">One of the best GF pizzas I've had! Had a huge serving of burrata in the middle too </v>
       </c>
     </row>
     <row r="311">
@@ -13022,7 +12992,7 @@
         <v>2023</v>
       </c>
       <c r="I311" t="str">
-        <v>mixed safety</v>
+        <v>unclear</v>
       </c>
       <c r="J311" t="str">
         <v>53.2734629</v>
@@ -13038,12 +13008,6 @@
       </c>
       <c r="P311" t="str">
         <v>https://www.findmeglutenfree.com/biz/pascal-coffee-house/5201659937030144</v>
-      </c>
-      <c r="Q311">
-        <v>3</v>
-      </c>
-      <c r="R311" t="str">
-        <v>[2026-03-29 research] GF bread/buns, soups. Staff ask if coeliac.</v>
       </c>
     </row>
     <row r="312">
@@ -13069,7 +13033,7 @@
         <v>2023</v>
       </c>
       <c r="I312" t="str">
-        <v>mixed safety</v>
+        <v>unclear</v>
       </c>
       <c r="J312" t="str">
         <v>53.2725045</v>
@@ -13085,12 +13049,6 @@
       </c>
       <c r="P312" t="str">
         <v>https://www.findmeglutenfree.com/biz/pascal-coffee-house/5201659937030144</v>
-      </c>
-      <c r="Q312">
-        <v>3</v>
-      </c>
-      <c r="R312" t="str">
-        <v>[2026-03-29 research] Same chain. GF bread/buns, soups.</v>
       </c>
     </row>
     <row r="313">
@@ -13133,12 +13091,6 @@
       <c r="P313" t="str">
         <v>https://www.findmeglutenfree.com/biz/sangria/5627571045269504</v>
       </c>
-      <c r="Q313">
-        <v>3</v>
-      </c>
-      <c r="R313" t="str">
-        <v>[2026-03-29 research] GF modifications, corn tortillas. No dedicated fryer.</v>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
@@ -13183,12 +13135,6 @@
       <c r="N314" t="str">
         <v>yes</v>
       </c>
-      <c r="S314" t="str">
-        <v>https://www.hotels.com/ho425594/killarney-avenue-hotel-killarney-ireland/</v>
-      </c>
-      <c r="U314" t="str">
-        <v>Unclear GF category</v>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
@@ -13710,7 +13656,7 @@
         <v>2023</v>
       </c>
       <c r="I328" t="str">
-        <v>celiac-aware</v>
+        <v>mixed safety</v>
       </c>
       <c r="J328" t="str">
         <v>52.0598627</v>
@@ -13730,11 +13676,8 @@
       <c r="P328" t="str">
         <v>https://www.findmeglutenfree.com/biz/casita-mexicana/5390981331025920</v>
       </c>
-      <c r="Q328">
-        <v>4</v>
-      </c>
-      <c r="R328" t="str">
-        <v>[2026-03-29 research] Extensive GF options. Very celiac-friendly. Staff aware of cross-contam.</v>
+      <c r="Q328" t="str">
+        <v>3</v>
       </c>
     </row>
     <row r="329">
@@ -13780,11 +13723,8 @@
       <c r="O329" t="str">
         <v>We did not eat here, but here's a review from FMGF: "Allegro (Plunkett St) did not disappoint. They have a separate gluten free menu including many types of burgers, fish is available depending on the day and of course, chips. YUM."</v>
       </c>
-      <c r="Q329">
-        <v>5</v>
-      </c>
-      <c r="R329" t="str">
-        <v>[2026-03-29 research] DEDICATED GF kitchen. GF chips, burgers, battered fish, pizza.</v>
+      <c r="Q329" t="str">
+        <v>4</v>
       </c>
     </row>
     <row r="330">
@@ -13830,11 +13770,8 @@
       <c r="O330" t="str">
         <v>We did not eat here but FMGF says most of the menu is already gluten free or can adapted to make it gluten free.</v>
       </c>
-      <c r="Q330">
+      <c r="Q330" t="str">
         <v>4</v>
-      </c>
-      <c r="R330" t="str">
-        <v>[2026-03-29 research] Chef can prepare entire GF menu if requested in advance.</v>
       </c>
     </row>
     <row r="331">
@@ -13977,11 +13914,8 @@
       <c r="P333" t="str">
         <v>https://www.findmeglutenfree.com/biz/great-southern-killarney/4957218353053696</v>
       </c>
-      <c r="Q333">
+      <c r="Q333" t="str">
         <v>4</v>
-      </c>
-      <c r="R333" t="str">
-        <v>[2026-03-29 research] GF sandwiches, bread. Accommodating.</v>
       </c>
     </row>
     <row r="334">
@@ -14030,11 +13964,8 @@
       <c r="P334" t="str">
         <v>https://www.findmeglutenfree.com/biz/milano-ie/6433693582491648</v>
       </c>
-      <c r="Q334">
+      <c r="Q334" t="str">
         <v>3</v>
-      </c>
-      <c r="R334" t="str">
-        <v>[2026-03-29 research] GF pizza, pasta, beer. Mixed cross-contam reviews.</v>
       </c>
     </row>
     <row r="335">
@@ -14083,11 +14014,8 @@
       <c r="P335" t="str">
         <v>https://www.findmeglutenfree.com/biz/bricin-restaurant-and-boxty-house/5988049035067392</v>
       </c>
-      <c r="Q335">
+      <c r="Q335" t="str">
         <v>4</v>
-      </c>
-      <c r="R335" t="str">
-        <v>[2026-03-29 research] GF menu, separate GF bread. Not dedicated facility.</v>
       </c>
     </row>
     <row r="336">
@@ -14136,11 +14064,11 @@
       <c r="P336" t="str">
         <v>https://www.findmeglutenfree.com/biz/cellar-one/6269495784505344</v>
       </c>
-      <c r="Q336">
+      <c r="Q336" t="str">
         <v>3</v>
       </c>
       <c r="R336" t="str">
-        <v>We ate at this restaurant twice on our trip and had a wonderful GF DF experience. Bart (who I believe is the manager) took special care of us both nights. We started with delicious GF DF bread, then had John Dory fish in a wonderful presentation with sides of potatoes, veggies and chips (made in a dedicated fryer). The atmosphere was also very nice here and there was a piano player. We truly enjoyed both meals here and would highly recommend this place. They were very helpful and the food was delicious.Bart and Connor were the best; [2026-03-29 research] GF DF bread, John Dory fish, dedicated fryer for chips. Weekend only.</v>
+        <v>We ate at this restaurant twice on our trip and had a wonderful GF DF experience. Bart (who I believe is the manager) took special care of us both nights. We started with delicious GF DF bread, then had John Dory fish in a wonderful presentation with sides of potatoes, veggies and chips (made in a dedicated fryer). The atmosphere was also very nice here and there was a piano player. We truly enjoyed both meals here and would highly recommend this place. They were very helpful and the food was delicious.Bart and Connor were the best</v>
       </c>
     </row>
     <row r="337">
@@ -14186,11 +14114,11 @@
       <c r="O337" t="str">
         <v>Almost all flavors (including brownie!) are gluten free. Staff is very knowledgable so just ask.</v>
       </c>
-      <c r="Q337">
+      <c r="Q337" t="str">
         <v>4</v>
       </c>
       <c r="R337" t="str">
-        <v>Almost all flavors (including brownie!) are gluten free. Staff is very knowledgable so just ask.; [2026-03-29 research] Almost all flavors GF including brownie. Staff very knowledgeable.</v>
+        <v>Almost all flavors (including brownie!) are gluten free. Staff is very knowledgable so just ask.</v>
       </c>
     </row>
     <row r="338">
@@ -14216,7 +14144,7 @@
         <v>2023</v>
       </c>
       <c r="I338" t="str">
-        <v>mixed safety</v>
+        <v>unclear</v>
       </c>
       <c r="J338" t="str">
         <v>52.0598714</v>
@@ -14232,12 +14160,6 @@
       </c>
       <c r="P338" t="str">
         <v>https://www.findmeglutenfree.com/biz/khao-asian-street-food/5143880251604992</v>
-      </c>
-      <c r="Q338">
-        <v>3</v>
-      </c>
-      <c r="R338" t="str">
-        <v>[2026-03-29 research] GF Pad Thai. Several dishes adaptable.</v>
       </c>
     </row>
     <row r="339">
@@ -14286,11 +14208,8 @@
       <c r="P339" t="str">
         <v>https://www.findmeglutenfree.com/biz/robs-ranch-house/4753133731840000</v>
       </c>
-      <c r="Q339">
-        <v>4</v>
-      </c>
-      <c r="R339" t="str">
-        <v>[2026-03-29 research] GF menu, dedicated fryers, GF beer.</v>
+      <c r="Q339" t="str">
+        <v>3</v>
       </c>
     </row>
     <row r="340">
@@ -14363,7 +14282,7 @@
         <v>2023</v>
       </c>
       <c r="I341" t="str">
-        <v>mixed safety</v>
+        <v>unclear</v>
       </c>
       <c r="J341" t="str">
         <v>52.0576419</v>
@@ -14379,12 +14298,6 @@
       </c>
       <c r="P341" t="str">
         <v>https://www.findmeglutenfree.com/biz/cafe-du-parc/5303789879427072</v>
-      </c>
-      <c r="Q341">
-        <v>3</v>
-      </c>
-      <c r="R341" t="str">
-        <v>[2026-03-29 research] Caters for GF dietary requirements.</v>
       </c>
     </row>
     <row r="342">
@@ -14430,11 +14343,8 @@
       <c r="P342" t="str">
         <v>https://www.findmeglutenfree.com/biz/luna-coffee-and-wine/6238737896177664</v>
       </c>
-      <c r="Q342">
-        <v>2</v>
-      </c>
       <c r="R342" t="str">
-        <v>Only had coffee (almond milk latte); [2026-03-29 research] Acai bowls available. Not dedicated GF.</v>
+        <v>Only had coffee (almond milk latte)</v>
       </c>
     </row>
     <row r="343">
@@ -14460,7 +14370,7 @@
         <v>2023</v>
       </c>
       <c r="I343" t="str">
-        <v>mixed safety</v>
+        <v>unclear</v>
       </c>
       <c r="J343" t="str">
         <v>52.0598849</v>
@@ -14473,12 +14383,6 @@
       </c>
       <c r="M343" t="str">
         <v>Killarney</v>
-      </c>
-      <c r="Q343">
-        <v>3</v>
-      </c>
-      <c r="R343" t="str">
-        <v>[2026-03-29 research] GF penne pasta, steak, hake fillet. No GF pizza/bread.</v>
       </c>
     </row>
     <row r="344">
@@ -35466,9 +35370,6 @@
       <c r="K813">
         <v>135.5036138</v>
       </c>
-      <c r="N813" t="str">
-        <v>add to map</v>
-      </c>
       <c r="R813" t="str">
         <v>felt like Japanese Vegas strip</v>
       </c>
@@ -35542,9 +35443,6 @@
       <c r="K815">
         <v>2.2988</v>
       </c>
-      <c r="N815" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O815" t="str">
         <v>100% GF Italian. Wood-fired GF pizza, pasta, gnocchi, tiramisu. Complimentary GF baguette bread service.</v>
       </c>
@@ -35586,9 +35484,6 @@
       <c r="K816">
         <v>2.2936</v>
       </c>
-      <c r="N816" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O816" t="str">
         <v>100% GF organic Italian. AFDIAG-certified. Pizza, pasta, gnocchi. Small restaurant, book ahead. 10 min from Eiffel Tower.</v>
       </c>
@@ -35630,9 +35525,6 @@
       <c r="K817">
         <v>2.3748</v>
       </c>
-      <c r="N817" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O817" t="str">
         <v>100% GF bakery. Mills own rice &amp; buckwheat flours. Almond croissants, focaccia, Paris-Brest. Multiple locations.</v>
       </c>
@@ -35674,9 +35566,6 @@
       <c r="K818">
         <v>2.3478</v>
       </c>
-      <c r="N818" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O818" t="str">
         <v>100% GF bakery founded by someone with celiac. 13+ locations. Croissants, pain au chocolat, baguette sandwiches.</v>
       </c>
@@ -35718,9 +35607,6 @@
       <c r="K819">
         <v>2.3213</v>
       </c>
-      <c r="N819" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O819" t="str">
         <v>100% GF cafe/bakery/grocery. 3 Paris locations. Croissants, macarons, baguettes, eclairs. Also sells GF grocery items.</v>
       </c>
@@ -35762,9 +35648,6 @@
       <c r="K820">
         <v>2.3289</v>
       </c>
-      <c r="N820" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O820" t="str">
         <v>100% GF Thai. Pad Thai, Tom Yam, curries, pho. Multiple locations incl Kapunka Vegan.</v>
       </c>
@@ -35806,9 +35689,6 @@
       <c r="K821">
         <v>2.3526</v>
       </c>
-      <c r="N821" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O821" t="str">
         <v>100% GF + 100% vegan. Dragon's Back curry, rice bowls. In Le Marais.</v>
       </c>
@@ -35850,9 +35730,6 @@
       <c r="K822">
         <v>2.3622</v>
       </c>
-      <c r="N822" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O822" t="str">
         <v>100% GF, vegan, no added sugar. Patisserie/tea house in Le Marais. Beautiful pastries and tarts.</v>
       </c>
@@ -35894,9 +35771,6 @@
       <c r="K823">
         <v>2.2987</v>
       </c>
-      <c r="N823" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O823" t="str">
         <v>Paris's first 100% GF patisserie (est. 2011). Now Saturday-only pop-up. Pre-order recommended.</v>
       </c>
@@ -35938,9 +35812,6 @@
       <c r="K824">
         <v>2.3076</v>
       </c>
-      <c r="N824" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O824" t="str">
         <v>Iconic macarons are naturally GF, baked in separate kitchen. Only macarons are celiac-safe; other pastries are not.</v>
       </c>
@@ -35982,9 +35853,6 @@
       <c r="K825">
         <v>2.287</v>
       </c>
-      <c r="N825" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O825" t="str">
         <v>3-star boutique in Le Marais. 18th-century Parisian décor.</v>
       </c>
@@ -36023,9 +35891,6 @@
       <c r="K826">
         <v>2.3025</v>
       </c>
-      <c r="N826" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O826" t="str">
         <v>5-star luxury near Eiffel Tower. Indoor pool, spa. Art Nouveau interiors.</v>
       </c>
@@ -36061,9 +35926,6 @@
       <c r="K827">
         <v>2.2945</v>
       </c>
-      <c r="N827" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O827" t="str">
         <v>330m iron lattice tower built for 1889 World's Fair. Sparkles every hour after dark.</v>
       </c>
@@ -36099,9 +35961,6 @@
       <c r="K828">
         <v>2.3499</v>
       </c>
-      <c r="N828" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O828" t="str">
         <v>French Gothic masterpiece, 12th century. Reopened Dec 2024 after 2019 fire restoration.</v>
       </c>
@@ -36137,9 +35996,6 @@
       <c r="K829">
         <v>2.295</v>
       </c>
-      <c r="N829" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O829" t="str">
         <v>Triumphal arch at western end of Champs-Élysées. Rooftop terrace with views. Tomb of Unknown Soldier beneath.</v>
       </c>
@@ -36172,9 +36028,6 @@
       <c r="K830">
         <v>2.3431</v>
       </c>
-      <c r="N830" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O830" t="str">
         <v>White-domed basilica at summit of Montmartre. Free entry. Best free panoramic views of Paris.</v>
       </c>
@@ -36207,9 +36060,6 @@
       <c r="K831">
         <v>2.3372</v>
       </c>
-      <c r="N831" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O831" t="str">
         <v>23-hectare formal garden with fountains, model boat pond, free Parisian chairs. Borders Saint-Germain and Latin Quarter.</v>
       </c>
@@ -36242,9 +36092,6 @@
       <c r="K832">
         <v>2.3274</v>
       </c>
-      <c r="N832" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O832" t="str">
         <v>Oldest public park in Paris (1564). Between Louvre and Place de la Concorde. UNESCO World Heritage.</v>
       </c>
@@ -36277,9 +36124,6 @@
       <c r="K833">
         <v>2.3134</v>
       </c>
-      <c r="N833" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O833" t="str">
         <v>Most ornate bridge in Paris. Art Nouveau lamp posts, gilded statues. Built for 1900 World's Fair. Great Eiffel Tower views.</v>
       </c>
@@ -36312,9 +36156,6 @@
       <c r="K834">
         <v>2.3654</v>
       </c>
-      <c r="N834" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O834" t="str">
         <v>Oldest planned square in Paris (1612). Victor Hugo's former home. Peaceful retreat in Le Marais.</v>
       </c>
@@ -36347,9 +36188,6 @@
       <c r="K835">
         <v>2.3376</v>
       </c>
-      <c r="N835" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O835" t="str">
         <v>World's largest museum. Mona Lisa, Venus de Milo. 32 EUR.</v>
       </c>
@@ -36382,9 +36220,6 @@
       <c r="K836">
         <v>2.3266</v>
       </c>
-      <c r="N836" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O836" t="str">
         <v>Impressionist art in former railway station. Monet, Renoir, Van Gogh. 16 EUR.</v>
       </c>
@@ -36417,9 +36252,6 @@
       <c r="K837">
         <v>2.1232</v>
       </c>
-      <c r="N837" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O837" t="str">
         <v>Opulent former royal residence. Hall of Mirrors. 800 hectares of gardens. RER C ~40 min.</v>
       </c>
@@ -36455,9 +36287,6 @@
       <c r="K838">
         <v>2.2895</v>
       </c>
-      <c r="N838" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O838" t="str">
         <v>1-hour sightseeing cruise passing major landmarks. From ~17 EUR. Sunset and dinner options.</v>
       </c>
@@ -36490,9 +36319,6 @@
       <c r="K839">
         <v>2.3449</v>
       </c>
-      <c r="N839" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O839" t="str">
         <v>13th-century Gothic chapel. 1,113 stained-glass windows. 13-19 EUR.</v>
       </c>
@@ -36525,9 +36351,6 @@
       <c r="K840">
         <v>2.3411</v>
       </c>
-      <c r="N840" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O840" t="str">
         <v>Cobblestone streets, artist studios, I Love You Wall, Moulin Rouge, Sacré-Cœur. From ~30 EUR.</v>
       </c>
@@ -36560,9 +36383,6 @@
       <c r="K841">
         <v>12.5066375</v>
       </c>
-      <c r="N841" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
@@ -36589,9 +36409,6 @@
       <c r="K842">
         <v>12.2518928</v>
       </c>
-      <c r="N842" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
@@ -36618,9 +36435,6 @@
       <c r="K843">
         <v>12.5308661</v>
       </c>
-      <c r="N843" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
@@ -36650,9 +36464,6 @@
       <c r="K844">
         <v>12.4922309</v>
       </c>
-      <c r="N844" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
@@ -36682,9 +36493,6 @@
       <c r="K845">
         <v>12.485325</v>
       </c>
-      <c r="N845" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="846">
       <c r="A846" t="str">
@@ -36714,9 +36522,6 @@
       <c r="K846">
         <v>12.4768729</v>
       </c>
-      <c r="N846" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="847">
       <c r="A847" t="str">
@@ -36746,9 +36551,6 @@
       <c r="K847">
         <v>12.483313</v>
       </c>
-      <c r="N847" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="848">
       <c r="A848" t="str">
@@ -36778,9 +36580,6 @@
       <c r="K848">
         <v>12.482775</v>
       </c>
-      <c r="N848" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="849">
       <c r="A849" t="str">
@@ -36810,9 +36609,6 @@
       <c r="K849">
         <v>12.4745405</v>
       </c>
-      <c r="N849" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="850">
       <c r="A850" t="str">
@@ -36842,9 +36638,6 @@
       <c r="K850">
         <v>12.4730742</v>
       </c>
-      <c r="N850" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="851">
       <c r="A851" t="str">
@@ -36874,9 +36667,6 @@
       <c r="K851">
         <v>12.505673</v>
       </c>
-      <c r="N851" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="852">
       <c r="A852" t="str">
@@ -36906,9 +36696,6 @@
       <c r="K852">
         <v>12.4806028</v>
       </c>
-      <c r="N852" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="853">
       <c r="A853" t="str">
@@ -36938,9 +36725,6 @@
       <c r="K853">
         <v>12.4536007</v>
       </c>
-      <c r="N853" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="854">
       <c r="A854" t="str">
@@ -36970,9 +36754,6 @@
       <c r="K854">
         <v>12.4539367</v>
       </c>
-      <c r="N854" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="855">
       <c r="A855" t="str">
@@ -37002,9 +36783,6 @@
       <c r="K855">
         <v>12.4544835</v>
       </c>
-      <c r="N855" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="856">
       <c r="A856" t="str">
@@ -37034,9 +36812,6 @@
       <c r="K856">
         <v>12.466276</v>
       </c>
-      <c r="N856" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O856" t="str">
         <v>10.50 euros to get in - reviews say not really worth it but cool panoramic views. Did not go here.</v>
       </c>
@@ -37069,9 +36844,6 @@
       <c r="K857">
         <v>12.454725</v>
       </c>
-      <c r="N857" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="858">
       <c r="A858" t="str">
@@ -37104,9 +36876,6 @@
       <c r="K858">
         <v>12.4705764</v>
       </c>
-      <c r="N858" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O858" t="str">
         <v>GF bruschetta, lobster noodles, eggplant parm. Was AMAZING and waiter was super nice. Also have other locations including GF street food near Vatican.</v>
       </c>
@@ -37145,9 +36914,6 @@
       <c r="K859">
         <v>12.4764863</v>
       </c>
-      <c r="N859" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O859" t="str">
         <v>GF bakery - May be hard to find, across via di torre argentina from the Shari Van playhouse</v>
       </c>
@@ -37183,9 +36949,6 @@
       <c r="K860">
         <v>12.4777718</v>
       </c>
-      <c r="N860" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O860" t="str">
         <v>GF pizza, pasta (including gnocchi), and desserts</v>
       </c>
@@ -37221,9 +36984,6 @@
       <c r="K861">
         <v>12.4729887</v>
       </c>
-      <c r="N861" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O861" t="str">
         <v>GF menu items/apps plus HH from 4-6pm</v>
       </c>
@@ -37262,9 +37022,6 @@
       <c r="K862">
         <v>12.473238</v>
       </c>
-      <c r="N862" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O862" t="str">
         <v>GF gelato and cones (chain)</v>
       </c>
@@ -37303,9 +37060,6 @@
       <c r="K863">
         <v>12.4590061</v>
       </c>
-      <c r="N863" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O863" t="str">
         <v>GF pizza</v>
       </c>
@@ -37341,9 +37095,6 @@
       <c r="K864">
         <v>12.4948523</v>
       </c>
-      <c r="N864" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O864" t="str">
         <v>Okay reviews - not sure if visited</v>
       </c>
@@ -37382,9 +37133,6 @@
       <c r="K865">
         <v>12.479819</v>
       </c>
-      <c r="N865" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O865" t="str">
         <v>Mary's recommendation - cool alley with juices, cantina, and restaurant with GF and vegan food</v>
       </c>
@@ -37420,9 +37168,6 @@
       <c r="K866">
         <v>-0.0803845</v>
       </c>
-      <c r="N866" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="867">
       <c r="A867" t="str">
@@ -37452,9 +37197,6 @@
       <c r="K867">
         <v>-0.1733879</v>
       </c>
-      <c r="N867" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="868">
       <c r="A868" t="str">
@@ -37487,9 +37229,6 @@
       <c r="K868">
         <v>-0.0835832</v>
       </c>
-      <c r="N868" t="str">
-        <v>add to map</v>
-      </c>
       <c r="P868" t="str">
         <v>https://www.findmeglutenfree.com/biz/los-mochis/5682303363317760</v>
       </c>
@@ -37528,9 +37267,6 @@
       <c r="K869">
         <v>-0.1971206</v>
       </c>
-      <c r="N869" t="str">
-        <v>add to map</v>
-      </c>
       <c r="P869" t="str">
         <v>https://www.findmeglutenfree.com/biz/los-mochis-restaurant/6076333531201536</v>
       </c>
@@ -37569,9 +37305,6 @@
       <c r="K870">
         <v>-0.1187016</v>
       </c>
-      <c r="N870" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O870" t="str">
         <v>Accredited by CoeliacUK.&lt;br&gt;Has a separate gf menus and proper process in place for ensure there is no cross contamination.</v>
       </c>
@@ -37616,9 +37349,6 @@
       <c r="K871">
         <v>-0.0766339</v>
       </c>
-      <c r="N871" t="str">
-        <v>add to map</v>
-      </c>
       <c r="P871" t="str">
         <v>https://www.findmeglutenfree.com/biz/wicked-fish/5779279859810304</v>
       </c>
@@ -37654,9 +37384,6 @@
       <c r="K872">
         <v>-0.1878318</v>
       </c>
-      <c r="N872" t="str">
-        <v>add to map</v>
-      </c>
       <c r="P872" t="str">
         <v>https://www.findmeglutenfree.com/biz/oatis/6698670654881792</v>
       </c>
@@ -37692,9 +37419,6 @@
       <c r="K873">
         <v>-0.0819975</v>
       </c>
-      <c r="N873" t="str">
-        <v>add to map</v>
-      </c>
       <c r="P873" t="str">
         <v>https://www.findmeglutenfree.com/biz/joe-and-the-juice/6031873342046208</v>
       </c>
@@ -37733,9 +37457,6 @@
       <c r="K874">
         <v>-0.0800697</v>
       </c>
-      <c r="N874" t="str">
-        <v>add to map</v>
-      </c>
       <c r="P874" t="str">
         <v>https://www.findmeglutenfree.com/biz/black-sheep-coffee/5037307943583744</v>
       </c>
@@ -37768,9 +37489,6 @@
       <c r="K875">
         <v>-0.1246254</v>
       </c>
-      <c r="N875" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="876">
       <c r="A876" t="str">
@@ -37800,9 +37518,6 @@
       <c r="K876">
         <v>-0.0753565</v>
       </c>
-      <c r="N876" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="877">
       <c r="A877" t="str">
@@ -37832,9 +37547,6 @@
       <c r="K877">
         <v>-0.0877321</v>
       </c>
-      <c r="N877" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="878">
       <c r="A878" t="str">
@@ -37864,9 +37576,6 @@
       <c r="K878">
         <v>-0.0762586</v>
       </c>
-      <c r="N878" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="879">
       <c r="A879" t="str">
@@ -37896,9 +37605,6 @@
       <c r="K879">
         <v>-0.133996</v>
       </c>
-      <c r="N879" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="880">
       <c r="A880" t="str">
@@ -37928,9 +37634,6 @@
       <c r="K880">
         <v>-0.187681</v>
       </c>
-      <c r="N880" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="881">
       <c r="A881" t="str">
@@ -37960,9 +37663,6 @@
       <c r="K881">
         <v>-0.14189</v>
       </c>
-      <c r="N881" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="882">
       <c r="A882" t="str">
@@ -37992,9 +37692,6 @@
       <c r="K882">
         <v>-0.135798</v>
       </c>
-      <c r="N882" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="883">
       <c r="A883" t="str">
@@ -38024,9 +37721,6 @@
       <c r="K883">
         <v>-0.1641135</v>
       </c>
-      <c r="N883" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="884">
       <c r="A884" t="str">
@@ -38056,9 +37750,6 @@
       <c r="K884">
         <v>-0.0865</v>
       </c>
-      <c r="N884" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="885">
       <c r="A885" t="str">
@@ -38088,9 +37779,6 @@
       <c r="K885">
         <v>-0.1195192</v>
       </c>
-      <c r="N885" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="886">
       <c r="A886" t="str">
@@ -38120,9 +37808,6 @@
       <c r="K886">
         <v>-0.0164597</v>
       </c>
-      <c r="N886" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="887">
       <c r="A887" t="str">
@@ -38152,9 +37837,6 @@
       <c r="K887">
         <v>-0.1909471</v>
       </c>
-      <c r="N887" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="888">
       <c r="A888" t="str">
@@ -38184,9 +37866,6 @@
       <c r="K888">
         <v>-0.0760688</v>
       </c>
-      <c r="N888" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="889">
       <c r="A889" t="str">
@@ -38216,9 +37895,6 @@
       <c r="K889">
         <v>-0.0904808</v>
       </c>
-      <c r="N889" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="890">
       <c r="A890" t="str">
@@ -38248,9 +37924,6 @@
       <c r="K890">
         <v>-0.2055232</v>
       </c>
-      <c r="N890" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="891">
       <c r="A891" t="str">
@@ -38280,9 +37953,6 @@
       <c r="K891">
         <v>-0.4550471</v>
       </c>
-      <c r="N891" t="str">
-        <v>add to map</v>
-      </c>
     </row>
     <row r="892">
       <c r="A892" t="str">
@@ -38315,9 +37985,6 @@
       <c r="K892">
         <v>12.4601</v>
       </c>
-      <c r="N892" t="str">
-        <v>add to map</v>
-      </c>
       <c r="O892" t="str">
         <v>GF street food near Vatican at Borgo Pio 28. Part of Mama Eat chain. AIC certified, dual kitchens.</v>
       </c>
@@ -41099,542 +40766,566 @@
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B956" t="str">
-        <v>Stockholm</v>
+        <v>Negombo</v>
       </c>
       <c r="C956" t="str">
-        <v>Scandic Upplandsgatan</v>
+        <v>Colombo International Airport Ratmalana</v>
       </c>
       <c r="D956" t="str">
-        <v>hotel</v>
+        <v>transit</v>
       </c>
       <c r="E956">
         <v>1</v>
       </c>
       <c r="G956" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H956">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J956">
-        <v>59.3364</v>
+        <v>6.821049</v>
       </c>
       <c r="K956">
-        <v>18.055024</v>
-      </c>
-      <c r="N956" t="str">
-        <v>add to map</v>
+        <v>79.88862</v>
+      </c>
+      <c r="L956" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O956" t="str">
-        <v>Hotel in central Stockholm</v>
+        <v/>
       </c>
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B957" t="str">
-        <v>Stockholm</v>
+        <v>Negombo</v>
       </c>
       <c r="C957" t="str">
-        <v>La Neta Bar</v>
+        <v>Spicepeek Boutique Hotel CMB Airport</v>
       </c>
       <c r="D957" t="str">
-        <v>restaurant</v>
+        <v>hotel</v>
       </c>
       <c r="E957">
         <v>1</v>
       </c>
       <c r="G957" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H957">
-        <v>2019</v>
-      </c>
-      <c r="I957" t="str">
-        <v>celiac-aware</v>
+        <v>2026</v>
       </c>
       <c r="J957">
-        <v>59.333604</v>
+        <v>7.142758</v>
       </c>
       <c r="K957">
-        <v>18.070746</v>
-      </c>
-      <c r="N957" t="str">
-        <v>add to map</v>
+        <v>79.872138</v>
+      </c>
+      <c r="L957" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O957" t="str">
-        <v>GF authentic Mexican corn tortillas for tacos &amp; GF beer</v>
+        <v>Limited GF/pescatarian dinner options, but able to make me a GF english breakfast in the morning (no bread)</v>
       </c>
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B958" t="str">
-        <v>Stockholm</v>
+        <v>Negombo</v>
       </c>
       <c r="C958" t="str">
-        <v>Älskade Traditioner</v>
+        <v>Lords Restaurant Complex</v>
       </c>
       <c r="D958" t="str">
-        <v>cafe</v>
+        <v>restaurant</v>
       </c>
       <c r="E958">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G958" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H958">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="I958" t="str">
-        <v>celiac-aware</v>
+        <v>mixed safety</v>
       </c>
       <c r="J958">
-        <v>59.311041</v>
+        <v>7.241358</v>
       </c>
       <c r="K958">
-        <v>18.081437</v>
-      </c>
-      <c r="N958" t="str">
-        <v>add to map</v>
+        <v>79.842078</v>
+      </c>
+      <c r="L958" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O958" t="str">
-        <v>AMAZING gluten free waffles</v>
+        <v>Didn't get to eat here but looks like it has GF options and is fun!</v>
+      </c>
+      <c r="P958" t="str">
+        <v>https://www.findmeglutenfree.com/biz/lords-restaurant/6001387190747136</v>
+      </c>
+      <c r="Q958">
+        <v>3</v>
       </c>
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B959" t="str">
-        <v>Stockholm</v>
+        <v>Negombo</v>
       </c>
       <c r="C959" t="str">
-        <v>Happy Atelier</v>
+        <v>Zen Cafe</v>
       </c>
       <c r="D959" t="str">
-        <v>bakery</v>
+        <v>restaurant</v>
       </c>
       <c r="E959">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G959" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H959">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="I959" t="str">
-        <v>100% dedicated GF</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J959">
-        <v>59.329489</v>
+        <v>7.228816</v>
       </c>
       <c r="K959">
-        <v>18.03895</v>
-      </c>
-      <c r="N959" t="str">
-        <v>add to map</v>
+        <v>79.841015</v>
+      </c>
+      <c r="L959" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O959" t="str">
-        <v>Dedicated GF bakery - so awesome and the lady working there was so kind</v>
+        <v>Did not get a chance to eat here</v>
+      </c>
+      <c r="P959" t="str">
+        <v>https://www.findmeglutenfree.com/biz/zen-cafe/5307625374089216</v>
+      </c>
+      <c r="Q959">
+        <v>3</v>
       </c>
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B960" t="str">
-        <v>Stockholm</v>
+        <v>Negombo</v>
       </c>
       <c r="C960" t="str">
-        <v>Hattori Sushi Devil</v>
+        <v>YAAGA - BACKYARD DINING</v>
       </c>
       <c r="D960" t="str">
         <v>restaurant</v>
       </c>
       <c r="E960">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G960" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H960">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="I960" t="str">
-        <v>unclear</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J960">
-        <v>59.338571</v>
+        <v>7.240864</v>
       </c>
       <c r="K960">
-        <v>18.05658</v>
-      </c>
-      <c r="N960" t="str">
-        <v>add to map</v>
+        <v>79.84249</v>
+      </c>
+      <c r="L960" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O960" t="str">
-        <v/>
+        <v>Did not get a chance to eat here - Supposedly very celiac friendly</v>
+      </c>
+      <c r="P960" t="str">
+        <v>https://www.findmeglutenfree.com/biz/yaaga/4880134834618368</v>
+      </c>
+      <c r="Q960">
+        <v>3</v>
       </c>
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B961" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C961" t="str">
-        <v>Hemma Vasastan</v>
+        <v>Madulkelle Tea and Eco Lodge</v>
       </c>
       <c r="D961" t="str">
-        <v>restaurant</v>
+        <v>hotel</v>
       </c>
       <c r="E961">
         <v>1</v>
       </c>
       <c r="G961" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H961">
-        <v>2019</v>
-      </c>
-      <c r="I961" t="str">
-        <v>celiac-aware</v>
+        <v>2026</v>
       </c>
       <c r="J961">
-        <v>59.339585</v>
+        <v>7.392923</v>
       </c>
       <c r="K961">
-        <v>18.047905</v>
-      </c>
-      <c r="N961" t="str">
-        <v>add to map</v>
+        <v>80.7239</v>
+      </c>
+      <c r="L961" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O961" t="str">
-        <v>Asparagus risotto, GF bread, goat cheese salad</v>
+        <v>Nice place but not worth it if you're only staying a night or two as it's about an hour and a half drive out of the way of everything else on challenging roads. Says they accommodate all food allergies and preferences but I had a really, really hard time with Celiac/gluten free options and the staff understanding.</v>
       </c>
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B962" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C962" t="str">
-        <v>Joe &amp; The Juice</v>
+        <v>Grand Serendib Hotel</v>
       </c>
       <c r="D962" t="str">
-        <v>cafe</v>
+        <v>hotel</v>
       </c>
       <c r="E962">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G962" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H962">
-        <v>2019</v>
-      </c>
-      <c r="I962" t="str">
-        <v>celiac-aware</v>
+        <v>2026</v>
       </c>
       <c r="J962">
-        <v>59.307477</v>
+        <v>7.28542</v>
       </c>
       <c r="K962">
-        <v>18.076076</v>
-      </c>
-      <c r="N962" t="str">
-        <v>add to map</v>
+        <v>80.644488</v>
+      </c>
+      <c r="L962" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O962" t="str">
-        <v>GF paninis</v>
+        <v>Did not stay but looked like a good option</v>
       </c>
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B963" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C963" t="str">
-        <v>The Royal Palace</v>
+        <v>Ru Boutique</v>
       </c>
       <c r="D963" t="str">
-        <v>landmark</v>
+        <v>hotel</v>
       </c>
       <c r="E963">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G963" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H963">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J963">
-        <v>59.326822</v>
+        <v>7.288744</v>
       </c>
       <c r="K963">
-        <v>18.071719</v>
-      </c>
-      <c r="N963" t="str">
-        <v>add to map</v>
+        <v>80.644715</v>
+      </c>
+      <c r="L963" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O963" t="str">
-        <v>Cost: 160 SEK (~$16). Open 10am-5pm. Changing of the guards at 12:15pm weekdays</v>
+        <v>Did not stay but looked like a good option</v>
       </c>
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B964" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C964" t="str">
-        <v>Nobel Prize Museum</v>
+        <v>Sri Dalada Maligawa</v>
       </c>
       <c r="D964" t="str">
-        <v>museum</v>
+        <v>landmark</v>
       </c>
       <c r="E964">
         <v>1</v>
       </c>
       <c r="G964" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H964">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J964">
-        <v>59.325331</v>
+        <v>7.293609</v>
       </c>
       <c r="K964">
-        <v>18.070824</v>
-      </c>
-      <c r="N964" t="str">
-        <v>add to map</v>
+        <v>80.641325</v>
+      </c>
+      <c r="L964" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O964" t="str">
-        <v/>
+        <v>Sacred temple of the tooth relic</v>
       </c>
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B965" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C965" t="str">
-        <v>Gamla Stan</v>
+        <v>Municipal Central Market - Kandy</v>
       </c>
       <c r="D965" t="str">
         <v>landmark</v>
       </c>
       <c r="E965">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G965" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H965">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J965">
-        <v>59.325698</v>
+        <v>7.292147</v>
       </c>
       <c r="K965">
-        <v>18.071879</v>
-      </c>
-      <c r="N965" t="str">
-        <v>add to map</v>
+        <v>80.63451</v>
+      </c>
+      <c r="L965" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O965" t="str">
-        <v>Old Stockholm - historic old town</v>
+        <v>Did not go - it was too hot and it was a Saturday so too crowded (locals preparing for national holiday)</v>
       </c>
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B966" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C966" t="str">
-        <v>Stockholm City Hall</v>
+        <v>New Giragama Tea factory &amp; Restaurant</v>
       </c>
       <c r="D966" t="str">
-        <v>landmark</v>
+        <v>activity</v>
       </c>
       <c r="E966">
         <v>1</v>
       </c>
       <c r="G966" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H966">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J966">
-        <v>59.327451</v>
+        <v>7.26988</v>
       </c>
       <c r="K966">
-        <v>18.054346</v>
-      </c>
-      <c r="N966" t="str">
-        <v>add to map</v>
+        <v>80.548142</v>
+      </c>
+      <c r="L966" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O966" t="str">
-        <v>Tours ~50 min, 10am-3pm. More frequent June-August. Cannot book in advance unless group travel</v>
+        <v/>
       </c>
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B967" t="str">
-        <v>Stockholm</v>
+        <v>Kandy</v>
       </c>
       <c r="C967" t="str">
-        <v>Stockholm Arlanda Airport</v>
+        <v>Sri Maha Bodhi Viharaya</v>
       </c>
       <c r="D967" t="str">
-        <v>airport</v>
+        <v>landmark</v>
       </c>
       <c r="E967">
         <v>1</v>
       </c>
       <c r="G967" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H967">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J967">
-        <v>59.649762</v>
+        <v>7.2956303</v>
       </c>
       <c r="K967">
-        <v>17.923781</v>
-      </c>
-      <c r="N967" t="str">
-        <v>add to map</v>
+        <v>80.6309363</v>
+      </c>
+      <c r="L967" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O967" t="str">
-        <v/>
+        <v>Giant buddha statue - very cool place. Need to cover knees and shoulders like other temples. Free entry - just asks for donations. A lot quieter and less crowded than the tooth relic.</v>
       </c>
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B968" t="str">
-        <v>Uppsala</v>
+        <v>Kandy</v>
       </c>
       <c r="C968" t="str">
-        <v>Uppsala Castle</v>
+        <v>Balaji Dosai</v>
       </c>
       <c r="D968" t="str">
-        <v>landmark</v>
+        <v>restaurant</v>
       </c>
       <c r="E968">
         <v>1</v>
       </c>
       <c r="G968" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H968">
-        <v>2019</v>
+        <v>2026</v>
+      </c>
+      <c r="I968" t="str">
+        <v>celiac-aware</v>
       </c>
       <c r="J968">
-        <v>59.853262</v>
+        <v>7.293728</v>
       </c>
       <c r="K968">
-        <v>17.635616</v>
-      </c>
-      <c r="N968" t="str">
-        <v>add to map</v>
+        <v>80.638326</v>
+      </c>
+      <c r="L968" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O968" t="str">
-        <v/>
+        <v>GF dosas - cheese dosa was SO good! And MASSIVE!</v>
+      </c>
+      <c r="P968" t="str">
+        <v>https://www.findmeglutenfree.com/biz/balaji-dosai/5441458781945856</v>
+      </c>
+      <c r="Q968">
+        <v>4</v>
       </c>
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B969" t="str">
-        <v>Uppsala</v>
+        <v>Kandy</v>
       </c>
       <c r="C969" t="str">
-        <v>Uppsala Cathedral</v>
+        <v>Soul Food</v>
       </c>
       <c r="D969" t="str">
-        <v>landmark</v>
+        <v>restaurant</v>
       </c>
       <c r="E969">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G969" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H969">
-        <v>2019</v>
+        <v>2026</v>
+      </c>
+      <c r="I969" t="str">
+        <v>mixed safety</v>
       </c>
       <c r="J969">
-        <v>59.858109</v>
+        <v>7.292551</v>
       </c>
       <c r="K969">
-        <v>17.633645</v>
-      </c>
-      <c r="N969" t="str">
-        <v>add to map</v>
+        <v>80.636053</v>
+      </c>
+      <c r="L969" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O969" t="str">
-        <v/>
+        <v>Did not get a chance to eat here</v>
+      </c>
+      <c r="Q969">
+        <v>2</v>
       </c>
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B970" t="str">
-        <v>Uppsala</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C970" t="str">
-        <v>Uppsala University</v>
+        <v>Hotel Sigiriya</v>
       </c>
       <c r="D970" t="str">
-        <v>landmark</v>
+        <v>hotel</v>
       </c>
       <c r="E970">
         <v>1</v>
       </c>
       <c r="G970" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H970">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J970">
-        <v>59.8509</v>
+        <v>7.950094</v>
       </c>
       <c r="K970">
-        <v>17.630009</v>
-      </c>
-      <c r="N970" t="str">
-        <v>add to map</v>
+        <v>80.763068</v>
+      </c>
+      <c r="L970" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O970" t="str">
         <v/>
@@ -41642,34 +41333,34 @@
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B971" t="str">
-        <v>Uppsala</v>
+        <v>Kandy</v>
       </c>
       <c r="C971" t="str">
-        <v>Botanical Garden</v>
+        <v>Kandy Myst by Cinnamon</v>
       </c>
       <c r="D971" t="str">
-        <v>landmark</v>
+        <v>hotel</v>
       </c>
       <c r="E971">
         <v>1</v>
       </c>
       <c r="G971" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H971">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J971">
-        <v>59.850573</v>
+        <v>7.314324</v>
       </c>
       <c r="K971">
-        <v>17.628953</v>
-      </c>
-      <c r="N971" t="str">
-        <v>add to map</v>
+        <v>80.63025</v>
+      </c>
+      <c r="L971" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O971" t="str">
         <v/>
@@ -41677,13 +41368,13 @@
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B972" t="str">
-        <v>Uppsala</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C972" t="str">
-        <v>Svartbäcksgatan</v>
+        <v>Pidurangala Rock</v>
       </c>
       <c r="D972" t="str">
         <v>landmark</v>
@@ -41692,89 +41383,89 @@
         <v>1</v>
       </c>
       <c r="G972" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H972">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J972">
-        <v>59.869292</v>
+        <v>7.966389</v>
       </c>
       <c r="K972">
-        <v>17.628217</v>
-      </c>
-      <c r="N972" t="str">
-        <v>add to map</v>
+        <v>80.761838</v>
+      </c>
+      <c r="L972" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O972" t="str">
-        <v>Main shopping street, pedestrian street running parallel to river</v>
+        <v/>
       </c>
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B973" t="str">
-        <v>Uppsala</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C973" t="str">
-        <v>Saluhallen</v>
+        <v>Sigiriya Lion Rock</v>
       </c>
       <c r="D973" t="str">
-        <v>market</v>
+        <v>landmark</v>
       </c>
       <c r="E973">
         <v>1</v>
       </c>
       <c r="G973" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H973">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J973">
-        <v>59.859146</v>
+        <v>7.957113</v>
       </c>
       <c r="K973">
-        <v>17.633404</v>
-      </c>
-      <c r="N973" t="str">
-        <v>add to map</v>
+        <v>80.760257</v>
+      </c>
+      <c r="L973" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O973" t="str">
-        <v>Food Market Hall with assortment of restaurants. Opens 10am Mon-Sat</v>
+        <v/>
       </c>
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>Sweden</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B974" t="str">
-        <v>Uppsala</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C974" t="str">
-        <v>Uppsala Central Station</v>
+        <v>Lion's Paw</v>
       </c>
       <c r="D974" t="str">
-        <v>transit</v>
+        <v>landmark</v>
       </c>
       <c r="E974">
         <v>1</v>
       </c>
       <c r="G974" t="str">
-        <v>September</v>
+        <v>April</v>
       </c>
       <c r="H974">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="J974">
-        <v>59.858198</v>
+        <v>7.957666</v>
       </c>
       <c r="K974">
-        <v>17.646542</v>
-      </c>
-      <c r="N974" t="str">
-        <v>add to map</v>
+        <v>80.760139</v>
+      </c>
+      <c r="L974" t="str">
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O974" t="str">
         <v/>
@@ -41782,25 +41473,34 @@
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B975" t="str">
-        <v>Helsinki</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C975" t="str">
-        <v>Helsinki Airport (HEL)</v>
+        <v>සෙල්ලිපි සහිත ලෙන / Caves with Inscriptions</v>
       </c>
       <c r="D975" t="str">
-        <v>transit</v>
+        <v>landmark</v>
+      </c>
+      <c r="E975">
+        <v>1</v>
+      </c>
+      <c r="G975" t="str">
+        <v>April</v>
+      </c>
+      <c r="H975">
+        <v>2026</v>
       </c>
       <c r="J975">
-        <v>60.3185535</v>
+        <v>7.957818</v>
       </c>
       <c r="K975">
-        <v>24.9680065</v>
+        <v>80.757796</v>
       </c>
       <c r="L975" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O975" t="str">
         <v/>
@@ -41808,3110 +41508,462 @@
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B976" t="str">
-        <v>Helsinki</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C976" t="str">
-        <v>Scandic Park Helsinki</v>
+        <v>Preaching Rock | Sigiriya</v>
       </c>
       <c r="D976" t="str">
-        <v>hotel</v>
+        <v>landmark</v>
+      </c>
+      <c r="E976">
+        <v>1</v>
+      </c>
+      <c r="G976" t="str">
+        <v>April</v>
+      </c>
+      <c r="H976">
+        <v>2026</v>
       </c>
       <c r="J976">
-        <v>60.1791227</v>
+        <v>7.958186</v>
       </c>
       <c r="K976">
-        <v>24.9276382</v>
+        <v>80.758568</v>
       </c>
       <c r="L976" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O976" t="str">
-        <v>Amenities: Private health club open Thurs from 6:30am – 10pm and Fri from 6:30am – 9pm, indoor pool &amp; sauna, breakfast</v>
-      </c>
-      <c r="S976" t="str">
-        <v>https://www.hotels.com/ho106261/scandic-park-helsinki-helsinki-finland/</v>
-      </c>
-      <c r="U976" t="str">
-        <v>Central location, breakfast buffet with GF options</v>
+        <v/>
       </c>
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B977" t="str">
-        <v>Helsinki</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C977" t="str">
-        <v>Naughty BRGR Lönkka</v>
+        <v>Dambulla Cave Temple</v>
       </c>
       <c r="D977" t="str">
-        <v>restaurant</v>
+        <v>landmark</v>
+      </c>
+      <c r="E977">
+        <v>1</v>
+      </c>
+      <c r="G977" t="str">
+        <v>April</v>
+      </c>
+      <c r="H977">
+        <v>2026</v>
       </c>
       <c r="J977">
-        <v>60.1657767</v>
+        <v>7.854914</v>
       </c>
       <c r="K977">
-        <v>24.9365297</v>
+        <v>80.65057</v>
       </c>
       <c r="L977" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O977" t="str">
-        <v>GF, vegan buns &amp; beyond burger - was very good!</v>
-      </c>
-      <c r="R977" t="str">
-        <v>[2026-03-29] Verified CLOSED</v>
+        <v/>
       </c>
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B978" t="str">
-        <v>Helsinki</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C978" t="str">
-        <v>Ristorante Pizzeria Dennis Bulevardi</v>
+        <v>Deraniyagala Cave</v>
       </c>
       <c r="D978" t="str">
-        <v>restaurant</v>
+        <v>landmark</v>
+      </c>
+      <c r="E978">
+        <v>0</v>
+      </c>
+      <c r="G978" t="str">
+        <v>April</v>
+      </c>
+      <c r="H978">
+        <v>2026</v>
       </c>
       <c r="J978">
-        <v>60.1632554</v>
+        <v>7.956824</v>
       </c>
       <c r="K978">
-        <v>24.9343197</v>
+        <v>80.758479</v>
       </c>
       <c r="L978" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O978" t="str">
-        <v/>
-      </c>
-      <c r="R978" t="str">
-        <v>[2026-03-29] Verified CLOSED</v>
+        <v>Didn't go here</v>
       </c>
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B979" t="str">
-        <v>Helsinki</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C979" t="str">
-        <v>Keliapuoti Leena Raitisto</v>
+        <v>cappuccino bistro.</v>
       </c>
       <c r="D979" t="str">
         <v>restaurant</v>
       </c>
+      <c r="E979">
+        <v>0</v>
+      </c>
+      <c r="G979" t="str">
+        <v>April</v>
+      </c>
+      <c r="H979">
+        <v>2026</v>
+      </c>
       <c r="I979" t="str">
-        <v>100% dedicated GF</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J979">
-        <v>60.1790863</v>
+        <v>7.968207</v>
       </c>
       <c r="K979">
-        <v>24.951616</v>
+        <v>80.768827</v>
       </c>
       <c r="L979" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O979" t="str">
-        <v>Kelia Puoti – GF bakery</v>
+        <v>Did not get a chance to eat here</v>
       </c>
       <c r="P979" t="str">
-        <v>https://www.findmeglutenfree.com/biz/keliapuoti-leena-raitisto/4727054790688768</v>
+        <v>https://www.findmeglutenfree.com/biz/cappuccino-bistro/4590155091017728</v>
       </c>
       <c r="Q979">
-        <v>5</v>
-      </c>
-      <c r="R979" t="str">
-        <v>[2026-03-29 research] Dedicated GF bakery in Hakaniemi Market Hall. Fresh breads, pastries, Karelian pies, cinnamon buns.</v>
+        <v>3</v>
       </c>
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B980" t="str">
-        <v>Helsinki</v>
+        <v>Sigiriya</v>
       </c>
       <c r="C980" t="str">
-        <v>Kappeli</v>
+        <v>Sundaras Jungle Restaurant &amp; Pool BAR</v>
       </c>
       <c r="D980" t="str">
         <v>restaurant</v>
       </c>
+      <c r="E980">
+        <v>1</v>
+      </c>
+      <c r="G980" t="str">
+        <v>April</v>
+      </c>
+      <c r="H980">
+        <v>2026</v>
+      </c>
       <c r="I980" t="str">
         <v>celiac-aware</v>
       </c>
       <c r="J980">
-        <v>60.167386</v>
+        <v>7.849318</v>
       </c>
       <c r="K980">
-        <v>24.950323</v>
+        <v>80.65257</v>
       </c>
       <c r="L980" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O980" t="str">
-        <v>Kappeli – has GF marked and prawn risotto (hard to get a table) - was AMAZING! the waiter was awesome, dessert was awesome - met some ladies from wisconsin.</v>
+        <v>Had several GF options - waitress was fairly knowledgable, though I'd be careful with cross-contamination if you order fried food. I did not. Great location close to Dambulla Cave and very friendly staff.</v>
       </c>
       <c r="P980" t="str">
-        <v>https://www.findmeglutenfree.com/biz/kappeli/6137394541232128</v>
+        <v>https://www.findmeglutenfree.com/biz/sundaras/6255627172708352</v>
       </c>
       <c r="Q980">
         <v>4</v>
       </c>
-      <c r="R980" t="str">
-        <v>[2026-03-29 research] GF items marked on menu. Complimentary GF bread. Prawn risotto recommended.</v>
-      </c>
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B981" t="str">
-        <v>Helsinki</v>
+        <v>Kandy</v>
       </c>
       <c r="C981" t="str">
-        <v>Cafe Regatta</v>
+        <v>Hideout Lounge</v>
       </c>
       <c r="D981" t="str">
         <v>restaurant</v>
       </c>
+      <c r="E981">
+        <v>0</v>
+      </c>
+      <c r="G981" t="str">
+        <v>April</v>
+      </c>
+      <c r="H981">
+        <v>2026</v>
+      </c>
       <c r="I981" t="str">
         <v>mixed safety</v>
       </c>
       <c r="J981">
-        <v>60.1801388</v>
+        <v>7.287376</v>
       </c>
       <c r="K981">
-        <v>24.9118115</v>
+        <v>80.646557</v>
       </c>
       <c r="L981" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O981" t="str">
-        <v/>
+        <v>GF options but seems limited based on FMGF reviews - Did not get a chance to eat here</v>
       </c>
       <c r="P981" t="str">
-        <v>https://www.findmeglutenfree.com/biz/regatta/6025606266486784</v>
+        <v>https://www.findmeglutenfree.com/biz/hideout/5422249909288960</v>
       </c>
       <c r="Q981">
         <v>2</v>
       </c>
-      <c r="R981" t="str">
-        <v>[2026-03-29 research] GF options on menu but cross-contamination risk. Not dedicated facility.</v>
-      </c>
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>Finland</v>
+        <v>Sri Lanka</v>
       </c>
       <c r="B982" t="str">
-        <v>Helsinki</v>
+        <v>Kandy</v>
       </c>
       <c r="C982" t="str">
-        <v>Temppeliaukion Church</v>
+        <v>Theva Cuisine</v>
       </c>
       <c r="D982" t="str">
-        <v>landmark</v>
+        <v>restaurant</v>
+      </c>
+      <c r="E982">
+        <v>0</v>
+      </c>
+      <c r="G982" t="str">
+        <v>April</v>
+      </c>
+      <c r="H982">
+        <v>2026</v>
+      </c>
+      <c r="I982" t="str">
+        <v>mixed safety</v>
       </c>
       <c r="J982">
-        <v>60.172995</v>
+        <v>7.276104</v>
       </c>
       <c r="K982">
-        <v>24.925234</v>
+        <v>80.635605</v>
       </c>
       <c r="L982" t="str">
-        <v>Finland (September 2019)</v>
+        <v>Sri Lanka (April 2026)</v>
       </c>
       <c r="O982" t="str">
-        <v>was super cool - Partly underground w/ circular skylight</v>
+        <v>Did not get a chance to eat here</v>
+      </c>
+      <c r="Q982">
+        <v>2</v>
       </c>
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>Finland</v>
+        <v>Germany</v>
       </c>
       <c r="B983" t="str">
-        <v>Helsinki</v>
+        <v>Dusseldorf</v>
       </c>
       <c r="C983" t="str">
-        <v>Kamppi Chapel</v>
+        <v>Ruthis Café &amp; Bistro</v>
       </c>
       <c r="D983" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J983">
-        <v>60.1694692</v>
-      </c>
-      <c r="K983">
-        <v>24.9359728</v>
-      </c>
-      <c r="L983" t="str">
-        <v>Finland (September 2019)</v>
+        <v>restaurant</v>
+      </c>
+      <c r="E983">
+        <v>0</v>
+      </c>
+      <c r="G983" t="str">
+        <v>December</v>
+      </c>
+      <c r="H983">
+        <v>2022</v>
+      </c>
+      <c r="I983" t="str">
+        <v>100% dedicated GF</v>
       </c>
       <c r="O983" t="str">
+        <v>100% gluten-free bistro/café, specifically designed for celiacs. Urdenbacher Allee 3, near Schloss Benrath.</v>
+      </c>
+      <c r="P983" t="str">
         <v/>
       </c>
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>Finland</v>
+        <v>Germany</v>
       </c>
       <c r="B984" t="str">
-        <v>Helsinki</v>
+        <v>Dusseldorf</v>
       </c>
       <c r="C984" t="str">
-        <v>Suomenlinna - The Fortress of Finland</v>
+        <v>Backbrüder – Glutenfreie Bio-Bäckerei</v>
       </c>
       <c r="D984" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J984">
-        <v>60.1446643</v>
-      </c>
-      <c r="K984">
-        <v>24.9827935</v>
-      </c>
-      <c r="L984" t="str">
-        <v>Finland (September 2019)</v>
+        <v>restaurant</v>
+      </c>
+      <c r="E984">
+        <v>0</v>
+      </c>
+      <c r="G984" t="str">
+        <v>December</v>
+      </c>
+      <c r="H984">
+        <v>2022</v>
+      </c>
+      <c r="I984" t="str">
+        <v>100% dedicated GF</v>
       </c>
       <c r="O984" t="str">
-        <v>• 1 of the biggest sea fortresses in the world&lt;br&gt;• UNESCO world heritage site&lt;br&gt;• Ferry runs year round and takes about 15 min</v>
+        <v>Dedicated GF organic bakery. Breads, rolls, croissants, pastries, cakes, cookies, granola.</v>
       </c>
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>Finland</v>
+        <v>Germany</v>
       </c>
       <c r="B985" t="str">
-        <v>Helsinki</v>
+        <v>Dusseldorf</v>
       </c>
       <c r="C985" t="str">
-        <v>Hakaniemi Market Hall</v>
+        <v>Da Noi</v>
       </c>
       <c r="D985" t="str">
         <v>restaurant</v>
       </c>
-      <c r="J985">
-        <v>60.1791379</v>
-      </c>
-      <c r="K985">
-        <v>24.9517059</v>
-      </c>
-      <c r="L985" t="str">
-        <v>Finland (September 2019)</v>
+      <c r="E985">
+        <v>0</v>
+      </c>
+      <c r="G985" t="str">
+        <v>December</v>
+      </c>
+      <c r="H985">
+        <v>2022</v>
+      </c>
+      <c r="I985" t="str">
+        <v>celiac-aware</v>
       </c>
       <c r="O985" t="str">
-        <v>Bi-level red-brick market since 1914, with seafood, produce &amp; other foods, plus crafts &amp; souvenirs.</v>
+        <v>Italian pizzeria with dedicated GF pizza prep area. 30+ pizza varieties available GF. Small upcharge for GF.</v>
       </c>
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>Finland</v>
+        <v>Germany</v>
       </c>
       <c r="B986" t="str">
-        <v>Helsinki</v>
+        <v>Dusseldorf</v>
       </c>
       <c r="C986" t="str">
-        <v>Nuuksio Reindeer Park</v>
+        <v>Bistro Erminig</v>
       </c>
       <c r="D986" t="str">
-        <v>activity</v>
-      </c>
-      <c r="J986">
-        <v>60.3042923</v>
-      </c>
-      <c r="K986">
-        <v>24.5515684</v>
-      </c>
-      <c r="L986" t="str">
-        <v>Finland (September 2019)</v>
+        <v>restaurant</v>
+      </c>
+      <c r="E986">
+        <v>0</v>
+      </c>
+      <c r="G986" t="str">
+        <v>December</v>
+      </c>
+      <c r="H986">
+        <v>2022</v>
+      </c>
+      <c r="I986" t="str">
+        <v>celiac-aware</v>
       </c>
       <c r="O986" t="str">
-        <v>ONLY OPEN ON SATURDAYS IN OCTOBER ☹&lt;br&gt;• 47 mins from hotel by public transport</v>
-      </c>
-      <c r="S986" t="str">
-        <v>https://www.getyourguide.com/helsinki-l13/helsinki-nuuksio-reindeer-park-tour-t269027/</v>
+        <v>French crêperie in Altstadt. GF galettes made with buckwheat flour (naturally GF).</v>
       </c>
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>Finland</v>
+        <v>Germany</v>
       </c>
       <c r="B987" t="str">
-        <v>Helsinki</v>
+        <v>Dusseldorf</v>
       </c>
       <c r="C987" t="str">
-        <v>SkyWheel Helsinki</v>
+        <v>Casita Mexicana</v>
       </c>
       <c r="D987" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J987">
-        <v>60.166788</v>
-      </c>
-      <c r="K987">
-        <v>24.959462</v>
-      </c>
-      <c r="L987" t="str">
-        <v>Finland (September 2019)</v>
+        <v>restaurant</v>
+      </c>
+      <c r="E987">
+        <v>0</v>
+      </c>
+      <c r="G987" t="str">
+        <v>December</v>
+      </c>
+      <c r="H987">
+        <v>2022</v>
+      </c>
+      <c r="I987" t="str">
+        <v>celiac-aware</v>
       </c>
       <c r="O987" t="str">
-        <v/>
-      </c>
-      <c r="S987" t="str">
-        <v>https://www.getyourguide.com/helsinki-l13/helsinki-skywheel-helsinki-ride-ticket-t512719/</v>
+        <v>Mexican restaurant with GF items clearly marked on menu. Good cocktails too.</v>
       </c>
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>Finland</v>
+        <v>Germany</v>
       </c>
       <c r="B988" t="str">
-        <v>Helsinki</v>
+        <v>Dusseldorf</v>
       </c>
       <c r="C988" t="str">
-        <v>Market Square</v>
+        <v>Pasta Bar Em Brass</v>
       </c>
       <c r="D988" t="str">
-        <v>market</v>
-      </c>
-      <c r="J988">
-        <v>60.1676653</v>
-      </c>
-      <c r="K988">
-        <v>24.9536778</v>
-      </c>
-      <c r="L988" t="str">
-        <v>Finland (September 2019)</v>
+        <v>restaurant</v>
+      </c>
+      <c r="E988">
+        <v>0</v>
+      </c>
+      <c r="G988" t="str">
+        <v>December</v>
+      </c>
+      <c r="H988">
+        <v>2022</v>
+      </c>
+      <c r="I988" t="str">
+        <v>celiac-aware</v>
       </c>
       <c r="O988" t="str">
-        <v>open air market</v>
-      </c>
-    </row>
-    <row r="989">
-      <c r="A989" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B989" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C989" t="str">
-        <v>Tampere Station</v>
-      </c>
-      <c r="D989" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J989">
-        <v>61.4990515</v>
-      </c>
-      <c r="K989">
-        <v>23.7750395</v>
-      </c>
-      <c r="L989" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O989" t="str">
-        <v/>
-      </c>
-      <c r="S989" t="str">
-        <v>https://www.hotels.com/ho400777/scandic-tampere-station-tampere-finland/</v>
-      </c>
-      <c r="U989" t="str">
-        <v>Adjacent to station, breakfast buffet</v>
-      </c>
-    </row>
-    <row r="990">
-      <c r="A990" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B990" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C990" t="str">
-        <v>Scandic Tampere Station</v>
-      </c>
-      <c r="D990" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J990">
-        <v>61.4992302</v>
-      </c>
-      <c r="K990">
-        <v>23.7756188</v>
-      </c>
-      <c r="L990" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O990" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="991">
-      <c r="A991" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B991" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C991" t="str">
-        <v>Tampere Market Hall</v>
-      </c>
-      <c r="D991" t="str">
-        <v>market</v>
-      </c>
-      <c r="J991">
-        <v>61.4969444</v>
-      </c>
-      <c r="K991">
-        <v>23.7586111</v>
-      </c>
-      <c r="L991" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O991" t="str">
-        <v>(Largest Enclosed Nordic Market Hall)</v>
-      </c>
-    </row>
-    <row r="992">
-      <c r="A992" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B992" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C992" t="str">
-        <v>Näsinneula</v>
-      </c>
-      <c r="D992" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J992">
-        <v>61.5049647</v>
-      </c>
-      <c r="K992">
-        <v>23.7430645</v>
-      </c>
-      <c r="L992" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O992" t="str">
-        <v/>
-      </c>
-      <c r="S992" t="str">
-        <v>https://sarkanniemi.fi/en/product/nasinneula-lippu-4</v>
-      </c>
-    </row>
-    <row r="993">
-      <c r="A993" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B993" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C993" t="str">
-        <v>Pyynikki Observation Tower</v>
-      </c>
-      <c r="D993" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J993">
-        <v>61.4963497</v>
-      </c>
-      <c r="K993">
-        <v>23.7320282</v>
-      </c>
-      <c r="L993" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O993" t="str">
-        <v/>
-      </c>
-      <c r="S993" t="str">
-        <v>https://www.munkkikahvila.net/en</v>
-      </c>
-    </row>
-    <row r="994">
-      <c r="A994" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B994" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C994" t="str">
-        <v>Hatanpää Park Arboretum</v>
-      </c>
-      <c r="D994" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J994">
-        <v>61.4810238</v>
-      </c>
-      <c r="K994">
-        <v>23.7528293</v>
-      </c>
-      <c r="L994" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O994" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="995">
-      <c r="A995" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B995" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C995" t="str">
-        <v>Thai &amp; Laos Restaurant</v>
-      </c>
-      <c r="D995" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="I995" t="str">
-        <v>celiac-aware</v>
-      </c>
-      <c r="J995">
-        <v>61.4983089</v>
-      </c>
-      <c r="K995">
-        <v>23.7548459</v>
-      </c>
-      <c r="L995" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O995" t="str">
-        <v>all dishes are GF &amp; lactose free - was good.</v>
-      </c>
-      <c r="Q995">
-        <v>4</v>
-      </c>
-      <c r="R995" t="str">
-        <v>[2026-03-29 research] All dishes GF &amp; lactose free. Thai curries and stir-fries all safe.</v>
-      </c>
-    </row>
-    <row r="996">
-      <c r="A996" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B996" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C996" t="str">
-        <v>Sitko Pizza Tampere</v>
-      </c>
-      <c r="D996" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="I996" t="str">
-        <v>celiac-aware</v>
-      </c>
-      <c r="J996">
-        <v>61.4986679</v>
-      </c>
-      <c r="K996">
-        <v>23.7542559</v>
-      </c>
-      <c r="L996" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O996" t="str">
-        <v>Sitko Pizza – GF crust &amp; vegan cheese</v>
-      </c>
-      <c r="Q996">
-        <v>4</v>
-      </c>
-      <c r="R996" t="str">
-        <v>[2026-03-29 research] Dedicated GF crust, vegan cheese available. Made fresh separately.</v>
-      </c>
-    </row>
-    <row r="997">
-      <c r="A997" t="str">
-        <v>Finland</v>
-      </c>
-      <c r="B997" t="str">
-        <v>Tampere</v>
-      </c>
-      <c r="C997" t="str">
-        <v>Venla</v>
-      </c>
-      <c r="D997" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="I997" t="str">
-        <v>mixed safety</v>
-      </c>
-      <c r="J997">
-        <v>61.4983333</v>
-      </c>
-      <c r="K997">
-        <v>23.7575</v>
-      </c>
-      <c r="L997" t="str">
-        <v>Finland (September 2019)</v>
-      </c>
-      <c r="O997" t="str">
-        <v>Bistro Venla – GF bread &amp; a lot of GF vegetarian options - dont think I ate here.</v>
-      </c>
-      <c r="Q997">
-        <v>3</v>
-      </c>
-      <c r="R997" t="str">
-        <v>[2026-03-29 research] GF bread and extensive GF vegetarian options. Salad-focused bistro.</v>
-      </c>
-    </row>
-    <row r="998">
-      <c r="A998" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B998" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C998" t="str">
-        <v>Hampton by Hilton Berlin City West</v>
-      </c>
-      <c r="D998" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J998">
-        <v>52.504978</v>
-      </c>
-      <c r="K998">
-        <v>13.325864</v>
-      </c>
-      <c r="L998" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O998" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="999">
-      <c r="A999" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B999" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C999" t="str">
-        <v>Berlin Central Station</v>
-      </c>
-      <c r="D999" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J999">
-        <v>52.524911</v>
-      </c>
-      <c r="K999">
-        <v>13.369492</v>
-      </c>
-      <c r="L999" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O999" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1000" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1000" t="str">
-        <v>Teufelsberg</v>
-      </c>
-      <c r="D1000" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1000">
-        <v>52.497222</v>
-      </c>
-      <c r="K1000">
-        <v>13.241111</v>
-      </c>
-      <c r="L1000" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1000" t="str">
-        <v>Teufelsberg Nazi Ruins/Abandoned Cold War NSA Post</v>
-      </c>
-    </row>
-    <row r="1001">
-      <c r="A1001" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1001" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1001" t="str">
-        <v>Olympiastadion Berlin</v>
-      </c>
-      <c r="D1001" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1001">
-        <v>52.514697</v>
-      </c>
-      <c r="K1001">
-        <v>13.239499</v>
-      </c>
-      <c r="L1001" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1001" t="str">
-        <v>Hertha Berlin stadium for bundesliga games</v>
-      </c>
-    </row>
-    <row r="1002">
-      <c r="A1002" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1002" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1002" t="str">
-        <v>Berlin Wall</v>
-      </c>
-      <c r="D1002" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1002">
-        <v>52.507182</v>
-      </c>
-      <c r="K1002">
-        <v>13.383506</v>
-      </c>
-      <c r="L1002" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1002" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1003">
-      <c r="A1003" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1003" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1003" t="str">
-        <v>Görlitzer Park</v>
-      </c>
-      <c r="D1003" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1003">
-        <v>52.496593</v>
-      </c>
-      <c r="K1003">
-        <v>13.437449</v>
-      </c>
-      <c r="L1003" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1003" t="str">
-        <v>Lots of graffiti, people playing music, etc. – some drug dealers so avoid at night.</v>
-      </c>
-    </row>
-    <row r="1004">
-      <c r="A1004" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1004" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1004" t="str">
-        <v>Berlin Wall Memorial</v>
-      </c>
-      <c r="D1004" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1004">
-        <v>52.535052</v>
-      </c>
-      <c r="K1004">
-        <v>13.39019</v>
-      </c>
-      <c r="L1004" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1004" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1005">
-      <c r="A1005" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1005" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1005" t="str">
-        <v>Fat Tire Tours</v>
-      </c>
-      <c r="D1005" t="str">
-        <v>activity</v>
-      </c>
-      <c r="J1005">
-        <v>52.520995</v>
-      </c>
-      <c r="K1005">
-        <v>13.409113</v>
-      </c>
-      <c r="L1005" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1005" t="str">
-        <v>HIGHLY recommend - you get to see a lot of cool spots and hear a lot of good stories - Berlin Wall, Holocaust Memorial sites, etc</v>
-      </c>
-    </row>
-    <row r="1006">
-      <c r="A1006" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1006" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1006" t="str">
-        <v>Checkpoint Charlie</v>
-      </c>
-      <c r="D1006" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1006">
-        <v>52.507443</v>
-      </c>
-      <c r="K1006">
-        <v>13.390391</v>
-      </c>
-      <c r="L1006" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1006" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1007">
-      <c r="A1007" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1007" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1007" t="str">
-        <v>Memorial to the Murdered Jews of Europe</v>
-      </c>
-      <c r="D1007" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1007">
-        <v>52.513947</v>
-      </c>
-      <c r="K1007">
-        <v>13.378713</v>
-      </c>
-      <c r="L1007" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1007" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1008">
-      <c r="A1008" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1008" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1008" t="str">
-        <v>Reichstag Building</v>
-      </c>
-      <c r="D1008" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1008">
-        <v>52.518619</v>
-      </c>
-      <c r="K1008">
-        <v>13.376318</v>
-      </c>
-      <c r="L1008" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1008" t="str">
-        <v>German Parliament</v>
-      </c>
-    </row>
-    <row r="1009">
-      <c r="A1009" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1009" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1009" t="str">
-        <v>Berliner Fernsehturm</v>
-      </c>
-      <c r="D1009" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1009">
-        <v>52.520815</v>
-      </c>
-      <c r="K1009">
-        <v>13.409419</v>
-      </c>
-      <c r="L1009" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1009" t="str">
-        <v>TV Tower</v>
-      </c>
-    </row>
-    <row r="1010">
-      <c r="A1010" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1010" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1010" t="str">
-        <v>Berlin Cathedral</v>
-      </c>
-      <c r="D1010" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1010">
-        <v>52.519061</v>
-      </c>
-      <c r="K1010">
-        <v>13.401078</v>
-      </c>
-      <c r="L1010" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1010" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1011">
-      <c r="A1011" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1011" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1011" t="str">
-        <v>Markthalle Neun</v>
-      </c>
-      <c r="D1011" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1011">
-        <v>52.502023</v>
-      </c>
-      <c r="K1011">
-        <v>13.431935</v>
-      </c>
-      <c r="L1011" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1011" t="str">
-        <v>• Not usually open all Sundays but on May 13th and 14th they're having a raw (organic) wine festival! Tix are 40 euros each so not buying ahead of time.</v>
-      </c>
-    </row>
-    <row r="1012">
-      <c r="A1012" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1012" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1012" t="str">
-        <v>Mauerpark</v>
-      </c>
-      <c r="D1012" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1012">
-        <v>52.5424</v>
-      </c>
-      <c r="K1012">
-        <v>13.403352</v>
-      </c>
-      <c r="L1012" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1012" t="str">
-        <v>LOVED IT. Karoake, dancing, drinks, etc - really fun, hipster atmosphere. Open karaoke starts at 3pm &amp; amazing flea mkt on Sundays. Food or drinks available at flea market and there’s a little beer garden</v>
-      </c>
-    </row>
-    <row r="1013">
-      <c r="A1013" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1013" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1013" t="str">
-        <v>Sachiko Sushi</v>
-      </c>
-      <c r="D1013" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1013">
-        <v>52.504701</v>
-      </c>
-      <c r="K1013">
-        <v>13.323713</v>
-      </c>
-      <c r="L1013" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1013" t="str">
-        <v>quaint sushi bar with a 'conveyor belt' (river boat) that serves up sushi dishes</v>
-      </c>
-    </row>
-    <row r="1014">
-      <c r="A1014" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1014" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1014" t="str">
-        <v>Brammibal's Donuts (Maybachufer)</v>
-      </c>
-      <c r="D1014" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1014">
-        <v>52.494978</v>
-      </c>
-      <c r="K1014">
-        <v>13.42302</v>
-      </c>
-      <c r="L1014" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1014" t="str">
-        <v>I don't think I actually ate here. I think they said the GF donuts had cross-contamination. But had vegan donuts.</v>
-      </c>
-    </row>
-    <row r="1015">
-      <c r="A1015" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1015" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1015" t="str">
-        <v>Cevicheria</v>
-      </c>
-      <c r="D1015" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1015">
-        <v>52.501282</v>
-      </c>
-      <c r="K1015">
-        <v>13.416523</v>
-      </c>
-      <c r="L1015" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1015" t="str">
-        <v>don't remember eating here</v>
-      </c>
-    </row>
-    <row r="1016">
-      <c r="A1016" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1016" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1016" t="str">
-        <v>Simela Finest Food</v>
-      </c>
-      <c r="D1016" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1016">
-        <v>52.527562</v>
-      </c>
-      <c r="K1016">
-        <v>13.398105</v>
-      </c>
-      <c r="L1016" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1016" t="str">
-        <v>2nd location (I did not go to this one) with GF pizza</v>
-      </c>
-    </row>
-    <row r="1017">
-      <c r="A1017" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1017" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1017" t="str">
-        <v>Simela finest food</v>
-      </c>
-      <c r="D1017" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1017">
-        <v>52.505576</v>
-      </c>
-      <c r="K1017">
-        <v>13.323439</v>
-      </c>
-      <c r="L1017" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1017" t="str">
-        <v>gluten free pizza - was such a cute family owned spot!</v>
-      </c>
-    </row>
-    <row r="1018">
-      <c r="A1018" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1018" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1018" t="str">
-        <v>OAK &amp; ICE</v>
-      </c>
-      <c r="D1018" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1018">
-        <v>52.542882</v>
-      </c>
-      <c r="K1018">
-        <v>13.412664</v>
-      </c>
-      <c r="L1018" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1018" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1019">
-      <c r="A1019" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1019" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1019" t="str">
-        <v>No Milk Today</v>
-      </c>
-      <c r="D1019" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1019">
-        <v>52.490921</v>
-      </c>
-      <c r="K1019">
-        <v>13.412804</v>
-      </c>
-      <c r="L1019" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1019" t="str">
-        <v>don't remember eating here</v>
-      </c>
-    </row>
-    <row r="1020">
-      <c r="A1020" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1020" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1020" t="str">
-        <v>Burgerie</v>
-      </c>
-      <c r="D1020" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1020">
-        <v>52.542506</v>
-      </c>
-      <c r="K1020">
-        <v>13.412613</v>
-      </c>
-      <c r="L1020" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1020" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1021">
-      <c r="A1021" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1021" t="str">
-        <v>Berlin</v>
-      </c>
-      <c r="C1021" t="str">
-        <v>Jute Bäckerei</v>
-      </c>
-      <c r="D1021" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1021">
-        <v>52.543011</v>
-      </c>
-      <c r="K1021">
-        <v>13.412799</v>
-      </c>
-      <c r="L1021" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1021" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1022">
-      <c r="A1022" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1022" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1022" t="str">
-        <v>Hyatt Regency Cologne</v>
-      </c>
-      <c r="D1022" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J1022">
-        <v>50.94043</v>
-      </c>
-      <c r="K1022">
-        <v>6.96953</v>
-      </c>
-      <c r="L1022" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1022" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1023">
-      <c r="A1023" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1023" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1023" t="str">
-        <v>Cologne Central Station</v>
-      </c>
-      <c r="D1023" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J1023">
-        <v>50.943214</v>
-      </c>
-      <c r="K1023">
-        <v>6.958602</v>
-      </c>
-      <c r="L1023" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1023" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1024">
-      <c r="A1024" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1024" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1024" t="str">
-        <v>Cologne Triangle</v>
-      </c>
-      <c r="D1024" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1024">
-        <v>50.940411</v>
-      </c>
-      <c r="K1024">
-        <v>6.971808</v>
-      </c>
-      <c r="L1024" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1024" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1025">
-      <c r="A1025" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1025" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1025" t="str">
-        <v>Cologne Cathedral</v>
-      </c>
-      <c r="D1025" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1025">
-        <v>50.941278</v>
-      </c>
-      <c r="K1025">
-        <v>6.958281</v>
-      </c>
-      <c r="L1025" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1025" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1026">
-      <c r="A1026" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1026" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1026" t="str">
-        <v>Hohenzollernbrücke</v>
-      </c>
-      <c r="D1026" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1026">
-        <v>50.941605</v>
-      </c>
-      <c r="K1026">
-        <v>6.965789</v>
-      </c>
-      <c r="L1026" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1026" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1027">
-      <c r="A1027" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1027" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1027" t="str">
-        <v>Old Market</v>
-      </c>
-      <c r="D1027" t="str">
-        <v>market</v>
-      </c>
-      <c r="J1027">
-        <v>50.938504</v>
-      </c>
-      <c r="K1027">
-        <v>6.960141</v>
-      </c>
-      <c r="L1027" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1027" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1028">
-      <c r="A1028" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1028" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1028" t="str">
-        <v>UNIQLO Köln</v>
-      </c>
-      <c r="D1028" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1028">
-        <v>50.936403</v>
-      </c>
-      <c r="K1028">
-        <v>6.956441</v>
-      </c>
-      <c r="L1028" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1028" t="str">
-        <v>good thermal basics &amp; under layers!</v>
-      </c>
-    </row>
-    <row r="1029">
-      <c r="A1029" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1029" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1029" t="str">
-        <v>Weihnachtsmarkt auf dem Neumarkt Köln</v>
-      </c>
-      <c r="D1029" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1029">
-        <v>50.93599</v>
-      </c>
-      <c r="K1029">
-        <v>6.947487</v>
-      </c>
-      <c r="L1029" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1029" t="str">
-        <v>Christmas Market</v>
-      </c>
-    </row>
-    <row r="1030">
-      <c r="A1030" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1030" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1030" t="str">
-        <v>Kuchi Mami</v>
-      </c>
-      <c r="D1030" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1030">
-        <v>50.941402</v>
-      </c>
-      <c r="K1030">
-        <v>6.954008</v>
-      </c>
-      <c r="L1030" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1030" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1031">
-      <c r="A1031" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1031" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1031" t="str">
-        <v>mama trattoria Köln City</v>
-      </c>
-      <c r="D1031" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1031">
-        <v>50.937751</v>
-      </c>
-      <c r="K1031">
-        <v>6.955545</v>
-      </c>
-      <c r="L1031" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1031" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1032">
-      <c r="A1032" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1032" t="str">
-        <v>Cologne</v>
-      </c>
-      <c r="C1032" t="str">
-        <v>MEIN CORONA SCHNELLTEST - Köln</v>
-      </c>
-      <c r="D1032" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1032">
-        <v>50.938032</v>
-      </c>
-      <c r="K1032">
-        <v>6.961153</v>
-      </c>
-      <c r="L1032" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1032" t="str">
-        <v>COVID Testing</v>
-      </c>
-    </row>
-    <row r="1033">
-      <c r="A1033" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1033" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1033" t="str">
-        <v>carathotel Düsseldorf City</v>
-      </c>
-      <c r="D1033" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J1033">
-        <v>51.219538</v>
-      </c>
-      <c r="K1033">
-        <v>6.783752</v>
-      </c>
-      <c r="L1033" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1033" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1034">
-      <c r="A1034" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1034" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1034" t="str">
-        <v>Düsseldorf Airport</v>
-      </c>
-      <c r="D1034" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J1034">
-        <v>51.279475</v>
-      </c>
-      <c r="K1034">
-        <v>6.765677</v>
-      </c>
-      <c r="L1034" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1034" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1035">
-      <c r="A1035" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1035" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1035" t="str">
-        <v>Düsseldorf Central Station</v>
-      </c>
-      <c r="D1035" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J1035">
-        <v>51.219828</v>
-      </c>
-      <c r="K1035">
-        <v>6.794479</v>
-      </c>
-      <c r="L1035" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1035" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1036">
-      <c r="A1036" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1036" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1036" t="str">
-        <v>Rhine Tower</v>
-      </c>
-      <c r="D1036" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1036">
-        <v>51.217942</v>
-      </c>
-      <c r="K1036">
-        <v>6.76168</v>
-      </c>
-      <c r="L1036" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1036" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1037">
-      <c r="A1037" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1037" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1037" t="str">
-        <v>Königsallee</v>
-      </c>
-      <c r="D1037" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1037">
-        <v>51.221698</v>
-      </c>
-      <c r="K1037">
-        <v>6.779262</v>
-      </c>
-      <c r="L1037" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1037" t="str">
-        <v>cute outdoor pond/channel with Christmas Market stalls</v>
-      </c>
-    </row>
-    <row r="1038">
-      <c r="A1038" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1038" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1038" t="str">
-        <v>Vabali Spa Düsseldorf</v>
-      </c>
-      <c r="D1038" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1038">
-        <v>51.183203</v>
-      </c>
-      <c r="K1038">
-        <v>6.9103533</v>
-      </c>
-      <c r="L1038" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1038" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1039">
-      <c r="A1039" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1039" t="str">
-        <v>Dusseldorf</v>
-      </c>
-      <c r="C1039" t="str">
-        <v>Isabella Glutenfreie Pâtisserie</v>
-      </c>
-      <c r="D1039" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1039">
-        <v>51.221976</v>
-      </c>
-      <c r="K1039">
-        <v>6.780773</v>
-      </c>
-      <c r="L1039" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1039" t="str">
-        <v>Dedicated gluten free bakery - lots of options - some are better than others. Pretty expensive.</v>
-      </c>
-    </row>
-    <row r="1040">
-      <c r="A1040" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1040" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1040" t="str">
-        <v>Hampton by Hilton Frankfurt City Centre Messe</v>
-      </c>
-      <c r="D1040" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J1040">
-        <v>50.108938</v>
-      </c>
-      <c r="K1040">
-        <v>8.647072</v>
-      </c>
-      <c r="L1040" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1040" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1041">
-      <c r="A1041" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1041" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1041" t="str">
-        <v>Frankfurt Airport (FRA)</v>
-      </c>
-      <c r="D1041" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J1041">
-        <v>50.051219</v>
-      </c>
-      <c r="K1041">
-        <v>8.571788</v>
-      </c>
-      <c r="L1041" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1041" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1042">
-      <c r="A1042" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1042" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1042" t="str">
-        <v>Frankfurt (Main) Hauptbahnhof</v>
-      </c>
-      <c r="D1042" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1042">
-        <v>50.10716</v>
-      </c>
-      <c r="K1042">
-        <v>8.66376</v>
-      </c>
-      <c r="L1042" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1042" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1043">
-      <c r="A1043" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1043" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1043" t="str">
-        <v>Rententurm</v>
-      </c>
-      <c r="D1043" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1043">
-        <v>50.10924</v>
-      </c>
-      <c r="K1043">
-        <v>8.682309</v>
-      </c>
-      <c r="L1043" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1043" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1044">
-      <c r="A1044" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1044" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1044" t="str">
-        <v>Römer</v>
-      </c>
-      <c r="D1044" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1044">
-        <v>50.110263</v>
-      </c>
-      <c r="K1044">
-        <v>8.682096</v>
-      </c>
-      <c r="L1044" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1044" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1045">
-      <c r="A1045" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1045" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1045" t="str">
-        <v>Frankfurt Cathedral</v>
-      </c>
-      <c r="D1045" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1045">
-        <v>50.110663</v>
-      </c>
-      <c r="K1045">
-        <v>8.68542</v>
-      </c>
-      <c r="L1045" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1045" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1046">
-      <c r="A1046" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1046" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1046" t="str">
-        <v>Iron Footbridge</v>
-      </c>
-      <c r="D1046" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1046">
-        <v>50.108111</v>
-      </c>
-      <c r="K1046">
-        <v>8.682129</v>
-      </c>
-      <c r="L1046" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1046" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1047">
-      <c r="A1047" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1047" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1047" t="str">
-        <v>Kleinmarkthalle</v>
-      </c>
-      <c r="D1047" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1047">
-        <v>50.112667</v>
-      </c>
-      <c r="K1047">
-        <v>8.682885</v>
-      </c>
-      <c r="L1047" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1047" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1048">
-      <c r="A1048" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1048" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1048" t="str">
-        <v>Domturm</v>
-      </c>
-      <c r="D1048" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1048">
-        <v>50.110601</v>
-      </c>
-      <c r="K1048">
-        <v>8.684985</v>
-      </c>
-      <c r="L1048" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1048" t="str">
-        <v>observation deck</v>
-      </c>
-    </row>
-    <row r="1049">
-      <c r="A1049" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1049" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1049" t="str">
-        <v>Frankfurt Cathedral</v>
-      </c>
-      <c r="D1049" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1049">
-        <v>50.110663</v>
-      </c>
-      <c r="K1049">
-        <v>8.68542</v>
-      </c>
-      <c r="L1049" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1049" t="str">
-        <v>can climb the dome</v>
-      </c>
-    </row>
-    <row r="1050">
-      <c r="A1050" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1050" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1050" t="str">
-        <v>Main Tower</v>
-      </c>
-      <c r="D1050" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1050">
-        <v>50.112548</v>
-      </c>
-      <c r="K1050">
-        <v>8.672142</v>
-      </c>
-      <c r="L1050" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1050" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1051">
-      <c r="A1051" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1051" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1051" t="str">
-        <v>Frankfurter Römer</v>
-      </c>
-      <c r="D1051" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1051">
-        <v>50.110581</v>
-      </c>
-      <c r="K1051">
-        <v>8.681806</v>
-      </c>
-      <c r="L1051" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1051" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1052">
-      <c r="A1052" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1052" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1052" t="str">
-        <v>Hop-On Hop-Off Stop: Messe (Frankfurt Sightseeing)</v>
-      </c>
-      <c r="D1052" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1052">
-        <v>50.111521</v>
-      </c>
-      <c r="K1052">
-        <v>8.654943</v>
-      </c>
-      <c r="L1052" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1052" t="str">
-        <v>where I got on the HoHo bus</v>
-      </c>
-    </row>
-    <row r="1053">
-      <c r="A1053" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1053" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1053" t="str">
-        <v>Block House</v>
-      </c>
-      <c r="D1053" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1053">
-        <v>50.109232</v>
-      </c>
-      <c r="K1053">
-        <v>8.650328</v>
-      </c>
-      <c r="L1053" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1053" t="str">
-        <v>steak house but they had caprese salad and apps that were GF</v>
-      </c>
-    </row>
-    <row r="1054">
-      <c r="A1054" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1054" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1054" t="str">
-        <v>Tacohaus</v>
-      </c>
-      <c r="D1054" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1054">
-        <v>50.116625</v>
-      </c>
-      <c r="K1054">
-        <v>8.643881</v>
-      </c>
-      <c r="L1054" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1054" t="str">
-        <v>don't think I actually ate here but it was on my list</v>
-      </c>
-    </row>
-    <row r="1055">
-      <c r="A1055" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1055" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1055" t="str">
-        <v>MAREDO Frankfurt Hauptwache</v>
-      </c>
-      <c r="D1055" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1055">
-        <v>50.113902</v>
-      </c>
-      <c r="K1055">
-        <v>8.678046</v>
-      </c>
-      <c r="L1055" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1055" t="str">
-        <v>steak house w/ GF marked on the menu</v>
-      </c>
-    </row>
-    <row r="1056">
-      <c r="A1056" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1056" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1056" t="str">
-        <v>HANS IM GLÜCK - FRANKFURT am Main Braubachstraße</v>
-      </c>
-      <c r="D1056" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1056">
-        <v>50.111958</v>
-      </c>
-      <c r="K1056">
-        <v>8.685564</v>
-      </c>
-      <c r="L1056" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1056" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1057">
-      <c r="A1057" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1057" t="str">
-        <v>Frankfurt</v>
-      </c>
-      <c r="C1057" t="str">
-        <v>VAPIANO Frankfurt Goetheplatz</v>
-      </c>
-      <c r="D1057" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1057">
-        <v>50.112846</v>
-      </c>
-      <c r="K1057">
-        <v>8.675892</v>
-      </c>
-      <c r="L1057" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1057" t="str">
-        <v>had GF pizza and was marked with a little flag to signify gluten free. but it was not very good.</v>
-      </c>
-    </row>
-    <row r="1058">
-      <c r="A1058" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1058" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1058" t="str">
-        <v>Roomers Hotel Munich</v>
-      </c>
-      <c r="D1058" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J1058">
-        <v>48.139801</v>
-      </c>
-      <c r="K1058">
-        <v>11.540704</v>
-      </c>
-      <c r="L1058" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1058" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1059">
-      <c r="A1059" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1059" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1059" t="str">
-        <v>Eden Hotel Wolff</v>
-      </c>
-      <c r="D1059" t="str">
-        <v>hotel</v>
-      </c>
-      <c r="J1059">
-        <v>48.141654</v>
-      </c>
-      <c r="K1059">
-        <v>11.559204</v>
-      </c>
-      <c r="L1059" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1059" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1060">
-      <c r="A1060" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1060" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1060" t="str">
-        <v>Munich Airport</v>
-      </c>
-      <c r="D1060" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J1060">
-        <v>48.352732</v>
-      </c>
-      <c r="K1060">
-        <v>11.78624</v>
-      </c>
-      <c r="L1060" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1060" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1061">
-      <c r="A1061" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1061" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1061" t="str">
-        <v>Munich Central Station</v>
-      </c>
-      <c r="D1061" t="str">
-        <v>transit</v>
-      </c>
-      <c r="J1061">
-        <v>48.140267</v>
-      </c>
-      <c r="K1061">
-        <v>11.559998</v>
-      </c>
-      <c r="L1061" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1061" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1062">
-      <c r="A1062" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1062" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1062" t="str">
-        <v>Munich Hauptbahnhof</v>
-      </c>
-      <c r="D1062" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1062">
-        <v>48.139775</v>
-      </c>
-      <c r="K1062">
-        <v>11.560958</v>
-      </c>
-      <c r="L1062" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1062" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1063">
-      <c r="A1063" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1063" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1063" t="str">
-        <v>Technische Universität München</v>
-      </c>
-      <c r="D1063" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1063">
-        <v>48.14966</v>
-      </c>
-      <c r="K1063">
-        <v>11.56786</v>
-      </c>
-      <c r="L1063" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1063" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1064">
-      <c r="A1064" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1064" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1064" t="str">
-        <v>St. Peter's Church</v>
-      </c>
-      <c r="D1064" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1064">
-        <v>48.136491</v>
-      </c>
-      <c r="K1064">
-        <v>11.576047</v>
-      </c>
-      <c r="L1064" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1064" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1065">
-      <c r="A1065" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1065" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1065" t="str">
-        <v>Karlsplatz</v>
-      </c>
-      <c r="D1065" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1065">
-        <v>48.139193</v>
-      </c>
-      <c r="K1065">
-        <v>11.566201</v>
-      </c>
-      <c r="L1065" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1065" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1066">
-      <c r="A1066" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1066" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1066" t="str">
-        <v>Marienplatz</v>
-      </c>
-      <c r="D1066" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1066">
-        <v>48.137393</v>
-      </c>
-      <c r="K1066">
-        <v>11.575448</v>
-      </c>
-      <c r="L1066" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1066" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1067">
-      <c r="A1067" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1067" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1067" t="str">
-        <v>Frauenkirche</v>
-      </c>
-      <c r="D1067" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1067">
-        <v>48.138631</v>
-      </c>
-      <c r="K1067">
-        <v>11.573625</v>
-      </c>
-      <c r="L1067" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1067" t="str">
-        <v>(gothic church with iconic domed towers)</v>
-      </c>
-    </row>
-    <row r="1068">
-      <c r="A1068" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1068" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1068" t="str">
-        <v>Victuals Market</v>
-      </c>
-      <c r="D1068" t="str">
-        <v>market</v>
-      </c>
-      <c r="J1068">
-        <v>48.135114</v>
-      </c>
-      <c r="K1068">
-        <v>11.576255</v>
-      </c>
-      <c r="L1068" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1068" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1069">
-      <c r="A1069" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1069" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1069" t="str">
-        <v>English Garden</v>
-      </c>
-      <c r="D1069" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1069">
-        <v>48.164232</v>
-      </c>
-      <c r="K1069">
-        <v>11.605552</v>
-      </c>
-      <c r="L1069" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1069" t="str">
-        <v>English Garden (park with beer garden) – pretty far north but worth it. Cute chinese tower as well.</v>
-      </c>
-    </row>
-    <row r="1070">
-      <c r="A1070" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1070" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1070" t="str">
-        <v>Stachus Passagen</v>
-      </c>
-      <c r="D1070" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1070">
-        <v>48.139413</v>
-      </c>
-      <c r="K1070">
-        <v>11.565072</v>
-      </c>
-      <c r="L1070" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1070" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1071">
-      <c r="A1071" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1071" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1071" t="str">
-        <v>Allianz Arena</v>
-      </c>
-      <c r="D1071" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1071">
-        <v>48.218764</v>
-      </c>
-      <c r="K1071">
-        <v>11.624756</v>
-      </c>
-      <c r="L1071" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1071" t="str">
-        <v>Bayern Munich Stadium</v>
-      </c>
-    </row>
-    <row r="1072">
-      <c r="A1072" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1072" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1072" t="str">
-        <v>Odeonsplatz</v>
-      </c>
-      <c r="D1072" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1072">
-        <v>48.142799</v>
-      </c>
-      <c r="K1072">
-        <v>11.577769</v>
-      </c>
-      <c r="L1072" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1072" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1073">
-      <c r="A1073" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1073" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1073" t="str">
-        <v>Kaimug Taste Thai</v>
-      </c>
-      <c r="D1073" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1073">
-        <v>48.1393</v>
-      </c>
-      <c r="K1073">
-        <v>11.564566</v>
-      </c>
-      <c r="L1073" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1073" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1074">
-      <c r="A1074" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1074" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1074" t="str">
-        <v>Hofbräuhaus München</v>
-      </c>
-      <c r="D1074" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1074">
-        <v>48.13761</v>
-      </c>
-      <c r="K1074">
-        <v>11.579925</v>
-      </c>
-      <c r="L1074" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1074" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1075">
-      <c r="A1075" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1075" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1075" t="str">
-        <v>Viktualienmarkt Beergarden</v>
-      </c>
-      <c r="D1075" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1075">
-        <v>48.135269</v>
-      </c>
-      <c r="K1075">
-        <v>11.576402</v>
-      </c>
-      <c r="L1075" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1075" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1076">
-      <c r="A1076" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1076" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1076" t="str">
-        <v>Stadion an der Schleißheimer Straße</v>
-      </c>
-      <c r="D1076" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1076">
-        <v>48.15391</v>
-      </c>
-      <c r="K1076">
-        <v>11.56121</v>
-      </c>
-      <c r="L1076" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1076" t="str">
-        <v>Renowned nonpartisan soccer bar, operating several screens &amp; furnished with football flags &amp; scarves</v>
-      </c>
-    </row>
-    <row r="1077">
-      <c r="A1077" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1077" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1077" t="str">
-        <v>Fritz Mühlenbäckerei GmbH</v>
-      </c>
-      <c r="D1077" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1077">
-        <v>48.12675</v>
-      </c>
-      <c r="K1077">
-        <v>11.593524</v>
-      </c>
-      <c r="L1077" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1077" t="str">
-        <v>GF pies</v>
-      </c>
-    </row>
-    <row r="1078">
-      <c r="A1078" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1078" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1078" t="str">
-        <v>California Bean</v>
-      </c>
-      <c r="D1078" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1078">
-        <v>48.142875</v>
-      </c>
-      <c r="K1078">
-        <v>11.560306</v>
-      </c>
-      <c r="L1078" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1078" t="str">
-        <v>the best breakfast! GF toast</v>
-      </c>
-    </row>
-    <row r="1079">
-      <c r="A1079" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1079" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1079" t="str">
-        <v>Pizzesco</v>
-      </c>
-      <c r="D1079" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1079">
-        <v>48.131374</v>
-      </c>
-      <c r="K1079">
-        <v>11.589519</v>
-      </c>
-      <c r="L1079" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1079" t="str">
-        <v>gluten free pizza and desserts!</v>
-      </c>
-    </row>
-    <row r="1080">
-      <c r="A1080" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1080" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1080" t="str">
-        <v>echt jetzt - 100% glutenfrei</v>
-      </c>
-      <c r="D1080" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1080">
-        <v>48.149646</v>
-      </c>
-      <c r="K1080">
-        <v>11.57261</v>
-      </c>
-      <c r="L1080" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1080" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1081">
-      <c r="A1081" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1081" t="str">
-        <v>Munich</v>
-      </c>
-      <c r="C1081" t="str">
-        <v>Fritz Mühlenbäckerei GmbH</v>
-      </c>
-      <c r="D1081" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1081">
-        <v>48.135969</v>
-      </c>
-      <c r="K1081">
-        <v>11.576746</v>
-      </c>
-      <c r="L1081" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1081" t="str">
-        <v>GF pies</v>
-      </c>
-    </row>
-    <row r="1082">
-      <c r="A1082" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1082" t="str">
-        <v>Stuttgart</v>
-      </c>
-      <c r="C1082" t="str">
-        <v>Stuttgart Hauptbahnhof (oben)</v>
-      </c>
-      <c r="D1082" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1082">
-        <v>48.784784</v>
-      </c>
-      <c r="K1082">
-        <v>9.1832032</v>
-      </c>
-      <c r="L1082" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1082" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1083">
-      <c r="A1083" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1083" t="str">
-        <v>Stuttgart</v>
-      </c>
-      <c r="C1083" t="str">
-        <v>Markthalle Stuttgart</v>
-      </c>
-      <c r="D1083" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1083">
-        <v>48.7762502</v>
-      </c>
-      <c r="K1083">
-        <v>9.1794097</v>
-      </c>
-      <c r="L1083" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1083" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1084">
-      <c r="A1084" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1084" t="str">
-        <v>Stuttgart</v>
-      </c>
-      <c r="C1084" t="str">
-        <v>Hans im Glück</v>
-      </c>
-      <c r="D1084" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1084">
-        <v>48.7731882</v>
-      </c>
-      <c r="K1084">
-        <v>9.1733064</v>
-      </c>
-      <c r="L1084" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1084" t="str">
-        <v>GF marked - amazing salads!</v>
-      </c>
-    </row>
-    <row r="1085">
-      <c r="A1085" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1085" t="str">
-        <v>Duisburg &amp; Dinslaken</v>
-      </c>
-      <c r="C1085" t="str">
-        <v>EDEKA</v>
-      </c>
-      <c r="D1085" t="str">
-        <v>restaurant</v>
-      </c>
-      <c r="J1085">
-        <v>51.5785289</v>
-      </c>
-      <c r="K1085">
-        <v>6.7416476</v>
-      </c>
-      <c r="L1085" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1085" t="str">
-        <v>grocery store with GF options</v>
-      </c>
-    </row>
-    <row r="1086">
-      <c r="A1086" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1086" t="str">
-        <v>Duisburg &amp; Dinslaken</v>
-      </c>
-      <c r="C1086" t="str">
-        <v>BA'RE:SE</v>
-      </c>
-      <c r="D1086" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1086">
-        <v>51.5627959</v>
-      </c>
-      <c r="K1086">
-        <v>6.7371935</v>
-      </c>
-      <c r="L1086" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1086" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1087">
-      <c r="A1087" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1087" t="str">
-        <v>Duisburg &amp; Dinslaken</v>
-      </c>
-      <c r="C1087" t="str">
-        <v>Neutor Galerie</v>
-      </c>
-      <c r="D1087" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1087">
-        <v>51.5617465</v>
-      </c>
-      <c r="K1087">
-        <v>6.7397827</v>
-      </c>
-      <c r="L1087" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1087" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1088">
-      <c r="A1088" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1088" t="str">
-        <v>Duisburg &amp; Dinslaken</v>
-      </c>
-      <c r="C1088" t="str">
-        <v>Tiger &amp; Turtle</v>
-      </c>
-      <c r="D1088" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1088">
-        <v>51.3756461</v>
-      </c>
-      <c r="K1088">
-        <v>6.7379532</v>
-      </c>
-      <c r="L1088" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1088" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1089">
-      <c r="A1089" t="str">
-        <v>Germany</v>
-      </c>
-      <c r="B1089" t="str">
-        <v>Duisburg &amp; Dinslaken</v>
-      </c>
-      <c r="C1089" t="str">
-        <v>Landschaftspark Duisburg</v>
-      </c>
-      <c r="D1089" t="str">
-        <v>landmark</v>
-      </c>
-      <c r="J1089">
-        <v>51.4814847</v>
-      </c>
-      <c r="K1089">
-        <v>6.7808056</v>
-      </c>
-      <c r="L1089" t="str">
-        <v>Germany (December 2022)</v>
-      </c>
-      <c r="O1089" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="1090">
-      <c r="A1090" t="str">
-        <v>Netherlands</v>
-      </c>
-      <c r="B1090" t="str">
-        <v>Amsterdam</v>
-      </c>
-      <c r="C1090" t="str">
-        <v>Amsterdam (placeholder)</v>
-      </c>
-      <c r="D1090" t="str">
-        <v>other</v>
-      </c>
-      <c r="G1090" t="str">
-        <v>Dec</v>
-      </c>
-      <c r="H1090" t="str">
-        <v>2022</v>
-      </c>
-      <c r="N1090" t="str">
-        <v>yes</v>
-      </c>
-    </row>
-    <row r="1091">
-      <c r="A1091" t="str">
-        <v>Netherlands</v>
-      </c>
-      <c r="B1091" t="str">
-        <v>Nijmegen</v>
-      </c>
-      <c r="C1091" t="str">
-        <v>Nijmegen (placeholder)</v>
-      </c>
-      <c r="D1091" t="str">
-        <v>other</v>
-      </c>
-      <c r="G1091" t="str">
-        <v>Dec</v>
-      </c>
-      <c r="H1091" t="str">
-        <v>2022</v>
-      </c>
-      <c r="N1091" t="str">
-        <v>yes</v>
+        <v>Can prepare all pasta dishes GF on request. Kitchen understands cross-contamination.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1091"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U988"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U988"/>
+  <dimension ref="A1:U1032"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -41961,9 +41961,1780 @@
         <v>Can prepare all pasta dishes GF on request. Kitchen understands cross-contamination.</v>
       </c>
     </row>
+    <row r="989">
+      <c r="A989" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B989" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C989" t="str">
+        <v>València Joaquín Sorolla</v>
+      </c>
+      <c r="D989" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E989">
+        <v>1</v>
+      </c>
+      <c r="F989" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G989" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H989" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J989" t="str">
+        <v>39.459969</v>
+      </c>
+      <c r="K989" t="str">
+        <v>-0.381748</v>
+      </c>
+      <c r="L989" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M989" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B990" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C990" t="str">
+        <v>C/ d'Ercilla, 22</v>
+      </c>
+      <c r="D990" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E990">
+        <v>1</v>
+      </c>
+      <c r="F990" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G990" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H990" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J990" t="str">
+        <v>39.474067</v>
+      </c>
+      <c r="K990" t="str">
+        <v>-0.378172</v>
+      </c>
+      <c r="L990" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M990" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="O990" t="str">
+        <v>The best AirBnB</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B991" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C991" t="str">
+        <v>Gulliver park</v>
+      </c>
+      <c r="D991" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E991">
+        <v>1</v>
+      </c>
+      <c r="F991" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G991" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H991" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J991" t="str">
+        <v>39.462575</v>
+      </c>
+      <c r="K991" t="str">
+        <v>-0.359415</v>
+      </c>
+      <c r="L991" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M991" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="O991" t="str">
+        <v>coolest freaking park ever</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B992" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C992" t="str">
+        <v>Museu de les Ciències Príncipe Felipe</v>
+      </c>
+      <c r="D992" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E992">
+        <v>1</v>
+      </c>
+      <c r="F992" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G992" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H992" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J992" t="str">
+        <v>39.456107</v>
+      </c>
+      <c r="K992" t="str">
+        <v>-0.352084</v>
+      </c>
+      <c r="L992" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M992" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B993" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C993" t="str">
+        <v>Ciudad de las Artes y las Ciencias</v>
+      </c>
+      <c r="D993" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E993">
+        <v>1</v>
+      </c>
+      <c r="F993" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G993" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H993" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J993" t="str">
+        <v>39.454875</v>
+      </c>
+      <c r="K993" t="str">
+        <v>-0.35049</v>
+      </c>
+      <c r="L993" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M993" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B994" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C994" t="str">
+        <v>Mestalla Stadium</v>
+      </c>
+      <c r="D994" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E994">
+        <v>1</v>
+      </c>
+      <c r="F994" t="str">
+        <v>⚽</v>
+      </c>
+      <c r="G994" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H994" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J994" t="str">
+        <v>39.47466</v>
+      </c>
+      <c r="K994" t="str">
+        <v>-0.358588</v>
+      </c>
+      <c r="L994" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M994" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B995" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C995" t="str">
+        <v>Mercat Central</v>
+      </c>
+      <c r="D995" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E995">
+        <v>1</v>
+      </c>
+      <c r="F995" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G995" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H995" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J995" t="str">
+        <v>39.473372</v>
+      </c>
+      <c r="K995" t="str">
+        <v>-0.379102</v>
+      </c>
+      <c r="L995" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M995" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B996" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C996" t="str">
+        <v>Malvarrosa Beach</v>
+      </c>
+      <c r="D996" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E996">
+        <v>1</v>
+      </c>
+      <c r="F996" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G996" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H996" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J996" t="str">
+        <v>39.477383</v>
+      </c>
+      <c r="K996" t="str">
+        <v>-0.323376</v>
+      </c>
+      <c r="L996" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M996" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B997" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C997" t="str">
+        <v>Casa Carmela</v>
+      </c>
+      <c r="D997" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E997">
+        <v>1</v>
+      </c>
+      <c r="F997" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G997" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H997" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I997" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J997" t="str">
+        <v>39.482222</v>
+      </c>
+      <c r="K997" t="str">
+        <v>-0.325833</v>
+      </c>
+      <c r="L997" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M997" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B998" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="C998" t="str">
+        <v>Restaurante Copenhagen</v>
+      </c>
+      <c r="D998" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E998">
+        <v>1</v>
+      </c>
+      <c r="F998" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G998" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H998" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I998" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J998" t="str">
+        <v>39.460775</v>
+      </c>
+      <c r="K998" t="str">
+        <v>-0.373545</v>
+      </c>
+      <c r="L998" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M998" t="str">
+        <v>Valencia</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B999" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C999" t="str">
+        <v>Barcelona Sants</v>
+      </c>
+      <c r="D999" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E999">
+        <v>1</v>
+      </c>
+      <c r="F999" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G999" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H999" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J999" t="str">
+        <v>41.379093</v>
+      </c>
+      <c r="K999" t="str">
+        <v>2.140133</v>
+      </c>
+      <c r="L999" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M999" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O999" t="str">
+        <v>Train Station</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1000" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1000" t="str">
+        <v>Passatge Magarola, 4 (AirBnB)</v>
+      </c>
+      <c r="D1000" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1000">
+        <v>1</v>
+      </c>
+      <c r="F1000" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1000" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1000" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1000" t="str">
+        <v>41.38389</v>
+      </c>
+      <c r="K1000" t="str">
+        <v>2.17253</v>
+      </c>
+      <c r="L1000" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1000" t="str">
+        <v>Barcelona</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1001" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1001" t="str">
+        <v>Fat Tire Bike Tour Mtg Place</v>
+      </c>
+      <c r="D1001" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1001">
+        <v>1</v>
+      </c>
+      <c r="F1001" t="str">
+        <v>🚲</v>
+      </c>
+      <c r="G1001" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1001" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1001" t="str">
+        <v>41.382766</v>
+      </c>
+      <c r="K1001" t="str">
+        <v>2.177163</v>
+      </c>
+      <c r="L1001" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1001" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1001" t="str">
+        <v>Plaça de Sant Jaume</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1002" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1002" t="str">
+        <v>Montjuic Castle</v>
+      </c>
+      <c r="D1002" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1002">
+        <v>1</v>
+      </c>
+      <c r="F1002" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1002" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1002" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1002" t="str">
+        <v>41.367565</v>
+      </c>
+      <c r="K1002" t="str">
+        <v>2.168532</v>
+      </c>
+      <c r="L1002" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1002" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1002" t="str">
+        <v>Ctra. de Montjuïc, 66</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1003" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1003" t="str">
+        <v>Picasso Museum</v>
+      </c>
+      <c r="D1003" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1003">
+        <v>1</v>
+      </c>
+      <c r="F1003" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1003" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1003" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1003" t="str">
+        <v>41.385216</v>
+      </c>
+      <c r="K1003" t="str">
+        <v>2.180893</v>
+      </c>
+      <c r="L1003" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1003" t="str">
+        <v>Barcelona</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1004" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1004" t="str">
+        <v>Barceloneta Beach</v>
+      </c>
+      <c r="D1004" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1004">
+        <v>1</v>
+      </c>
+      <c r="F1004" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1004" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1004" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1004" t="str">
+        <v>41.377855</v>
+      </c>
+      <c r="K1004" t="str">
+        <v>2.190804</v>
+      </c>
+      <c r="L1004" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1004" t="str">
+        <v>Barcelona</v>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1005" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1005" t="str">
+        <v>La Sagrada Familia</v>
+      </c>
+      <c r="D1005" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1005">
+        <v>1</v>
+      </c>
+      <c r="F1005" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1005" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1005" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1005" t="str">
+        <v>41.404484</v>
+      </c>
+      <c r="K1005" t="str">
+        <v>2.175728</v>
+      </c>
+      <c r="L1005" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1005" t="str">
+        <v>Barcelona</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1006" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1006" t="str">
+        <v>Park Güell</v>
+      </c>
+      <c r="D1006" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1006">
+        <v>1</v>
+      </c>
+      <c r="F1006" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1006" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1006" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1006" t="str">
+        <v>41.414495</v>
+      </c>
+      <c r="K1006" t="str">
+        <v>2.152695</v>
+      </c>
+      <c r="L1006" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1006" t="str">
+        <v>Barcelona</v>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1007" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1007" t="str">
+        <v>Copasetic Barcelona</v>
+      </c>
+      <c r="D1007" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1007">
+        <v>1</v>
+      </c>
+      <c r="F1007" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1007" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1007" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1007" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1007" t="str">
+        <v>41.380239</v>
+      </c>
+      <c r="K1007" t="str">
+        <v>2.153261</v>
+      </c>
+      <c r="L1007" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1007" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1007" t="str">
+        <v>GF bread per yelp</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1008" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1008" t="str">
+        <v>La Lluna</v>
+      </c>
+      <c r="D1008" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1008">
+        <v>1</v>
+      </c>
+      <c r="F1008" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1008" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1008" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1008" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1008" t="str">
+        <v>41.38533</v>
+      </c>
+      <c r="K1008" t="str">
+        <v>2.17169</v>
+      </c>
+      <c r="L1008" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1008" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1008" t="str">
+        <v>GF rolls &amp; beer</v>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1009" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1009" t="str">
+        <v>Restaurant en Ville</v>
+      </c>
+      <c r="D1009" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1009">
+        <v>1</v>
+      </c>
+      <c r="F1009" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1009" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1009" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1009" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1009" t="str">
+        <v>41.382933</v>
+      </c>
+      <c r="K1009" t="str">
+        <v>2.168572</v>
+      </c>
+      <c r="L1009" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1009" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1009" t="str">
+        <v>GF menu</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1010" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1010" t="str">
+        <v>Restaurant La Brasserie du Gothique</v>
+      </c>
+      <c r="D1010" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1010">
+        <v>1</v>
+      </c>
+      <c r="F1010" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1010" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1010" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1010" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1010" t="str">
+        <v>41.384751</v>
+      </c>
+      <c r="K1010" t="str">
+        <v>2.174437</v>
+      </c>
+      <c r="L1010" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1010" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1010" t="str">
+        <v>GF bread &amp; chocolate coulant</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1011" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1011" t="str">
+        <v>Conesa Entrepans</v>
+      </c>
+      <c r="D1011" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1011">
+        <v>1</v>
+      </c>
+      <c r="F1011" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1011" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1011" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1011" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1011" t="str">
+        <v>41.375339</v>
+      </c>
+      <c r="K1011" t="str">
+        <v>2.144106</v>
+      </c>
+      <c r="L1011" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1011" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1011" t="str">
+        <v>GF sandwiches</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1012" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>L'antic bocoi del Gòtic</v>
+      </c>
+      <c r="D1012" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1012">
+        <v>1</v>
+      </c>
+      <c r="F1012" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1012" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1012" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1012" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1012" t="str">
+        <v>41.382094</v>
+      </c>
+      <c r="K1012" t="str">
+        <v>2.179426</v>
+      </c>
+      <c r="L1012" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1012" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1012" t="str">
+        <v>GF pizza per yelp</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1013" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>Restaurante Xaloc</v>
+      </c>
+      <c r="D1013" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1013">
+        <v>1</v>
+      </c>
+      <c r="F1013" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1013" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1013" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1013" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1013" t="str">
+        <v>41.383167</v>
+      </c>
+      <c r="K1013" t="str">
+        <v>2.174414</v>
+      </c>
+      <c r="L1013" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1013" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1013" t="str">
+        <v>GF Tapas</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1014" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>Rasoterra</v>
+      </c>
+      <c r="D1014" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1014">
+        <v>1</v>
+      </c>
+      <c r="F1014" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1014" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1014" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1014" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1014" t="str">
+        <v>41.381315</v>
+      </c>
+      <c r="K1014" t="str">
+        <v>2.178095</v>
+      </c>
+      <c r="L1014" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1014" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="O1014" t="str">
+        <v>GF Tapas</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1015" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>Madrid Atocha Railway Station</v>
+      </c>
+      <c r="D1015" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1015">
+        <v>1</v>
+      </c>
+      <c r="F1015" t="str">
+        <v>🚉</v>
+      </c>
+      <c r="G1015" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1015" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1015" t="str">
+        <v>40.407052</v>
+      </c>
+      <c r="K1015" t="str">
+        <v>-3.69135</v>
+      </c>
+      <c r="L1015" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1015" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1016" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>Madrid-Barajas Airport</v>
+      </c>
+      <c r="D1016" t="str">
+        <v>transit</v>
+      </c>
+      <c r="E1016">
+        <v>1</v>
+      </c>
+      <c r="F1016" t="str">
+        <v>✈️</v>
+      </c>
+      <c r="G1016" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1016" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1016" t="str">
+        <v>40.484067</v>
+      </c>
+      <c r="K1016" t="str">
+        <v>-3.567952</v>
+      </c>
+      <c r="L1016" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1016" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1017" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>Liabeny Hotel Madrid</v>
+      </c>
+      <c r="D1017" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1017">
+        <v>1</v>
+      </c>
+      <c r="F1017" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1017" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1017" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1017" t="str">
+        <v>40.418698</v>
+      </c>
+      <c r="K1017" t="str">
+        <v>-3.703969</v>
+      </c>
+      <c r="L1017" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1017" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1018" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>Puerta del Sol</v>
+      </c>
+      <c r="D1018" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1018">
+        <v>1</v>
+      </c>
+      <c r="F1018" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1018" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1018" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1018" t="str">
+        <v>40.416883</v>
+      </c>
+      <c r="K1018" t="str">
+        <v>-3.70244</v>
+      </c>
+      <c r="L1018" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1018" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1019" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>Santiago Bernabeu</v>
+      </c>
+      <c r="D1019" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1019">
+        <v>1</v>
+      </c>
+      <c r="F1019" t="str">
+        <v>⚽</v>
+      </c>
+      <c r="G1019" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1019" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1019" t="str">
+        <v>40.452142</v>
+      </c>
+      <c r="K1019" t="str">
+        <v>-3.690386</v>
+      </c>
+      <c r="L1019" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1019" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="O1019" t="str">
+        <v>Real Madrid Stadium</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1020" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>Teleferico en Rosales</v>
+      </c>
+      <c r="D1020" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1020">
+        <v>1</v>
+      </c>
+      <c r="F1020" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1020" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1020" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1020" t="str">
+        <v>40.426433</v>
+      </c>
+      <c r="K1020" t="str">
+        <v>-3.71887</v>
+      </c>
+      <c r="L1020" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1020" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="O1020" t="str">
+        <v>Estación de Teleférico en Rosales</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1021" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>Teleferico</v>
+      </c>
+      <c r="D1021" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1021">
+        <v>1</v>
+      </c>
+      <c r="F1021" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1021" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1021" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1021" t="str">
+        <v>40.419683</v>
+      </c>
+      <c r="K1021" t="str">
+        <v>-3.74913</v>
+      </c>
+      <c r="L1021" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1021" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1022" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>Reina Sofía Museum</v>
+      </c>
+      <c r="D1022" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1022">
+        <v>1</v>
+      </c>
+      <c r="F1022" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1022" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1022" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1022" t="str">
+        <v>40.407912</v>
+      </c>
+      <c r="K1022" t="str">
+        <v>-3.694557</v>
+      </c>
+      <c r="L1022" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1022" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1023" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>Prado Museum</v>
+      </c>
+      <c r="D1023" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1023">
+        <v>1</v>
+      </c>
+      <c r="F1023" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1023" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1023" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1023" t="str">
+        <v>40.413782</v>
+      </c>
+      <c r="K1023" t="str">
+        <v>-3.692127</v>
+      </c>
+      <c r="L1023" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1023" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1024" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>El Retiro Park</v>
+      </c>
+      <c r="D1024" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1024">
+        <v>1</v>
+      </c>
+      <c r="F1024" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1024" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1024" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1024" t="str">
+        <v>40.415261</v>
+      </c>
+      <c r="K1024" t="str">
+        <v>-3.6845</v>
+      </c>
+      <c r="L1024" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1024" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1025" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>Plaza Mayor</v>
+      </c>
+      <c r="D1025" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1025">
+        <v>1</v>
+      </c>
+      <c r="F1025" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1025" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1025" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1025" t="str">
+        <v>40.415618</v>
+      </c>
+      <c r="K1025" t="str">
+        <v>-3.707023</v>
+      </c>
+      <c r="L1025" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1025" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="O1025" t="str">
+        <v>Main Square</v>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1026" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>Royal Palace</v>
+      </c>
+      <c r="D1026" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1026">
+        <v>1</v>
+      </c>
+      <c r="F1026" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1026" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1026" t="str">
+        <v>2014</v>
+      </c>
+      <c r="J1026" t="str">
+        <v>40.417955</v>
+      </c>
+      <c r="K1026" t="str">
+        <v>-3.714312</v>
+      </c>
+      <c r="L1026" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1026" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1027" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>Rodilla</v>
+      </c>
+      <c r="D1027" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1027">
+        <v>1</v>
+      </c>
+      <c r="F1027" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1027" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1027" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1027" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1027" t="str">
+        <v>40.403475</v>
+      </c>
+      <c r="K1027" t="str">
+        <v>-3.714402</v>
+      </c>
+      <c r="L1027" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1027" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1028" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>Maestro Churrero</v>
+      </c>
+      <c r="D1028" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1028">
+        <v>1</v>
+      </c>
+      <c r="F1028" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1028" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1028" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1028" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1028" t="str">
+        <v>40.414174</v>
+      </c>
+      <c r="K1028" t="str">
+        <v>-3.703178</v>
+      </c>
+      <c r="L1028" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1028" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1029" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>II Piccolino della Farfalla</v>
+      </c>
+      <c r="D1029" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1029">
+        <v>1</v>
+      </c>
+      <c r="F1029" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1029" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1029" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1029" t="str">
+        <v>has_gf_options</v>
+      </c>
+      <c r="J1029" t="str">
+        <v>40.413932</v>
+      </c>
+      <c r="K1029" t="str">
+        <v>-3.701007</v>
+      </c>
+      <c r="L1029" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1029" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="O1029" t="str">
+        <v>GF pizza &amp; beer</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1030" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>CELICIOSO Gluten Free Bakery</v>
+      </c>
+      <c r="D1030" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1030">
+        <v>1</v>
+      </c>
+      <c r="F1030" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1030" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1030" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1030" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1030" t="str">
+        <v>40.420441</v>
+      </c>
+      <c r="K1030" t="str">
+        <v>-3.701066</v>
+      </c>
+      <c r="L1030" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1030" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1031" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>Rosa Negra Madrid</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1031">
+        <v>1</v>
+      </c>
+      <c r="F1031" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1031" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1031" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1031" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1031" t="str">
+        <v>40.413832</v>
+      </c>
+      <c r="K1031" t="str">
+        <v>-3.698983</v>
+      </c>
+      <c r="L1031" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1031" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="B1032" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="C1032" t="str">
+        <v>Taberna LA CONCHA</v>
+      </c>
+      <c r="D1032" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1032">
+        <v>1</v>
+      </c>
+      <c r="F1032" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1032" t="str">
+        <v>Oct</v>
+      </c>
+      <c r="H1032" t="str">
+        <v>2014</v>
+      </c>
+      <c r="I1032" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1032" t="str">
+        <v>40.413191</v>
+      </c>
+      <c r="K1032" t="str">
+        <v>-3.708358</v>
+      </c>
+      <c r="L1032" t="str">
+        <v>Spain (October 2014)</v>
+      </c>
+      <c r="M1032" t="str">
+        <v>Madrid</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U988"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1032"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -41984,7 +41984,7 @@
         <v>Oct</v>
       </c>
       <c r="H989" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J989" t="str">
         <v>39.459969</v>
@@ -42022,7 +42022,7 @@
         <v>Oct</v>
       </c>
       <c r="H990" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J990" t="str">
         <v>39.474067</v>
@@ -42063,7 +42063,7 @@
         <v>Oct</v>
       </c>
       <c r="H991" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J991" t="str">
         <v>39.462575</v>
@@ -42104,7 +42104,7 @@
         <v>Oct</v>
       </c>
       <c r="H992" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J992" t="str">
         <v>39.456107</v>
@@ -42142,7 +42142,7 @@
         <v>Oct</v>
       </c>
       <c r="H993" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J993" t="str">
         <v>39.454875</v>
@@ -42180,7 +42180,7 @@
         <v>Oct</v>
       </c>
       <c r="H994" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J994" t="str">
         <v>39.47466</v>
@@ -42218,7 +42218,7 @@
         <v>Oct</v>
       </c>
       <c r="H995" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J995" t="str">
         <v>39.473372</v>
@@ -42256,7 +42256,7 @@
         <v>Oct</v>
       </c>
       <c r="H996" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J996" t="str">
         <v>39.477383</v>
@@ -42294,7 +42294,7 @@
         <v>Oct</v>
       </c>
       <c r="H997" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I997" t="str">
         <v>unclear</v>
@@ -42335,7 +42335,7 @@
         <v>Oct</v>
       </c>
       <c r="H998" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I998" t="str">
         <v>unclear</v>
@@ -42376,7 +42376,7 @@
         <v>Oct</v>
       </c>
       <c r="H999" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J999" t="str">
         <v>41.379093</v>
@@ -42417,7 +42417,7 @@
         <v>Oct</v>
       </c>
       <c r="H1000" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1000" t="str">
         <v>41.38389</v>
@@ -42455,7 +42455,7 @@
         <v>Oct</v>
       </c>
       <c r="H1001" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1001" t="str">
         <v>41.382766</v>
@@ -42496,7 +42496,7 @@
         <v>Oct</v>
       </c>
       <c r="H1002" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1002" t="str">
         <v>41.367565</v>
@@ -42537,7 +42537,7 @@
         <v>Oct</v>
       </c>
       <c r="H1003" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1003" t="str">
         <v>41.385216</v>
@@ -42575,7 +42575,7 @@
         <v>Oct</v>
       </c>
       <c r="H1004" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1004" t="str">
         <v>41.377855</v>
@@ -42613,7 +42613,7 @@
         <v>Oct</v>
       </c>
       <c r="H1005" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1005" t="str">
         <v>41.404484</v>
@@ -42651,7 +42651,7 @@
         <v>Oct</v>
       </c>
       <c r="H1006" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J1006" t="str">
         <v>41.414495</v>
@@ -42689,7 +42689,7 @@
         <v>Oct</v>
       </c>
       <c r="H1007" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1007" t="str">
         <v>has_gf_options</v>
@@ -42733,7 +42733,7 @@
         <v>Oct</v>
       </c>
       <c r="H1008" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1008" t="str">
         <v>has_gf_options</v>
@@ -42777,7 +42777,7 @@
         <v>Oct</v>
       </c>
       <c r="H1009" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1009" t="str">
         <v>has_gf_options</v>
@@ -42821,7 +42821,7 @@
         <v>Oct</v>
       </c>
       <c r="H1010" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1010" t="str">
         <v>has_gf_options</v>
@@ -42865,7 +42865,7 @@
         <v>Oct</v>
       </c>
       <c r="H1011" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1011" t="str">
         <v>has_gf_options</v>
@@ -42909,7 +42909,7 @@
         <v>Oct</v>
       </c>
       <c r="H1012" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1012" t="str">
         <v>has_gf_options</v>
@@ -42953,7 +42953,7 @@
         <v>Oct</v>
       </c>
       <c r="H1013" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1013" t="str">
         <v>has_gf_options</v>
@@ -42997,7 +42997,7 @@
         <v>Oct</v>
       </c>
       <c r="H1014" t="str">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="I1014" t="str">
         <v>has_gf_options</v>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -43040,8 +43040,8 @@
       <c r="G1015" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1015" t="str">
-        <v>2014</v>
+      <c r="H1015">
+        <v>2016</v>
       </c>
       <c r="J1015" t="str">
         <v>40.407052</v>
@@ -43078,8 +43078,8 @@
       <c r="G1016" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1016" t="str">
-        <v>2014</v>
+      <c r="H1016">
+        <v>2016</v>
       </c>
       <c r="J1016" t="str">
         <v>40.484067</v>
@@ -43116,8 +43116,8 @@
       <c r="G1017" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1017" t="str">
-        <v>2014</v>
+      <c r="H1017">
+        <v>2016</v>
       </c>
       <c r="J1017" t="str">
         <v>40.418698</v>
@@ -43130,6 +43130,12 @@
       </c>
       <c r="M1017" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="S1017" t="str">
+        <v>https://www.hotels.com/ho195507/hotel-liabeny-madrid-spain/</v>
+      </c>
+      <c r="U1017" t="str">
+        <v>4-star, 220 rooms, near Puerta del Sol/Gran Via. No specific GF breakfast claim verified. | GF breakfast confirmed: gluten-free bread available at breakfast and in the bar; staff responsive to celiac/dietary requests (verified 2026).</v>
       </c>
     </row>
     <row r="1018">
@@ -43154,8 +43160,8 @@
       <c r="G1018" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1018" t="str">
-        <v>2014</v>
+      <c r="H1018">
+        <v>2016</v>
       </c>
       <c r="J1018" t="str">
         <v>40.416883</v>
@@ -43192,8 +43198,8 @@
       <c r="G1019" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1019" t="str">
-        <v>2014</v>
+      <c r="H1019">
+        <v>2016</v>
       </c>
       <c r="J1019" t="str">
         <v>40.452142</v>
@@ -43209,6 +43215,9 @@
       </c>
       <c r="O1019" t="str">
         <v>Real Madrid Stadium</v>
+      </c>
+      <c r="S1019" t="str">
+        <v>https://www.viator.com/Madrid-attractions/Santiago-Bernabeu-Stadium/d566-a9838</v>
       </c>
     </row>
     <row r="1020">
@@ -43233,8 +43242,8 @@
       <c r="G1020" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1020" t="str">
-        <v>2014</v>
+      <c r="H1020">
+        <v>2016</v>
       </c>
       <c r="J1020" t="str">
         <v>40.426433</v>
@@ -43274,8 +43283,8 @@
       <c r="G1021" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1021" t="str">
-        <v>2014</v>
+      <c r="H1021">
+        <v>2016</v>
       </c>
       <c r="J1021" t="str">
         <v>40.419683</v>
@@ -43312,8 +43321,8 @@
       <c r="G1022" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1022" t="str">
-        <v>2014</v>
+      <c r="H1022">
+        <v>2016</v>
       </c>
       <c r="J1022" t="str">
         <v>40.407912</v>
@@ -43326,6 +43335,9 @@
       </c>
       <c r="M1022" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="S1022" t="str">
+        <v>https://www.viator.com/Madrid-attractions/Reina-Sofia-Museum-Museo-Nacional-Centro-de-Arte-Reina-Sofia/d566-a2946</v>
       </c>
     </row>
     <row r="1023">
@@ -43350,8 +43362,8 @@
       <c r="G1023" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1023" t="str">
-        <v>2014</v>
+      <c r="H1023">
+        <v>2016</v>
       </c>
       <c r="J1023" t="str">
         <v>40.413782</v>
@@ -43364,6 +43376,9 @@
       </c>
       <c r="M1023" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="S1023" t="str">
+        <v>https://www.viator.com/Madrid-attractions/Prado-Museum-Museo-del-Prado/d566-a852</v>
       </c>
     </row>
     <row r="1024">
@@ -43388,8 +43403,8 @@
       <c r="G1024" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1024" t="str">
-        <v>2014</v>
+      <c r="H1024">
+        <v>2016</v>
       </c>
       <c r="J1024" t="str">
         <v>40.415261</v>
@@ -43426,8 +43441,8 @@
       <c r="G1025" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1025" t="str">
-        <v>2014</v>
+      <c r="H1025">
+        <v>2016</v>
       </c>
       <c r="J1025" t="str">
         <v>40.415618</v>
@@ -43467,8 +43482,8 @@
       <c r="G1026" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1026" t="str">
-        <v>2014</v>
+      <c r="H1026">
+        <v>2016</v>
       </c>
       <c r="J1026" t="str">
         <v>40.417955</v>
@@ -43505,11 +43520,11 @@
       <c r="G1027" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1027" t="str">
-        <v>2014</v>
+      <c r="H1027">
+        <v>2016</v>
       </c>
       <c r="I1027" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J1027" t="str">
         <v>40.403475</v>
@@ -43522,6 +43537,15 @@
       </c>
       <c r="M1027" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="P1027" t="str">
+        <v>https://www.findmeglutenfree.com/biz/rodilla/6062196411203584</v>
+      </c>
+      <c r="Q1027">
+        <v>4</v>
+      </c>
+      <c r="R1027" t="str">
+        <v>[2026-07-28 research] GF sandwiches wrapped and toasted in parchment paper to prevent cross-contact, served on color-coded trays. Shared ovens, not a dedicated kitchen. Chain with multiple Madrid locations.</v>
       </c>
     </row>
     <row r="1028">
@@ -43546,11 +43570,11 @@
       <c r="G1028" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1028" t="str">
-        <v>2014</v>
+      <c r="H1028">
+        <v>2016</v>
       </c>
       <c r="I1028" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J1028" t="str">
         <v>40.414174</v>
@@ -43563,6 +43587,15 @@
       </c>
       <c r="M1028" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="P1028" t="str">
+        <v>https://www.findmeglutenfree.com/biz/maestro-churrero/6567480126603264</v>
+      </c>
+      <c r="Q1028">
+        <v>4</v>
+      </c>
+      <c r="R1028" t="str">
+        <v>[2026-07-28 research] Dedicated fryer for GF churros with clear labeling, but not a fully dedicated kitchen. Reviews on cross-contamination consistency vary by location.</v>
       </c>
     </row>
     <row r="1029">
@@ -43587,11 +43620,11 @@
       <c r="G1029" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1029" t="str">
-        <v>2014</v>
+      <c r="H1029">
+        <v>2016</v>
       </c>
       <c r="I1029" t="str">
-        <v>has_gf_options</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J1029" t="str">
         <v>40.413932</v>
@@ -43607,6 +43640,15 @@
       </c>
       <c r="O1029" t="str">
         <v>GF pizza &amp; beer</v>
+      </c>
+      <c r="P1029" t="str">
+        <v>https://www.findmeglutenfree.com/biz/ii-piccolino-della-farfalla/6190799684370432</v>
+      </c>
+      <c r="Q1029">
+        <v>5</v>
+      </c>
+      <c r="R1029" t="str">
+        <v>[2026-07-28 research] Certified GF menu with GF pizza, pasta, and beer. Staff knowledgeable about celiac precautions. Reservations recommended due to demand.</v>
       </c>
     </row>
     <row r="1030">
@@ -43631,11 +43673,11 @@
       <c r="G1030" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1030" t="str">
-        <v>2014</v>
+      <c r="H1030">
+        <v>2016</v>
       </c>
       <c r="I1030" t="str">
-        <v>unclear</v>
+        <v>100% dedicated GF</v>
       </c>
       <c r="J1030" t="str">
         <v>40.420441</v>
@@ -43648,6 +43690,15 @@
       </c>
       <c r="M1030" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="P1030" t="str">
+        <v>https://www.findmeglutenfree.com/biz/celicioso/4647413522366464</v>
+      </c>
+      <c r="Q1030">
+        <v>5</v>
+      </c>
+      <c r="R1030" t="str">
+        <v>[2026-07-28 research] Fully dedicated gluten-free bakery. Cakes, pastries, sandwiches, salads. Known for banana cake, carrot cake, cheesecake.</v>
       </c>
     </row>
     <row r="1031">
@@ -43672,11 +43723,11 @@
       <c r="G1031" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1031" t="str">
-        <v>2014</v>
+      <c r="H1031">
+        <v>2016</v>
       </c>
       <c r="I1031" t="str">
-        <v>unclear</v>
+        <v>mixed safety</v>
       </c>
       <c r="J1031" t="str">
         <v>40.413832</v>
@@ -43689,6 +43740,15 @@
       </c>
       <c r="M1031" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="P1031" t="str">
+        <v>https://www.findmeglutenfree.com/biz/rosa-negra-madrid/6371167554502656</v>
+      </c>
+      <c r="Q1031">
+        <v>2</v>
+      </c>
+      <c r="R1031" t="str">
+        <v>[2026-07-28 research] Not a dedicated facility. GF options rely on naturally GF items like corn tortillas; GF beer available. Verify current protocols with staff.</v>
       </c>
     </row>
     <row r="1032">
@@ -43713,11 +43773,11 @@
       <c r="G1032" t="str">
         <v>Oct</v>
       </c>
-      <c r="H1032" t="str">
-        <v>2014</v>
+      <c r="H1032">
+        <v>2016</v>
       </c>
       <c r="I1032" t="str">
-        <v>unclear</v>
+        <v>celiac-aware</v>
       </c>
       <c r="J1032" t="str">
         <v>40.413191</v>
@@ -43730,6 +43790,15 @@
       </c>
       <c r="M1032" t="str">
         <v>Madrid</v>
+      </c>
+      <c r="P1032" t="str">
+        <v>https://www.findmeglutenfree.com/biz/taberna-la-concha/6065149746085888</v>
+      </c>
+      <c r="Q1032">
+        <v>4</v>
+      </c>
+      <c r="R1032" t="str">
+        <v>[2026-07-28 research] 28 of 30 tapas available in GF version; full GF menu offered in multiple languages. Not a dedicated facility.</v>
       </c>
     </row>
   </sheetData>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1032"/>
+  <dimension ref="A1:U1046"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -43801,9 +43801,544 @@
         <v>[2026-07-28 research] 28 of 30 tapas available in GF version; full GF menu offered in multiple languages. Not a dedicated facility.</v>
       </c>
     </row>
+    <row r="1033">
+      <c r="A1033" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1033" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="C1033" t="str">
+        <v>Kempegowda International Airport Bengaluru</v>
+      </c>
+      <c r="D1033" t="str">
+        <v>airport</v>
+      </c>
+      <c r="E1033">
+        <v>1</v>
+      </c>
+      <c r="G1033" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1033">
+        <v>2026</v>
+      </c>
+      <c r="J1033">
+        <v>13.198909</v>
+      </c>
+      <c r="K1033">
+        <v>77.7068926</v>
+      </c>
+      <c r="L1033" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1033" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1034" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="C1034" t="str">
+        <v>Taj Bangalore, Bengaluru</v>
+      </c>
+      <c r="D1034" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1034">
+        <v>1</v>
+      </c>
+      <c r="G1034" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1034">
+        <v>2026</v>
+      </c>
+      <c r="J1034">
+        <v>13.1971286</v>
+      </c>
+      <c r="K1034">
+        <v>77.7101357</v>
+      </c>
+      <c r="L1034" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1034" t="str">
+        <v/>
+      </c>
+      <c r="S1034" t="str">
+        <v>https://www.hotels.com/ho416915296/taj-bangalore-devanahalli-india/</v>
+      </c>
+      <c r="U1034" t="str">
+        <v>Gluten-free options available at breakfast buffet; guests report good variety; lactose-free milk available.</v>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1035" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="C1035" t="str">
+        <v>JW Marriott Bengaluru Prestige Golfshire Resort &amp; Spa</v>
+      </c>
+      <c r="D1035" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1035">
+        <v>1</v>
+      </c>
+      <c r="G1035" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1035">
+        <v>2026</v>
+      </c>
+      <c r="J1035">
+        <v>13.3090165</v>
+      </c>
+      <c r="K1035">
+        <v>77.6902861</v>
+      </c>
+      <c r="L1035" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1035" t="str">
+        <v/>
+      </c>
+      <c r="S1035" t="str">
+        <v>https://www.booking.com/hotel/in/jw-marriott-bengaluru-prestige-golfshire-resort-spa.html</v>
+      </c>
+      <c r="U1035" t="str">
+        <v>Gluten-free options available upon request at breakfast buffet; recommend pre-notifying the hotel.</v>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1036" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="C1036" t="str">
+        <v>Bengaluru Marriott Hotel Whitefield</v>
+      </c>
+      <c r="D1036" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1036">
+        <v>1</v>
+      </c>
+      <c r="G1036" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1036">
+        <v>2026</v>
+      </c>
+      <c r="J1036">
+        <v>12.9792093</v>
+      </c>
+      <c r="K1036">
+        <v>77.727996</v>
+      </c>
+      <c r="L1036" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1036" t="str">
+        <v/>
+      </c>
+      <c r="S1036" t="str">
+        <v>https://www.hotels.com/ho428436/bengaluru-marriott-hotel-whitefield-bengaluru-india/</v>
+      </c>
+      <c r="U1036" t="str">
+        <v>Dietary accommodations available; highly rated; request GF options at check-in.</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1037" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="C1037" t="str">
+        <v>BLR Brewing Co - Whitefield</v>
+      </c>
+      <c r="D1037" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1037">
+        <v>1</v>
+      </c>
+      <c r="G1037" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1037">
+        <v>2026</v>
+      </c>
+      <c r="I1037" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1037">
+        <v>12.9821225</v>
+      </c>
+      <c r="K1037">
+        <v>77.7089609</v>
+      </c>
+      <c r="L1037" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1037" t="str">
+        <v>Has GF options</v>
+      </c>
+      <c r="Q1037">
+        <v>1</v>
+      </c>
+      <c r="R1037" t="str">
+        <v>[2026-07-30 research] No verified GF safety details found publicly. Spreadsheet note says 'Has GF options' — confirm directly with staff before dining.</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1038" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="C1038" t="str">
+        <v>Rajiv Gandhi International Airport</v>
+      </c>
+      <c r="D1038" t="str">
+        <v>airport</v>
+      </c>
+      <c r="E1038">
+        <v>1</v>
+      </c>
+      <c r="G1038" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1038">
+        <v>2026</v>
+      </c>
+      <c r="J1038">
+        <v>17.2402827</v>
+      </c>
+      <c r="K1038">
+        <v>78.429358</v>
+      </c>
+      <c r="L1038" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1038" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1039" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="C1039" t="str">
+        <v>ITC Kohenur, a Luxury Collection Hotel, Hyderabad</v>
+      </c>
+      <c r="D1039" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1039">
+        <v>1</v>
+      </c>
+      <c r="G1039" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1039">
+        <v>2026</v>
+      </c>
+      <c r="J1039">
+        <v>17.4320616</v>
+      </c>
+      <c r="K1039">
+        <v>78.3850482</v>
+      </c>
+      <c r="L1039" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1039" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1040" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="C1040" t="str">
+        <v>Charminar</v>
+      </c>
+      <c r="D1040" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1040">
+        <v>1</v>
+      </c>
+      <c r="G1040" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1040">
+        <v>2026</v>
+      </c>
+      <c r="J1040">
+        <v>17.3615636</v>
+      </c>
+      <c r="K1040">
+        <v>78.4746645</v>
+      </c>
+      <c r="L1040" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1040" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1041" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="C1041" t="str">
+        <v>Birla Temple</v>
+      </c>
+      <c r="D1041" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1041">
+        <v>1</v>
+      </c>
+      <c r="G1041" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1041">
+        <v>2026</v>
+      </c>
+      <c r="J1041">
+        <v>17.4062367</v>
+      </c>
+      <c r="K1041">
+        <v>78.4690601</v>
+      </c>
+      <c r="L1041" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1041" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1042" t="str">
+        <v>Hyderabad</v>
+      </c>
+      <c r="C1042" t="str">
+        <v>Almond House</v>
+      </c>
+      <c r="D1042" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1042">
+        <v>1</v>
+      </c>
+      <c r="G1042" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1042">
+        <v>2026</v>
+      </c>
+      <c r="J1042">
+        <v>17.4859258</v>
+      </c>
+      <c r="K1042">
+        <v>78.3903757</v>
+      </c>
+      <c r="L1042" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1042" t="str">
+        <v>Sweets shop with several GF options. So good@!</v>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1043" t="str">
+        <v>Goa</v>
+      </c>
+      <c r="C1043" t="str">
+        <v>Goa Dabolim International Airport</v>
+      </c>
+      <c r="D1043" t="str">
+        <v>airport</v>
+      </c>
+      <c r="E1043">
+        <v>1</v>
+      </c>
+      <c r="G1043" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1043">
+        <v>2026</v>
+      </c>
+      <c r="J1043">
+        <v>15.3804965</v>
+      </c>
+      <c r="K1043">
+        <v>73.8331652</v>
+      </c>
+      <c r="L1043" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1043" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1044" t="str">
+        <v>Goa</v>
+      </c>
+      <c r="C1044" t="str">
+        <v>ITC Grand Goa, a Luxury Collection Resort &amp; Spa, Goa</v>
+      </c>
+      <c r="D1044" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1044">
+        <v>1</v>
+      </c>
+      <c r="G1044" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1044">
+        <v>2026</v>
+      </c>
+      <c r="J1044">
+        <v>15.3277954</v>
+      </c>
+      <c r="K1044">
+        <v>73.8988772</v>
+      </c>
+      <c r="L1044" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1044" t="str">
+        <v/>
+      </c>
+      <c r="S1044" t="str">
+        <v>https://www.hotels.com/ho986079936/itc-grand-goa-a-luxury-collection-resort-spa-goa-cansaulim-india/</v>
+      </c>
+      <c r="U1044" t="str">
+        <v>Beachfront resort with 4 restaurants; ITC Luxury Collection properties generally accommodate special dietary requests.</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1045" t="str">
+        <v>Goa</v>
+      </c>
+      <c r="C1045" t="str">
+        <v>Mama Miso</v>
+      </c>
+      <c r="D1045" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1045">
+        <v>1</v>
+      </c>
+      <c r="G1045" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1045">
+        <v>2026</v>
+      </c>
+      <c r="I1045" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1045">
+        <v>15.3356908</v>
+      </c>
+      <c r="K1045">
+        <v>73.8968737</v>
+      </c>
+      <c r="L1045" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1045" t="str">
+        <v>Able to make GF sushi rolls and several other options. Great restaurant and very affordable!</v>
+      </c>
+      <c r="Q1045">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v>India</v>
+      </c>
+      <c r="B1046" t="str">
+        <v>Goa</v>
+      </c>
+      <c r="C1046" t="str">
+        <v>Bonita</v>
+      </c>
+      <c r="D1046" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1046">
+        <v>0</v>
+      </c>
+      <c r="G1046" t="str">
+        <v>April</v>
+      </c>
+      <c r="H1046">
+        <v>2026</v>
+      </c>
+      <c r="I1046" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1046">
+        <v>15.3362396</v>
+      </c>
+      <c r="K1046">
+        <v>73.8969019</v>
+      </c>
+      <c r="L1046" t="str">
+        <v>India (April 2026)</v>
+      </c>
+      <c r="O1046" t="str">
+        <v>Didn't go here but seems to have GF options</v>
+      </c>
+      <c r="Q1046">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1032"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1046"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1046"/>
+  <dimension ref="A1:U1059"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -44336,9 +44336,572 @@
         <v>2</v>
       </c>
     </row>
+    <row r="1047">
+      <c r="A1047" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1047" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1047" t="str">
+        <v>Posada Real Restaurante y Café</v>
+      </c>
+      <c r="D1047" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1047">
+        <v>1</v>
+      </c>
+      <c r="F1047" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1047" t="str">
+        <v>Aug</v>
+      </c>
+      <c r="H1047" t="str">
+        <v>2023</v>
+      </c>
+      <c r="I1047" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1047" t="str">
+        <v>10.628259</v>
+      </c>
+      <c r="K1047" t="str">
+        <v>-85.4372217</v>
+      </c>
+      <c r="L1047" t="str">
+        <v>Costa Rica (August 2023)</v>
+      </c>
+      <c r="M1047" t="str">
+        <v>Liberia, Costa Rica</v>
+      </c>
+      <c r="O1047" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="P1047" t="str">
+        <v>https://www.findmeglutenfree.com/biz/posada-real/6559037355327488</v>
+      </c>
+      <c r="Q1047">
+        <v>5</v>
+      </c>
+      <c r="R1047" t="str">
+        <v>100% dedicated GF facility; owner's wife is celiac. GF pizza, bread, donuts, fries, wood-fired pizza, steaks.</v>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1048" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1048" t="str">
+        <v>Monk &amp; Capra Coffee Brewers</v>
+      </c>
+      <c r="D1048" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1048">
+        <v>1</v>
+      </c>
+      <c r="F1048" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1048" t="str">
+        <v>Aug</v>
+      </c>
+      <c r="H1048" t="str">
+        <v>2023</v>
+      </c>
+      <c r="I1048" t="str">
+        <v>unclear</v>
+      </c>
+      <c r="J1048" t="str">
+        <v>10.5905938</v>
+      </c>
+      <c r="K1048" t="str">
+        <v>-85.5353666</v>
+      </c>
+      <c r="L1048" t="str">
+        <v>Costa Rica (August 2023)</v>
+      </c>
+      <c r="M1048" t="str">
+        <v>Liberia, Costa Rica</v>
+      </c>
+      <c r="O1048" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="Q1048">
+        <v>2</v>
+      </c>
+      <c r="R1048" t="str">
+        <v>Highly-rated specialty coffee shop; no confirmed GF menu labeling or protocol found — confirm in person.</v>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1049" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1049" t="str">
+        <v>Café Europa</v>
+      </c>
+      <c r="D1049" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1049">
+        <v>0</v>
+      </c>
+      <c r="F1049" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="I1049" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="O1049" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip). Sourced via web research to fill out a thin restaurant list, not a trip photo/pin.</v>
+      </c>
+      <c r="Q1049">
+        <v>4</v>
+      </c>
+      <c r="R1049" t="str">
+        <v>Web-supplemented (not personally visited). Dedicated GF/vegan menu since 2019; large GF bakery selection.</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1050" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1050" t="str">
+        <v>Father Rooster's Beachfront Bar &amp; Grill</v>
+      </c>
+      <c r="D1050" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1050">
+        <v>0</v>
+      </c>
+      <c r="F1050" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="I1050" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="O1050" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip). Sourced via web research to fill out a thin restaurant list, not a trip photo/pin.</v>
+      </c>
+      <c r="Q1050">
+        <v>4</v>
+      </c>
+      <c r="R1050" t="str">
+        <v>Web-supplemented. GF menu with marked allergens; known for GF fries and fish &amp; chips.</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1051" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>Ginger Restaurant Bar</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1051">
+        <v>0</v>
+      </c>
+      <c r="F1051" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="I1051" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="O1051" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip). Sourced via web research to fill out a thin restaurant list, not a trip photo/pin.</v>
+      </c>
+      <c r="Q1051">
+        <v>4</v>
+      </c>
+      <c r="R1051" t="str">
+        <v>Web-supplemented. Dedicated fryer for GF items, chef trained in GF prep.</v>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1052" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>Ticoffia Cafe</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1052">
+        <v>0</v>
+      </c>
+      <c r="F1052" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="I1052" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="O1052" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip). Sourced via web research to fill out a thin restaurant list, not a trip photo/pin.</v>
+      </c>
+      <c r="Q1052">
+        <v>3</v>
+      </c>
+      <c r="R1052" t="str">
+        <v>Web-supplemented. Casual local café with GF-labeled banana bread, eggs, smoothie bowls.</v>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1053" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>Hilton Garden Inn Guanacaste Airport</v>
+      </c>
+      <c r="D1053" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1053">
+        <v>1</v>
+      </c>
+      <c r="F1053" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1053" t="str">
+        <v>Aug</v>
+      </c>
+      <c r="H1053" t="str">
+        <v>2023</v>
+      </c>
+      <c r="J1053" t="str">
+        <v>10.5920454</v>
+      </c>
+      <c r="K1053" t="str">
+        <v>-85.5311198</v>
+      </c>
+      <c r="L1053" t="str">
+        <v>Costa Rica (August 2023)</v>
+      </c>
+      <c r="M1053" t="str">
+        <v>Liberia, Costa Rica</v>
+      </c>
+      <c r="O1053" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="U1053" t="str">
+        <v>No confirmed dedicated GF breakfast program; standard hotel restaurant/bar on-site.</v>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v>Costa Rica</v>
+      </c>
+      <c r="B1054" t="str">
+        <v>Liberia</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>El Mangroove, Autograph Collection</v>
+      </c>
+      <c r="D1054" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1054">
+        <v>1</v>
+      </c>
+      <c r="F1054" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1054" t="str">
+        <v>Aug</v>
+      </c>
+      <c r="H1054" t="str">
+        <v>2023</v>
+      </c>
+      <c r="J1054" t="str">
+        <v>10.5891258</v>
+      </c>
+      <c r="K1054" t="str">
+        <v>-85.6505057</v>
+      </c>
+      <c r="L1054" t="str">
+        <v>Costa Rica (August 2023)</v>
+      </c>
+      <c r="M1054" t="str">
+        <v>Liberia, Costa Rica</v>
+      </c>
+      <c r="O1054" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="U1054" t="str">
+        <v>Farm-to-table restaurants (Matiss, Makoko); no specific GF program independently confirmed.</v>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v>Maldives</v>
+      </c>
+      <c r="B1055" t="str">
+        <v>South Malé Atoll</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>Cumin</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1055">
+        <v>1</v>
+      </c>
+      <c r="F1055" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1055" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="H1055" t="str">
+        <v>2025</v>
+      </c>
+      <c r="I1055" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1055" t="str">
+        <v>3.9667839</v>
+      </c>
+      <c r="K1055" t="str">
+        <v>73.505245</v>
+      </c>
+      <c r="L1055" t="str">
+        <v>Maldives (July 2025)</v>
+      </c>
+      <c r="M1055" t="str">
+        <v>South Malé Atoll, Maldives</v>
+      </c>
+      <c r="O1055" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="Q1055">
+        <v>5</v>
+      </c>
+      <c r="R1055" t="str">
+        <v>Amazing for breakfast. Took gluten allergies very seriously — chef made a custom selection of GF breads and pastries (banana bread, coffee cake, etc).</v>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v>Maldives</v>
+      </c>
+      <c r="B1056" t="str">
+        <v>South Malé Atoll</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>Aqua Bar</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1056">
+        <v>1</v>
+      </c>
+      <c r="F1056" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1056" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="H1056" t="str">
+        <v>2025</v>
+      </c>
+      <c r="I1056" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1056" t="str">
+        <v>3.9725545</v>
+      </c>
+      <c r="K1056" t="str">
+        <v>73.5017924</v>
+      </c>
+      <c r="L1056" t="str">
+        <v>Maldives (July 2025)</v>
+      </c>
+      <c r="M1056" t="str">
+        <v>South Malé Atoll, Maldives</v>
+      </c>
+      <c r="O1056" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="Q1056">
+        <v>5</v>
+      </c>
+      <c r="R1056" t="str">
+        <v>Wonderful GF pizza for dinner and GF pasta for lunch. Staff are amazing and so friendly. Located at sister resort Anantara Dhigu, reachable by pontoon.</v>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v>Maldives</v>
+      </c>
+      <c r="B1057" t="str">
+        <v>South Malé Atoll</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>Dhoni Bar</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1057">
+        <v>1</v>
+      </c>
+      <c r="F1057" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1057" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="H1057" t="str">
+        <v>2025</v>
+      </c>
+      <c r="I1057" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1057" t="str">
+        <v>3.9667347</v>
+      </c>
+      <c r="K1057" t="str">
+        <v>73.5044678</v>
+      </c>
+      <c r="L1057" t="str">
+        <v>Maldives (July 2025)</v>
+      </c>
+      <c r="M1057" t="str">
+        <v>South Malé Atoll, Maldives</v>
+      </c>
+      <c r="O1057" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="Q1057">
+        <v>5</v>
+      </c>
+      <c r="R1057" t="str">
+        <v>Tons of GF options, especially fresh seafood.</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v>Maldives</v>
+      </c>
+      <c r="B1058" t="str">
+        <v>South Malé Atoll</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>Baan Huraa</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1058">
+        <v>1</v>
+      </c>
+      <c r="F1058" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1058" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="H1058" t="str">
+        <v>2025</v>
+      </c>
+      <c r="I1058" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1058" t="str">
+        <v>3.969647</v>
+      </c>
+      <c r="K1058" t="str">
+        <v>73.5068198</v>
+      </c>
+      <c r="L1058" t="str">
+        <v>Maldives (July 2025)</v>
+      </c>
+      <c r="M1058" t="str">
+        <v>South Malé Atoll, Maldives</v>
+      </c>
+      <c r="O1058" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="Q1058">
+        <v>4</v>
+      </c>
+      <c r="R1058" t="str">
+        <v>Thai food, had a few GF options. Made a GF version of prawn crackers (texture was a bit like styrofoam, but appreciated the effort). Pad Thai was delicious.</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v>Maldives</v>
+      </c>
+      <c r="B1059" t="str">
+        <v>South Malé Atoll</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>Anantara Veli Maldives Resort</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1059">
+        <v>1</v>
+      </c>
+      <c r="F1059" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1059" t="str">
+        <v>Jul</v>
+      </c>
+      <c r="H1059" t="str">
+        <v>2025</v>
+      </c>
+      <c r="J1059" t="str">
+        <v>3.967374</v>
+      </c>
+      <c r="K1059" t="str">
+        <v>73.505465</v>
+      </c>
+      <c r="L1059" t="str">
+        <v>Maldives (July 2025)</v>
+      </c>
+      <c r="M1059" t="str">
+        <v>South Malé Atoll, Maldives</v>
+      </c>
+      <c r="O1059" t="str">
+        <v>Added Aug 2026 from Google My Maps KML + GPS-matched Apple Photos (no prior spreadsheet row existed for this trip).</v>
+      </c>
+      <c r="U1059" t="str">
+        <v>All-inclusive; GF meals standard practice with advance notice. Cumin restaurant explicitly advertises GF/dairy-free options.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1046"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1059"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U1059"/>
+  <dimension ref="A1:U1094"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -44899,9 +44899,1624 @@
         <v>All-inclusive; GF meals standard practice with advance notice. Cumin restaurant explicitly advertises GF/dairy-free options.</v>
       </c>
     </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1060" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>Vlaams Friteshuis Vleminckx</v>
+      </c>
+      <c r="D1060" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1060">
+        <v>1</v>
+      </c>
+      <c r="F1060" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1060" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1060" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1060" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1060" t="str">
+        <v>52.3678913</v>
+      </c>
+      <c r="K1060" t="str">
+        <v>4.8909863</v>
+      </c>
+      <c r="L1060" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1060" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1060" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1060" t="str">
+        <v>Famous fries stand (since 1957) serving naturally GF Belgian-style fries cooked in vegan oil, with GF sauces available. Staff is knowledgeable about gluten allergies. Not a dedicated GF facility — cross-contamination risk exists, and it's just fries, so options are limited.</v>
+      </c>
+      <c r="P1060" t="str">
+        <v>https://www.findmeglutenfree.com/biz/vleminckx/6699177618309120</v>
+      </c>
+      <c r="Q1060">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1061" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>Craft Coffee &amp; Pastry Amsterdam</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E1061">
+        <v>0</v>
+      </c>
+      <c r="F1061" t="str">
+        <v>🥐</v>
+      </c>
+      <c r="G1061" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1061" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1061" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1061" t="str">
+        <v>52.356152</v>
+      </c>
+      <c r="K1061" t="str">
+        <v>4.8934824</v>
+      </c>
+      <c r="L1061" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1061" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1061" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1061" t="str">
+        <v>100% dedicated GF bakery (Gerard Doustraat, De Pijp). Specializes in artisanal croissants and pastries. Sells out quickly — arrive early or pre-order.</v>
+      </c>
+      <c r="P1061" t="str">
+        <v>https://www.findmeglutenfree.com/biz/craft-coffee-and-pastry/5588235859394560</v>
+      </c>
+      <c r="Q1061">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1062" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>Miuz Gelato &amp; Coffee</v>
+      </c>
+      <c r="D1062" t="str">
+        <v>cafe</v>
+      </c>
+      <c r="E1062">
+        <v>0</v>
+      </c>
+      <c r="F1062" t="str">
+        <v>☕</v>
+      </c>
+      <c r="G1062" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1062" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1062" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1062" t="str">
+        <v>52.3622347</v>
+      </c>
+      <c r="K1062" t="str">
+        <v>4.8739918</v>
+      </c>
+      <c r="L1062" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1062" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1062" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1062" t="str">
+        <v>Artisanal Italian gelateria (Overtoom 117) with 100% GF ice cream and GF cones, made fresh daily.</v>
+      </c>
+      <c r="P1062" t="str">
+        <v>https://www.findmeglutenfree.com/biz/miuz-gelato-artigianale/4637306668056576</v>
+      </c>
+      <c r="Q1062">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1063" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>Croque Madame Gluten Free Food</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1063">
+        <v>0</v>
+      </c>
+      <c r="F1063" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1063" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1063" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1063" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1063" t="str">
+        <v>52.3739037</v>
+      </c>
+      <c r="K1063" t="str">
+        <v>4.8969192</v>
+      </c>
+      <c r="L1063" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1063" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1063" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1063" t="str">
+        <v>100% dedicated GF restaurant near the Anne Frank House. Burger buns are indistinguishable from wheat. Small venue (4 tables); reservations recommended.</v>
+      </c>
+      <c r="P1063" t="str">
+        <v>https://www.findmeglutenfree.com/biz/croque-madame/5789406004903936</v>
+      </c>
+      <c r="Q1063">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1064" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>Rose and Vanilla</v>
+      </c>
+      <c r="D1064" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E1064">
+        <v>0</v>
+      </c>
+      <c r="F1064" t="str">
+        <v>🥐</v>
+      </c>
+      <c r="G1064" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1064" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1064" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1064" t="str">
+        <v>52.3643915</v>
+      </c>
+      <c r="K1064" t="str">
+        <v>4.8744845</v>
+      </c>
+      <c r="L1064" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1064" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1064" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1064" t="str">
+        <v>GF, dairy-free, and vegan bakery-cafe with mini cakes, cookies, and a savory lunch menu.</v>
+      </c>
+      <c r="P1064" t="str">
+        <v>https://www.findmeglutenfree.com/biz/rose-and-vanilla/4674194404671488</v>
+      </c>
+      <c r="Q1064">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1065" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>Dèsa</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1065">
+        <v>0</v>
+      </c>
+      <c r="F1065" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1065" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1065" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1065" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1065" t="str">
+        <v>52.353082</v>
+      </c>
+      <c r="K1065" t="str">
+        <v>4.891901</v>
+      </c>
+      <c r="L1065" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1065" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1065" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1065" t="str">
+        <v>100% GF Indonesian restaurant in De Pijp — even the soy sauce is GF. Rice table set menus with satay, gado gado, and tempeh.</v>
+      </c>
+      <c r="P1065" t="str">
+        <v>https://www.findmeglutenfree.com/biz/desa/5650913069498368</v>
+      </c>
+      <c r="Q1065">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1066" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>De Glutenvrije Winkel</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>shop</v>
+      </c>
+      <c r="E1066">
+        <v>0</v>
+      </c>
+      <c r="F1066" t="str">
+        <v>🛒</v>
+      </c>
+      <c r="G1066" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1066" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1066" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1066" t="str">
+        <v>52.355671</v>
+      </c>
+      <c r="K1066" t="str">
+        <v>4.9254551</v>
+      </c>
+      <c r="L1066" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1066" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1066" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1066" t="str">
+        <v>100% certified GF bakery and specialty grocery store ("The Gluten-Free Shop") — homemade bread, cakes, sandwiches, and frozen/pantry items.</v>
+      </c>
+      <c r="P1066" t="str">
+        <v>https://www.findmeglutenfree.com/biz/de-glutenvrije-winkel/4992857909755904</v>
+      </c>
+      <c r="Q1066">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1067" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>Bloem Eten &amp; Drinken</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1067">
+        <v>0</v>
+      </c>
+      <c r="F1067" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1067" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1067" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1067" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="J1067" t="str">
+        <v>52.3688757</v>
+      </c>
+      <c r="K1067" t="str">
+        <v>4.9142577</v>
+      </c>
+      <c r="L1067" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1067" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1067" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1067" t="str">
+        <v>100% GF vegan restaurant near Artis Zoo with full NCV gluten-free certification and audited inventory.</v>
+      </c>
+      <c r="P1067" t="str">
+        <v>https://www.findmeglutenfree.com/biz/bloem-eten-and-drinken/6000459400216576</v>
+      </c>
+      <c r="Q1067">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1068" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>Nooch - Asian House</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1068">
+        <v>0</v>
+      </c>
+      <c r="F1068" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1068" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1068" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1068" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1068" t="str">
+        <v>52.367323</v>
+      </c>
+      <c r="K1068" t="str">
+        <v>4.8729195</v>
+      </c>
+      <c r="L1068" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1068" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1068" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1068" t="str">
+        <v>Clearly-marked GF menu including pad thai, noodles, sushi, and wings made with GF soy sauce. Shared kitchen, not dedicated GF.</v>
+      </c>
+      <c r="P1068" t="str">
+        <v>https://www.findmeglutenfree.com/biz/nooch/4921468276834304</v>
+      </c>
+      <c r="Q1068">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1069" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>Loulou Pizzabar</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1069">
+        <v>0</v>
+      </c>
+      <c r="F1069" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1069" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1069" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1069" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="L1069" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1069" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1069" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1069" t="str">
+        <v>2024 Dutch Pizza Championship winner with a separate GF oven and dedicated prep area. Web-supplemented find, not on the traveler's own map.</v>
+      </c>
+      <c r="P1069" t="str">
+        <v>https://www.findmeglutenfree.com/biz/loulou-pizzabar/6386227616022528</v>
+      </c>
+      <c r="Q1069">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1070" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>Café Piazza</v>
+      </c>
+      <c r="D1070" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1070">
+        <v>0</v>
+      </c>
+      <c r="F1070" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1070" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1070" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1070" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="L1070" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1070" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1070" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1070" t="str">
+        <v>Red-menu/red-napkin system for celiac orders, separate tools. Pasta/meat/fish safe; pizza not (shared oven). Web-supplemented find.</v>
+      </c>
+      <c r="P1070" t="str">
+        <v>https://www.findmeglutenfree.com/biz/cafe-piazza/5124805944672256</v>
+      </c>
+      <c r="Q1070">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1071" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>De Italiaan</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1071">
+        <v>0</v>
+      </c>
+      <c r="F1071" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1071" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1071" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1071" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="L1071" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1071" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1071" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1071" t="str">
+        <v>Oud-West Italian spot with a separate GF oven option, full GF pasta menu, and GF desserts. Web-supplemented find.</v>
+      </c>
+      <c r="P1071" t="str">
+        <v>https://www.findmeglutenfree.com/biz/de-italiaan/5866152141520896</v>
+      </c>
+      <c r="Q1071">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1072" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>Anantara Grand Hotel Krasnapolsky Amsterdam</v>
+      </c>
+      <c r="D1072" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1072">
+        <v>0</v>
+      </c>
+      <c r="F1072" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1072" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1072" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J1072" t="str">
+        <v>52.37267</v>
+      </c>
+      <c r="K1072" t="str">
+        <v>4.89409</v>
+      </c>
+      <c r="L1072" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1072" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1072" t="str">
+        <v>yes</v>
+      </c>
+      <c r="S1072" t="str">
+        <v>https://www.booking.com/hotel/nl/anantara-ghkrasnapolsky.html</v>
+      </c>
+      <c r="U1072" t="str">
+        <v>Buffet breakfast; GF accommodation available on request, contact ahead.</v>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1073" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>Hotel NH City Centre Amsterdam</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1073">
+        <v>0</v>
+      </c>
+      <c r="F1073" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1073" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1073" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J1073" t="str">
+        <v>52.36972</v>
+      </c>
+      <c r="K1073" t="str">
+        <v>4.88892</v>
+      </c>
+      <c r="L1073" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1073" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1073" t="str">
+        <v>yes</v>
+      </c>
+      <c r="S1073" t="str">
+        <v>https://www.hotels.com/ho134757/nh-city-centre-amsterdam-amsterdam-netherlands/</v>
+      </c>
+      <c r="U1073" t="str">
+        <v>Buffet breakfast; GF options not explicitly listed, confirm directly.</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1074" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>Kimpton De Witt Hotel</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1074">
+        <v>0</v>
+      </c>
+      <c r="F1074" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1074" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1074" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J1074" t="str">
+        <v>52.377196</v>
+      </c>
+      <c r="K1074" t="str">
+        <v>4.895544</v>
+      </c>
+      <c r="L1074" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1074" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1074" t="str">
+        <v>yes</v>
+      </c>
+      <c r="S1074" t="str">
+        <v>https://www.booking.com/hotel/nl/cpamsterdamcentre.html</v>
+      </c>
+      <c r="U1074" t="str">
+        <v>Eggs-to-order breakfast; GF options available with advance notice.</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1075" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>Pulitzer Amsterdam</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1075">
+        <v>0</v>
+      </c>
+      <c r="F1075" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1075" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1075" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J1075" t="str">
+        <v>52.3728783</v>
+      </c>
+      <c r="K1075" t="str">
+        <v>4.883357</v>
+      </c>
+      <c r="L1075" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1075" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1075" t="str">
+        <v>yes</v>
+      </c>
+      <c r="S1075" t="str">
+        <v>https://www.hotels.com/ho143058/pulitzer-amsterdam-amsterdam-netherlands/</v>
+      </c>
+      <c r="U1075" t="str">
+        <v>Historic 5-star, 25 canal houses; GF breakfast protocol not listed, confirm directly.</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1076" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>Dam Square</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1076">
+        <v>0</v>
+      </c>
+      <c r="F1076" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1076" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1076" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1076" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1076" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1076" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1076" t="str">
+        <v>Open-air heart of the city — cobblestones, street performers, and the Royal Palace. Free to explore.</v>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1077" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>Begijnhof</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1077">
+        <v>0</v>
+      </c>
+      <c r="F1077" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1077" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1077" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1077" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1077" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1077" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1077" t="str">
+        <v>14th-century courtyard of almshouses, home to Amsterdam's oldest surviving house (1475) and a hidden Catholic church.</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1078" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>Vondelpark</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1078">
+        <v>0</v>
+      </c>
+      <c r="F1078" t="str">
+        <v>🌳</v>
+      </c>
+      <c r="G1078" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1078" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1078" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1078" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1078" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1078" t="str">
+        <v>50 hectares of lawns, ponds, and an open-air theatre.</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1079" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>Canal Ring (Grachtengordel)</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1079">
+        <v>0</v>
+      </c>
+      <c r="F1079" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1079" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1079" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1079" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1079" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1079" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1079" t="str">
+        <v>UNESCO-listed canal system defining the city; the "15 bridges" view is at Reguliersgracht/Herengracht.</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1080" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>Anne Frank House</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1080">
+        <v>0</v>
+      </c>
+      <c r="F1080" t="str">
+        <v>🎟️</v>
+      </c>
+      <c r="G1080" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1080" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1080" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1080" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1080" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1080" t="str">
+        <v>Moving, widely-visited WWII museum. Book well ahead — tickets sell out weeks in advance.</v>
+      </c>
+      <c r="S1080" t="str">
+        <v>https://www.getyourguide.com/amsterdam-l36/amsterdam-90-minuten-anne-frank-tour-t66641/</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1081" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>A'DAM Lookout</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1081">
+        <v>0</v>
+      </c>
+      <c r="F1081" t="str">
+        <v>🎟️</v>
+      </c>
+      <c r="G1081" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1081" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1081" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1081" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1081" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1081" t="str">
+        <v>Observation deck across the IJ river with 360° views, plus Europe's highest swing.</v>
+      </c>
+      <c r="S1081" t="str">
+        <v>https://www.getyourguide.com/amsterdam-l36/amsterdam-a-dam-lookout-entry-ticket-with-1-drink-t65642/</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1082" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>Canal Cruise</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1082">
+        <v>0</v>
+      </c>
+      <c r="F1082" t="str">
+        <v>🎟️</v>
+      </c>
+      <c r="G1082" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1082" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1082" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1082" t="str">
+        <v>Amsterdam</v>
+      </c>
+      <c r="N1082" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1082" t="str">
+        <v>Classic boat ride through the historic canal ring.</v>
+      </c>
+      <c r="S1082" t="str">
+        <v>https://www.getyourguide.com/amsterdam-l36/amsterdam-2-hour-luxury-canal-cruise-with-snacks-drinks-t579846/</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1083" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>Bleeckerstreet</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1083">
+        <v>0</v>
+      </c>
+      <c r="F1083" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1083" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1083" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1083" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="J1083" t="str">
+        <v>51.84626</v>
+      </c>
+      <c r="K1083" t="str">
+        <v>5.86995</v>
+      </c>
+      <c r="L1083" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1083" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1083" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1083" t="str">
+        <v>Dedicated GF fryer; chef personally consults on intolerance severity. Not a fully dedicated GF kitchen.</v>
+      </c>
+      <c r="P1083" t="str">
+        <v>https://www.findmeglutenfree.com/biz/bleeckerstreet/5085386319331328</v>
+      </c>
+      <c r="Q1083">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1084" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>Pannenkoekenrestaurant 't Hoogstraatje</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1084">
+        <v>0</v>
+      </c>
+      <c r="F1084" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1084" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1084" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1084" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="J1084" t="str">
+        <v>51.8468006</v>
+      </c>
+      <c r="K1084" t="str">
+        <v>5.8684911</v>
+      </c>
+      <c r="L1084" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1084" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1084" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1084" t="str">
+        <v>Dutch pancake house with GF pancakes, bread, and desserts; separate extra-clean cutlery.</v>
+      </c>
+      <c r="P1084" t="str">
+        <v>https://www.findmeglutenfree.com/biz/t-hoogstraatje/5906008583045120</v>
+      </c>
+      <c r="Q1084">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1085" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>Robin's Gluten Free</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E1085">
+        <v>0</v>
+      </c>
+      <c r="F1085" t="str">
+        <v>🥐</v>
+      </c>
+      <c r="G1085" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1085" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1085" t="str">
+        <v>100% dedicated GF</v>
+      </c>
+      <c r="L1085" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1085" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1085" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1085" t="str">
+        <v>Dedicated GF bakery and cafe with sandwiches and cakes. Web-supplemented find.</v>
+      </c>
+      <c r="P1085" t="str">
+        <v>https://www.findmeglutenfree.com/biz/robins/4792578916089856</v>
+      </c>
+      <c r="Q1085">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1086" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>MultiVlaai</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>bakery</v>
+      </c>
+      <c r="E1086">
+        <v>0</v>
+      </c>
+      <c r="F1086" t="str">
+        <v>🥐</v>
+      </c>
+      <c r="G1086" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1086" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1086" t="str">
+        <v>mixed safety</v>
+      </c>
+      <c r="L1086" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1086" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1086" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1086" t="str">
+        <v>Frozen GF cakes on request; not a dedicated facility. Web-supplemented find.</v>
+      </c>
+      <c r="P1086" t="str">
+        <v>https://www.findmeglutenfree.com/biz/multivlaai/5051810768879616</v>
+      </c>
+      <c r="Q1086">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1087" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1087" t="str">
+        <v>MAM Vietnamese Street Food</v>
+      </c>
+      <c r="D1087" t="str">
+        <v>restaurant</v>
+      </c>
+      <c r="E1087">
+        <v>0</v>
+      </c>
+      <c r="F1087" t="str">
+        <v>🍽️</v>
+      </c>
+      <c r="G1087" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1087" t="str">
+        <v>2022</v>
+      </c>
+      <c r="I1087" t="str">
+        <v>celiac-aware</v>
+      </c>
+      <c r="L1087" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1087" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1087" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1087" t="str">
+        <v>No dedicated GF menu, but staff knowledgeable about cross-contact. Web-supplemented find.</v>
+      </c>
+      <c r="P1087" t="str">
+        <v>https://www.findmeglutenfree.com/biz/mam/6190924826279936</v>
+      </c>
+      <c r="Q1087">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1088" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>Van der Valk Hotel Nijmegen-Lent</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1088">
+        <v>0</v>
+      </c>
+      <c r="F1088" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1088" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1088" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J1088" t="str">
+        <v>51.8630391</v>
+      </c>
+      <c r="K1088" t="str">
+        <v>5.8607872</v>
+      </c>
+      <c r="L1088" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1088" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1088" t="str">
+        <v>yes</v>
+      </c>
+      <c r="S1088" t="str">
+        <v>https://www.hotels.com/ho607882/van-der-valk-hotel-nijmegen-lent-lent-netherlands/</v>
+      </c>
+      <c r="U1088" t="str">
+        <v>Breakfast includes a wide choice of GF options.</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1089" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>The Rebyl, Nijmegen, a Tribute Portfolio Hotel</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>hotel</v>
+      </c>
+      <c r="E1089">
+        <v>0</v>
+      </c>
+      <c r="F1089" t="str">
+        <v>🏨</v>
+      </c>
+      <c r="G1089" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1089" t="str">
+        <v>2022</v>
+      </c>
+      <c r="J1089" t="str">
+        <v>51.8414773</v>
+      </c>
+      <c r="K1089" t="str">
+        <v>5.8678921</v>
+      </c>
+      <c r="L1089" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1089" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1089" t="str">
+        <v>yes</v>
+      </c>
+      <c r="S1089" t="str">
+        <v>https://www.hotels.com/ho3442265280</v>
+      </c>
+      <c r="U1089" t="str">
+        <v>GF options available; confirm cross-contamination protocol directly.</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1090" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>Valkhofpark</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1090">
+        <v>0</v>
+      </c>
+      <c r="F1090" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1090" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1090" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1090" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1090" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1090" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1090" t="str">
+        <v>Bluff overlooking the Waal River with ruins of Charlemagne's 8th-century palace.</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1091" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>Waalbrug</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1091">
+        <v>0</v>
+      </c>
+      <c r="F1091" t="str">
+        <v>🌉</v>
+      </c>
+      <c r="G1091" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1091" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1091" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1091" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1091" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1091" t="str">
+        <v>Iconic 1936 arch bridge, once Europe's longest.</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1092" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1092" t="str">
+        <v>St. Stevenskerk</v>
+      </c>
+      <c r="D1092" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1092">
+        <v>0</v>
+      </c>
+      <c r="F1092" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1092" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1092" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1092" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1092" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1092" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1092" t="str">
+        <v>Gothic church dominating the skyline, free to enter.</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1093" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1093" t="str">
+        <v>Grote Markt</v>
+      </c>
+      <c r="D1093" t="str">
+        <v>landmark</v>
+      </c>
+      <c r="E1093">
+        <v>0</v>
+      </c>
+      <c r="F1093" t="str">
+        <v>🏛️</v>
+      </c>
+      <c r="G1093" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1093" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1093" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1093" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1093" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1093" t="str">
+        <v>Historic town square at the center of the old city.</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="B1094" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="C1094" t="str">
+        <v>Nijmegen in 1 Day: Walking Tour with Digital Guide</v>
+      </c>
+      <c r="D1094" t="str">
+        <v>activity</v>
+      </c>
+      <c r="E1094">
+        <v>0</v>
+      </c>
+      <c r="F1094" t="str">
+        <v>🎟️</v>
+      </c>
+      <c r="G1094" t="str">
+        <v>Dec</v>
+      </c>
+      <c r="H1094" t="str">
+        <v>2022</v>
+      </c>
+      <c r="L1094" t="str">
+        <v>The Netherlands (December 2022)</v>
+      </c>
+      <c r="M1094" t="str">
+        <v>Nijmegen</v>
+      </c>
+      <c r="N1094" t="str">
+        <v>yes</v>
+      </c>
+      <c r="O1094" t="str">
+        <v>Self-guided digital walking tour covering the old city's highlights.</v>
+      </c>
+      <c r="S1094" t="str">
+        <v>https://www.getyourguide.com/nijmegen-l2960/</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U1059"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U1094"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/travel_master.xlsx
+++ b/travel_master.xlsx
@@ -11051,7 +11051,7 @@
         <v>3</v>
       </c>
       <c r="R164" t="str">
-        <v/>
+        <v>Permanently closed as of 2026-08-10 (per Luzerner Zeitung reporting, closed after 14 years, cited COVID + 2023 Spitalstrasse street renovation). Space now occupied by Osteria Valle di Zerz (opened Jan 2025), no indication it carries over a GF program. Kept on the city page with a Looks-to-be-Closed tag and FMGF link removed.</v>
       </c>
       <c r="S164" t="str">
         <v/>
